--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3D-特效" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$21</definedName>
@@ -549,7 +549,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="46">
     <border/>
     <border>
       <left style="medium">
@@ -971,11 +971,29 @@
         <color rgb="FFD9E2F3"/>
       </bottom>
     </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF446170"/>
+      </right>
+      <bottom style="medium">
+        <color rgb="FF446170"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF446170"/>
+      </right>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="FF446170"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="396">
+  <cellXfs count="399">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1892,6 +1910,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -2371,16 +2394,16 @@
         </is>
       </c>
       <c r="D9" s="323" t="n"/>
-      <c r="E9" s="320" t="inlineStr">
+      <c r="E9" s="396" t="inlineStr">
         <is>
           <t>本账本只登记上列大类；跨域搬运资产须同步主账本《分类与编码》并重跑门禁</t>
         </is>
       </c>
-      <c r="F9" s="125" t="n"/>
-      <c r="G9" s="125" t="n"/>
-      <c r="H9" s="125" t="n"/>
-      <c r="I9" s="125" t="n"/>
-      <c r="J9" s="126" t="n"/>
+      <c r="F9" s="397" t="n"/>
+      <c r="G9" s="397" t="n"/>
+      <c r="H9" s="397" t="n"/>
+      <c r="I9" s="397" t="n"/>
+      <c r="J9" s="398" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="301" t="inlineStr">
@@ -5169,7 +5192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5200,7 +5223,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="377" t="inlineStr">
         <is>
-          <t>特效按独立 Prefab 原则：每个特效一个独立 .tscn；Prefab 是特效唯一出口；账本和调用代码读 Prefab。本 sheet 共 10 条，按 5 大类分组，每条 VFX 有内部编号 FX&lt;大类&gt;-&lt;序号&gt;。状态：✅ 完成（Prefab + 脚本 + 接入齐）/ 🟡 待落地（已登记 AssetID，文件未创建）/ 🟠 老形态（迁移完成后删除）。规范见 docs/v0.1/14.6_特效系统与制作规范.md。【2026-09-11 进度】FX01 战斗反馈 5 条 + FX02 受击飘字 2 条 共 7 条完成；FX03/04 已实装但命名待对齐。</t>
+          <t>特效按独立 Prefab 原则：每个特效一个独立 .tscn；Prefab 是特效唯一出口；账本和调用代码读 Prefab。本 sheet 共 11 条，按 5 大类分组，每条 VFX 有内部编号 FX&lt;大类&gt;-&lt;序号&gt;。状态：✅ 完成（Prefab + 脚本 + 接入齐）/ 🟡 待落地（已登记 AssetID，文件未创建）/ 🟠 老形态（迁移完成后删除）。规范见 docs/v0.1/14.6_特效系统与制作规范.md。【2026-09-11 进度】FX01 战斗反馈 5 条 + FX02 受击飘字 2 条 共 7 条完成；FX03/04 已实装但命名待对齐。【2026-09-21 进度】新增 FX01-06 VFX-BULLET-VISUAL-3D（飞行子弹纯视觉，含 ProjectileLight，由 Projectile3D 持有、不进 VfxPool）；FX01-01 / FX01-02 升 v002 卡通重做（枪口新增 MuzzleLight、命中改按命中法线对齐）；三类共同验收 verify_combat_vfx_toon_v002。</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5462,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>枪械/投射物开火时的瞬时火光；SphereMesh 闪核 + TorusMesh 环；参数 effect_color（火焰色）/ effect_size（火光强度）。</t>
+          <t>枪械开火时的瞬时枪口花火（卡通 v002）：铂金亮芯 + 橙金/弹药色立体楔形火焰（CylinderMesh top_radius=0，Godot 4.x 无 ConeMesh）+ 交叉面尖瓣 + 5 枚飞散火星 + 短冲击环 + 一盏 OmniLight3D（名 MuzzleLight，shadow_enabled=false）。经 VfxPool3D 按 AssetID 路由。</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -5464,12 +5487,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>约 0.18m 半径；lifetime 0.12s</t>
+          <t>亮芯约 0.18m；火焰长 0.7~1.8×size；lifetime 0.16s；MuzzleLight range 3.5m×size、峰值 light_energy 5.0、寿命末端归零</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>原点=根节点中心；朝向=local -Z 正面</t>
+          <t>原点=根节点中心；朝向=Basis.looking_at(context.forward)，local -Z 对齐射击方向</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -5484,12 +5507,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>v001</t>
+          <t>v002</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_muzzle_flash_root_top3d_v001.tscn + 脚本=src/vfx/VfxMuzzleFlash3D.gd；根节点=VfxMuzzleFlash3D(Node3D)；FX编号 FX01-01；调用方：PlayerMeleeCombat3D/Enemy3D 经 VfxPool3D 路由</t>
+          <t>v002 卡通重做；Prefab=assets/art/vfx/combat_3d/vfx_muzzle_flash_root_top3d.tscn（去版本化路径，N1/N2 后不再带 _v001）+ 脚本=src/vfx/VfxMuzzleFlash3D.gd；根节点=VfxMuzzleFlash3D(Node3D)；FX编号 FX01-01；调用方：WeaponModel3D._spawn_muzzle_effect 经 VfxPool3D.acquire(FX01_MUZZLE_FLASH, …, {"forward": -global_basis.z})；验收：verify_combat_vfx_toon_v002。注：旧版备注中的 ..._v001.tscn 路径已废弃。</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5541,7 @@
       <c r="F9" s="388" t="n"/>
       <c r="G9" s="388" t="inlineStr">
         <is>
-          <t>子弹/投射物命中目标时的爆点；SphereMesh 核心 + TorusMesh 环；参数 effect_color（命中火花色）/ effect_size（爆点半径）。</t>
+          <t>子弹/投射物命中表面的爆点（卡通 v002）：亮芯 + 冲击环（TorusMesh） + 7 道错峰星芒（BoxMesh，Quaternion(UP,dir) 放射） + 8 块错峰旋转碎屑；UNSHADED 半透明材质、透明重叠受控。</t>
         </is>
       </c>
       <c r="H9" s="388" t="inlineStr">
@@ -5543,12 +5566,12 @@
       </c>
       <c r="L9" s="388" t="inlineStr">
         <is>
-          <t>约 0.16m 核心；lifetime 0.24s</t>
+          <t>亮芯约 0.16m；冲击环 0.2→2.4×size；lifetime 0.32s</t>
         </is>
       </c>
       <c r="M9" s="388" t="inlineStr">
         <is>
-          <t>原点=根节点中心；朝向=local -Z 正面</t>
+          <t>原点=根节点中心；朝向=Basis(Quaternion(UP, context.normal))，local +Y 对齐命中法线</t>
         </is>
       </c>
       <c r="N9" s="388" t="inlineStr">
@@ -5563,12 +5586,12 @@
       </c>
       <c r="P9" s="388" t="inlineStr">
         <is>
-          <t>v001</t>
+          <t>v002</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_impact_root_top3d_v001.tscn + 脚本=src/vfx/VfxImpact3D.gd；根节点=VfxImpact3D(Node3D)；FX编号 FX01-02；调用方：PlayerMeleeCombat3D/Enemy3D 经 VfxPool3D 路由</t>
+          <t>v002 卡通重做；Prefab=assets/art/vfx/combat_3d/vfx_impact_root_top3d.tscn（去版本化路径）+ 脚本=src/vfx/VfxImpact3D.gd；根节点=VfxImpact3D(Node3D)；FX编号 FX01-02；调用方：Projectile3D._spawn_effect(VfxPool3D.FX01_IMPACT, …) 传 hit_context={"normal":…, "position":…}；Enemy3D / PlayerMeleeCombat3D 亦经 VfxPool3D 路由；验收：verify_combat_vfx_toon_v002。注：旧版备注中的 ..._v001.tscn 路径已废弃。</t>
         </is>
       </c>
     </row>
@@ -5804,377 +5827,454 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="387" t="inlineStr">
+      <c r="A13" s="391" t="inlineStr">
+        <is>
+          <t>FX01-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-VISUAL-3D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>飞行子弹纯视觉特效</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_visual_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>飞行中子弹的纯视觉表现（卡通 v002 风格同族）：铂金亮芯胶囊 + 弹色半透明外壳 + 沿弹道拖尾锥（CylinderMesh top_radius=0，宽端贴弹体、尖端向身后） + 每弹一盏 OmniLight3D（名 ProjectileLight，shadow_enabled=false，light_energy 1.2、omni_range 1.8）。由 Projectile3D 作为子节点持有，生命周期随宿主（ProjectilePool3D），不进 VfxPool 自动计时，避免双池 ownership。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBulletVisual3D.gd</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>弹芯 CapsuleMesh r=0.045/h=0.20；外壳 r=0.075/h=0.18；拖尾锥底半径 0.06/长 0.5；灯 range 1.8m</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>原点=宿主原点（local position 保持 0，随 Projectile3D 变换）；朝向=弹体沿 local -Z，拖尾向 local +Z（身后）</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>玩家/敌人飞行子弹（远程 7 枪 + 各类投射物）</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_visual_root_top3d.tscn + 脚本=src/vfx/VfxBulletVisual3D.gd；根节点=VfxBulletVisual3D(Node3D)；FX编号 FX01-06；调用方：Projectile3D._build_visual() 实例化为子节点并委托 activate/deactivate/apply_growth/set_trail_visible；碰撞由 Projectile3D 自持（半径 0.12 球），本视觉 Prefab 内无碰撞体；验收：verify_combat_vfx_toon_v002。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="387" t="inlineStr">
         <is>
           <t>▼ 02 受击飘字</t>
         </is>
       </c>
-      <c r="B13" s="388" t="n"/>
-      <c r="C13" s="388" t="n"/>
-      <c r="D13" s="388" t="n"/>
-      <c r="E13" s="388" t="n"/>
-      <c r="F13" s="388" t="n"/>
-      <c r="G13" s="388" t="n"/>
-      <c r="H13" s="388" t="n"/>
-      <c r="I13" s="388" t="n"/>
-      <c r="J13" s="388" t="n"/>
-      <c r="K13" s="388" t="n"/>
-      <c r="L13" s="388" t="n"/>
-      <c r="M13" s="388" t="n"/>
-      <c r="N13" s="388" t="n"/>
-      <c r="O13" s="388" t="n"/>
-      <c r="P13" s="388" t="n"/>
-      <c r="Q13" s="388" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="391" t="inlineStr">
-        <is>
-          <t>FX02-01</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>VFX-DAMAGE-NUMBER-3D</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>伤害数字飘字特效</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>assets/art/vfx/combat_3d/vfx_damage_number_root_top3d.tscn</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>受击伤害数字上升飘字；Label3D + 黑边 + 颜色编码（红/橙/暴击金）；参数 effect_color + context.text_value。</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>src/vfx/VfxDamageNumber3D.gd</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Label3D pixel_size=0.010；lifetime 0.72s</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>原点=根节点中心；朝向=local -Z 正面</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>玩家/敌人受击伤害显示</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>完成</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>v001</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_damage_number_root_top3d_v001.tscn + 脚本=src/vfx/VfxDamageNumber3D.gd；根节点=VfxDamageNumber3D(Node3D)；FX编号 FX02-01；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value</t>
-        </is>
-      </c>
+      <c r="B14" s="388" t="n"/>
+      <c r="C14" s="388" t="n"/>
+      <c r="D14" s="388" t="n"/>
+      <c r="E14" s="388" t="n"/>
+      <c r="F14" s="388" t="n"/>
+      <c r="G14" s="388" t="n"/>
+      <c r="H14" s="388" t="n"/>
+      <c r="I14" s="388" t="n"/>
+      <c r="J14" s="388" t="n"/>
+      <c r="K14" s="388" t="n"/>
+      <c r="L14" s="388" t="n"/>
+      <c r="M14" s="388" t="n"/>
+      <c r="N14" s="388" t="n"/>
+      <c r="O14" s="388" t="n"/>
+      <c r="P14" s="388" t="n"/>
+      <c r="Q14" s="388" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="391" t="inlineStr">
         <is>
+          <t>FX02-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VFX-DAMAGE-NUMBER-3D</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>伤害数字飘字特效</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_damage_number_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>受击伤害数字上升飘字；Label3D + 黑边 + 颜色编码（红/橙/暴击金）；参数 effect_color + context.text_value。</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxDamageNumber3D.gd</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Label3D pixel_size=0.010；lifetime 0.72s</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>原点=根节点中心；朝向=local -Z 正面</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>玩家/敌人受击伤害显示</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_damage_number_root_top3d_v001.tscn + 脚本=src/vfx/VfxDamageNumber3D.gd；根节点=VfxDamageNumber3D(Node3D)；FX编号 FX02-01；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="391" t="inlineStr">
+        <is>
           <t>FX02-02</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>VFX-HEAL-NUMBER-3D</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>治疗数字飘字特效</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>assets/art/vfx/combat_3d/vfx_heal_number_root_top3d.tscn</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>治疗/恢复数字上升飘字；Label3D + 绿色调（+ 白色描边）；参数 context.text_value。</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>src/vfx/VfxHealNumber3D.gd</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Label3D pixel_size=0.010；lifetime 0.72s</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>原点=根节点中心；朝向=local -Z 正面</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>玩家/队友治疗显示</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>v001</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_heal_number_root_top3d_v001.tscn + 脚本=src/vfx/VfxHealNumber3D.gd；根节点=VfxHealNumber3D(Node3D)；FX编号 FX02-02；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="387" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="387" t="inlineStr">
         <is>
           <t>▼ 03 环境场</t>
         </is>
       </c>
-      <c r="B16" s="388" t="n"/>
-      <c r="C16" s="388" t="n"/>
-      <c r="D16" s="388" t="n"/>
-      <c r="E16" s="388" t="n"/>
-      <c r="F16" s="388" t="n"/>
-      <c r="G16" s="388" t="n"/>
-      <c r="H16" s="388" t="n"/>
-      <c r="I16" s="388" t="n"/>
-      <c r="J16" s="388" t="n"/>
-      <c r="K16" s="388" t="n"/>
-      <c r="L16" s="388" t="n"/>
-      <c r="M16" s="388" t="n"/>
-      <c r="N16" s="388" t="n"/>
-      <c r="O16" s="388" t="n"/>
-      <c r="P16" s="388" t="n"/>
-      <c r="Q16" s="388" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="391" t="inlineStr">
+      <c r="B17" s="388" t="n"/>
+      <c r="C17" s="388" t="n"/>
+      <c r="D17" s="388" t="n"/>
+      <c r="E17" s="388" t="n"/>
+      <c r="F17" s="388" t="n"/>
+      <c r="G17" s="388" t="n"/>
+      <c r="H17" s="388" t="n"/>
+      <c r="I17" s="388" t="n"/>
+      <c r="J17" s="388" t="n"/>
+      <c r="K17" s="388" t="n"/>
+      <c r="L17" s="388" t="n"/>
+      <c r="M17" s="388" t="n"/>
+      <c r="N17" s="388" t="n"/>
+      <c r="O17" s="388" t="n"/>
+      <c r="P17" s="388" t="n"/>
+      <c r="Q17" s="388" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="391" t="inlineStr">
         <is>
           <t>FX03-01</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>VFX-HAZARD-FIELD-3D</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>房间危险场3D特效</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>assets/art/vfx/environment_3d/vfx_hazard_field_root_top3d.tscn</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>房间危险场 Area3D 特效；脚本生成的环形危险区域；触发时产生伤害 + 视觉脉冲。</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>src/world3d/HazardField3D.gd</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Prefab自身</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>脚本生成</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>PackedScene/程序环形特效</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>未声明</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>陷阱房</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>v001</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>已实装；命名待 14.6 §6 迁移时对齐（改名 VfxHazardField3D + 移至 src/vfx/）</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="387" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="387" t="inlineStr">
         <is>
           <t>▼ 04 可见性</t>
         </is>
       </c>
-      <c r="B18" s="388" t="n"/>
-      <c r="C18" s="388" t="n"/>
-      <c r="D18" s="388" t="n"/>
-      <c r="E18" s="388" t="n"/>
-      <c r="F18" s="388" t="n"/>
-      <c r="G18" s="388" t="n"/>
-      <c r="H18" s="388" t="n"/>
-      <c r="I18" s="388" t="n"/>
-      <c r="J18" s="388" t="n"/>
-      <c r="K18" s="388" t="n"/>
-      <c r="L18" s="388" t="n"/>
-      <c r="M18" s="388" t="n"/>
-      <c r="N18" s="388" t="n"/>
-      <c r="O18" s="388" t="n"/>
-      <c r="P18" s="388" t="n"/>
-      <c r="Q18" s="388" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="391" t="inlineStr">
+      <c r="B19" s="388" t="n"/>
+      <c r="C19" s="388" t="n"/>
+      <c r="D19" s="388" t="n"/>
+      <c r="E19" s="388" t="n"/>
+      <c r="F19" s="388" t="n"/>
+      <c r="G19" s="388" t="n"/>
+      <c r="H19" s="388" t="n"/>
+      <c r="I19" s="388" t="n"/>
+      <c r="J19" s="388" t="n"/>
+      <c r="K19" s="388" t="n"/>
+      <c r="L19" s="388" t="n"/>
+      <c r="M19" s="388" t="n"/>
+      <c r="N19" s="388" t="n"/>
+      <c r="O19" s="388" t="n"/>
+      <c r="P19" s="388" t="n"/>
+      <c r="Q19" s="388" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="391" t="inlineStr">
         <is>
           <t>FX04-01</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>VFX-PLAYER-FLASHLIGHT-3D</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>玩家真实探照灯组件3D</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>assets/art/vfx/visibility_3d/vfx_player_flashlight_root_top3d.tscn</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>玩家真实探照灯 Node3D 组件；2 SpotLight3D + 1 OmniLight3D 组合；3D 行动区/靶场/基地覆盖。</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>src/player3d/PlayerFlashlight3D.gd</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>PackedScene/2 SpotLight3D+1 OmniLight3D</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>未声明</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>3D行动区/靶场/基地</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>v001</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>已实装；命名待 14.6 §6 迁移时对齐（改名 VfxPlayerFlashlight3D + 移至 src/vfx/）</t>
         </is>
@@ -6206,7 +6306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6307,6 +6407,43 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="301" t="inlineStr">
+        <is>
+          <t>v0.1.1</t>
+        </is>
+      </c>
+      <c r="B7" s="301" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C7" s="301" t="inlineStr">
+        <is>
+          <t>条目更新 + 新增</t>
+        </is>
+      </c>
+      <c r="D7" s="301" t="inlineStr">
+        <is>
+          <t>特效 · 3D-特效</t>
+        </is>
+      </c>
+      <c r="E7" s="301" t="inlineStr">
+        <is>
+          <t>FX01-01 枪口花火 / FX01-02 命中爆点 卡通 v002 重做（枪口新增 OmniLight3D MuzzleLight 与 forward 对齐；命中改为按 context.normal 对齐）；新增 FX01-06 VFX-BULLET-VISUAL-3D 飞行子弹纯视觉 Prefab（含 ProjectileLight）；同期修正备注中已废弃的 ..._v001.tscn 路径写法。</t>
+        </is>
+      </c>
+      <c r="F7" s="301" t="inlineStr">
+        <is>
+          <t>AssetID 不变；仅新增一条 FX01-06；Prefab 路径保持去版本化；资产主表未改动</t>
+        </is>
+      </c>
+      <c r="G7" s="301" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -2328,22 +2328,22 @@
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="321">
-        <f>COUNTA('资产主表'!$A$6:$A$21)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$22)</f>
         <v/>
       </c>
       <c r="B6" s="354" t="n"/>
       <c r="C6" s="321">
-        <f>COUNTIF('资产主表'!$K$6:$K$21,"已完成")+COUNTIF('资产主表'!$K$6:$K$21,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$21,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$21,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$21,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$21,"已导入；优化完成")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$22,"已完成")+COUNTIF('资产主表'!$K$6:$K$22,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$22,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$22,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$22,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$22,"已导入；优化完成")</f>
         <v/>
       </c>
       <c r="D6" s="354" t="n"/>
       <c r="E6" s="321">
-        <f>COUNTIF('资产主表'!$K$6:$K$21,"待制作")+COUNTIF('资产主表'!$K$6:$K$21,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$22,"待制作")+COUNTIF('资产主表'!$K$6:$K$22,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="354" t="n"/>
       <c r="G6" s="321">
-        <f>COUNTIF('资产主表'!$S$6:$S$21,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$22,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="354" t="n"/>
@@ -2412,11 +2412,11 @@
         </is>
       </c>
       <c r="B10" s="301">
-        <f>COUNTIF('资产主表'!$C$6:$C$21,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$22,A10)</f>
         <v/>
       </c>
       <c r="C10" s="301">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$21=A10)*(('资产主表'!$K$6:$K$21="已完成")+('资产主表'!$K$6:$K$21="原型已接入")+('资产主表'!$K$6:$K$21="正式美术已接入")+('资产主表'!$K$6:$K$21="已优化并正式接入")+('资产主表'!$K$6:$K$21="Blender源已完成")+('资产主表'!$K$6:$K$21="已导入；优化完成")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$22=A10)*(('资产主表'!$K$6:$K$22="已完成")+('资产主表'!$K$6:$K$22="原型已接入")+('资产主表'!$K$6:$K$22="正式美术已接入")+('资产主表'!$K$6:$K$22="已优化并正式接入")+('资产主表'!$K$6:$K$22="Blender源已完成")+('资产主表'!$K$6:$K$22="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D10" s="301" t="n"/>
@@ -2984,7 +2984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3256,7 +3256,7 @@
         <v/>
       </c>
       <c r="S6" s="138">
-        <f>IF(COUNTIF($R$6:$R$21,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="138" t="str"/>
@@ -3359,7 +3359,7 @@
         <v/>
       </c>
       <c r="S7" s="138">
-        <f>IF(COUNTIF($R$6:$R$21,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="138" t="str"/>
@@ -3462,7 +3462,7 @@
         <v/>
       </c>
       <c r="S8" s="138">
-        <f>IF(COUNTIF($R$6:$R$21,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="138" t="str"/>
@@ -3565,7 +3565,7 @@
         <v/>
       </c>
       <c r="S9" s="138">
-        <f>IF(COUNTIF($R$6:$R$21,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="138" t="str"/>
@@ -3672,7 +3672,7 @@
         <v/>
       </c>
       <c r="S10" s="138">
-        <f>IF(COUNTIF($R$6:$R$21,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="138" t="str"/>
@@ -3779,7 +3779,7 @@
         <v/>
       </c>
       <c r="S11" s="138">
-        <f>IF(COUNTIF($R$6:$R$21,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="138" t="str"/>
@@ -3886,7 +3886,7 @@
         <v/>
       </c>
       <c r="S12" s="138">
-        <f>IF(COUNTIF($R$6:$R$21,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="138" t="str"/>
@@ -3993,7 +3993,7 @@
         <v/>
       </c>
       <c r="S13" s="138">
-        <f>IF(COUNTIF($R$6:$R$21,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="138" t="str"/>
@@ -4100,7 +4100,7 @@
         <v/>
       </c>
       <c r="S14" s="138">
-        <f>IF(COUNTIF($R$6:$R$21,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="138" t="str"/>
@@ -4211,7 +4211,7 @@
         <v/>
       </c>
       <c r="S15" s="138">
-        <f>IF(COUNTIF($R$6:$R$21,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="138" t="inlineStr">
@@ -4323,7 +4323,7 @@
         <v/>
       </c>
       <c r="S16" s="138">
-        <f>IF(COUNTIF($R$6:$R$21,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="138" t="str"/>
@@ -4430,7 +4430,7 @@
         <v/>
       </c>
       <c r="S17" s="138">
-        <f>IF(COUNTIF($R$6:$R$21,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="138" t="str"/>
@@ -4549,7 +4549,7 @@
         <v/>
       </c>
       <c r="S18" s="392">
-        <f>IF(COUNTIF($R$6:$R$21,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="392" t="inlineStr">
@@ -4668,7 +4668,7 @@
         <v/>
       </c>
       <c r="S19" s="392">
-        <f>IF(COUNTIF($R$6:$R$21,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="392" t="inlineStr">
@@ -4791,7 +4791,7 @@
         <v/>
       </c>
       <c r="S20" s="392">
-        <f>IF(COUNTIF($R$6:$R$21,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="392" t="inlineStr">
@@ -4915,7 +4915,7 @@
         <v/>
       </c>
       <c r="S21" s="392">
-        <f>IF(COUNTIF($R$6:$R$21,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="392" t="inlineStr">
@@ -4945,6 +4945,121 @@
         <is>
           <t>v0.1：ForwardBeam仅照环境layer1，shadow_caster_mask也仅包含layer1，明确排除玩家、穿戴物与手持枪layer2；AvatarFrontFill无阴影。玩家网格保留cast_shadow=ON，由太阳和室内灯产生外部投影；准星禁用投影。曝光预算固定为主聚光7.2、环境溢光0.7、角色柔光2.8，并通过真实渲染验收。
 2026-08-03：主聚光保持能量7.2/范围25m/角度66°与环境层隔离；Compatibility阴影采样固定 bias=0.18、normal_bias=1.6、blur=1.2，消除远处斜角墙面横纹，不改变玩家自身不投影契约；已通过近25m真GPU画面验收。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="392" t="inlineStr">
+        <is>
+          <t>VFX-SHELL-CASING-3D</t>
+        </is>
+      </c>
+      <c r="B22" s="392" t="inlineStr">
+        <is>
+          <t>抛壳落地特效</t>
+        </is>
+      </c>
+      <c r="C22" s="392" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D22" s="392" t="inlineStr">
+        <is>
+          <t>战斗反馈</t>
+        </is>
+      </c>
+      <c r="E22" s="392" t="inlineStr">
+        <is>
+          <t>FX01-07</t>
+        </is>
+      </c>
+      <c r="F22" s="392" t="n"/>
+      <c r="G22" s="392" t="n"/>
+      <c r="H22" s="392" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I22" s="392" t="inlineStr">
+        <is>
+          <t>开火抛壳/落地</t>
+        </is>
+      </c>
+      <c r="J22" s="392" t="inlineStr">
+        <is>
+          <t>玩家/敌人远程枪械</t>
+        </is>
+      </c>
+      <c r="K22" s="392" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L22" s="392" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M22" s="392" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N22" s="392" t="inlineStr">
+        <is>
+          <t>PackedScene/程序运动</t>
+        </is>
+      </c>
+      <c r="O22" s="392" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_shell_casing_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P22" s="392" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxShellCasing3D.gd</t>
+        </is>
+      </c>
+      <c r="Q22" s="392" t="inlineStr">
+        <is>
+          <t>弹壳,抛壳,落地,枪械反馈</t>
+        </is>
+      </c>
+      <c r="R22" s="392">
+        <f>LOWER(TRIM(C22)&amp;"|"&amp;TRIM(D22)&amp;"|"&amp;TRIM(E22)&amp;"|"&amp;TRIM(F22)&amp;"|"&amp;TRIM(H22)&amp;"|"&amp;TRIM(I22))</f>
+        <v/>
+      </c>
+      <c r="S22" s="392">
+        <f>IF(COUNTIF($R$6:$R$22,R22)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T22" s="392" t="inlineStr">
+        <is>
+          <t>f848a7fa405457b1d420329ae574d32bf0d65898358b75036a40360c563fbeef</t>
+        </is>
+      </c>
+      <c r="U22" s="392" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V22" s="348" t="n">
+        <v>46287</v>
+      </c>
+      <c r="W22" s="348" t="inlineStr">
+        <is>
+          <t>原创程序几何</t>
+        </is>
+      </c>
+      <c r="X22" s="375" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y22" s="392" t="inlineStr">
+        <is>
+          <t>独立纯视觉 Prefab，无碰撞体；每次成功开火生成 1 枚；从枪械右侧抛出，重力 9.8m/s²，命中地板最多 2 次小弹跳后静止，3.2s 回收；验收 verify_combat_vfx_toon_v002。</t>
         </is>
       </c>
     </row>
@@ -5169,13 +5284,13 @@
     <cfRule type="containsText" priority="3" operator="containsText" dxfId="2" text="待制作"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5192,7 +5307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5223,7 +5338,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="377" t="inlineStr">
         <is>
-          <t>特效按独立 Prefab 原则：每个特效一个独立 .tscn；Prefab 是特效唯一出口；账本和调用代码读 Prefab。本 sheet 共 11 条，按 5 大类分组，每条 VFX 有内部编号 FX&lt;大类&gt;-&lt;序号&gt;。状态：✅ 完成（Prefab + 脚本 + 接入齐）/ 🟡 待落地（已登记 AssetID，文件未创建）/ 🟠 老形态（迁移完成后删除）。规范见 docs/v0.1/14.6_特效系统与制作规范.md。【2026-09-11 进度】FX01 战斗反馈 5 条 + FX02 受击飘字 2 条 共 7 条完成；FX03/04 已实装但命名待对齐。【2026-09-21 进度】新增 FX01-06 VFX-BULLET-VISUAL-3D（飞行子弹纯视觉，含 ProjectileLight，由 Projectile3D 持有、不进 VfxPool）；FX01-01 / FX01-02 升 v002 卡通重做（枪口新增 MuzzleLight、命中改按命中法线对齐）；三类共同验收 verify_combat_vfx_toon_v002。</t>
+          <t>特效按独立 Prefab 原则：每个特效一个独立 .tscn；Prefab 是特效唯一出口；账本和调用代码读 Prefab。本 sheet 共 12 条，按 5 大类分组，每条 VFX 有内部编号 FX&lt;大类&gt;-&lt;序号&gt;。状态：✅ 完成（Prefab + 脚本 + 接入齐）/ 🟡 待落地（已登记 AssetID，文件未创建）/ 🟠 老形态（迁移完成后删除）。规范见 docs/v0.1/14.6_特效系统与制作规范.md。【2026-09-11 进度】FX01 战斗反馈 5 条 + FX02 受击飘字 2 条 共 7 条完成；FX03/04 已实装但命名待对齐。【2026-09-21 进度】新增 FX01-06 VFX-BULLET-VISUAL-3D（飞行子弹纯视觉，含 ProjectileLight，由 Projectile3D 持有、不进 VfxPool）；FX01-01 / FX01-02 升 v002 卡通重做（枪口新增 MuzzleLight、命中改按命中法线对齐）；三类共同验收 verify_combat_vfx_toon_v002。【2026-09-22 进度】新增 FX01-07 VFX-SHELL-CASING-3D：开火抛壳、重力落地、最多两次小弹跳后静止，接入 WeaponModel3D 与 VfxPool3D。</t>
         </is>
       </c>
     </row>
@@ -5904,377 +6019,454 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="387" t="inlineStr">
+      <c r="A14" s="391" t="inlineStr">
+        <is>
+          <t>FX01-07</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VFX-SHELL-CASING-3D</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>抛壳落地特效</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_shell_casing_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>枪械开火时从枪械右侧飞出的弹壳：黄铜色圆柱弹壳 + 底缘圆环 + 底火；由 VfxPool3D 按 AssetID 路由。弹壳脱离武器挂点进入世界空间，程序化重力 9.8m/s² 下落，命中地板最多 2 次小弹跳后静止，寿命 3.2s 回收。</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxShellCasing3D.gd</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>程序射线落地</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>直径约 0.09m；长度 0.24m；弹出初速度右向 2.1m/s + 上抛 1.55m/s；lifetime 3.2s</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>原点=弹壳中心；朝向=圆柱 local Y 为壳体长轴；出生点取 EjectionSocket/TacticalSocket</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>玩家/敌人远程枪械开火反馈</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_shell_casing_root_top3d.tscn；脚本=src/vfx/VfxShellCasing3D.gd；根节点=VfxShellCasing3D(Node3D)；FX编号 FX01-07；调用方=WeaponModel3D._fire_now → _spawn_shell_casing；纯视觉无碰撞体，落地由现有物理射线或 floor_y 兜底；验收=verify_combat_vfx_toon_v002，含端到端右侧抛壳与反向对照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="387" t="inlineStr">
         <is>
           <t>▼ 02 受击飘字</t>
         </is>
       </c>
-      <c r="B14" s="388" t="n"/>
-      <c r="C14" s="388" t="n"/>
-      <c r="D14" s="388" t="n"/>
-      <c r="E14" s="388" t="n"/>
-      <c r="F14" s="388" t="n"/>
-      <c r="G14" s="388" t="n"/>
-      <c r="H14" s="388" t="n"/>
-      <c r="I14" s="388" t="n"/>
-      <c r="J14" s="388" t="n"/>
-      <c r="K14" s="388" t="n"/>
-      <c r="L14" s="388" t="n"/>
-      <c r="M14" s="388" t="n"/>
-      <c r="N14" s="388" t="n"/>
-      <c r="O14" s="388" t="n"/>
-      <c r="P14" s="388" t="n"/>
-      <c r="Q14" s="388" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="391" t="inlineStr">
-        <is>
-          <t>FX02-01</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>VFX-DAMAGE-NUMBER-3D</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>伤害数字飘字特效</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>assets/art/vfx/combat_3d/vfx_damage_number_root_top3d.tscn</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>受击伤害数字上升飘字；Label3D + 黑边 + 颜色编码（红/橙/暴击金）；参数 effect_color + context.text_value。</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>src/vfx/VfxDamageNumber3D.gd</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Label3D pixel_size=0.010；lifetime 0.72s</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>原点=根节点中心；朝向=local -Z 正面</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>玩家/敌人受击伤害显示</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>完成</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>v001</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_damage_number_root_top3d_v001.tscn + 脚本=src/vfx/VfxDamageNumber3D.gd；根节点=VfxDamageNumber3D(Node3D)；FX编号 FX02-01；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value</t>
-        </is>
-      </c>
+      <c r="B15" s="388" t="n"/>
+      <c r="C15" s="388" t="n"/>
+      <c r="D15" s="388" t="n"/>
+      <c r="E15" s="388" t="n"/>
+      <c r="F15" s="388" t="n"/>
+      <c r="G15" s="388" t="n"/>
+      <c r="H15" s="388" t="n"/>
+      <c r="I15" s="388" t="n"/>
+      <c r="J15" s="388" t="n"/>
+      <c r="K15" s="388" t="n"/>
+      <c r="L15" s="388" t="n"/>
+      <c r="M15" s="388" t="n"/>
+      <c r="N15" s="388" t="n"/>
+      <c r="O15" s="388" t="n"/>
+      <c r="P15" s="388" t="n"/>
+      <c r="Q15" s="388" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="391" t="inlineStr">
         <is>
+          <t>FX02-01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VFX-DAMAGE-NUMBER-3D</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>伤害数字飘字特效</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_damage_number_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>受击伤害数字上升飘字；Label3D + 黑边 + 颜色编码（红/橙/暴击金）；参数 effect_color + context.text_value。</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxDamageNumber3D.gd</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Label3D pixel_size=0.010；lifetime 0.72s</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>原点=根节点中心；朝向=local -Z 正面</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>玩家/敌人受击伤害显示</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_damage_number_root_top3d_v001.tscn + 脚本=src/vfx/VfxDamageNumber3D.gd；根节点=VfxDamageNumber3D(Node3D)；FX编号 FX02-01；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="391" t="inlineStr">
+        <is>
           <t>FX02-02</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>VFX-HEAL-NUMBER-3D</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>治疗数字飘字特效</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>assets/art/vfx/combat_3d/vfx_heal_number_root_top3d.tscn</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>治疗/恢复数字上升飘字；Label3D + 绿色调（+ 白色描边）；参数 context.text_value。</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>src/vfx/VfxHealNumber3D.gd</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Label3D pixel_size=0.010；lifetime 0.72s</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>原点=根节点中心；朝向=local -Z 正面</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>玩家/队友治疗显示</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>v001</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_heal_number_root_top3d_v001.tscn + 脚本=src/vfx/VfxHealNumber3D.gd；根节点=VfxHealNumber3D(Node3D)；FX编号 FX02-02；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="387" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="387" t="inlineStr">
         <is>
           <t>▼ 03 环境场</t>
         </is>
       </c>
-      <c r="B17" s="388" t="n"/>
-      <c r="C17" s="388" t="n"/>
-      <c r="D17" s="388" t="n"/>
-      <c r="E17" s="388" t="n"/>
-      <c r="F17" s="388" t="n"/>
-      <c r="G17" s="388" t="n"/>
-      <c r="H17" s="388" t="n"/>
-      <c r="I17" s="388" t="n"/>
-      <c r="J17" s="388" t="n"/>
-      <c r="K17" s="388" t="n"/>
-      <c r="L17" s="388" t="n"/>
-      <c r="M17" s="388" t="n"/>
-      <c r="N17" s="388" t="n"/>
-      <c r="O17" s="388" t="n"/>
-      <c r="P17" s="388" t="n"/>
-      <c r="Q17" s="388" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="391" t="inlineStr">
+      <c r="B18" s="388" t="n"/>
+      <c r="C18" s="388" t="n"/>
+      <c r="D18" s="388" t="n"/>
+      <c r="E18" s="388" t="n"/>
+      <c r="F18" s="388" t="n"/>
+      <c r="G18" s="388" t="n"/>
+      <c r="H18" s="388" t="n"/>
+      <c r="I18" s="388" t="n"/>
+      <c r="J18" s="388" t="n"/>
+      <c r="K18" s="388" t="n"/>
+      <c r="L18" s="388" t="n"/>
+      <c r="M18" s="388" t="n"/>
+      <c r="N18" s="388" t="n"/>
+      <c r="O18" s="388" t="n"/>
+      <c r="P18" s="388" t="n"/>
+      <c r="Q18" s="388" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="391" t="inlineStr">
         <is>
           <t>FX03-01</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>VFX-HAZARD-FIELD-3D</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>房间危险场3D特效</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>assets/art/vfx/environment_3d/vfx_hazard_field_root_top3d.tscn</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>房间危险场 Area3D 特效；脚本生成的环形危险区域；触发时产生伤害 + 视觉脉冲。</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>src/world3d/HazardField3D.gd</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Prefab自身</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>脚本生成</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>PackedScene/程序环形特效</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>未声明</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>陷阱房</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>v001</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>已实装；命名待 14.6 §6 迁移时对齐（改名 VfxHazardField3D + 移至 src/vfx/）</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="387" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="387" t="inlineStr">
         <is>
           <t>▼ 04 可见性</t>
         </is>
       </c>
-      <c r="B19" s="388" t="n"/>
-      <c r="C19" s="388" t="n"/>
-      <c r="D19" s="388" t="n"/>
-      <c r="E19" s="388" t="n"/>
-      <c r="F19" s="388" t="n"/>
-      <c r="G19" s="388" t="n"/>
-      <c r="H19" s="388" t="n"/>
-      <c r="I19" s="388" t="n"/>
-      <c r="J19" s="388" t="n"/>
-      <c r="K19" s="388" t="n"/>
-      <c r="L19" s="388" t="n"/>
-      <c r="M19" s="388" t="n"/>
-      <c r="N19" s="388" t="n"/>
-      <c r="O19" s="388" t="n"/>
-      <c r="P19" s="388" t="n"/>
-      <c r="Q19" s="388" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="391" t="inlineStr">
+      <c r="B20" s="388" t="n"/>
+      <c r="C20" s="388" t="n"/>
+      <c r="D20" s="388" t="n"/>
+      <c r="E20" s="388" t="n"/>
+      <c r="F20" s="388" t="n"/>
+      <c r="G20" s="388" t="n"/>
+      <c r="H20" s="388" t="n"/>
+      <c r="I20" s="388" t="n"/>
+      <c r="J20" s="388" t="n"/>
+      <c r="K20" s="388" t="n"/>
+      <c r="L20" s="388" t="n"/>
+      <c r="M20" s="388" t="n"/>
+      <c r="N20" s="388" t="n"/>
+      <c r="O20" s="388" t="n"/>
+      <c r="P20" s="388" t="n"/>
+      <c r="Q20" s="388" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="391" t="inlineStr">
         <is>
           <t>FX04-01</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>VFX-PLAYER-FLASHLIGHT-3D</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>玩家真实探照灯组件3D</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>assets/art/vfx/visibility_3d/vfx_player_flashlight_root_top3d.tscn</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>玩家真实探照灯 Node3D 组件；2 SpotLight3D + 1 OmniLight3D 组合；3D 行动区/靶场/基地覆盖。</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>src/player3d/PlayerFlashlight3D.gd</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>PackedScene/2 SpotLight3D+1 OmniLight3D</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>未声明</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>3D行动区/靶场/基地</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>v001</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>已实装；命名待 14.6 §6 迁移时对齐（改名 VfxPlayerFlashlight3D + 移至 src/vfx/）</t>
         </is>
@@ -6306,7 +6498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6481,6 +6673,43 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>v0.1.3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>新增条目</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>特效 · 3D-特效</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>新增 FX01-07 VFX-SHELL-CASING-3D 抛壳落地特效：独立 Prefab + 脚本，接入 WeaponModel3D 开火链路与 VfxPool3D；弹壳从枪械右侧抛出，按重力下落，最多两次小弹跳后静止并回收；补专项验收与反向对照。</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>新增一个 AssetID；不改既有 AssetID；纯视觉无碰撞体；开火调用向后兼容。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -5036,7 +5036,7 @@
       </c>
       <c r="T22" s="392" t="inlineStr">
         <is>
-          <t>f848a7fa405457b1d420329ae574d32bf0d65898358b75036a40360c563fbeef</t>
+          <t>df2cb64e06aa312f19a4c330a13c37b8c36f6884308c900181a7597a051fbf93</t>
         </is>
       </c>
       <c r="U22" s="392" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="Y22" s="392" t="inlineStr">
         <is>
-          <t>独立纯视觉 Prefab，无碰撞体；每次成功开火生成 1 枚；从枪械右侧抛出，重力 9.8m/s²，命中地板最多 2 次小弹跳后静止，3.2s 回收；验收 verify_combat_vfx_toon_v002。</t>
+          <t>独立纯视觉 Prefab，无碰撞体；每次成功开火生成 1 枚；从枪械右侧抛出，重力 9.8m/s²，命中地板最多 2 次小弹跳后静止，3.2s 回收；验收 verify_combat_vfx_toon_v002。 PBR 定档：金属度 metallic=0.8 / 反光度（roughness）=0.6，壳体/底缘/底火三件统一（2026-09-22 指定）。 【模拟碰撞】落地改为**纯程序化模拟碰撞**（解析式越线，不做任何物理射线/空间查询，Prefab 无碰撞体）：弹壳中心 y 越过「地面高度 + 贴地半径」即视为碰撞；运动为 飞行(弹跳) → 贴地滚动 → 躺平静止 三阶段；触地带挤压包络。视觉尺寸缩到原基准 **80%**（WeaponModel3D.SHELL_CASING_SIZE=0.8）。⚠️ context.floor_y 必须由调用方按真实世界给，禁以 0 兜底 —— 塔楼楼层向下建（98F ≈ -1176m），兜底 0 会让弹壳出生即判触地、瞬移到世界原点而看不见（2026-09-22 实机缺陷）；调用方口径 = 射击者站立面 y，见 WeaponModel3D._resolve_shell_floor_y()。贴地半径取三件最大径向半展 0.058（底缘），非壳体 0.045。</t>
         </is>
       </c>
     </row>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>枪械开火时从枪械右侧飞出的弹壳：黄铜色圆柱弹壳 + 底缘圆环 + 底火；由 VfxPool3D 按 AssetID 路由。弹壳脱离武器挂点进入世界空间，程序化重力 9.8m/s² 下落，命中地板最多 2 次小弹跳后静止，寿命 3.2s 回收。</t>
+          <t>枪械开火时从枪械右侧飞出的弹壳：黄铜色圆柱弹壳 + 底缘圆环 + 底火；由 VfxPool3D 按 AssetID 路由。弹壳脱离武器挂点进入世界空间，程序化重力 9.8m/s² 下落。【模拟碰撞】落地为纯程序化模拟碰撞（解析式越线判定，不做物理射线/空间查询，Prefab 无碰撞体）：弹壳中心越过「地面高度 + 贴地半径」即触地；运动三阶段 飞行(含弹跳) → 贴地滚动 → 躺平静止；触地带挤压包络。手感参数：恢复系数 0.32 / 地面摩擦 0.42 / 自旋保留 0.68 / 最多 2 次弹跳 / 滚动衰减 3.4。视觉尺寸缩到原基准 80%，寿命 3.2s 回收。PBR 定档（2026-09-22）：金属度 metallic=0.8、反光度（roughness）=0.6，三件统一，常量 SHELL_METALLIC / SHELL_ROUGHNESS。</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>程序射线落地</t>
+          <t>程序化模拟碰撞（解析式越线，无物理引擎）</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>直径约 0.09m；长度 0.24m；弹出初速度右向 2.1m/s + 上抛 1.55m/s；lifetime 3.2s</t>
+          <t>视觉尺寸 80%（原基准 ×0.8）：壳体直径 0.046×2×0.8≈0.074m、底缘直径 0.058×2×0.8≈0.093m、长度 0.24×0.8=0.192m；弹出初速度右向 2.1m/s + 上抛 1.55m/s；lifetime 3.2s</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_shell_casing_root_top3d.tscn；脚本=src/vfx/VfxShellCasing3D.gd；根节点=VfxShellCasing3D(Node3D)；FX编号 FX01-07；调用方=WeaponModel3D._fire_now → _spawn_shell_casing；纯视觉无碰撞体，落地由现有物理射线或 floor_y 兜底；验收=verify_combat_vfx_toon_v002，含端到端右侧抛壳与反向对照。</t>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_shell_casing_root_top3d.tscn；脚本=src/vfx/VfxShellCasing3D.gd；根节点=VfxShellCasing3D(Node3D)；FX编号 FX01-07；调用方=WeaponModel3D._fire_now → _spawn_shell_casing；纯视觉无碰撞体，落地由现有物理射线或 floor_y 兜底；验收=verify_combat_vfx_toon_v002，含端到端右侧抛壳与反向对照。 PBR：metallic=0.8 / roughness=0.6（常量 SHELL_METALLIC / SHELL_ROUGHNESS）；验收读已挂载材质真值（非常量回读）并附反向对照。 【模拟碰撞】落地已由「物理射线/floor_y 兜底」改为**解析式模拟碰撞**（脚本内无任何物理 API，验收有源码级静态门禁）；尺寸缩到原基准 80%；贴地半径取三件最大径向半展 0.058（底缘 outer_radius）。⚠️ floor_y 必须由调用方按真实世界给（塔楼 98F ≈ -1176m），禁以 0 兜底，调用方=WeaponModel3D._resolve_shell_floor_y(shooter)（取射击者站立面）。验收 samples=14，含非零楼层端到端与弹壳出生于抛壳挂点断言；真渲染探针 probe_shell_casing_visual（3 机位）。</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6525,6 +6525,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="298" t="inlineStr">
         <is>
@@ -6705,6 +6706,80 @@
         </is>
       </c>
       <c r="G9" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>v0.1.4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>条目更新</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>特效 · 3D-特效</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FX01-07 VFX-SHELL-CASING-3D：PBR 定档为金属度 metallic=0.8、反光度 roughness=0.6，壳体/底缘/底火三件统一；原先三件各自分散的数值收敛为单一常量组 SHELL_METALLIC / SHELL_ROUGHNESS（各件仅保留基色差异）；专项验收新增 PBR 真值断言（读已挂载材质，期望值硬编码于验收侧）并附反向对照。</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>仅材质参数变化，不影响 AssetID / Prefab 路径 / 尺寸契约 / 运动与落地行为；观感为更暗哑统一的黄铜金属弹壳。</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>v0.1.5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>条目更新</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>特效 · 3D-特效</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FX01-07 VFX-SHELL-CASING-3D 弹壳：落地由「物理射线 / floor_y 兜底」改为**纯程序化模拟碰撞**（解析式越线判定，Prefab 无碰撞体，脚本内无任何物理查询 API）；运动改为 飞行(弹跳) → 贴地滚动 → 躺平静止 三阶段 + 触地挤压包络，手感常量收敛为一组；视觉尺寸缩到原基准 **80%**；贴地半径由壳体 0.045 修正为三件最大径向半展 0.058（底缘）；修复实机缺陷「弹壳特效没了」——floor_y 原硬编码 0，而塔楼楼层向下建（98F ≈ -1176m），导致弹壳出生即判触地、瞬移到世界原点；现由 WeaponModel3D._resolve_shell_floor_y(shooter) 取射击者站立面。资产主表 row22 哈希同步刷新为磁盘真值（Prefab 于 08:47 被重存、去掉 load_steps 提示行）。</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AssetID / Prefab 路径 / 版本号 v001 / PBR 定档值均不变；仅行为、尺寸常量与落地判据变化；调用方签名 _spawn_shell_casing(world) → (shooter: Node3D)（内部方法，无外部调用者）。</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>摩斯拉</t>
         </is>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3D-特效" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -22,8 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -601,7 +602,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -903,6 +904,24 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1420,22 +1439,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="52">
       <c r="A6" s="57">
-        <f>COUNTA('资产主表'!$A$6:$A$21)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$22)</f>
         <v/>
       </c>
       <c r="B6" s="55" t="n"/>
       <c r="C6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$21,"已完成")+COUNTIF('资产主表'!$K$6:$K$21,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$21,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$21,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$21,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$21,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$21,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$22,"已完成")+COUNTIF('资产主表'!$K$6:$K$22,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$22,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$22,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$22,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$22,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$22,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="55" t="n"/>
       <c r="E6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$21,"待制作")+COUNTIF('资产主表'!$K$6:$K$21,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$22,"待制作")+COUNTIF('资产主表'!$K$6:$K$22,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="55" t="n"/>
       <c r="G6" s="57">
-        <f>COUNTIF('资产主表'!$S$6:$S$21,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$22,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="55" t="n"/>
@@ -1504,11 +1523,11 @@
         </is>
       </c>
       <c r="B10" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$21,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$22,A10)</f>
         <v/>
       </c>
       <c r="C10" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$21=A10)*(('资产主表'!$K$6:$K$21="已完成")+('资产主表'!$K$6:$K$21="原型已接入")+('资产主表'!$K$6:$K$21="正式美术已接入")+('资产主表'!$K$6:$K$21="已优化并正式接入")+('资产主表'!$K$6:$K$21="Blender源已完成")+('资产主表'!$K$6:$K$21="已导入；优化完成")+('资产主表'!$K$6:$K$21="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$22=A10)*(('资产主表'!$K$6:$K$22="已完成")+('资产主表'!$K$6:$K$22="原型已接入")+('资产主表'!$K$6:$K$22="正式美术已接入")+('资产主表'!$K$6:$K$22="已优化并正式接入")+('资产主表'!$K$6:$K$22="Blender源已完成")+('资产主表'!$K$6:$K$22="已导入；优化完成")+('资产主表'!$K$6:$K$22="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="62" t="n"/>
@@ -1526,11 +1545,11 @@
         </is>
       </c>
       <c r="B11" s="58">
-        <f>COUNTIF('资产主表'!$C$6:$C$21,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$22,A11)</f>
         <v/>
       </c>
       <c r="C11" s="58">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$21=A11)*(('资产主表'!$K$6:$K$21="已完成")+('资产主表'!$K$6:$K$21="原型已接入")+('资产主表'!$K$6:$K$21="正式美术已接入")+('资产主表'!$K$6:$K$21="已优化并正式接入")+('资产主表'!$K$6:$K$21="Blender源已完成")+('资产主表'!$K$6:$K$21="已导入；优化完成")+('资产主表'!$K$6:$K$21="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$22=A11)*(('资产主表'!$K$6:$K$22="已完成")+('资产主表'!$K$6:$K$22="原型已接入")+('资产主表'!$K$6:$K$22="正式美术已接入")+('资产主表'!$K$6:$K$22="已优化并正式接入")+('资产主表'!$K$6:$K$22="Blender源已完成")+('资产主表'!$K$6:$K$22="已导入；优化完成")+('资产主表'!$K$6:$K$22="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="58" t="n"/>
@@ -1757,6 +1776,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="52">
       <c r="A5" s="58" t="inlineStr">
         <is>
@@ -2078,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="51" min="1" max="1"/>
@@ -2350,7 +2370,7 @@
         <v/>
       </c>
       <c r="S6" s="63">
-        <f>IF(COUNTIF($R$6:$R$21,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="63" t="n"/>
@@ -2453,7 +2473,7 @@
         <v/>
       </c>
       <c r="S7" s="63">
-        <f>IF(COUNTIF($R$6:$R$21,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="63" t="n"/>
@@ -2556,7 +2576,7 @@
         <v/>
       </c>
       <c r="S8" s="63">
-        <f>IF(COUNTIF($R$6:$R$21,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="63" t="n"/>
@@ -2659,7 +2679,7 @@
         <v/>
       </c>
       <c r="S9" s="63">
-        <f>IF(COUNTIF($R$6:$R$21,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="63" t="n"/>
@@ -2766,7 +2786,7 @@
         <v/>
       </c>
       <c r="S10" s="63">
-        <f>IF(COUNTIF($R$6:$R$21,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="63" t="n"/>
@@ -2873,7 +2893,7 @@
         <v/>
       </c>
       <c r="S11" s="63">
-        <f>IF(COUNTIF($R$6:$R$21,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="63" t="n"/>
@@ -2980,7 +3000,7 @@
         <v/>
       </c>
       <c r="S12" s="63">
-        <f>IF(COUNTIF($R$6:$R$21,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="63" t="n"/>
@@ -3087,7 +3107,7 @@
         <v/>
       </c>
       <c r="S13" s="63">
-        <f>IF(COUNTIF($R$6:$R$21,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="63" t="n"/>
@@ -3194,7 +3214,7 @@
         <v/>
       </c>
       <c r="S14" s="63">
-        <f>IF(COUNTIF($R$6:$R$21,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="63" t="n"/>
@@ -3301,7 +3321,7 @@
         <v/>
       </c>
       <c r="S15" s="63">
-        <f>IF(COUNTIF($R$6:$R$21,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="63" t="n"/>
@@ -3408,7 +3428,7 @@
         <v/>
       </c>
       <c r="S16" s="63">
-        <f>IF(COUNTIF($R$6:$R$21,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="63" t="n"/>
@@ -3527,7 +3547,7 @@
         <v/>
       </c>
       <c r="S17" s="55">
-        <f>IF(COUNTIF($R$6:$R$21,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="79" t="inlineStr">
@@ -3646,7 +3666,7 @@
         <v/>
       </c>
       <c r="S18" s="55">
-        <f>IF(COUNTIF($R$6:$R$21,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="79" t="inlineStr">
@@ -3769,7 +3789,7 @@
         <v/>
       </c>
       <c r="S19" s="55">
-        <f>IF(COUNTIF($R$6:$R$21,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="79" t="inlineStr">
@@ -3893,7 +3913,7 @@
         <v/>
       </c>
       <c r="S20" s="55">
-        <f>IF(COUNTIF($R$6:$R$21,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="79" t="inlineStr">
@@ -4009,7 +4029,7 @@
         <v/>
       </c>
       <c r="S21" s="55">
-        <f>IF(COUNTIF($R$6:$R$21,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="79" t="inlineStr">
@@ -4038,6 +4058,125 @@
       <c r="Y21" s="55" t="inlineStr">
         <is>
           <t>独立纯视觉 Prefab，无碰撞体；每次成功开火生成 1 枚；从枪械右侧抛出，重力 9.8m/s²，命中地板最多 2 次小弹跳后静止，3.2s 回收；验收 verify_combat_vfx_toon_v002。 PBR 定档：金属度 metallic=0.8 / 反光度（roughness）=0.6，壳体/底缘/底火三件统一（2026-09-22 指定）。 【模拟碰撞】落地改为**纯程序化模拟碰撞**（解析式越线，不做任何物理射线/空间查询，Prefab 无碰撞体）：弹壳中心 y 越过「地面高度 + 贴地半径」即视为碰撞；运动为 飞行(弹跳) → 贴地滚动 → 躺平静止 三阶段；触地带挤压包络。视觉尺寸缩到原基准 **80%**（WeaponModel3D.SHELL_CASING_SIZE=0.8）。⚠️ context.floor_y 必须由调用方按真实世界给，禁以 0 兜底 —— 塔楼楼层向下建（98F ≈ -1176m），兜底 0 会让弹壳出生即判触地、瞬移到世界原点而看不见（2026-09-22 实机缺陷）；调用方口径 = 射击者站立面 y，见 WeaponModel3D._resolve_shell_floor_y()。贴地半径取三件最大径向半展 0.058（底缘），非壳体 0.045。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="120" customHeight="1" s="52">
+      <c r="A22" s="79" t="inlineStr">
+        <is>
+          <t>VFX-ENV-CLOUD-SEA-3D</t>
+        </is>
+      </c>
+      <c r="B22" s="55" t="inlineStr">
+        <is>
+          <t>主塔柔软体积云海与漂浮小云</t>
+        </is>
+      </c>
+      <c r="C22" s="55" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D22" s="79" t="inlineStr">
+        <is>
+          <t>environment</t>
+        </is>
+      </c>
+      <c r="E22" s="79" t="inlineStr">
+        <is>
+          <t>outdoor_cloud_sea</t>
+        </is>
+      </c>
+      <c r="F22" s="79" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G22" s="79" t="n"/>
+      <c r="H22" s="55" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I22" s="79" t="inlineStr">
+        <is>
+          <t>slow_flow</t>
+        </is>
+      </c>
+      <c r="J22" s="55" t="inlineStr">
+        <is>
+          <t>主塔与周边塔楼99F以下室外</t>
+        </is>
+      </c>
+      <c r="K22" s="55" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L22" s="79" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M22" s="79" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="N22" s="79" t="inlineStr">
+        <is>
+          <t>连续世界密度云海476×90×536m，Y=-105～-15，云顶圆润起伏、云内遮光、下层薄雾、楼边透出下方楼层。24块漂浮小云，低档12块；高/中/低96/64/40步体积采样、4/3/2步定向透射。image-2原创1024²灰度密度，128³ RGB周期云结构，256×80×288 R8建筑避让；无碰撞。</t>
+        </is>
+      </c>
+      <c r="O22" s="79" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/environment_3d/cloud_sea/vfx_env_cloud_sea_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P22" s="79" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxCloudSea3D.gd; docs/v0.1/design/outdoor_cloud_sea.md; source/v002</t>
+        </is>
+      </c>
+      <c r="Q22" s="55" t="inlineStr">
+        <is>
+          <t>云海;体积云;光遇风格;柔软;漂浮;薄雾;室外</t>
+        </is>
+      </c>
+      <c r="R22" s="79">
+        <f>LOWER(TRIM(C22)&amp;"|"&amp;TRIM(D22)&amp;"|"&amp;TRIM(E22)&amp;"|"&amp;TRIM(F22)&amp;"|"&amp;TRIM(H22)&amp;"|"&amp;TRIM(I22))</f>
+        <v/>
+      </c>
+      <c r="S22" s="55">
+        <f>IF(COUNTIF($R$6:$R$22,R22)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T22" s="79" t="inlineStr">
+        <is>
+          <t>f7830ac829de78bdbf189b89ab16a2c5d8b8730e2cb0a694809e7472fa60d63c</t>
+        </is>
+      </c>
+      <c r="U22" s="79" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V22" s="104" t="n">
+        <v>46295</v>
+      </c>
+      <c r="W22" s="55" t="inlineStr">
+        <is>
+          <t>项目原创Shader/三维程序密度；gpt-image-2原创灰度云贴图，用户参考图仅作风格参考</t>
+        </is>
+      </c>
+      <c r="X22" s="78" t="inlineStr">
+        <is>
+          <t>FX03-02 / procedural_cloud_sea</t>
+        </is>
+      </c>
+      <c r="Y22" s="55" t="inlineStr">
+        <is>
+          <t>v002品质优先版，尚未专项优化。主场景OutdoorClouds持有；主塔全高度禁云，700建筑边界遮罩随最新布局重烘焙。实际天台520m及99F145m视距均验证云可见、亮部有余量；GPU实际纹理采样、暂停、60秒流动、失效遮罩拒绝通过。原AssetID升级，不新增行。</t>
         </is>
       </c>
     </row>
@@ -4249,17 +4388,17 @@
     <row r="427" ht="84.75" customHeight="1" s="52"/>
     <row r="429" ht="120" customHeight="1" s="52"/>
   </sheetData>
-  <autoFilter ref="A5:X21"/>
+  <autoFilter ref="A5:X22"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
   </mergeCells>
-  <conditionalFormatting sqref="S6:S21">
+  <conditionalFormatting sqref="S6:S22">
     <cfRule type="containsText" rank="0" priority="2" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="6" text="重复" percent="0" bottom="0">
       <formula>NOT(ISERROR(SEARCH("重复",S6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K21">
+  <conditionalFormatting sqref="K6:K22">
     <cfRule type="containsText" rank="0" priority="3" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="7" text="已完成" percent="0" bottom="0">
       <formula>NOT(ISERROR(SEARCH("已完成",K6)))</formula>
     </cfRule>
@@ -5461,15 +5600,107 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="52">
-      <c r="H22" s="101" t="n"/>
-      <c r="I22" s="51" t="n"/>
-      <c r="N22" s="51" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="52">
-      <c r="H23" s="101" t="n"/>
-      <c r="I23" s="51" t="n"/>
-      <c r="N23" s="51" t="n"/>
+    <row r="22" ht="18" customHeight="1" s="52">
+      <c r="A22" s="103" t="inlineStr">
+        <is>
+          <t>▼ 03 环境场（续）</t>
+        </is>
+      </c>
+      <c r="B22" s="92" t="n"/>
+      <c r="C22" s="92" t="n"/>
+      <c r="D22" s="92" t="n"/>
+      <c r="E22" s="92" t="n"/>
+      <c r="F22" s="92" t="n"/>
+      <c r="G22" s="92" t="n"/>
+      <c r="H22" s="102" t="n"/>
+      <c r="I22" s="92" t="n"/>
+      <c r="J22" s="92" t="n"/>
+      <c r="K22" s="92" t="n"/>
+      <c r="L22" s="92" t="n"/>
+      <c r="M22" s="92" t="n"/>
+      <c r="N22" s="92" t="n"/>
+      <c r="O22" s="92" t="n"/>
+      <c r="P22" s="92" t="n"/>
+      <c r="Q22" s="92" t="n"/>
+    </row>
+    <row r="23" ht="144" customHeight="1" s="52">
+      <c r="A23" s="106" t="inlineStr">
+        <is>
+          <t>FX03-02</t>
+        </is>
+      </c>
+      <c r="B23" s="107" t="inlineStr">
+        <is>
+          <t>VFX-ENV-CLOUD-SEA-3D</t>
+        </is>
+      </c>
+      <c r="C23" s="108" t="inlineStr">
+        <is>
+          <t>主塔柔软体积云海与漂浮小云</t>
+        </is>
+      </c>
+      <c r="D23" s="107" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/environment_3d/cloud_sea/vfx_env_cloud_sea_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E23" s="109" t="n"/>
+      <c r="F23" s="109" t="n"/>
+      <c r="G23" s="108" t="inlineStr">
+        <is>
+          <t>室外常驻连续云海、下沉雾层、柔软漂浮小云</t>
+        </is>
+      </c>
+      <c r="H23" s="107" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxCloudSea3D.gd</t>
+        </is>
+      </c>
+      <c r="I23" s="108" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J23" s="107" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K23" s="108" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L23" s="107" t="inlineStr">
+        <is>
+          <t>连续世界密度云海476×90×536m，Y=-105～-15，云顶圆润起伏、云内遮光、下层薄雾、楼边透出下方楼层。24块漂浮小云，低档12块；高/中/低96/64/40步体积采样、4/3/2步定向透射。image-2原创1024²灰度密度，128³ RGB周期云结构，256×80×288 R8建筑避让；无碰撞。</t>
+        </is>
+      </c>
+      <c r="M23" s="108" t="inlineStr">
+        <is>
+          <t>项目原创Shader/三维程序密度；gpt-image-2原创灰度云贴图，用户参考图仅作风格参考</t>
+        </is>
+      </c>
+      <c r="N23" s="108" t="inlineStr">
+        <is>
+          <t>主塔与周围大楼99F以下的室外空间</t>
+        </is>
+      </c>
+      <c r="O23" s="108" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="P23" s="107" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="Q23" s="108" t="inlineStr">
+        <is>
+          <t>源：assets/art/vfx/environment_3d/cloud_sea/source/v002；Manifest：assets/art/vfx/environment_3d/cloud_sea/asset_manifest.json；v002品质优先版，尚未专项优化。主场景OutdoorClouds持有；主塔全高度禁云，700建筑边界遮罩随最新布局重烘焙。实际天台520m及99F145m视距均验证云可见、亮部有余量；GPU实际纹理采样、暂停、60秒流动、失效遮罩拒绝通过。原AssetID升级，不新增行。</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="52">
       <c r="H24" s="101" t="n"/>
@@ -6637,7 +6868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="51" min="1" max="1"/>
@@ -6664,6 +6895,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="52">
       <c r="A5" s="58" t="inlineStr">
         <is>
@@ -6920,6 +7152,76 @@
       <c r="G11" s="51" t="inlineStr">
         <is>
           <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="84" customHeight="1" s="52">
+      <c r="A12" s="101" t="inlineStr">
+        <is>
+          <t>v0.1.6</t>
+        </is>
+      </c>
+      <c r="B12" s="105" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C12" s="51" t="inlineStr">
+        <is>
+          <t>新增资产登记</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>特效 · 资产主表</t>
+        </is>
+      </c>
+      <c r="E12" s="101" t="inlineStr">
+        <is>
+          <t>新增 VFX-ENV-CLOUD-SEA-3D：主塔及周边楼群99F以下的室外卡通云海。独立Prefab、缓慢流动与分层半透明表现；避让建筑、桥面及室内。同步查重范围、总览与无损基线。</t>
+        </is>
+      </c>
+      <c r="F12" s="101" t="inlineStr">
+        <is>
+          <t>新增一个稳定AssetID与Prefab路径；既有条目的身份、路径、状态及哈希保留。</t>
+        </is>
+      </c>
+      <c r="G12" s="51" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="84" customHeight="1" s="52">
+      <c r="A13" s="101" t="inlineStr">
+        <is>
+          <t>v0.1.7</t>
+        </is>
+      </c>
+      <c r="B13" s="105" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>新增Prefab分页</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>特效 · 3D-特效</t>
+        </is>
+      </c>
+      <c r="E13" s="101" t="inlineStr">
+        <is>
+          <t>FX03-02 已登记独立 VFX-ENV-CLOUD-SEA-3D Prefab。记录生成脚本、Shader源、正式放置、建筑与室内避让，以及分层缓慢流动参数。Prefab分页采用独立事务更新对应sheet摘要。</t>
+        </is>
+      </c>
+      <c r="F13" s="101" t="inlineStr">
+        <is>
+          <t>资产主表不变；特效无碰撞/伤害/交互逻辑，生命周期由所属场景持有。</t>
+        </is>
+      </c>
+      <c r="G13" s="51" t="inlineStr">
+        <is>
+          <t>Codex</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -4176,7 +4176,7 @@
       </c>
       <c r="Y22" s="55" t="inlineStr">
         <is>
-          <t>v002品质优先版，尚未专项优化。主场景OutdoorClouds持有；主塔全高度禁云，700建筑边界遮罩随最新布局重烘焙。实际天台520m及99F145m视距均验证云可见、亮部有余量；GPU实际纹理采样、暂停、60秒流动、失效遮罩拒绝通过。原AssetID升级，不新增行。</t>
+          <t>v002品质优先版，尚未专项优化。主场景OutdoorClouds持有；主塔全高度禁云，700建筑边界随最新布局重烘焙；建筑改变时用最多16个保守解析区域单独避让，不再隐藏整套云。正式西北楼角、天台520m及99F145m视距均验证云可见、亮部有余量；GPU纹理与实际兜底参数、暂停、60秒流动及变动建筑继续避让通过。原AssetID原行更新。</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Q23" s="108" t="inlineStr">
         <is>
-          <t>源：assets/art/vfx/environment_3d/cloud_sea/source/v002；Manifest：assets/art/vfx/environment_3d/cloud_sea/asset_manifest.json；v002品质优先版，尚未专项优化。主场景OutdoorClouds持有；主塔全高度禁云，700建筑边界遮罩随最新布局重烘焙。实际天台520m及99F145m视距均验证云可见、亮部有余量；GPU实际纹理采样、暂停、60秒流动、失效遮罩拒绝通过。原AssetID升级，不新增行。</t>
+          <t>源：assets/art/vfx/environment_3d/cloud_sea/source/v002；Manifest：assets/art/vfx/environment_3d/cloud_sea/asset_manifest.json；v002品质优先版，尚未专项优化。主场景OutdoorClouds持有；主塔全高度禁云，700建筑边界随最新布局重烘焙；建筑改变时用最多16个保守解析区域单独避让，不再隐藏整套云。正式西北楼角、天台520m及99F145m视距均验证云可见、亮部有余量；GPU纹理与实际兜底参数、暂停、60秒流动及变动建筑继续避让通过。原AssetID原行更新。</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -1439,22 +1439,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="52">
       <c r="A6" s="57">
-        <f>COUNTA('资产主表'!$A$6:$A$22)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$23)</f>
         <v/>
       </c>
       <c r="B6" s="55" t="n"/>
       <c r="C6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$22,"已完成")+COUNTIF('资产主表'!$K$6:$K$22,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$22,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$22,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$22,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$22,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$22,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$23,"已完成")+COUNTIF('资产主表'!$K$6:$K$23,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$23,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$23,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$23,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$23,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$23,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="55" t="n"/>
       <c r="E6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$22,"待制作")+COUNTIF('资产主表'!$K$6:$K$22,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$23,"待制作")+COUNTIF('资产主表'!$K$6:$K$23,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="55" t="n"/>
       <c r="G6" s="57">
-        <f>COUNTIF('资产主表'!$S$6:$S$22,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$23,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="55" t="n"/>
@@ -1523,11 +1523,11 @@
         </is>
       </c>
       <c r="B10" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$22,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$23,A10)</f>
         <v/>
       </c>
       <c r="C10" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$22=A10)*(('资产主表'!$K$6:$K$22="已完成")+('资产主表'!$K$6:$K$22="原型已接入")+('资产主表'!$K$6:$K$22="正式美术已接入")+('资产主表'!$K$6:$K$22="已优化并正式接入")+('资产主表'!$K$6:$K$22="Blender源已完成")+('资产主表'!$K$6:$K$22="已导入；优化完成")+('资产主表'!$K$6:$K$22="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$23=A10)*(('资产主表'!$K$6:$K$23="已完成")+('资产主表'!$K$6:$K$23="原型已接入")+('资产主表'!$K$6:$K$23="正式美术已接入")+('资产主表'!$K$6:$K$23="已优化并正式接入")+('资产主表'!$K$6:$K$23="Blender源已完成")+('资产主表'!$K$6:$K$23="已导入；优化完成")+('资产主表'!$K$6:$K$23="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="62" t="n"/>
@@ -1545,11 +1545,11 @@
         </is>
       </c>
       <c r="B11" s="58">
-        <f>COUNTIF('资产主表'!$C$6:$C$22,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$23,A11)</f>
         <v/>
       </c>
       <c r="C11" s="58">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$22=A11)*(('资产主表'!$K$6:$K$22="已完成")+('资产主表'!$K$6:$K$22="原型已接入")+('资产主表'!$K$6:$K$22="正式美术已接入")+('资产主表'!$K$6:$K$22="已优化并正式接入")+('资产主表'!$K$6:$K$22="Blender源已完成")+('资产主表'!$K$6:$K$22="已导入；优化完成")+('资产主表'!$K$6:$K$22="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$23=A11)*(('资产主表'!$K$6:$K$23="已完成")+('资产主表'!$K$6:$K$23="原型已接入")+('资产主表'!$K$6:$K$23="正式美术已接入")+('资产主表'!$K$6:$K$23="已优化并正式接入")+('资产主表'!$K$6:$K$23="Blender源已完成")+('资产主表'!$K$6:$K$23="已导入；优化完成")+('资产主表'!$K$6:$K$23="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="58" t="n"/>
@@ -1776,7 +1776,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="52">
       <c r="A5" s="58" t="inlineStr">
         <is>
@@ -2098,7 +2097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="51" min="1" max="1"/>
@@ -2370,7 +2369,7 @@
         <v/>
       </c>
       <c r="S6" s="63">
-        <f>IF(COUNTIF($R$6:$R$22,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="63" t="n"/>
@@ -2473,7 +2472,7 @@
         <v/>
       </c>
       <c r="S7" s="63">
-        <f>IF(COUNTIF($R$6:$R$22,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="63" t="n"/>
@@ -2576,7 +2575,7 @@
         <v/>
       </c>
       <c r="S8" s="63">
-        <f>IF(COUNTIF($R$6:$R$22,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="63" t="n"/>
@@ -2679,7 +2678,7 @@
         <v/>
       </c>
       <c r="S9" s="63">
-        <f>IF(COUNTIF($R$6:$R$22,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="63" t="n"/>
@@ -2786,7 +2785,7 @@
         <v/>
       </c>
       <c r="S10" s="63">
-        <f>IF(COUNTIF($R$6:$R$22,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="63" t="n"/>
@@ -2893,7 +2892,7 @@
         <v/>
       </c>
       <c r="S11" s="63">
-        <f>IF(COUNTIF($R$6:$R$22,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="63" t="n"/>
@@ -3000,7 +2999,7 @@
         <v/>
       </c>
       <c r="S12" s="63">
-        <f>IF(COUNTIF($R$6:$R$22,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="63" t="n"/>
@@ -3107,7 +3106,7 @@
         <v/>
       </c>
       <c r="S13" s="63">
-        <f>IF(COUNTIF($R$6:$R$22,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="63" t="n"/>
@@ -3214,7 +3213,7 @@
         <v/>
       </c>
       <c r="S14" s="63">
-        <f>IF(COUNTIF($R$6:$R$22,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="63" t="n"/>
@@ -3321,7 +3320,7 @@
         <v/>
       </c>
       <c r="S15" s="63">
-        <f>IF(COUNTIF($R$6:$R$22,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="63" t="n"/>
@@ -3428,7 +3427,7 @@
         <v/>
       </c>
       <c r="S16" s="63">
-        <f>IF(COUNTIF($R$6:$R$22,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="63" t="n"/>
@@ -3547,7 +3546,7 @@
         <v/>
       </c>
       <c r="S17" s="55">
-        <f>IF(COUNTIF($R$6:$R$22,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="79" t="inlineStr">
@@ -3666,7 +3665,7 @@
         <v/>
       </c>
       <c r="S18" s="55">
-        <f>IF(COUNTIF($R$6:$R$22,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="79" t="inlineStr">
@@ -3789,7 +3788,7 @@
         <v/>
       </c>
       <c r="S19" s="55">
-        <f>IF(COUNTIF($R$6:$R$22,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="79" t="inlineStr">
@@ -3913,7 +3912,7 @@
         <v/>
       </c>
       <c r="S20" s="55">
-        <f>IF(COUNTIF($R$6:$R$22,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="79" t="inlineStr">
@@ -4029,7 +4028,7 @@
         <v/>
       </c>
       <c r="S21" s="55">
-        <f>IF(COUNTIF($R$6:$R$22,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="79" t="inlineStr">
@@ -4148,7 +4147,7 @@
         <v/>
       </c>
       <c r="S22" s="55">
-        <f>IF(COUNTIF($R$6:$R$22,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="79" t="inlineStr">
@@ -4177,6 +4176,125 @@
       <c r="Y22" s="55" t="inlineStr">
         <is>
           <t>v002品质优先版，尚未专项优化。主场景OutdoorClouds持有；主塔全高度禁云，700建筑边界随最新布局重烘焙；建筑改变时用最多16个保守解析区域单独避让，不再隐藏整套云。正式西北楼角、天台520m及99F145m视距均验证云可见、亮部有余量；GPU纹理与实际兜底参数、暂停、60秒流动及变动建筑继续避让通过。原AssetID原行更新。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="120" customHeight="1" s="52">
+      <c r="A23" s="79" t="inlineStr">
+        <is>
+          <t>VFX-RADIO-MUSIC-NOTES-3D</t>
+        </is>
+      </c>
+      <c r="B23" s="55" t="inlineStr">
+        <is>
+          <t>收音机音乐上飘音符</t>
+        </is>
+      </c>
+      <c r="C23" s="55" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D23" s="79" t="inlineStr">
+        <is>
+          <t>environment</t>
+        </is>
+      </c>
+      <c r="E23" s="79" t="inlineStr">
+        <is>
+          <t>base99_radio_music_notes</t>
+        </is>
+      </c>
+      <c r="F23" s="79" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G23" s="79" t="n"/>
+      <c r="H23" s="55" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I23" s="79" t="inlineStr">
+        <is>
+          <t>continuous_music</t>
+        </is>
+      </c>
+      <c r="J23" s="55" t="inlineStr">
+        <is>
+          <t>99F收音机/复用radio附件</t>
+        </is>
+      </c>
+      <c r="K23" s="55" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L23" s="79" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M23" s="79" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N23" s="79" t="inlineStr">
+        <is>
+          <t>独立radio child纯视觉持续附件；5预制QuadMesh槽位/10三角形；Godot生成四分/八分/双八分音符纹理，无字体依赖；billboard当前相机；淡青绿/暖金unshaded无emission；2.5发/s、寿命1.8s、上飘1.1m、横摆0.09m、尺度0.88~1.06、淡入0.16s、末0.45s淡出；本地挂点Y1.42m；无碰撞/灯光/音频；真实playing驱动，A/B连续，off/离99/exit同步清空；不进任何战斗池。 单符Quad最终0.46×0.52m、出生横向偏移±0.22m。</t>
+        </is>
+      </c>
+      <c r="O23" s="79" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/environment_3d/radio_music_notes/vfx_radio_music_notes_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P23" s="79" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxRadioMusicNotes3D.gd; src/base3d/Base99Radio3D.gd; tests/verification/verify_base99_radio_music_notes.tscn</t>
+        </is>
+      </c>
+      <c r="Q23" s="55" t="inlineStr">
+        <is>
+          <t>音符;音乐;收音机;八分;双八分;billboard</t>
+        </is>
+      </c>
+      <c r="R23" s="79">
+        <f>LOWER(TRIM(C23)&amp;"|"&amp;TRIM(D23)&amp;"|"&amp;TRIM(E23)&amp;"|"&amp;TRIM(F23)&amp;"|"&amp;TRIM(H23)&amp;"|"&amp;TRIM(I23))</f>
+        <v/>
+      </c>
+      <c r="S23" s="55">
+        <f>IF(COUNTIF($R$6:$R$23,R23)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T23" s="79" t="inlineStr">
+        <is>
+          <t>f4f3382a58135ff5aafd394d7360f5a2f1e084fb5731519f05f2c18648f77a12</t>
+        </is>
+      </c>
+      <c r="U23" s="79" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
+        </is>
+      </c>
+      <c r="V23" s="104" t="n">
+        <v>46303</v>
+      </c>
+      <c r="W23" s="55" t="inlineStr">
+        <is>
+          <t>原创Godot ImageTexture/QuadMesh；无第三方字体</t>
+        </is>
+      </c>
+      <c r="X23" s="78" t="inlineStr">
+        <is>
+          <t>FX03-03</t>
+        </is>
+      </c>
+      <c r="Y23" s="55" t="inlineStr">
+        <is>
+          <t>宿主唯一生命周期；固定槽位非live节点增殖；off全部槽位隐藏、alpha=0、age=-1；主体599面独立统计。</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4506,7 @@
     <row r="427" ht="84.75" customHeight="1" s="52"/>
     <row r="429" ht="120" customHeight="1" s="52"/>
   </sheetData>
-  <autoFilter ref="A5:X22"/>
+  <autoFilter ref="A5:Y23"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -4407,15 +4525,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="C6:C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K6:K22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="K6:K23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L6:L22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="L6:L23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"P0,P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4469,7 +4587,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="84" t="inlineStr">
         <is>
@@ -5702,10 +5819,92 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="52">
-      <c r="H24" s="101" t="n"/>
-      <c r="I24" s="51" t="n"/>
-      <c r="N24" s="51" t="n"/>
+    <row r="24" ht="144" customHeight="1" s="52">
+      <c r="A24" s="106" t="inlineStr">
+        <is>
+          <t>FX03-03</t>
+        </is>
+      </c>
+      <c r="B24" s="107" t="inlineStr">
+        <is>
+          <t>VFX-RADIO-MUSIC-NOTES-3D</t>
+        </is>
+      </c>
+      <c r="C24" s="108" t="inlineStr">
+        <is>
+          <t>收音机音乐上飘音符</t>
+        </is>
+      </c>
+      <c r="D24" s="107" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/environment_3d/radio_music_notes/vfx_radio_music_notes_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E24" s="109" t="inlineStr">
+        <is>
+          <t>无（预制QuadMesh/ImageTexture）</t>
+        </is>
+      </c>
+      <c r="F24" s="109" t="inlineStr">
+        <is>
+          <t>无（Godot资源生成）</t>
+        </is>
+      </c>
+      <c r="G24" s="108" t="inlineStr">
+        <is>
+          <t>独立radio child纯视觉持续附件；5预制QuadMesh槽位/10三角形；Godot生成四分/八分/双八分音符纹理，无字体依赖；billboard当前相机；淡青绿/暖金unshaded无emission；2.5发/s、寿命1.8s、上飘1.1m、横摆0.09m、尺度0.88~1.06、淡入0.16s、末0.45s淡出；本地挂点Y1.42m；无碰撞/灯光/音频；真实playing驱动，A/B连续，off/离99/exit同步清空；不进任何战斗池。 单符Quad最终0.46×0.52m、出生横向偏移±0.22m。</t>
+        </is>
+      </c>
+      <c r="H24" s="107" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxRadioMusicNotes3D.gd</t>
+        </is>
+      </c>
+      <c r="I24" s="108" t="inlineStr">
+        <is>
+          <t>关</t>
+        </is>
+      </c>
+      <c r="J24" s="107" t="inlineStr">
+        <is>
+          <t>无：纯视觉附件</t>
+        </is>
+      </c>
+      <c r="K24" s="108" t="inlineStr">
+        <is>
+          <t>无CollisionObject3D/CollisionShape3D</t>
+        </is>
+      </c>
+      <c r="L24" s="107" t="inlineStr">
+        <is>
+          <t>每音符0.46×0.52m；上飘1.1m</t>
+        </is>
+      </c>
+      <c r="M24" s="108" t="inlineStr">
+        <is>
+          <t>radio本地Y=1.42m；billboard当前相机</t>
+        </is>
+      </c>
+      <c r="N24" s="108" t="inlineStr">
+        <is>
+          <t>收音机MusicNotes子节点</t>
+        </is>
+      </c>
+      <c r="O24" s="108" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="P24" s="107" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q24" s="108" t="inlineStr">
+        <is>
+          <t>独立PackedScene；radio唯一持有，不进池；验收 verify_base99_radio_music_notes。</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="52">
       <c r="H25" s="101" t="n"/>
@@ -6868,7 +7067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="51" min="1" max="1"/>
@@ -6895,7 +7094,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="52">
       <c r="A5" s="58" t="inlineStr">
         <is>
@@ -7222,6 +7420,76 @@
       <c r="G13" s="51" t="inlineStr">
         <is>
           <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="101" t="inlineStr">
+        <is>
+          <t>v0.1.8</t>
+        </is>
+      </c>
+      <c r="B14" s="105" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C14" s="51" t="inlineStr">
+        <is>
+          <t>新增资产主表</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>特效 · 资产主表</t>
+        </is>
+      </c>
+      <c r="E14" s="101" t="inlineStr">
+        <is>
+          <t>新增VFX-RADIO-MUSIC-NOTES-3D，查重/总览/DV扩至新行；纯视觉radio附件，不进池。</t>
+        </is>
+      </c>
+      <c r="F14" s="101" t="inlineStr">
+        <is>
+          <t>稳定ID/路径不变；主体v005几何与灯帽不变；不改点击或玩法</t>
+        </is>
+      </c>
+      <c r="G14" s="51" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="101" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="B15" s="105" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C15" s="51" t="inlineStr">
+        <is>
+          <t>新增Prefab专表</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="inlineStr">
+        <is>
+          <t>特效 · 3D-特效</t>
+        </is>
+      </c>
+      <c r="E15" s="101" t="inlineStr">
+        <is>
+          <t>登记FX03-03收音机音符独立PackedScene，纯视觉无碰撞；专表独立事务更新摘要。</t>
+        </is>
+      </c>
+      <c r="F15" s="101" t="inlineStr">
+        <is>
+          <t>稳定ID/路径不变；主体v005几何与灯帽不变；不改点击或玩法</t>
+        </is>
+      </c>
+      <c r="G15" s="51" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3D-特效" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -22,9 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -602,7 +603,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -923,6 +924,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1439,22 +1441,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="52">
       <c r="A6" s="57">
-        <f>COUNTA('资产主表'!$A$6:$A$23)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$25)</f>
         <v/>
       </c>
       <c r="B6" s="55" t="n"/>
       <c r="C6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$23,"已完成")+COUNTIF('资产主表'!$K$6:$K$23,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$23,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$23,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$23,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$23,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$23,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$25,"已完成")+COUNTIF('资产主表'!$K$6:$K$25,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$25,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$25,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$25,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$25,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$25,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="55" t="n"/>
       <c r="E6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$23,"待制作")+COUNTIF('资产主表'!$K$6:$K$23,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$25,"待制作")+COUNTIF('资产主表'!$K$6:$K$25,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="55" t="n"/>
       <c r="G6" s="57">
-        <f>COUNTIF('资产主表'!$S$6:$S$23,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$25,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="55" t="n"/>
@@ -1523,11 +1525,11 @@
         </is>
       </c>
       <c r="B10" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$23,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$25,A10)</f>
         <v/>
       </c>
       <c r="C10" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$23=A10)*(('资产主表'!$K$6:$K$23="已完成")+('资产主表'!$K$6:$K$23="原型已接入")+('资产主表'!$K$6:$K$23="正式美术已接入")+('资产主表'!$K$6:$K$23="已优化并正式接入")+('资产主表'!$K$6:$K$23="Blender源已完成")+('资产主表'!$K$6:$K$23="已导入；优化完成")+('资产主表'!$K$6:$K$23="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$25=A10)*(('资产主表'!$K$6:$K$25="已完成")+('资产主表'!$K$6:$K$25="原型已接入")+('资产主表'!$K$6:$K$25="正式美术已接入")+('资产主表'!$K$6:$K$25="已优化并正式接入")+('资产主表'!$K$6:$K$25="Blender源已完成")+('资产主表'!$K$6:$K$25="已导入；优化完成")+('资产主表'!$K$6:$K$25="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="62" t="n"/>
@@ -1545,11 +1547,11 @@
         </is>
       </c>
       <c r="B11" s="58">
-        <f>COUNTIF('资产主表'!$C$6:$C$23,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$25,A11)</f>
         <v/>
       </c>
       <c r="C11" s="58">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$23=A11)*(('资产主表'!$K$6:$K$23="已完成")+('资产主表'!$K$6:$K$23="原型已接入")+('资产主表'!$K$6:$K$23="正式美术已接入")+('资产主表'!$K$6:$K$23="已优化并正式接入")+('资产主表'!$K$6:$K$23="Blender源已完成")+('资产主表'!$K$6:$K$23="已导入；优化完成")+('资产主表'!$K$6:$K$23="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$25=A11)*(('资产主表'!$K$6:$K$25="已完成")+('资产主表'!$K$6:$K$25="原型已接入")+('资产主表'!$K$6:$K$25="正式美术已接入")+('资产主表'!$K$6:$K$25="已优化并正式接入")+('资产主表'!$K$6:$K$25="Blender源已完成")+('资产主表'!$K$6:$K$25="已导入；优化完成")+('资产主表'!$K$6:$K$25="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="58" t="n"/>
@@ -2097,7 +2099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="51" min="1" max="1"/>
@@ -2369,7 +2371,7 @@
         <v/>
       </c>
       <c r="S6" s="63">
-        <f>IF(COUNTIF($R$6:$R$23,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="63" t="n"/>
@@ -2472,7 +2474,7 @@
         <v/>
       </c>
       <c r="S7" s="63">
-        <f>IF(COUNTIF($R$6:$R$23,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="63" t="n"/>
@@ -2575,7 +2577,7 @@
         <v/>
       </c>
       <c r="S8" s="63">
-        <f>IF(COUNTIF($R$6:$R$23,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="63" t="n"/>
@@ -2678,7 +2680,7 @@
         <v/>
       </c>
       <c r="S9" s="63">
-        <f>IF(COUNTIF($R$6:$R$23,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="63" t="n"/>
@@ -2785,7 +2787,7 @@
         <v/>
       </c>
       <c r="S10" s="63">
-        <f>IF(COUNTIF($R$6:$R$23,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="63" t="n"/>
@@ -2892,7 +2894,7 @@
         <v/>
       </c>
       <c r="S11" s="63">
-        <f>IF(COUNTIF($R$6:$R$23,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="63" t="n"/>
@@ -2999,7 +3001,7 @@
         <v/>
       </c>
       <c r="S12" s="63">
-        <f>IF(COUNTIF($R$6:$R$23,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="63" t="n"/>
@@ -3106,7 +3108,7 @@
         <v/>
       </c>
       <c r="S13" s="63">
-        <f>IF(COUNTIF($R$6:$R$23,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="63" t="n"/>
@@ -3213,7 +3215,7 @@
         <v/>
       </c>
       <c r="S14" s="63">
-        <f>IF(COUNTIF($R$6:$R$23,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="63" t="n"/>
@@ -3320,7 +3322,7 @@
         <v/>
       </c>
       <c r="S15" s="63">
-        <f>IF(COUNTIF($R$6:$R$23,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="63" t="n"/>
@@ -3427,7 +3429,7 @@
         <v/>
       </c>
       <c r="S16" s="63">
-        <f>IF(COUNTIF($R$6:$R$23,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="63" t="n"/>
@@ -3546,7 +3548,7 @@
         <v/>
       </c>
       <c r="S17" s="55">
-        <f>IF(COUNTIF($R$6:$R$23,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="79" t="inlineStr">
@@ -3665,7 +3667,7 @@
         <v/>
       </c>
       <c r="S18" s="55">
-        <f>IF(COUNTIF($R$6:$R$23,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="79" t="inlineStr">
@@ -3788,7 +3790,7 @@
         <v/>
       </c>
       <c r="S19" s="55">
-        <f>IF(COUNTIF($R$6:$R$23,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="79" t="inlineStr">
@@ -3912,7 +3914,7 @@
         <v/>
       </c>
       <c r="S20" s="55">
-        <f>IF(COUNTIF($R$6:$R$23,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="79" t="inlineStr">
@@ -4028,7 +4030,7 @@
         <v/>
       </c>
       <c r="S21" s="55">
-        <f>IF(COUNTIF($R$6:$R$23,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="79" t="inlineStr">
@@ -4147,7 +4149,7 @@
         <v/>
       </c>
       <c r="S22" s="55">
-        <f>IF(COUNTIF($R$6:$R$23,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="79" t="inlineStr">
@@ -4266,7 +4268,7 @@
         <v/>
       </c>
       <c r="S23" s="55">
-        <f>IF(COUNTIF($R$6:$R$23,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$25,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="79" t="inlineStr">
@@ -4295,6 +4297,248 @@
       <c r="Y23" s="55" t="inlineStr">
         <is>
           <t>宿主唯一生命周期；固定槽位非live节点增殖；off全部槽位隐藏、alpha=0、age=-1；主体599面独立统计。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="120" customHeight="1" s="52">
+      <c r="A24" s="79" t="inlineStr">
+        <is>
+          <t>VFX-ENV-BIRDS-FLYBY-3D</t>
+        </is>
+      </c>
+      <c r="B24" s="55" t="inlineStr">
+        <is>
+          <t>鸟群空中掠过</t>
+        </is>
+      </c>
+      <c r="C24" s="55" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D24" s="79" t="inlineStr">
+        <is>
+          <t>environment</t>
+        </is>
+      </c>
+      <c r="E24" s="79" t="inlineStr">
+        <is>
+          <t>env_birds_flyby</t>
+        </is>
+      </c>
+      <c r="F24" s="79" t="inlineStr">
+        <is>
+          <t>flock_root</t>
+        </is>
+      </c>
+      <c r="G24" s="79" t="n"/>
+      <c r="H24" s="55" t="inlineStr">
+        <is>
+          <t>3D</t>
+        </is>
+      </c>
+      <c r="I24" s="79" t="inlineStr">
+        <is>
+          <t>flyby</t>
+        </is>
+      </c>
+      <c r="J24" s="55" t="inlineStr">
+        <is>
+          <t>室外场景环境氛围</t>
+        </is>
+      </c>
+      <c r="K24" s="55" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L24" s="79" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M24" s="79" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N24" s="79" t="inlineStr">
+        <is>
+          <t>7只；12秒；30fps；每鸟296三角面/11骨骼；独立错峰关键帧；共享场景哑光材质/PaletteUV R10C10冷白；无碰撞</t>
+        </is>
+      </c>
+      <c r="O24" s="79" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/environment_3d/bird_flocks/runtime/flyby/vfx_env_birds_flyby_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P24" s="79" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/environment_3d/bird_flocks/source/flyby/v001/asset_manifest.json; GLB; Godot PackedScene</t>
+        </is>
+      </c>
+      <c r="Q24" s="55" t="inlineStr">
+        <is>
+          <t>鸟群;场景特效;低模;白色;拍翼;落地;啄地</t>
+        </is>
+      </c>
+      <c r="R24" s="79">
+        <f>LOWER(TRIM(C24)&amp;"|"&amp;TRIM(D24)&amp;"|"&amp;TRIM(E24)&amp;"|"&amp;TRIM(F24)&amp;"|"&amp;TRIM(H24)&amp;"|"&amp;TRIM(I24))</f>
+        <v/>
+      </c>
+      <c r="S24" s="55">
+        <f>IF(COUNTIF($R$6:$R$25,R24)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T24" s="79" t="inlineStr">
+        <is>
+          <t>7f42f76978488604f7f6e21f5e9333794236a8ce213ca276676e7db298ce237a</t>
+        </is>
+      </c>
+      <c r="U24" s="79" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V24" s="104" t="inlineStr">
+        <is>
+          <t>2026-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="W24" s="55" t="inlineStr">
+        <is>
+          <t>原创程序建模与人工动作编排；项目共享材质</t>
+        </is>
+      </c>
+      <c r="X24" s="78" t="inlineStr">
+        <is>
+          <t>02_游戏输出_鸟群资产包</t>
+        </is>
+      </c>
+      <c r="Y24" s="55" t="inlineStr">
+        <is>
+          <t>Godot已接入；环境循环(播12s+停20s)；无碰撞；运行时归属场景特效；塔2正上方+吊桥第1跨中段上空，世界锚点(20.0,1.6,-64.5)，rotation_y=0.2rad。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="120" customHeight="1" s="52">
+      <c r="A25" s="79" t="inlineStr">
+        <is>
+          <t>VFX-ENV-BIRDS-GROUND-3D</t>
+        </is>
+      </c>
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t>鸟群落地停留再起飞</t>
+        </is>
+      </c>
+      <c r="C25" s="55" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D25" s="79" t="inlineStr">
+        <is>
+          <t>environment</t>
+        </is>
+      </c>
+      <c r="E25" s="79" t="inlineStr">
+        <is>
+          <t>env_birds_ground</t>
+        </is>
+      </c>
+      <c r="F25" s="79" t="inlineStr">
+        <is>
+          <t>flock_root</t>
+        </is>
+      </c>
+      <c r="G25" s="79" t="n"/>
+      <c r="H25" s="55" t="inlineStr">
+        <is>
+          <t>3D</t>
+        </is>
+      </c>
+      <c r="I25" s="79" t="inlineStr">
+        <is>
+          <t>land_walk_peck_takeoff</t>
+        </is>
+      </c>
+      <c r="J25" s="55" t="inlineStr">
+        <is>
+          <t>室外场景环境氛围</t>
+        </is>
+      </c>
+      <c r="K25" s="55" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L25" s="79" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M25" s="79" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N25" s="79" t="inlineStr">
+        <is>
+          <t>7只；24秒；30fps；每鸟296三角面/11骨骼；独立错峰关键帧；共享场景哑光材质/PaletteUV R10C10冷白；无碰撞</t>
+        </is>
+      </c>
+      <c r="O25" s="79" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/environment_3d/bird_flocks/runtime/ground/vfx_env_birds_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P25" s="79" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/environment_3d/bird_flocks/source/ground/v001/asset_manifest.json; GLB; Godot PackedScene</t>
+        </is>
+      </c>
+      <c r="Q25" s="55" t="inlineStr">
+        <is>
+          <t>鸟群;场景特效;低模;白色;拍翼;落地;啄地</t>
+        </is>
+      </c>
+      <c r="R25" s="79">
+        <f>LOWER(TRIM(C25)&amp;"|"&amp;TRIM(D25)&amp;"|"&amp;TRIM(E25)&amp;"|"&amp;TRIM(F25)&amp;"|"&amp;TRIM(H25)&amp;"|"&amp;TRIM(I25))</f>
+        <v/>
+      </c>
+      <c r="S25" s="55">
+        <f>IF(COUNTIF($R$6:$R$25,R25)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T25" s="79" t="inlineStr">
+        <is>
+          <t>37ebd978d40612def1521aec5f3fb671b2a13237ed807137bb4ed449b6e5125d</t>
+        </is>
+      </c>
+      <c r="U25" s="79" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V25" s="104" t="inlineStr">
+        <is>
+          <t>2026-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="W25" s="55" t="inlineStr">
+        <is>
+          <t>原创程序建模与人工动作编排；项目共享材质</t>
+        </is>
+      </c>
+      <c r="X25" s="78" t="inlineStr">
+        <is>
+          <t>02_游戏输出_鸟群资产包</t>
+        </is>
+      </c>
+      <c r="Y25" s="55" t="inlineStr">
+        <is>
+          <t>Godot已接入；环境循环(播24s+停30s)；无碰撞；运行时归属场景特效；主塔100F天台吊桥北出口以东，局部锚点(25.0,0.0,-31.0)。</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4750,7 @@
     <row r="427" ht="84.75" customHeight="1" s="52"/>
     <row r="429" ht="120" customHeight="1" s="52"/>
   </sheetData>
-  <autoFilter ref="A5:Y23"/>
+  <autoFilter ref="A5:Y25"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -4525,15 +4769,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="C6:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K6:K23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="K6:K25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L6:L23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="L6:L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"P0,P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7067,7 +7311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="51" min="1" max="1"/>
@@ -7493,6 +7737,78 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="51" t="inlineStr">
+        <is>
+          <t>v0.1.10</t>
+        </is>
+      </c>
+      <c r="B16" s="110" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>新增Blender源资产</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="inlineStr">
+        <is>
+          <t>特效 / 资产主表</t>
+        </is>
+      </c>
+      <c r="E16" s="51" t="inlineStr">
+        <is>
+          <t>新增两套7鸟环境动画；同步查重、总览、下拉范围和无损基线。</t>
+        </is>
+      </c>
+      <c r="F16" s="51" t="inlineStr">
+        <is>
+          <t>仅源阶段；3D-特效Prefab专表保持不变。</t>
+        </is>
+      </c>
+      <c r="G16" s="51" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="51" t="inlineStr">
+        <is>
+          <t>v0.1.11</t>
+        </is>
+      </c>
+      <c r="B17" s="110" t="inlineStr">
+        <is>
+          <t>2026-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="C17" s="51" t="inlineStr">
+        <is>
+          <t>运行时摆位与播放修正</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="inlineStr">
+        <is>
+          <t>特效 / 资产主表</t>
+        </is>
+      </c>
+      <c r="E17" s="51" t="inlineStr">
+        <is>
+          <t>修正两套鸟群运行时接入：① 逐鸟播放(每鸟一条Action，原只播第一条致6只冻结)；② 单次演出改为环境循环(原播完即销毁，玩家看不到)；③ 飞行组移至塔2上方+吊桥第1跨中段(20.0,1.6,-64.5)；停留组移至100F天台吊桥北出口以东局部(25.0,0.0,-31.0)。</t>
+        </is>
+      </c>
+      <c r="F17" s="51" t="inlineStr">
+        <is>
+          <t>稳定ID/路径/版本v001不变；GLB与源动画未改；SHA归属仍为runtime tscn；无碰撞、不改玩法。</t>
+        </is>
+      </c>
+      <c r="G17" s="51" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3D-特效" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$25</definedName>
@@ -1778,6 +1778,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="52">
       <c r="A5" s="58" t="inlineStr">
         <is>
@@ -4374,7 +4375,7 @@
       </c>
       <c r="P24" s="79" t="inlineStr">
         <is>
-          <t>assets/art/vfx/environment_3d/bird_flocks/source/flyby/v001/asset_manifest.json; GLB; Godot PackedScene</t>
+          <t>art_source/vfx/environment_3d/bird_flocks/source/flyby/v001/asset_manifest.json; GLB; Godot PackedScene</t>
         </is>
       </c>
       <c r="Q24" s="55" t="inlineStr">
@@ -4495,7 +4496,7 @@
       </c>
       <c r="P25" s="79" t="inlineStr">
         <is>
-          <t>assets/art/vfx/environment_3d/bird_flocks/source/ground/v001/asset_manifest.json; GLB; Godot PackedScene</t>
+          <t>art_source/vfx/environment_3d/bird_flocks/source/ground/v001/asset_manifest.json; GLB; Godot PackedScene</t>
         </is>
       </c>
       <c r="Q25" s="55" t="inlineStr">
@@ -4831,6 +4832,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="84" t="inlineStr">
         <is>
@@ -6059,7 +6061,7 @@
       </c>
       <c r="Q23" s="108" t="inlineStr">
         <is>
-          <t>源：assets/art/vfx/environment_3d/cloud_sea/source/v002；Manifest：assets/art/vfx/environment_3d/cloud_sea/asset_manifest.json；v002品质优先版，尚未专项优化。主场景OutdoorClouds持有；主塔全高度禁云，700建筑边界随最新布局重烘焙；建筑改变时用最多16个保守解析区域单独避让，不再隐藏整套云。正式西北楼角、天台520m及99F145m视距均验证云可见、亮部有余量；GPU纹理与实际兜底参数、暂停、60秒流动及变动建筑继续避让通过。原AssetID原行更新。</t>
+          <t>源：art_source/vfx/environment_3d/cloud_sea/source/v002；Manifest：assets/art/vfx/environment_3d/cloud_sea/asset_manifest.json；v002品质优先版，尚未专项优化。主场景OutdoorClouds持有；主塔全高度禁云，700建筑边界随最新布局重烘焙；建筑改变时用最多16个保守解析区域单独避让，不再隐藏整套云。正式西北楼角、天台520m及99F145m视距均验证云可见、亮部有余量；GPU纹理与实际兜底参数、暂停、60秒流动及变动建筑继续避让通过。原AssetID原行更新。</t>
         </is>
       </c>
     </row>
@@ -7338,6 +7340,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="52">
       <c r="A5" s="58" t="inlineStr">
         <is>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -4360,12 +4360,12 @@
       </c>
       <c r="M24" s="79" t="inlineStr">
         <is>
-          <t>v001</t>
+          <t>v003</t>
         </is>
       </c>
       <c r="N24" s="79" t="inlineStr">
         <is>
-          <t>7只；12秒；30fps；每鸟296三角面/11骨骼；独立错峰关键帧；共享场景哑光材质/PaletteUV R10C10冷白；无碰撞</t>
+          <t>7只；每鸟296三角面/11骨骼；导入尺度75%（上版150%），每鸟±10%错落；共享场景哑光材质/PaletteUV R10C10冷白；无碰撞；200m/24s，速度8.33m/s为上版50%；错落编队；振翅135%保持</t>
         </is>
       </c>
       <c r="O24" s="79" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="T24" s="79" t="inlineStr">
         <is>
-          <t>7f42f76978488604f7f6e21f5e9333794236a8ce213ca276676e7db298ce237a</t>
+          <t>f2f77648bad2e897294293474faaedf3a0777d8ca662bd9d3aae8a9c5e4c4413</t>
         </is>
       </c>
       <c r="U24" s="79" t="inlineStr">
@@ -4401,10 +4401,8 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V24" s="104" t="inlineStr">
-        <is>
-          <t>2026-10-09 00:00:00</t>
-        </is>
+      <c r="V24" s="104" t="n">
+        <v>46307</v>
       </c>
       <c r="W24" s="55" t="inlineStr">
         <is>
@@ -4418,7 +4416,7 @@
       </c>
       <c r="Y24" s="55" t="inlineStr">
         <is>
-          <t>Godot已接入；环境循环(播12s+停20s)；无碰撞；运行时归属场景特效；塔2正上方+吊桥第1跨中段上空，世界锚点(20.0,1.6,-64.5)，rotation_y=0.2rad。</t>
+          <t>运行包装v003，Blender/GLB母版v001；24秒+间隔20秒；桥上(20,1.6,-64.5)，桥下塔2屋顶上方(20,-9,-70)，后一组延迟5秒；独立实例裁剪动画，不改GLB资源。；按吊桥玩家摄像机红框纠正位置，路线移近桥边，穿过左右两侧空域。；本轮各鸟比上版大50%并±10%错落，空中速度减半，航程200m/24s。</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4479,12 @@
       </c>
       <c r="M25" s="79" t="inlineStr">
         <is>
-          <t>v001</t>
+          <t>v003</t>
         </is>
       </c>
       <c r="N25" s="79" t="inlineStr">
         <is>
-          <t>7只；24秒；30fps；每鸟296三角面/11骨骼；独立错峰关键帧；共享场景哑光材质/PaletteUV R10C10冷白；无碰撞</t>
+          <t>7只；每鸟296三角面/11骨骼；导入尺度75%（上版150%），每鸟±10%错落；共享场景哑光材质/PaletteUV R10C10冷白；无碰撞；24秒落地/啄地/起飞演出；尺寸变化补偿脚底高度</t>
         </is>
       </c>
       <c r="O25" s="79" t="inlineStr">
@@ -4514,7 +4512,7 @@
       </c>
       <c r="T25" s="79" t="inlineStr">
         <is>
-          <t>37ebd978d40612def1521aec5f3fb671b2a13237ed807137bb4ed449b6e5125d</t>
+          <t>0c2584b52972808854c94e9885a1550538eba47cc52b2ea076afb00fa7edd666</t>
         </is>
       </c>
       <c r="U25" s="79" t="inlineStr">
@@ -4522,10 +4520,8 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V25" s="104" t="inlineStr">
-        <is>
-          <t>2026-10-09 00:00:00</t>
-        </is>
+      <c r="V25" s="104" t="n">
+        <v>46307</v>
       </c>
       <c r="W25" s="55" t="inlineStr">
         <is>
@@ -4539,7 +4535,7 @@
       </c>
       <c r="Y25" s="55" t="inlineStr">
         <is>
-          <t>Godot已接入；环境循环(播24s+停30s)；无碰撞；运行时归属场景特效；主塔100F天台吊桥北出口以东，局部锚点(25.0,0.0,-31.0)。</t>
+          <t>运行包装v003，Blender/GLB母版v001；24秒+间隔30秒；100F天台局部(25,0,-31)；尺寸75%±10%，路径保持，补偿脚底高度。；本轮各鸟比上版大50%并±10%错落，空中速度减半，航程200m/24s。</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="51" min="1" max="1"/>
@@ -7812,6 +7808,76 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="51" t="inlineStr">
+        <is>
+          <t>v0.1.12</t>
+        </is>
+      </c>
+      <c r="B18" s="110" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C18" s="51" t="inlineStr">
+        <is>
+          <t>环境鸟群运行表现调整</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="inlineStr">
+        <is>
+          <t>特效 / 资产主表</t>
+        </is>
+      </c>
+      <c r="E18" s="51" t="inlineStr">
+        <is>
+          <t>鸟尺寸50%；空中200m/12s；错落队形、振翅135%；新增吊桥下塔2屋顶上方实例。</t>
+        </is>
+      </c>
+      <c r="F18" s="51" t="inlineStr">
+        <is>
+          <t>仅现有两行；模型与GLB仍v001。</t>
+        </is>
+      </c>
+      <c r="G18" s="51" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>v0.1.13</t>
+        </is>
+      </c>
+      <c r="B19" s="110" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>鸟群尺寸与速度调整</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>特效 / 资产主表</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>尺寸比上版大50%，各鸟±10%变化；空中速度减半为200m/24s。</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>运行包装v003；既有两个AssetID。</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3D-特效" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -1441,22 +1441,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="52">
       <c r="A6" s="57">
-        <f>COUNTA('资产主表'!$A$6:$A$25)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$34)</f>
         <v/>
       </c>
       <c r="B6" s="55" t="n"/>
       <c r="C6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$25,"已完成")+COUNTIF('资产主表'!$K$6:$K$25,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$25,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$25,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$25,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$25,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$25,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$34,"已完成")+COUNTIF('资产主表'!$K$6:$K$34,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$34,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$34,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$34,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$34,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$34,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="55" t="n"/>
       <c r="E6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$25,"待制作")+COUNTIF('资产主表'!$K$6:$K$25,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$34,"待制作")+COUNTIF('资产主表'!$K$6:$K$34,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="55" t="n"/>
       <c r="G6" s="57">
-        <f>COUNTIF('资产主表'!$S$6:$S$25,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$34,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="55" t="n"/>
@@ -1525,11 +1525,11 @@
         </is>
       </c>
       <c r="B10" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$25,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$34,A10)</f>
         <v/>
       </c>
       <c r="C10" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$25=A10)*(('资产主表'!$K$6:$K$25="已完成")+('资产主表'!$K$6:$K$25="原型已接入")+('资产主表'!$K$6:$K$25="正式美术已接入")+('资产主表'!$K$6:$K$25="已优化并正式接入")+('资产主表'!$K$6:$K$25="Blender源已完成")+('资产主表'!$K$6:$K$25="已导入；优化完成")+('资产主表'!$K$6:$K$25="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$34=A10)*(('资产主表'!$K$6:$K$34="已完成")+('资产主表'!$K$6:$K$34="原型已接入")+('资产主表'!$K$6:$K$34="正式美术已接入")+('资产主表'!$K$6:$K$34="已优化并正式接入")+('资产主表'!$K$6:$K$34="Blender源已完成")+('资产主表'!$K$6:$K$34="已导入；优化完成")+('资产主表'!$K$6:$K$34="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="62" t="n"/>
@@ -1540,163 +1540,173 @@
       <c r="I10" s="62" t="n"/>
       <c r="J10" s="62" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="52">
-      <c r="A11" s="58" t="inlineStr">
+    <row r="11" ht="21.75" customHeight="1" s="52">
+      <c r="A11" s="62" t="inlineStr">
+        <is>
+          <t>子弹特效</t>
+        </is>
+      </c>
+      <c r="B11" s="62">
+        <f>COUNTIF('资产主表'!$C$6:$C$34,A11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="62">
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$34=A11)*(('资产主表'!$K$6:$K$34="已完成")+('资产主表'!$K$6:$K$34="原型已接入")+('资产主表'!$K$6:$K$34="正式美术已接入")+('资产主表'!$K$6:$K$34="已优化并正式接入")+('资产主表'!$K$6:$K$34="Blender源已完成")+('资产主表'!$K$6:$K$34="已导入；优化完成")+('资产主表'!$K$6:$K$34="白模源已完成；QA PASS")))</f>
+        <v/>
+      </c>
+      <c r="D11" s="62" t="n"/>
+      <c r="E11" s="62" t="n"/>
+      <c r="F11" s="62" t="n"/>
+      <c r="G11" s="62" t="n"/>
+      <c r="H11" s="62" t="n"/>
+      <c r="I11" s="62" t="n"/>
+      <c r="J11" s="62" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="52">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B11" s="58">
-        <f>COUNTIF('资产主表'!$C$6:$C$25,A11)</f>
+      <c r="B12" s="58">
+        <f>SUM(B10:B11)</f>
         <v/>
       </c>
-      <c r="C11" s="58">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$25=A11)*(('资产主表'!$K$6:$K$25="已完成")+('资产主表'!$K$6:$K$25="原型已接入")+('资产主表'!$K$6:$K$25="正式美术已接入")+('资产主表'!$K$6:$K$25="已优化并正式接入")+('资产主表'!$K$6:$K$25="Blender源已完成")+('资产主表'!$K$6:$K$25="已导入；优化完成")+('资产主表'!$K$6:$K$25="白模源已完成；QA PASS")))</f>
+      <c r="C12" s="58">
+        <f>SUM(C10:C11)</f>
         <v/>
       </c>
-      <c r="D11" s="58" t="n"/>
-      <c r="E11" s="58" t="n"/>
-      <c r="F11" s="58" t="n"/>
-      <c r="G11" s="58" t="n"/>
-      <c r="H11" s="58" t="n"/>
-      <c r="I11" s="58" t="n"/>
-      <c r="J11" s="58" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="52">
-      <c r="A12" s="63" t="n"/>
-      <c r="B12" s="63" t="n"/>
-      <c r="C12" s="63" t="n"/>
-      <c r="D12" s="55" t="n"/>
-      <c r="E12" s="64" t="n"/>
-      <c r="F12" s="63" t="n"/>
-      <c r="G12" s="63" t="n"/>
-      <c r="H12" s="55" t="n"/>
-      <c r="I12" s="55" t="n"/>
-      <c r="J12" s="55" t="n"/>
+      <c r="D12" s="58" t="n"/>
+      <c r="E12" s="58" t="n"/>
+      <c r="F12" s="58" t="n"/>
+      <c r="G12" s="58" t="n"/>
+      <c r="H12" s="58" t="n"/>
+      <c r="I12" s="58" t="n"/>
+      <c r="J12" s="58" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="52">
-      <c r="A13" s="65" t="inlineStr">
+      <c r="A13" s="63" t="n"/>
+      <c r="B13" s="63" t="n"/>
+      <c r="C13" s="63" t="n"/>
+      <c r="D13" s="55" t="n"/>
+      <c r="E13" s="64" t="n"/>
+      <c r="F13" s="63" t="n"/>
+      <c r="G13" s="63" t="n"/>
+      <c r="H13" s="55" t="n"/>
+      <c r="I13" s="55" t="n"/>
+      <c r="J13" s="55" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="52">
+      <c r="A14" s="65" t="inlineStr">
         <is>
           <t>域内 3D Prefab 分页统计（快照口径与本账本分页一致；权威清单在各分页表）</t>
         </is>
       </c>
-      <c r="B13" s="66" t="n"/>
-      <c r="C13" s="66" t="n"/>
-      <c r="D13" s="66" t="n"/>
-      <c r="E13" s="66" t="n"/>
-      <c r="F13" s="66" t="n"/>
-      <c r="G13" s="66" t="n"/>
-      <c r="H13" s="66" t="n"/>
-      <c r="I13" s="66" t="n"/>
-      <c r="J13" s="67" t="n"/>
-    </row>
-    <row r="14" ht="39.55" customHeight="1" s="52">
-      <c r="A14" s="56" t="inlineStr">
+      <c r="B14" s="66" t="n"/>
+      <c r="C14" s="66" t="n"/>
+      <c r="D14" s="66" t="n"/>
+      <c r="E14" s="66" t="n"/>
+      <c r="F14" s="66" t="n"/>
+      <c r="G14" s="66" t="n"/>
+      <c r="H14" s="66" t="n"/>
+      <c r="I14" s="66" t="n"/>
+      <c r="J14" s="67" t="n"/>
+    </row>
+    <row r="15" ht="39.55" customHeight="1" s="52">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>分页</t>
         </is>
       </c>
-      <c r="B14" s="68" t="inlineStr">
+      <c r="B15" s="68" t="inlineStr">
         <is>
           <t>Prefab 数</t>
         </is>
       </c>
-      <c r="C14" s="56" t="inlineStr">
+      <c r="C15" s="56" t="inlineStr">
         <is>
           <t>直接引用 GLB</t>
         </is>
       </c>
-      <c r="D14" s="56" t="inlineStr">
+      <c r="D15" s="56" t="inlineStr">
         <is>
           <t>有功能脚本</t>
         </is>
       </c>
-      <c r="E14" s="56" t="inlineStr">
+      <c r="E15" s="56" t="inlineStr">
         <is>
           <t>碰撞开启</t>
         </is>
       </c>
-      <c r="F14" s="56" t="inlineStr">
+      <c r="F15" s="56" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="G14" s="63" t="n"/>
-      <c r="H14" s="55" t="n"/>
-      <c r="I14" s="55" t="n"/>
-      <c r="J14" s="55" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="52">
-      <c r="A15" s="69" t="inlineStr">
+      <c r="G15" s="63" t="n"/>
+      <c r="H15" s="55" t="n"/>
+      <c r="I15" s="55" t="n"/>
+      <c r="J15" s="55" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="52">
+      <c r="A16" s="69" t="inlineStr">
         <is>
           <t>3D-特效</t>
         </is>
       </c>
-      <c r="B15" s="62">
+      <c r="B16" s="62">
         <f>COUNTA('3D-特效'!$A$5:$A$204)</f>
         <v/>
       </c>
-      <c r="C15" s="62">
+      <c r="C16" s="62">
         <f>COUNTIF('3D-特效'!$D$5:$D$204,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D15" s="62">
+      <c r="D16" s="62">
         <f>COUNTIF('3D-特效'!$G$5:$G$204,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E15" s="62">
+      <c r="E16" s="62">
         <f>COUNTIF('3D-特效'!$H$5:$H$204,"开")</f>
         <v/>
       </c>
-      <c r="F15" s="62" t="inlineStr">
+      <c r="F16" s="62" t="inlineStr">
         <is>
           <t>一行 = 一个实际存在的 Godot PackedScene</t>
         </is>
       </c>
-      <c r="G15" s="62" t="n"/>
-      <c r="H15" s="62" t="n"/>
-      <c r="I15" s="62" t="n"/>
-      <c r="J15" s="62" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="52">
-      <c r="A16" s="58" t="inlineStr">
+      <c r="G16" s="62" t="n"/>
+      <c r="H16" s="62" t="n"/>
+      <c r="I16" s="62" t="n"/>
+      <c r="J16" s="62" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="52">
+      <c r="A17" s="58" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B16" s="58">
-        <f>SUM(B15)</f>
+      <c r="B17" s="58">
+        <f>SUM(B16)</f>
         <v/>
       </c>
-      <c r="C16" s="58">
-        <f>SUM(C15)</f>
+      <c r="C17" s="58">
+        <f>SUM(C16)</f>
         <v/>
       </c>
-      <c r="D16" s="58">
-        <f>SUM(D15)</f>
+      <c r="D17" s="58">
+        <f>SUM(D16)</f>
         <v/>
       </c>
-      <c r="E16" s="58">
-        <f>SUM(E15)</f>
+      <c r="E17" s="58">
+        <f>SUM(E16)</f>
         <v/>
       </c>
-      <c r="F16" s="58" t="n"/>
-      <c r="G16" s="58" t="n"/>
-      <c r="H16" s="58" t="n"/>
-      <c r="I16" s="58" t="n"/>
-      <c r="J16" s="58" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="52">
-      <c r="A17" s="63" t="n"/>
-      <c r="B17" s="63" t="n"/>
-      <c r="C17" s="63" t="n"/>
-      <c r="D17" s="55" t="n"/>
-      <c r="E17" s="55" t="n"/>
-      <c r="F17" s="55" t="n"/>
-      <c r="G17" s="55" t="n"/>
-      <c r="H17" s="55" t="n"/>
-      <c r="I17" s="55" t="n"/>
-      <c r="J17" s="55" t="n"/>
+      <c r="F17" s="58" t="n"/>
+      <c r="G17" s="58" t="n"/>
+      <c r="H17" s="58" t="n"/>
+      <c r="I17" s="58" t="n"/>
+      <c r="J17" s="58" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="52">
       <c r="A18" s="63" t="n"/>
@@ -1738,9 +1748,9 @@
   <mergeCells count="5">
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="I6:J6"/>
+    <mergeCell ref="A14:J14"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="E9:J9"/>
-    <mergeCell ref="A13:J13"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1778,7 +1788,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="52">
       <c r="A5" s="58" t="inlineStr">
         <is>
@@ -1835,7 +1844,7 @@
       </c>
       <c r="B8" s="62" t="inlineStr">
         <is>
-          <t>特效</t>
+          <t>特效 / 子弹特效</t>
         </is>
       </c>
       <c r="C8" s="62" t="n"/>
@@ -2100,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Y34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="51" min="1" max="1"/>
@@ -2372,7 +2381,7 @@
         <v/>
       </c>
       <c r="S6" s="63">
-        <f>IF(COUNTIF($R$6:$R$25,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="63" t="n"/>
@@ -2475,7 +2484,7 @@
         <v/>
       </c>
       <c r="S7" s="63">
-        <f>IF(COUNTIF($R$6:$R$25,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="63" t="n"/>
@@ -2578,7 +2587,7 @@
         <v/>
       </c>
       <c r="S8" s="63">
-        <f>IF(COUNTIF($R$6:$R$25,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="63" t="n"/>
@@ -2681,7 +2690,7 @@
         <v/>
       </c>
       <c r="S9" s="63">
-        <f>IF(COUNTIF($R$6:$R$25,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="63" t="n"/>
@@ -2788,7 +2797,7 @@
         <v/>
       </c>
       <c r="S10" s="63">
-        <f>IF(COUNTIF($R$6:$R$25,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="63" t="n"/>
@@ -2895,7 +2904,7 @@
         <v/>
       </c>
       <c r="S11" s="63">
-        <f>IF(COUNTIF($R$6:$R$25,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="63" t="n"/>
@@ -3002,7 +3011,7 @@
         <v/>
       </c>
       <c r="S12" s="63">
-        <f>IF(COUNTIF($R$6:$R$25,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="63" t="n"/>
@@ -3109,7 +3118,7 @@
         <v/>
       </c>
       <c r="S13" s="63">
-        <f>IF(COUNTIF($R$6:$R$25,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="63" t="n"/>
@@ -3216,7 +3225,7 @@
         <v/>
       </c>
       <c r="S14" s="63">
-        <f>IF(COUNTIF($R$6:$R$25,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="63" t="n"/>
@@ -3323,7 +3332,7 @@
         <v/>
       </c>
       <c r="S15" s="63">
-        <f>IF(COUNTIF($R$6:$R$25,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="63" t="n"/>
@@ -3430,7 +3439,7 @@
         <v/>
       </c>
       <c r="S16" s="63">
-        <f>IF(COUNTIF($R$6:$R$25,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="63" t="n"/>
@@ -3549,7 +3558,7 @@
         <v/>
       </c>
       <c r="S17" s="55">
-        <f>IF(COUNTIF($R$6:$R$25,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="79" t="inlineStr">
@@ -3668,7 +3677,7 @@
         <v/>
       </c>
       <c r="S18" s="55">
-        <f>IF(COUNTIF($R$6:$R$25,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="79" t="inlineStr">
@@ -3791,7 +3800,7 @@
         <v/>
       </c>
       <c r="S19" s="55">
-        <f>IF(COUNTIF($R$6:$R$25,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="79" t="inlineStr">
@@ -3915,7 +3924,7 @@
         <v/>
       </c>
       <c r="S20" s="55">
-        <f>IF(COUNTIF($R$6:$R$25,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="79" t="inlineStr">
@@ -4031,7 +4040,7 @@
         <v/>
       </c>
       <c r="S21" s="55">
-        <f>IF(COUNTIF($R$6:$R$25,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="79" t="inlineStr">
@@ -4150,7 +4159,7 @@
         <v/>
       </c>
       <c r="S22" s="55">
-        <f>IF(COUNTIF($R$6:$R$25,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="79" t="inlineStr">
@@ -4269,7 +4278,7 @@
         <v/>
       </c>
       <c r="S23" s="55">
-        <f>IF(COUNTIF($R$6:$R$25,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="79" t="inlineStr">
@@ -4388,7 +4397,7 @@
         <v/>
       </c>
       <c r="S24" s="55">
-        <f>IF(COUNTIF($R$6:$R$25,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="79" t="inlineStr">
@@ -4507,7 +4516,7 @@
         <v/>
       </c>
       <c r="S25" s="55">
-        <f>IF(COUNTIF($R$6:$R$25,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="79" t="inlineStr">
@@ -4536,6 +4545,1063 @@
       <c r="Y25" s="55" t="inlineStr">
         <is>
           <t>运行包装v003，Blender/GLB母版v001；24秒+间隔30秒；100F天台局部(25,0,-31)；尺寸75%±10%，路径保持，补偿脚底高度。；本轮各鸟比上版大50%并±10%错落，空中速度减半，航程200m/24s。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="931.3" customHeight="1" s="52">
+      <c r="A26" s="79" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-VISUAL-3D</t>
+        </is>
+      </c>
+      <c r="B26" s="79" t="inlineStr">
+        <is>
+          <t>飞行子弹通用弹体视觉（共用父体）</t>
+        </is>
+      </c>
+      <c r="C26" s="79" t="inlineStr">
+        <is>
+          <t>子弹特效</t>
+        </is>
+      </c>
+      <c r="D26" s="79" t="inlineStr">
+        <is>
+          <t>bullet_shared</t>
+        </is>
+      </c>
+      <c r="E26" s="79" t="inlineStr">
+        <is>
+          <t>FX01-06</t>
+        </is>
+      </c>
+      <c r="F26" s="79" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G26" s="79" t="n"/>
+      <c r="H26" s="79" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I26" s="79" t="inlineStr">
+        <is>
+          <t>flight</t>
+        </is>
+      </c>
+      <c r="J26" s="79" t="inlineStr">
+        <is>
+          <t>玩家/敌人飞行子弹</t>
+        </is>
+      </c>
+      <c r="K26" s="79" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L26" s="79" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M26" s="79" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N26" s="79" t="inlineStr">
+        <is>
+          <t>PackedScene/程序几何（铂金亮芯胶囊 + 弹色半透明外壳 + 沿弹道拖尾锥 + 跟随灯）</t>
+        </is>
+      </c>
+      <c r="O26" s="79" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_visual_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P26" s="79" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBulletVisual3D.gd; src/combat3d/Projectile3D.gd</t>
+        </is>
+      </c>
+      <c r="Q26" s="79" t="inlineStr">
+        <is>
+          <t>子弹;弹体;尾迹;飞行;投射物;projectile;bullet;3D;共用弹体</t>
+        </is>
+      </c>
+      <c r="R26" s="79">
+        <f>LOWER(TRIM(C26)&amp;"|"&amp;TRIM(D26)&amp;"|"&amp;TRIM(E26)&amp;"|"&amp;TRIM(F26)&amp;"|"&amp;TRIM(H26)&amp;"|"&amp;TRIM(I26))</f>
+        <v/>
+      </c>
+      <c r="S26" s="79">
+        <f>IF(COUNTIF($R$6:$R$34,R26)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T26" s="79" t="inlineStr">
+        <is>
+          <t>a3c84c7e8842369fee46a224880589f1470e2beb68b2205a5ad41c4659832685</t>
+        </is>
+      </c>
+      <c r="U26" s="79" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V26" s="79" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="W26" s="79" t="inlineStr">
+        <is>
+          <t>原创程序几何</t>
+        </is>
+      </c>
+      <c r="X26" s="79" t="inlineStr">
+        <is>
+          <t>FX01-06</t>
+        </is>
+      </c>
+      <c r="Y26" s="79" t="inlineStr">
+        <is>
+          <t>由《3D-特效》分页 FX01-06 补登进《资产主表》——该 Prefab 此前只登记在分页，主表缺行，与「《资产主表》＝唯一登记源」的口径不符。宿主唯一生命周期：由 Projectile3D 作为子节点持有，随 ProjectilePool3D 回收；刻意不进 VfxPool3D 注册表，避免弹体池与特效池双重所有权（见 14.6 §… 与 skill vfx-combat-effect-authoring）。本行同时是 8 个弹种专属弹体特效的变体父体（G 列指向本 AssetID），弹种专属 Prefab 落地后仍复用本行的弹芯/外壳/拖尾几何分层，仅按弹种替换外观与行为段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22.35" customHeight="1" s="52">
+      <c r="A27" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-STANDARD-3D</t>
+        </is>
+      </c>
+      <c r="B27" s="76" t="inlineStr">
+        <is>
+          <t>标准子弹弹体与尾迹特效</t>
+        </is>
+      </c>
+      <c r="C27" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效</t>
+        </is>
+      </c>
+      <c r="D27" s="76" t="inlineStr">
+        <is>
+          <t>bullet_standard</t>
+        </is>
+      </c>
+      <c r="E27" s="76" t="inlineStr">
+        <is>
+          <t>mod_bullet_standard</t>
+        </is>
+      </c>
+      <c r="F27" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G27" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-VISUAL-3D</t>
+        </is>
+      </c>
+      <c r="H27" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I27" s="76" t="inlineStr">
+        <is>
+          <t>flight_neutral</t>
+        </is>
+      </c>
+      <c r="J27" s="76" t="inlineStr">
+        <is>
+          <t>标准子弹模块（mod_bullet_standard）</t>
+        </is>
+      </c>
+      <c r="K27" s="76" t="inlineStr">
+        <is>
+          <t>待制作</t>
+        </is>
+      </c>
+      <c r="L27" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M27" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N27" s="76" t="inlineStr">
+        <is>
+          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+        </is>
+      </c>
+      <c r="O27" s="76" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="P27" s="76" t="inlineStr">
+        <is>
+          <t>docs/v0.1/04_技术施工_战斗与局内成长.md §6.2（子弹模块必填 visual_id）; docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#武器 S17/T17; src/base/BlueprintRegistry.gd（mod_bullet_standard）</t>
+        </is>
+      </c>
+      <c r="Q27" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效;标准子弹;标准弹;中性弹体;尾迹;kinetic;standard;3D</t>
+        </is>
+      </c>
+      <c r="R27" s="76">
+        <f>LOWER(TRIM(C27)&amp;"|"&amp;TRIM(D27)&amp;"|"&amp;TRIM(E27)&amp;"|"&amp;TRIM(F27)&amp;"|"&amp;TRIM(H27)&amp;"|"&amp;TRIM(I27))</f>
+        <v/>
+      </c>
+      <c r="S27" s="76">
+        <f>IF(COUNTIF($R$6:$R$34,R27)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T27" s="76" t="n"/>
+      <c r="U27" s="76" t="inlineStr">
+        <is>
+          <t>待分配</t>
+        </is>
+      </c>
+      <c r="V27" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="W27" s="76" t="inlineStr">
+        <is>
+          <t>待制作/原创程序几何</t>
+        </is>
+      </c>
+      <c r="X27" s="76" t="n"/>
+      <c r="Y27" s="76" t="inlineStr">
+        <is>
+          <t>设计依据（内容库《武器》S17 原文）：「使用清晰中性弹体、尾迹和命中；不附加误导性的元素效果」；内容库 T17：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_standard = Color(0.76, 0.86, 0.92)，标签 kinetic;standard），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22.35" customHeight="1" s="52">
+      <c r="A28" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-STICKY-3D</t>
+        </is>
+      </c>
+      <c r="B28" s="76" t="inlineStr">
+        <is>
+          <t>黏黏弹附着与倒计时特效</t>
+        </is>
+      </c>
+      <c r="C28" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效</t>
+        </is>
+      </c>
+      <c r="D28" s="76" t="inlineStr">
+        <is>
+          <t>bullet_sticky</t>
+        </is>
+      </c>
+      <c r="E28" s="76" t="inlineStr">
+        <is>
+          <t>mod_bullet_sticky</t>
+        </is>
+      </c>
+      <c r="F28" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G28" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-VISUAL-3D</t>
+        </is>
+      </c>
+      <c r="H28" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I28" s="76" t="inlineStr">
+        <is>
+          <t>attach_countdown</t>
+        </is>
+      </c>
+      <c r="J28" s="76" t="inlineStr">
+        <is>
+          <t>黏黏弹模块（mod_bullet_sticky）</t>
+        </is>
+      </c>
+      <c r="K28" s="76" t="inlineStr">
+        <is>
+          <t>待制作</t>
+        </is>
+      </c>
+      <c r="L28" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M28" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N28" s="76" t="inlineStr">
+        <is>
+          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+        </is>
+      </c>
+      <c r="O28" s="76" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="P28" s="76" t="inlineStr">
+        <is>
+          <t>docs/v0.1/04_技术施工_战斗与局内成长.md §6.2（子弹模块必填 visual_id）; docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#武器 S18/T18; src/base/BlueprintRegistry.gd（mod_bullet_sticky）</t>
+        </is>
+      </c>
+      <c r="Q28" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效;黏黏弹;附着;倒计时;持续伤害;sticky;dot;3D</t>
+        </is>
+      </c>
+      <c r="R28" s="76">
+        <f>LOWER(TRIM(C28)&amp;"|"&amp;TRIM(D28)&amp;"|"&amp;TRIM(E28)&amp;"|"&amp;TRIM(F28)&amp;"|"&amp;TRIM(H28)&amp;"|"&amp;TRIM(I28))</f>
+        <v/>
+      </c>
+      <c r="S28" s="76">
+        <f>IF(COUNTIF($R$6:$R$34,R28)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T28" s="76" t="n"/>
+      <c r="U28" s="76" t="inlineStr">
+        <is>
+          <t>待分配</t>
+        </is>
+      </c>
+      <c r="V28" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="W28" s="76" t="inlineStr">
+        <is>
+          <t>待制作/原创程序几何</t>
+        </is>
+      </c>
+      <c r="X28" s="76" t="n"/>
+      <c r="Y28" s="76" t="inlineStr">
+        <is>
+          <t>设计依据（内容库《武器》S18 原文）：「命中后弹体留在表面并显示倒计时/状态，结束时反馈与结算同步」；内容库 T18：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_sticky = Color(0.32, 0.92, 0.62)，标签 sticky;dot），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22.35" customHeight="1" s="52">
+      <c r="A29" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-BOUNCE-3D</t>
+        </is>
+      </c>
+      <c r="B29" s="76" t="inlineStr">
+        <is>
+          <t>回旋镖弹反弹折线与计数特效</t>
+        </is>
+      </c>
+      <c r="C29" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效</t>
+        </is>
+      </c>
+      <c r="D29" s="76" t="inlineStr">
+        <is>
+          <t>bullet_bounce</t>
+        </is>
+      </c>
+      <c r="E29" s="76" t="inlineStr">
+        <is>
+          <t>mod_bullet_bounce</t>
+        </is>
+      </c>
+      <c r="F29" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G29" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-VISUAL-3D</t>
+        </is>
+      </c>
+      <c r="H29" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I29" s="76" t="inlineStr">
+        <is>
+          <t>bounce_ricochet</t>
+        </is>
+      </c>
+      <c r="J29" s="76" t="inlineStr">
+        <is>
+          <t>回旋镖弹模块（mod_bullet_bounce）</t>
+        </is>
+      </c>
+      <c r="K29" s="76" t="inlineStr">
+        <is>
+          <t>待制作</t>
+        </is>
+      </c>
+      <c r="L29" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M29" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N29" s="76" t="inlineStr">
+        <is>
+          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+        </is>
+      </c>
+      <c r="O29" s="76" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="P29" s="76" t="inlineStr">
+        <is>
+          <t>docs/v0.1/04_技术施工_战斗与局内成长.md §6.2（子弹模块必填 visual_id）; docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#武器 S13/T13; src/base/BlueprintRegistry.gd（mod_bullet_bounce）</t>
+        </is>
+      </c>
+      <c r="Q29" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效;回旋镖弹;反弹;弹跳;折线闪光;计数递减;ricochet;3D</t>
+        </is>
+      </c>
+      <c r="R29" s="76">
+        <f>LOWER(TRIM(C29)&amp;"|"&amp;TRIM(D29)&amp;"|"&amp;TRIM(E29)&amp;"|"&amp;TRIM(F29)&amp;"|"&amp;TRIM(H29)&amp;"|"&amp;TRIM(I29))</f>
+        <v/>
+      </c>
+      <c r="S29" s="76">
+        <f>IF(COUNTIF($R$6:$R$34,R29)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T29" s="76" t="n"/>
+      <c r="U29" s="76" t="inlineStr">
+        <is>
+          <t>待分配</t>
+        </is>
+      </c>
+      <c r="V29" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="W29" s="76" t="inlineStr">
+        <is>
+          <t>待制作/原创程序几何</t>
+        </is>
+      </c>
+      <c r="X29" s="76" t="n"/>
+      <c r="Y29" s="76" t="inlineStr">
+        <is>
+          <t>设计依据（内容库《武器》S13 原文）：「反弹点有折线闪光与计数递减，飞行方向变化清楚可读」；内容库 T13：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_bounce = Color(0.30, 0.70, 1.0)，标签 bounce;ricochet），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22.35" customHeight="1" s="52">
+      <c r="A30" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-PIERCING-3D</t>
+        </is>
+      </c>
+      <c r="B30" s="76" t="inlineStr">
+        <is>
+          <t>穿甲弹贯穿线与层数特效</t>
+        </is>
+      </c>
+      <c r="C30" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效</t>
+        </is>
+      </c>
+      <c r="D30" s="76" t="inlineStr">
+        <is>
+          <t>bullet_piercing</t>
+        </is>
+      </c>
+      <c r="E30" s="76" t="inlineStr">
+        <is>
+          <t>mod_bullet_piercing</t>
+        </is>
+      </c>
+      <c r="F30" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G30" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-VISUAL-3D</t>
+        </is>
+      </c>
+      <c r="H30" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I30" s="76" t="inlineStr">
+        <is>
+          <t>pierce_through</t>
+        </is>
+      </c>
+      <c r="J30" s="76" t="inlineStr">
+        <is>
+          <t>穿甲弹模块（mod_bullet_piercing）</t>
+        </is>
+      </c>
+      <c r="K30" s="76" t="inlineStr">
+        <is>
+          <t>待制作</t>
+        </is>
+      </c>
+      <c r="L30" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M30" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N30" s="76" t="inlineStr">
+        <is>
+          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+        </is>
+      </c>
+      <c r="O30" s="76" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="P30" s="76" t="inlineStr">
+        <is>
+          <t>docs/v0.1/04_技术施工_战斗与局内成长.md §6.2（子弹模块必填 visual_id）; docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#武器 S16/T16; src/base/BlueprintRegistry.gd（mod_bullet_piercing）</t>
+        </is>
+      </c>
+      <c r="Q30" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效;穿甲弹;穿透;贯穿线;剩余层数;piercing;armor;3D</t>
+        </is>
+      </c>
+      <c r="R30" s="76">
+        <f>LOWER(TRIM(C30)&amp;"|"&amp;TRIM(D30)&amp;"|"&amp;TRIM(E30)&amp;"|"&amp;TRIM(F30)&amp;"|"&amp;TRIM(H30)&amp;"|"&amp;TRIM(I30))</f>
+        <v/>
+      </c>
+      <c r="S30" s="76">
+        <f>IF(COUNTIF($R$6:$R$34,R30)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T30" s="76" t="n"/>
+      <c r="U30" s="76" t="inlineStr">
+        <is>
+          <t>待分配</t>
+        </is>
+      </c>
+      <c r="V30" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="W30" s="76" t="inlineStr">
+        <is>
+          <t>待制作/原创程序几何</t>
+        </is>
+      </c>
+      <c r="X30" s="76" t="n"/>
+      <c r="Y30" s="76" t="inlineStr">
+        <is>
+          <t>设计依据（内容库《武器》S16 原文）：「穿透命中显示连续贯穿线与剩余层数，不在首个目标处假性消失」；内容库 T16：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_piercing = Color(1.0, 0.78, 0.22)，标签 piercing;armor），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22.35" customHeight="1" s="52">
+      <c r="A31" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-EXPLOSIVE-3D</t>
+        </is>
+      </c>
+      <c r="B31" s="76" t="inlineStr">
+        <is>
+          <t>爆炸弹弹体与爆炸时点特效</t>
+        </is>
+      </c>
+      <c r="C31" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效</t>
+        </is>
+      </c>
+      <c r="D31" s="76" t="inlineStr">
+        <is>
+          <t>bullet_explosive</t>
+        </is>
+      </c>
+      <c r="E31" s="76" t="inlineStr">
+        <is>
+          <t>mod_bullet_explosive</t>
+        </is>
+      </c>
+      <c r="F31" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G31" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-VISUAL-3D</t>
+        </is>
+      </c>
+      <c r="H31" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I31" s="76" t="inlineStr">
+        <is>
+          <t>flight_to_detonate</t>
+        </is>
+      </c>
+      <c r="J31" s="76" t="inlineStr">
+        <is>
+          <t>爆炸弹模块（mod_bullet_explosive）</t>
+        </is>
+      </c>
+      <c r="K31" s="76" t="inlineStr">
+        <is>
+          <t>待制作</t>
+        </is>
+      </c>
+      <c r="L31" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M31" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N31" s="76" t="inlineStr">
+        <is>
+          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+        </is>
+      </c>
+      <c r="O31" s="76" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="P31" s="76" t="inlineStr">
+        <is>
+          <t>docs/v0.1/04_技术施工_战斗与局内成长.md §6.2（子弹模块必填 visual_id）; docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#武器 S14/T14; src/base/BlueprintRegistry.gd（mod_bullet_explosive）</t>
+        </is>
+      </c>
+      <c r="Q31" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效;爆炸弹;范围伤害;爆炸半径;伤害时点;低特效轮廓圈;explosive;area;3D</t>
+        </is>
+      </c>
+      <c r="R31" s="76">
+        <f>LOWER(TRIM(C31)&amp;"|"&amp;TRIM(D31)&amp;"|"&amp;TRIM(E31)&amp;"|"&amp;TRIM(F31)&amp;"|"&amp;TRIM(H31)&amp;"|"&amp;TRIM(I31))</f>
+        <v/>
+      </c>
+      <c r="S31" s="76">
+        <f>IF(COUNTIF($R$6:$R$34,R31)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T31" s="76" t="n"/>
+      <c r="U31" s="76" t="inlineStr">
+        <is>
+          <t>待分配</t>
+        </is>
+      </c>
+      <c r="V31" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="W31" s="76" t="inlineStr">
+        <is>
+          <t>待制作/原创程序几何</t>
+        </is>
+      </c>
+      <c r="X31" s="76" t="n"/>
+      <c r="Y31" s="76" t="inlineStr">
+        <is>
+          <t>设计依据（内容库《武器》S14 原文）：「弹体、尾迹、爆炸半径与伤害时点同步，低特效下保留轮廓圈」；内容库 T14：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_explosive = Color(1.0, 0.28, 0.08)，标签 explosive;area），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22.35" customHeight="1" s="52">
+      <c r="A32" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-HOMING-3D</t>
+        </is>
+      </c>
+      <c r="B32" s="76" t="inlineStr">
+        <is>
+          <t>蜂卵弹锁定框与弯曲尾迹特效</t>
+        </is>
+      </c>
+      <c r="C32" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效</t>
+        </is>
+      </c>
+      <c r="D32" s="76" t="inlineStr">
+        <is>
+          <t>bullet_homing</t>
+        </is>
+      </c>
+      <c r="E32" s="76" t="inlineStr">
+        <is>
+          <t>mod_bullet_homing</t>
+        </is>
+      </c>
+      <c r="F32" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G32" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-VISUAL-3D</t>
+        </is>
+      </c>
+      <c r="H32" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I32" s="76" t="inlineStr">
+        <is>
+          <t>homing_curve</t>
+        </is>
+      </c>
+      <c r="J32" s="76" t="inlineStr">
+        <is>
+          <t>蜂卵弹模块（mod_bullet_homing）</t>
+        </is>
+      </c>
+      <c r="K32" s="76" t="inlineStr">
+        <is>
+          <t>待制作</t>
+        </is>
+      </c>
+      <c r="L32" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M32" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N32" s="76" t="inlineStr">
+        <is>
+          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+        </is>
+      </c>
+      <c r="O32" s="76" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="P32" s="76" t="inlineStr">
+        <is>
+          <t>docs/v0.1/04_技术施工_战斗与局内成长.md §6.2（子弹模块必填 visual_id）; docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#武器 S15/T15; src/base/BlueprintRegistry.gd（mod_bullet_homing）</t>
+        </is>
+      </c>
+      <c r="Q32" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效;蜂卵弹;追踪;锁定框;弯曲尾迹;解除提示;homing;3D</t>
+        </is>
+      </c>
+      <c r="R32" s="76">
+        <f>LOWER(TRIM(C32)&amp;"|"&amp;TRIM(D32)&amp;"|"&amp;TRIM(E32)&amp;"|"&amp;TRIM(F32)&amp;"|"&amp;TRIM(H32)&amp;"|"&amp;TRIM(I32))</f>
+        <v/>
+      </c>
+      <c r="S32" s="76">
+        <f>IF(COUNTIF($R$6:$R$34,R32)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T32" s="76" t="n"/>
+      <c r="U32" s="76" t="inlineStr">
+        <is>
+          <t>待分配</t>
+        </is>
+      </c>
+      <c r="V32" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="W32" s="76" t="inlineStr">
+        <is>
+          <t>待制作/原创程序几何</t>
+        </is>
+      </c>
+      <c r="X32" s="76" t="n"/>
+      <c r="Y32" s="76" t="inlineStr">
+        <is>
+          <t>设计依据（内容库《武器》S15 原文）：「锁定框、弯曲尾迹和转向动作一致；目标丢失有解除提示」；内容库 T15：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_homing = Color(0.50, 1.0, 0.42)，标签 homing;summon），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22.35" customHeight="1" s="52">
+      <c r="A33" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-BLACKHOLE-3D</t>
+        </is>
+      </c>
+      <c r="B33" s="76" t="inlineStr">
+        <is>
+          <t>黑洞弹核心与吸入流线特效</t>
+        </is>
+      </c>
+      <c r="C33" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效</t>
+        </is>
+      </c>
+      <c r="D33" s="76" t="inlineStr">
+        <is>
+          <t>bullet_blackhole</t>
+        </is>
+      </c>
+      <c r="E33" s="76" t="inlineStr">
+        <is>
+          <t>mod_bullet_blackhole</t>
+        </is>
+      </c>
+      <c r="F33" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G33" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-VISUAL-3D</t>
+        </is>
+      </c>
+      <c r="H33" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I33" s="76" t="inlineStr">
+        <is>
+          <t>blackhole_pull</t>
+        </is>
+      </c>
+      <c r="J33" s="76" t="inlineStr">
+        <is>
+          <t>黑洞弹模块（mod_bullet_blackhole）</t>
+        </is>
+      </c>
+      <c r="K33" s="76" t="inlineStr">
+        <is>
+          <t>待制作</t>
+        </is>
+      </c>
+      <c r="L33" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M33" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N33" s="76" t="inlineStr">
+        <is>
+          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+        </is>
+      </c>
+      <c r="O33" s="76" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="P33" s="76" t="inlineStr">
+        <is>
+          <t>docs/v0.1/04_技术施工_战斗与局内成长.md §6.2（子弹模块必填 visual_id）; docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#武器 S12/T12; src/base/BlueprintRegistry.gd（mod_bullet_blackhole）</t>
+        </is>
+      </c>
+      <c r="Q33" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效;黑洞弹;黑洞核心;吸入流线;范围边界;收束反馈;pull;3D</t>
+        </is>
+      </c>
+      <c r="R33" s="76">
+        <f>LOWER(TRIM(C33)&amp;"|"&amp;TRIM(D33)&amp;"|"&amp;TRIM(E33)&amp;"|"&amp;TRIM(F33)&amp;"|"&amp;TRIM(H33)&amp;"|"&amp;TRIM(I33))</f>
+        <v/>
+      </c>
+      <c r="S33" s="76">
+        <f>IF(COUNTIF($R$6:$R$34,R33)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T33" s="76" t="n"/>
+      <c r="U33" s="76" t="inlineStr">
+        <is>
+          <t>待分配</t>
+        </is>
+      </c>
+      <c r="V33" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="W33" s="76" t="inlineStr">
+        <is>
+          <t>待制作/原创程序几何</t>
+        </is>
+      </c>
+      <c r="X33" s="76" t="n"/>
+      <c r="Y33" s="76" t="inlineStr">
+        <is>
+          <t>设计依据（内容库《武器》S12 原文）：「黑洞核心、吸入流线和范围边界清晰；命中/结束有收束反馈」；内容库 T12：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_blackhole = Color(0.68, 0.25, 0.95)，标签 blackhole;pull），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22.35" customHeight="1" s="52">
+      <c r="A34" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-BALLOON-3D</t>
+        </is>
+      </c>
+      <c r="B34" s="76" t="inlineStr">
+        <is>
+          <t>气球弹膨胀弹体与命中体积特效</t>
+        </is>
+      </c>
+      <c r="C34" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效</t>
+        </is>
+      </c>
+      <c r="D34" s="76" t="inlineStr">
+        <is>
+          <t>bullet_balloon</t>
+        </is>
+      </c>
+      <c r="E34" s="76" t="inlineStr">
+        <is>
+          <t>mod_bullet_balloon</t>
+        </is>
+      </c>
+      <c r="F34" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G34" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-VISUAL-3D</t>
+        </is>
+      </c>
+      <c r="H34" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I34" s="76" t="inlineStr">
+        <is>
+          <t>inflate_flight</t>
+        </is>
+      </c>
+      <c r="J34" s="76" t="inlineStr">
+        <is>
+          <t>气球弹模块（mod_bullet_balloon）</t>
+        </is>
+      </c>
+      <c r="K34" s="76" t="inlineStr">
+        <is>
+          <t>待制作</t>
+        </is>
+      </c>
+      <c r="L34" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M34" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N34" s="76" t="inlineStr">
+        <is>
+          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+        </is>
+      </c>
+      <c r="O34" s="76" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="P34" s="76" t="inlineStr">
+        <is>
+          <t>docs/v0.1/04_技术施工_战斗与局内成长.md §6.2（子弹模块必填 visual_id）; docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#武器 S11/T11; src/base/BlueprintRegistry.gd（mod_bullet_balloon）</t>
+        </is>
+      </c>
+      <c r="Q34" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效;气球弹;膨胀弹体;命中体积;低速;balloon;big;3D</t>
+        </is>
+      </c>
+      <c r="R34" s="76">
+        <f>LOWER(TRIM(C34)&amp;"|"&amp;TRIM(D34)&amp;"|"&amp;TRIM(E34)&amp;"|"&amp;TRIM(F34)&amp;"|"&amp;TRIM(H34)&amp;"|"&amp;TRIM(I34))</f>
+        <v/>
+      </c>
+      <c r="S34" s="76">
+        <f>IF(COUNTIF($R$6:$R$34,R34)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T34" s="76" t="n"/>
+      <c r="U34" s="76" t="inlineStr">
+        <is>
+          <t>待分配</t>
+        </is>
+      </c>
+      <c r="V34" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="W34" s="76" t="inlineStr">
+        <is>
+          <t>待制作/原创程序几何</t>
+        </is>
+      </c>
+      <c r="X34" s="76" t="n"/>
+      <c r="Y34" s="76" t="inlineStr">
+        <is>
+          <t>设计依据（内容库《武器》S11 原文）：「膨胀弹体、较重尾迹与命中体积一致，不能只改伤害数值」；内容库 T11：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_balloon = Color(0.98, 0.35, 0.72)，标签 balloon;big），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
         </is>
       </c>
     </row>
@@ -4747,36 +5813,27 @@
     <row r="427" ht="84.75" customHeight="1" s="52"/>
     <row r="429" ht="120" customHeight="1" s="52"/>
   </sheetData>
-  <autoFilter ref="A5:Y25"/>
+  <autoFilter ref="A5:Y34"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
   </mergeCells>
-  <conditionalFormatting sqref="S6:S22">
-    <cfRule type="containsText" rank="0" priority="2" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="6" text="重复" percent="0" bottom="0">
-      <formula>NOT(ISERROR(SEARCH("重复",S6)))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="S6:S34">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="6" text="重复"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K22">
-    <cfRule type="containsText" rank="0" priority="3" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="7" text="已完成" percent="0" bottom="0">
-      <formula>NOT(ISERROR(SEARCH("已完成",K6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" rank="0" priority="4" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="8" text="待制作" percent="0" bottom="0">
-      <formula>NOT(ISERROR(SEARCH("待制作",K6)))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="K6:K34">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="7" text="已完成"/>
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="8" text="待制作"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
-      <formula2>0</formula2>
+    <dataValidation sqref="C6:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,子弹特效,音效,音乐"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
-      <formula2>0</formula2>
+    <dataValidation sqref="K6:K34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,design_only,authored,exported_pending_godot_validation,validated,active,已从运行场景移除,白盒组件"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="L6:L34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -7309,7 +8366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="51" min="1" max="1"/>
@@ -7336,7 +8393,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="52">
       <c r="A5" s="58" t="inlineStr">
         <is>
@@ -7844,7 +8900,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="51" t="inlineStr">
         <is>
           <t>v0.1.13</t>
         </is>
@@ -7852,29 +8908,66 @@
       <c r="B19" s="110" t="n">
         <v>46307</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="51" t="inlineStr">
         <is>
           <t>鸟群尺寸与速度调整</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="51" t="inlineStr">
         <is>
           <t>特效 / 资产主表</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="51" t="inlineStr">
         <is>
           <t>尺寸比上版大50%，各鸟±10%变化；空中速度减半为200m/24s。</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="51" t="inlineStr">
         <is>
           <t>运行包装v003；既有两个AssetID。</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="51" t="inlineStr">
         <is>
           <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1" s="52">
+      <c r="A20" s="51" t="inlineStr">
+        <is>
+          <t>v0.1.14</t>
+        </is>
+      </c>
+      <c r="B20" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C20" s="51" t="inlineStr">
+        <is>
+          <t>新增大类 + 新增条目</t>
+        </is>
+      </c>
+      <c r="D20" s="51" t="inlineStr">
+        <is>
+          <t>特效 / 子弹特效</t>
+        </is>
+      </c>
+      <c r="E20" s="51" t="inlineStr">
+        <is>
+          <t>新增域内第二大类「子弹特效」：逐弹种专属弹体/尾迹/命中特效各占一行，8 个弹种（标准/黏黏弹/回旋镖弹/穿甲弹/爆炸弹/蜂卵弹/黑洞弹/气球弹）全部为「待制作」，以内容库《武器》S 列表现要求与 04 §6.2 子弹模块 visual_id 契约为设计依据；同时把原只登记在《3D-特效》分页的通用弹体 VFX-BULLET-VISUAL-3D 补登进《资产主表》并作为 8 条的变体父体。同步：C 列下拉加入新大类、S 列查重区间与总览公式区间 $25→$34、条件格式与 auto_filter 扩到 r34；《3D-特效》分页刻意未改（8 条尚无 PackedScene，且该页一行 = 一个实际存在的 PackedScene）。</t>
+        </is>
+      </c>
+      <c r="F20" s="51" t="inlineStr">
+        <is>
+          <t>稳定 AssetID 与既有 Prefab 路径不变；《3D-特效》逐格不变；主目录《分账本索引》特效行大类数 1→2、《分类与编码》新增一行；纯登记变更，不改玩法数值与运行时行为。</t>
+        </is>
+      </c>
+      <c r="G20" s="51" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -4665,11 +4665,11 @@
       </c>
       <c r="Y26" s="79" t="inlineStr">
         <is>
-          <t>由《3D-特效》分页 FX01-06 补登进《资产主表》——该 Prefab 此前只登记在分页，主表缺行，与「《资产主表》＝唯一登记源」的口径不符。宿主唯一生命周期：由 Projectile3D 作为子节点持有，随 ProjectilePool3D 回收；刻意不进 VfxPool3D 注册表，避免弹体池与特效池双重所有权（见 14.6 §… 与 skill vfx-combat-effect-authoring）。本行同时是 8 个弹种专属弹体特效的变体父体（G 列指向本 AssetID），弹种专属 Prefab 落地后仍复用本行的弹芯/外壳/拖尾几何分层，仅按弹种替换外观与行为段。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22.35" customHeight="1" s="52">
+          <t>由《3D-特效》分页 FX01-06 补登进《资产主表》——该 Prefab 此前只登记在分页，主表缺行，与「《资产主表》＝唯一登记源」的口径不符。宿主唯一生命周期：由 Projectile3D 作为子节点持有，随 ProjectilePool3D 回收；刻意不进 VfxPool3D 注册表，避免弹体池与特效池双重所有权（见 14.6 §1.3/§3.5 与 skill vfx-combat-effect-authoring）。本行同时是 8 个弹种专属弹体特效的变体父体（G 列指向本 AssetID），弹种专属 Prefab 落地后仍复用本行的弹芯/外壳/拖尾几何分层，仅按弹种替换外观与行为段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="931.3" customHeight="1" s="52">
       <c r="A27" s="76" t="inlineStr">
         <is>
           <t>VFX-BULLET-STANDARD-3D</t>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="K27" s="76" t="inlineStr">
         <is>
-          <t>待制作</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L27" s="76" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="N27" s="76" t="inlineStr">
         <is>
-          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+          <t>弹芯胶囊 r=0.045/h=0.20；外壳 r=0.075/h=0.18；单锥尾迹 底0.055/长0.46；灯 energy1.15/range1.75m</t>
         </is>
       </c>
       <c r="O27" s="76" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_standard_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P27" s="76" t="inlineStr">
@@ -4763,10 +4763,14 @@
         <f>IF(COUNTIF($R$6:$R$34,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T27" s="76" t="n"/>
+      <c r="T27" s="76" t="inlineStr">
+        <is>
+          <t>d85bb501f79d65493fa2225b0af3516873bf73e1b5c8060e6055fc6bdd7a6530</t>
+        </is>
+      </c>
       <c r="U27" s="76" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>摩斯拉</t>
         </is>
       </c>
       <c r="V27" s="76" t="inlineStr">
@@ -4776,17 +4780,17 @@
       </c>
       <c r="W27" s="76" t="inlineStr">
         <is>
-          <t>待制作/原创程序几何</t>
+          <t>原创程序几何</t>
         </is>
       </c>
       <c r="X27" s="76" t="n"/>
       <c r="Y27" s="76" t="inlineStr">
         <is>
-          <t>设计依据（内容库《武器》S17 原文）：「使用清晰中性弹体、尾迹和命中；不附加误导性的元素效果」；内容库 T17：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_standard = Color(0.76, 0.86, 0.92)，标签 kinetic;standard），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22.35" customHeight="1" s="52">
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_standard_root_top3d.tscn + 脚本=src/vfx/VfxBulletStandard3D.gd；根节点=VfxBulletStandard3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S17「使用清晰中性弹体、尾迹和命中；不附加误导性的元素效果」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="931.3" customHeight="1" s="52">
       <c r="A28" s="76" t="inlineStr">
         <is>
           <t>VFX-BULLET-STICKY-3D</t>
@@ -4839,7 +4843,7 @@
       </c>
       <c r="K28" s="76" t="inlineStr">
         <is>
-          <t>待制作</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L28" s="76" t="inlineStr">
@@ -4854,12 +4858,12 @@
       </c>
       <c r="N28" s="76" t="inlineStr">
         <is>
-          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+          <t>弹芯胶囊 r=0.050/h=0.16；外壳 r=0.086/h=0.16；锥尾迹 底0.062/长0.34 + 3 滴落珠；灯 energy1.20/range1.80m</t>
         </is>
       </c>
       <c r="O28" s="76" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_sticky_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P28" s="76" t="inlineStr">
@@ -4880,10 +4884,14 @@
         <f>IF(COUNTIF($R$6:$R$34,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T28" s="76" t="n"/>
+      <c r="T28" s="76" t="inlineStr">
+        <is>
+          <t>a9ecbcc2cf4b74001414b802a5acb0615289fdc8d28ed96fa1360cca52665c4b</t>
+        </is>
+      </c>
       <c r="U28" s="76" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>摩斯拉</t>
         </is>
       </c>
       <c r="V28" s="76" t="inlineStr">
@@ -4893,17 +4901,17 @@
       </c>
       <c r="W28" s="76" t="inlineStr">
         <is>
-          <t>待制作/原创程序几何</t>
+          <t>原创程序几何</t>
         </is>
       </c>
       <c r="X28" s="76" t="n"/>
       <c r="Y28" s="76" t="inlineStr">
         <is>
-          <t>设计依据（内容库《武器》S18 原文）：「命中后弹体留在表面并显示倒计时/状态，结束时反馈与结算同步」；内容库 T18：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_sticky = Color(0.32, 0.92, 0.62)，标签 sticky;dot），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22.35" customHeight="1" s="52">
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_sticky_root_top3d.tscn + 脚本=src/vfx/VfxBulletSticky3D.gd；根节点=VfxBulletSticky3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S18「命中后弹体留在表面并显示倒计时/状态，结束时反馈与结算同步」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="931.3" customHeight="1" s="52">
       <c r="A29" s="76" t="inlineStr">
         <is>
           <t>VFX-BULLET-BOUNCE-3D</t>
@@ -4956,7 +4964,7 @@
       </c>
       <c r="K29" s="76" t="inlineStr">
         <is>
-          <t>待制作</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L29" s="76" t="inlineStr">
@@ -4971,12 +4979,12 @@
       </c>
       <c r="N29" s="76" t="inlineStr">
         <is>
-          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+          <t>弹芯胶囊 r=0.048/h=0.14；外壳 r=0.072/h=0.13；三段折线锥 底0.052/0.040/0.030；灯 energy1.20/range1.80m</t>
         </is>
       </c>
       <c r="O29" s="76" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_bounce_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P29" s="76" t="inlineStr">
@@ -4997,10 +5005,14 @@
         <f>IF(COUNTIF($R$6:$R$34,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T29" s="76" t="n"/>
+      <c r="T29" s="76" t="inlineStr">
+        <is>
+          <t>49bd24a7c468a829e6e7dffe5b6d79c93e9edb4dd3986d9489d151058ba8f6bd</t>
+        </is>
+      </c>
       <c r="U29" s="76" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>摩斯拉</t>
         </is>
       </c>
       <c r="V29" s="76" t="inlineStr">
@@ -5010,17 +5022,17 @@
       </c>
       <c r="W29" s="76" t="inlineStr">
         <is>
-          <t>待制作/原创程序几何</t>
+          <t>原创程序几何</t>
         </is>
       </c>
       <c r="X29" s="76" t="n"/>
       <c r="Y29" s="76" t="inlineStr">
         <is>
-          <t>设计依据（内容库《武器》S13 原文）：「反弹点有折线闪光与计数递减，飞行方向变化清楚可读」；内容库 T13：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_bounce = Color(0.30, 0.70, 1.0)，标签 bounce;ricochet），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22.35" customHeight="1" s="52">
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_bounce_root_top3d.tscn + 脚本=src/vfx/VfxBulletBounce3D.gd；根节点=VfxBulletBounce3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S13「反弹点有折线闪光与计数递减，飞行方向变化清楚可读」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="931.3" customHeight="1" s="52">
       <c r="A30" s="76" t="inlineStr">
         <is>
           <t>VFX-BULLET-PIERCING-3D</t>
@@ -5073,7 +5085,7 @@
       </c>
       <c r="K30" s="76" t="inlineStr">
         <is>
-          <t>待制作</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L30" s="76" t="inlineStr">
@@ -5088,12 +5100,12 @@
       </c>
       <c r="N30" s="76" t="inlineStr">
         <is>
-          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+          <t>弹芯胶囊 r=0.028/h=0.30；外壳 r=0.044/h=0.28；两段针形尾迹 底0.036/0.022；灯 energy1.35/range1.95m</t>
         </is>
       </c>
       <c r="O30" s="76" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_piercing_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P30" s="76" t="inlineStr">
@@ -5114,10 +5126,14 @@
         <f>IF(COUNTIF($R$6:$R$34,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T30" s="76" t="n"/>
+      <c r="T30" s="76" t="inlineStr">
+        <is>
+          <t>450125ae4af8dfe45964f78542d09c5e604bc348a56ef52454378b1430daa37c</t>
+        </is>
+      </c>
       <c r="U30" s="76" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>摩斯拉</t>
         </is>
       </c>
       <c r="V30" s="76" t="inlineStr">
@@ -5127,17 +5143,17 @@
       </c>
       <c r="W30" s="76" t="inlineStr">
         <is>
-          <t>待制作/原创程序几何</t>
+          <t>原创程序几何</t>
         </is>
       </c>
       <c r="X30" s="76" t="n"/>
       <c r="Y30" s="76" t="inlineStr">
         <is>
-          <t>设计依据（内容库《武器》S16 原文）：「穿透命中显示连续贯穿线与剩余层数，不在首个目标处假性消失」；内容库 T16：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_piercing = Color(1.0, 0.78, 0.22)，标签 piercing;armor），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22.35" customHeight="1" s="52">
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_piercing_root_top3d.tscn + 脚本=src/vfx/VfxBulletPiercing3D.gd；根节点=VfxBulletPiercing3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S16「穿透命中显示连续贯穿线与剩余层数，不在首个目标处假性消失」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="931.3" customHeight="1" s="52">
       <c r="A31" s="76" t="inlineStr">
         <is>
           <t>VFX-BULLET-EXPLOSIVE-3D</t>
@@ -5190,7 +5206,7 @@
       </c>
       <c r="K31" s="76" t="inlineStr">
         <is>
-          <t>待制作</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L31" s="76" t="inlineStr">
@@ -5205,12 +5221,12 @@
       </c>
       <c r="N31" s="76" t="inlineStr">
         <is>
-          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+          <t>弹芯胶囊 r=0.055/h=0.22；外壳 r=0.094/h=0.20；锥尾迹 底0.078/长0.40 + 3 火星条；灯 energy1.65/range2.40m</t>
         </is>
       </c>
       <c r="O31" s="76" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_explosive_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P31" s="76" t="inlineStr">
@@ -5231,10 +5247,14 @@
         <f>IF(COUNTIF($R$6:$R$34,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T31" s="76" t="n"/>
+      <c r="T31" s="76" t="inlineStr">
+        <is>
+          <t>8c1ce8b1e775b884b01e6644cd75f57d9cb47cd18e1a3a41e8374f600d84e93d</t>
+        </is>
+      </c>
       <c r="U31" s="76" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>摩斯拉</t>
         </is>
       </c>
       <c r="V31" s="76" t="inlineStr">
@@ -5244,17 +5264,17 @@
       </c>
       <c r="W31" s="76" t="inlineStr">
         <is>
-          <t>待制作/原创程序几何</t>
+          <t>原创程序几何</t>
         </is>
       </c>
       <c r="X31" s="76" t="n"/>
       <c r="Y31" s="76" t="inlineStr">
         <is>
-          <t>设计依据（内容库《武器》S14 原文）：「弹体、尾迹、爆炸半径与伤害时点同步，低特效下保留轮廓圈」；内容库 T14：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_explosive = Color(1.0, 0.28, 0.08)，标签 explosive;area），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22.35" customHeight="1" s="52">
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_explosive_root_top3d.tscn + 脚本=src/vfx/VfxBulletExplosive3D.gd；根节点=VfxBulletExplosive3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S14「弹体、尾迹、爆炸半径与伤害时点同步，低特效下保留轮廓圈」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="931.3" customHeight="1" s="52">
       <c r="A32" s="76" t="inlineStr">
         <is>
           <t>VFX-BULLET-HOMING-3D</t>
@@ -5307,7 +5327,7 @@
       </c>
       <c r="K32" s="76" t="inlineStr">
         <is>
-          <t>待制作</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L32" s="76" t="inlineStr">
@@ -5322,12 +5342,12 @@
       </c>
       <c r="N32" s="76" t="inlineStr">
         <is>
-          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+          <t>弹芯胶囊 r=0.050/h=0.18；外壳 r=0.082/h=0.16；三段摆动尾迹；灯 energy1.25/range1.90m</t>
         </is>
       </c>
       <c r="O32" s="76" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_homing_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P32" s="76" t="inlineStr">
@@ -5348,10 +5368,14 @@
         <f>IF(COUNTIF($R$6:$R$34,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T32" s="76" t="n"/>
+      <c r="T32" s="76" t="inlineStr">
+        <is>
+          <t>f3f7ad5dcce3205908cf0a115ce425f6030daf4427ede2d394b6997192546032</t>
+        </is>
+      </c>
       <c r="U32" s="76" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>摩斯拉</t>
         </is>
       </c>
       <c r="V32" s="76" t="inlineStr">
@@ -5361,17 +5385,17 @@
       </c>
       <c r="W32" s="76" t="inlineStr">
         <is>
-          <t>待制作/原创程序几何</t>
+          <t>原创程序几何</t>
         </is>
       </c>
       <c r="X32" s="76" t="n"/>
       <c r="Y32" s="76" t="inlineStr">
         <is>
-          <t>设计依据（内容库《武器》S15 原文）：「锁定框、弯曲尾迹和转向动作一致；目标丢失有解除提示」；内容库 T15：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_homing = Color(0.50, 1.0, 0.42)，标签 homing;summon），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22.35" customHeight="1" s="52">
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_homing_root_top3d.tscn + 脚本=src/vfx/VfxBulletHoming3D.gd；根节点=VfxBulletHoming3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S15「锁定框、弯曲尾迹和转向动作一致；目标丢失有解除提示」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="931.3" customHeight="1" s="52">
       <c r="A33" s="76" t="inlineStr">
         <is>
           <t>VFX-BULLET-BLACKHOLE-3D</t>
@@ -5424,7 +5448,7 @@
       </c>
       <c r="K33" s="76" t="inlineStr">
         <is>
-          <t>待制作</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L33" s="76" t="inlineStr">
@@ -5439,12 +5463,12 @@
       </c>
       <c r="N33" s="76" t="inlineStr">
         <is>
-          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+          <t>弹芯球 r=0.058；外壳球 r=0.098；外扩喇叭三段 底0.040/0.068/0.096；灯 energy1.45/range2.20m</t>
         </is>
       </c>
       <c r="O33" s="76" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_blackhole_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P33" s="76" t="inlineStr">
@@ -5465,10 +5489,14 @@
         <f>IF(COUNTIF($R$6:$R$34,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T33" s="76" t="n"/>
+      <c r="T33" s="76" t="inlineStr">
+        <is>
+          <t>1f7c02ebe353097eda9d818ce583b9a12935917c69f80929bfc0142d7fa417f2</t>
+        </is>
+      </c>
       <c r="U33" s="76" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>摩斯拉</t>
         </is>
       </c>
       <c r="V33" s="76" t="inlineStr">
@@ -5478,17 +5506,17 @@
       </c>
       <c r="W33" s="76" t="inlineStr">
         <is>
-          <t>待制作/原创程序几何</t>
+          <t>原创程序几何</t>
         </is>
       </c>
       <c r="X33" s="76" t="n"/>
       <c r="Y33" s="76" t="inlineStr">
         <is>
-          <t>设计依据（内容库《武器》S12 原文）：「黑洞核心、吸入流线和范围边界清晰；命中/结束有收束反馈」；内容库 T12：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_blackhole = Color(0.68, 0.25, 0.95)，标签 blackhole;pull），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22.35" customHeight="1" s="52">
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_blackhole_root_top3d.tscn + 脚本=src/vfx/VfxBulletBlackhole3D.gd；根节点=VfxBulletBlackhole3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S12「黑洞核心、吸入流线和范围边界清晰；命中/结束有收束反馈」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="931.3" customHeight="1" s="52">
       <c r="A34" s="76" t="inlineStr">
         <is>
           <t>VFX-BULLET-BALLOON-3D</t>
@@ -5541,7 +5569,7 @@
       </c>
       <c r="K34" s="76" t="inlineStr">
         <is>
-          <t>待制作</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L34" s="76" t="inlineStr">
@@ -5556,12 +5584,12 @@
       </c>
       <c r="N34" s="76" t="inlineStr">
         <is>
-          <t>待定（弹体 / 尾迹 / 命中三段；程序几何或动画序列）</t>
+          <t>弹芯球 r=0.070；外壳球 r=0.118；粗短锥尾迹 底0.104/长0.36；灯 energy1.30/range2.05m</t>
         </is>
       </c>
       <c r="O34" s="76" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_balloon_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P34" s="76" t="inlineStr">
@@ -5582,10 +5610,14 @@
         <f>IF(COUNTIF($R$6:$R$34,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T34" s="76" t="n"/>
+      <c r="T34" s="76" t="inlineStr">
+        <is>
+          <t>e711140cc2daba69230168a54f8f1e03a958015e2c88be8baeaf6f3b1d320e6d</t>
+        </is>
+      </c>
       <c r="U34" s="76" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>摩斯拉</t>
         </is>
       </c>
       <c r="V34" s="76" t="inlineStr">
@@ -5595,13 +5627,13 @@
       </c>
       <c r="W34" s="76" t="inlineStr">
         <is>
-          <t>待制作/原创程序几何</t>
+          <t>原创程序几何</t>
         </is>
       </c>
       <c r="X34" s="76" t="n"/>
       <c r="Y34" s="76" t="inlineStr">
         <is>
-          <t>设计依据（内容库《武器》S11 原文）：「膨胀弹体、较重尾迹与命中体积一致，不能只改伤害数值」；内容库 T11：[部分完成] 实例尾号、槽位、已装配件与命运刻印已可视；逐条专属VFX/音频仍待QA。当前该弹种只有 WeaponModel3D.BULLET_COLORS 的配色区分（mod_bullet_balloon = Color(0.98, 0.35, 0.72)，标签 balloon;big），无专属 Prefab；本行即为该弹种专属弹体/尾迹/命中特效的排产入口。制成后必须在《3D-特效》分页登记实际存在的 PackedScene、回填 O 列路径与 T 列 SHA-256，并把本行 K 列推进到「已完成」。</t>
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_balloon_root_top3d.tscn + 脚本=src/vfx/VfxBulletBalloon3D.gd；根节点=VfxBulletBalloon3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S11「膨胀弹体、较重尾迹与命中体积一致，不能只改伤害数值」。</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5913,7 @@
     <row r="2" ht="33.75" customHeight="1" s="52">
       <c r="A2" s="83" t="inlineStr">
         <is>
-          <t>特效按独立 Prefab 原则：每个特效一个独立 .tscn；Prefab 是特效唯一出口；账本和调用代码读 Prefab。本 sheet 共 12 条，按 5 大类分组，每条 VFX 有内部编号 FX&lt;大类&gt;-&lt;序号&gt;。状态：✅ 完成（Prefab + 脚本 + 接入齐）/ 🟡 待落地（已登记 AssetID，文件未创建）/ 🟠 老形态（迁移完成后删除）。规范见 docs/v0.1/14.6_特效系统与制作规范.md。【2026-09-11 进度】FX01 战斗反馈 5 条 + FX02 受击飘字 2 条 共 7 条完成；FX03/04 已实装但命名待对齐。【2026-09-21 进度】新增 FX01-06 VFX-BULLET-VISUAL-3D（飞行子弹纯视觉，含 ProjectileLight，由 Projectile3D 持有、不进 VfxPool）；FX01-01 / FX01-02 升 v002 卡通重做（枪口新增 MuzzleLight、命中改按命中法线对齐）；三类共同验收 verify_combat_vfx_toon_v002。【2026-09-22 进度】新增 FX01-07 VFX-SHELL-CASING-3D：开火抛壳、重力落地、最多两次小弹跳后静止，接入 WeaponModel3D 与 VfxPool3D。</t>
+          <t>特效按独立 Prefab 原则：每个特效一个独立 .tscn；Prefab 是特效唯一出口；账本和调用代码读 Prefab。本 sheet 共 22 条，按 5 大类分组，每条 VFX 有内部编号 FX&lt;大类&gt;-&lt;序号&gt;。状态：✅ 完成（Prefab + 脚本 + 接入齐）/ 🟡 待落地（已登记 AssetID，文件未创建）/ 🟠 老形态（迁移完成后删除）。规范见 docs/v0.1/14.6_特效系统与制作规范.md。【2026-09-11 进度】FX01 战斗反馈 5 条 + FX02 受击飘字 2 条 共 7 条完成；FX03/04 已实装但命名待对齐。【2026-09-21 进度】新增 FX01-06 VFX-BULLET-VISUAL-3D（飞行子弹纯视觉，含 ProjectileLight，由 Projectile3D 持有、不进 VfxPool）；FX01-01 / FX01-02 升 v002 卡通重做（枪口新增 MuzzleLight、命中改按命中法线对齐）；三类共同验收 verify_combat_vfx_toon_v002。【2026-09-22 进度】新增 FX01-07 VFX-SHELL-CASING-3D：开火抛壳、重力落地、最多两次小弹跳后静止，接入 WeaponModel3D 与 VfxPool3D。。 【2026-10-13 进度】新增 8 个逐弹种专属弹体 Prefab（FX01-08..FX01-15，VFX-BULLET-{STANDARD,STICKY,BOUNCE,PIERCING,EXPLOSIVE,HOMING,BLACKHOLE,BALLOON}-3D），为 FX01-06 通用弹体的弹种专属变体：共享基类 VfxBulletBody3D（弹芯/外壳/尾迹/跟随灯分层），由 Projectile3D 依 visual_id 路由、随 ProjectilePool3D 回收，不进 VfxPool；专项验收 verify_bullet_vfx_profiles。</t>
         </is>
       </c>
     </row>
@@ -7205,50 +7237,724 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="52">
-      <c r="H25" s="101" t="n"/>
-      <c r="I25" s="51" t="n"/>
-      <c r="N25" s="51" t="n"/>
+    <row r="25" ht="66" customHeight="1" s="52">
+      <c r="A25" s="97" t="inlineStr">
+        <is>
+          <t>▼ 01 战斗反馈（续）· 子弹特效（FX01-06 系列）</t>
+        </is>
+      </c>
+      <c r="B25" s="98" t="n"/>
+      <c r="C25" s="98" t="n"/>
+      <c r="D25" s="98" t="n"/>
+      <c r="E25" s="98" t="n"/>
+      <c r="F25" s="98" t="n"/>
+      <c r="G25" s="98" t="n"/>
+      <c r="H25" s="98" t="n"/>
+      <c r="I25" s="98" t="n"/>
+      <c r="J25" s="98" t="n"/>
+      <c r="K25" s="98" t="n"/>
+      <c r="L25" s="98" t="n"/>
+      <c r="M25" s="98" t="n"/>
+      <c r="N25" s="98" t="n"/>
+      <c r="O25" s="98" t="n"/>
+      <c r="P25" s="99" t="n"/>
+      <c r="Q25" s="92" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="52">
-      <c r="H26" s="101" t="n"/>
-      <c r="I26" s="51" t="n"/>
-      <c r="N26" s="51" t="n"/>
+      <c r="A26" s="100" t="inlineStr">
+        <is>
+          <t>FX01-08</t>
+        </is>
+      </c>
+      <c r="B26" s="101" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-STANDARD-3D</t>
+        </is>
+      </c>
+      <c r="C26" s="51" t="inlineStr">
+        <is>
+          <t>标准子弹弹体与尾迹特效</t>
+        </is>
+      </c>
+      <c r="D26" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_standard_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="G26" s="51" t="inlineStr">
+        <is>
+          <t>中性基准弹体：细胶囊弹芯 + 柔和单锥尾迹，无任何元素附加物，不误导观感。</t>
+        </is>
+      </c>
+      <c r="H26" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBulletStandard3D.gd</t>
+        </is>
+      </c>
+      <c r="I26" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J26" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K26" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L26" s="51" t="inlineStr">
+        <is>
+          <t>弹芯胶囊 r=0.045/h=0.20；外壳 r=0.075/h=0.18；单锥尾迹 底0.055/长0.46；灯 energy1.15/range1.75m</t>
+        </is>
+      </c>
+      <c r="M26" s="51" t="inlineStr">
+        <is>
+          <t>原点=宿主原点（local position 保持 0，随 Projectile3D 变换）；朝向=弹体沿 local -Z，拖尾向 local +Z（身后）</t>
+        </is>
+      </c>
+      <c r="N26" s="51" t="inlineStr">
+        <is>
+          <t>玩家/敌人 标准子弹模块（mod_bullet_standard）</t>
+        </is>
+      </c>
+      <c r="O26" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P26" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q26" s="51" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_standard_root_top3d.tscn + 脚本=src/vfx/VfxBulletStandard3D.gd；根节点=VfxBulletStandard3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="52">
-      <c r="H27" s="101" t="n"/>
-      <c r="I27" s="51" t="n"/>
-      <c r="N27" s="51" t="n"/>
+      <c r="A27" s="100" t="inlineStr">
+        <is>
+          <t>FX01-09</t>
+        </is>
+      </c>
+      <c r="B27" s="101" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-STICKY-3D</t>
+        </is>
+      </c>
+      <c r="C27" s="51" t="inlineStr">
+        <is>
+          <t>黏黏弹附着与倒计时特效</t>
+        </is>
+      </c>
+      <c r="D27" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_sticky_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="G27" s="51" t="inlineStr">
+        <is>
+          <t>短粗黏稠弹体 + 滴落小珠尾迹（drip 动画），强调「附着」质感。</t>
+        </is>
+      </c>
+      <c r="H27" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBulletSticky3D.gd</t>
+        </is>
+      </c>
+      <c r="I27" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J27" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K27" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L27" s="51" t="inlineStr">
+        <is>
+          <t>弹芯胶囊 r=0.050/h=0.16；外壳 r=0.086/h=0.16；锥尾迹 底0.062/长0.34 + 3 滴落珠；灯 energy1.20/range1.80m</t>
+        </is>
+      </c>
+      <c r="M27" s="51" t="inlineStr">
+        <is>
+          <t>原点=宿主原点（local position 保持 0，随 Projectile3D 变换）；朝向=弹体沿 local -Z，拖尾向 local +Z（身后）</t>
+        </is>
+      </c>
+      <c r="N27" s="51" t="inlineStr">
+        <is>
+          <t>玩家/敌人 黏黏弹模块（mod_bullet_sticky）</t>
+        </is>
+      </c>
+      <c r="O27" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P27" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q27" s="51" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_sticky_root_top3d.tscn + 脚本=src/vfx/VfxBulletSticky3D.gd；根节点=VfxBulletSticky3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="52">
-      <c r="H28" s="101" t="n"/>
-      <c r="I28" s="51" t="n"/>
-      <c r="N28" s="51" t="n"/>
+      <c r="A28" s="100" t="inlineStr">
+        <is>
+          <t>FX01-10</t>
+        </is>
+      </c>
+      <c r="B28" s="101" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-BOUNCE-3D</t>
+        </is>
+      </c>
+      <c r="C28" s="51" t="inlineStr">
+        <is>
+          <t>回旋镖弹反弹折线与计数特效</t>
+        </is>
+      </c>
+      <c r="D28" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_bounce_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="G28" s="51" t="inlineStr">
+        <is>
+          <t>圆润弹体 + 三段左右错位的折线尾迹，方向变化一眼可读。</t>
+        </is>
+      </c>
+      <c r="H28" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBulletBounce3D.gd</t>
+        </is>
+      </c>
+      <c r="I28" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J28" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K28" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L28" s="51" t="inlineStr">
+        <is>
+          <t>弹芯胶囊 r=0.048/h=0.14；外壳 r=0.072/h=0.13；三段折线锥 底0.052/0.040/0.030；灯 energy1.20/range1.80m</t>
+        </is>
+      </c>
+      <c r="M28" s="51" t="inlineStr">
+        <is>
+          <t>原点=宿主原点（local position 保持 0，随 Projectile3D 变换）；朝向=弹体沿 local -Z，拖尾向 local +Z（身后）</t>
+        </is>
+      </c>
+      <c r="N28" s="51" t="inlineStr">
+        <is>
+          <t>玩家/敌人 回旋镖弹模块（mod_bullet_bounce）</t>
+        </is>
+      </c>
+      <c r="O28" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P28" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q28" s="51" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_bounce_root_top3d.tscn + 脚本=src/vfx/VfxBulletBounce3D.gd；根节点=VfxBulletBounce3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="52">
-      <c r="H29" s="101" t="n"/>
-      <c r="I29" s="51" t="n"/>
-      <c r="N29" s="51" t="n"/>
+      <c r="A29" s="100" t="inlineStr">
+        <is>
+          <t>FX01-11</t>
+        </is>
+      </c>
+      <c r="B29" s="101" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-PIERCING-3D</t>
+        </is>
+      </c>
+      <c r="C29" s="51" t="inlineStr">
+        <is>
+          <t>穿甲弹贯穿线与层数特效</t>
+        </is>
+      </c>
+      <c r="D29" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_piercing_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="G29" s="51" t="inlineStr">
+        <is>
+          <t>细长针形弹体 + 细长双段贯穿尾迹，笔直的贯穿感。</t>
+        </is>
+      </c>
+      <c r="H29" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBulletPiercing3D.gd</t>
+        </is>
+      </c>
+      <c r="I29" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J29" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K29" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L29" s="51" t="inlineStr">
+        <is>
+          <t>弹芯胶囊 r=0.028/h=0.30；外壳 r=0.044/h=0.28；两段针形尾迹 底0.036/0.022；灯 energy1.35/range1.95m</t>
+        </is>
+      </c>
+      <c r="M29" s="51" t="inlineStr">
+        <is>
+          <t>原点=宿主原点（local position 保持 0，随 Projectile3D 变换）；朝向=弹体沿 local -Z，拖尾向 local +Z（身后）</t>
+        </is>
+      </c>
+      <c r="N29" s="51" t="inlineStr">
+        <is>
+          <t>玩家/敌人 穿甲弹模块（mod_bullet_piercing）</t>
+        </is>
+      </c>
+      <c r="O29" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P29" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q29" s="51" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_piercing_root_top3d.tscn + 脚本=src/vfx/VfxBulletPiercing3D.gd；根节点=VfxBulletPiercing3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="52">
-      <c r="H30" s="101" t="n"/>
-      <c r="I30" s="51" t="n"/>
-      <c r="N30" s="51" t="n"/>
+      <c r="A30" s="100" t="inlineStr">
+        <is>
+          <t>FX01-12</t>
+        </is>
+      </c>
+      <c r="B30" s="101" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-EXPLOSIVE-3D</t>
+        </is>
+      </c>
+      <c r="C30" s="51" t="inlineStr">
+        <is>
+          <t>爆炸弹弹体与爆炸时点特效</t>
+        </is>
+      </c>
+      <c r="D30" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_explosive_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="G30" s="51" t="inlineStr">
+        <is>
+          <t>粗壮弹体 + 带飞散火星的锥尾迹（flicker 动画），体积感与弹重匹配。</t>
+        </is>
+      </c>
+      <c r="H30" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBulletExplosive3D.gd</t>
+        </is>
+      </c>
+      <c r="I30" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J30" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K30" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L30" s="51" t="inlineStr">
+        <is>
+          <t>弹芯胶囊 r=0.055/h=0.22；外壳 r=0.094/h=0.20；锥尾迹 底0.078/长0.40 + 3 火星条；灯 energy1.65/range2.40m</t>
+        </is>
+      </c>
+      <c r="M30" s="51" t="inlineStr">
+        <is>
+          <t>原点=宿主原点（local position 保持 0，随 Projectile3D 变换）；朝向=弹体沿 local -Z，拖尾向 local +Z（身后）</t>
+        </is>
+      </c>
+      <c r="N30" s="51" t="inlineStr">
+        <is>
+          <t>玩家/敌人 爆炸弹模块（mod_bullet_explosive）</t>
+        </is>
+      </c>
+      <c r="O30" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P30" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q30" s="51" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_explosive_root_top3d.tscn + 脚本=src/vfx/VfxBulletExplosive3D.gd；根节点=VfxBulletExplosive3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="52">
-      <c r="H31" s="101" t="n"/>
-      <c r="I31" s="51" t="n"/>
-      <c r="N31" s="51" t="n"/>
+      <c r="A31" s="100" t="inlineStr">
+        <is>
+          <t>FX01-13</t>
+        </is>
+      </c>
+      <c r="B31" s="101" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-HOMING-3D</t>
+        </is>
+      </c>
+      <c r="C31" s="51" t="inlineStr">
+        <is>
+          <t>蜂卵弹锁定框与弯曲尾迹特效</t>
+        </is>
+      </c>
+      <c r="D31" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_homing_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="G31" s="51" t="inlineStr">
+        <is>
+          <t>椭圆蜂卵弹体 + 向两侧摆动的弯曲尾迹（wave 动画），读得出「在追」。</t>
+        </is>
+      </c>
+      <c r="H31" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBulletHoming3D.gd</t>
+        </is>
+      </c>
+      <c r="I31" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J31" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K31" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L31" s="51" t="inlineStr">
+        <is>
+          <t>弹芯胶囊 r=0.050/h=0.18；外壳 r=0.082/h=0.16；三段摆动尾迹；灯 energy1.25/range1.90m</t>
+        </is>
+      </c>
+      <c r="M31" s="51" t="inlineStr">
+        <is>
+          <t>原点=宿主原点（local position 保持 0，随 Projectile3D 变换）；朝向=弹体沿 local -Z，拖尾向 local +Z（身后）</t>
+        </is>
+      </c>
+      <c r="N31" s="51" t="inlineStr">
+        <is>
+          <t>玩家/敌人 蜂卵弹模块（mod_bullet_homing）</t>
+        </is>
+      </c>
+      <c r="O31" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P31" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q31" s="51" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_homing_root_top3d.tscn + 脚本=src/vfx/VfxBulletHoming3D.gd；根节点=VfxBulletHoming3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="52">
-      <c r="H32" s="101" t="n"/>
-      <c r="I32" s="51" t="n"/>
-      <c r="N32" s="51" t="n"/>
+      <c r="A32" s="100" t="inlineStr">
+        <is>
+          <t>FX01-14</t>
+        </is>
+      </c>
+      <c r="B32" s="101" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-BLACKHOLE-3D</t>
+        </is>
+      </c>
+      <c r="C32" s="51" t="inlineStr">
+        <is>
+          <t>黑洞弹核心与吸入流线特效</t>
+        </is>
+      </c>
+      <c r="D32" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_blackhole_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="G32" s="51" t="inlineStr">
+        <is>
+          <t>暗核球形 + 紫光环 + 外扩喇叭尾迹（spin 旋转），读得出「在吸」。</t>
+        </is>
+      </c>
+      <c r="H32" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBulletBlackhole3D.gd</t>
+        </is>
+      </c>
+      <c r="I32" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J32" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K32" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L32" s="51" t="inlineStr">
+        <is>
+          <t>弹芯球 r=0.058；外壳球 r=0.098；外扩喇叭三段 底0.040/0.068/0.096；灯 energy1.45/range2.20m</t>
+        </is>
+      </c>
+      <c r="M32" s="51" t="inlineStr">
+        <is>
+          <t>原点=宿主原点（local position 保持 0，随 Projectile3D 变换）；朝向=弹体沿 local -Z，拖尾向 local +Z（身后）</t>
+        </is>
+      </c>
+      <c r="N32" s="51" t="inlineStr">
+        <is>
+          <t>玩家/敌人 黑洞弹模块（mod_bullet_blackhole）</t>
+        </is>
+      </c>
+      <c r="O32" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P32" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q32" s="51" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_blackhole_root_top3d.tscn + 脚本=src/vfx/VfxBulletBlackhole3D.gd；根节点=VfxBulletBlackhole3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="52">
-      <c r="H33" s="101" t="n"/>
-      <c r="I33" s="51" t="n"/>
-      <c r="N33" s="51" t="n"/>
+      <c r="A33" s="100" t="inlineStr">
+        <is>
+          <t>FX01-15</t>
+        </is>
+      </c>
+      <c r="B33" s="101" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-BALLOON-3D</t>
+        </is>
+      </c>
+      <c r="C33" s="51" t="inlineStr">
+        <is>
+          <t>气球弹膨胀弹体与命中体积特效</t>
+        </is>
+      </c>
+      <c r="D33" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_bullet_balloon_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="G33" s="51" t="inlineStr">
+        <is>
+          <t>大球体弹体 + 粗短厚重尾迹，并支持 apply_growth 继续膨胀。</t>
+        </is>
+      </c>
+      <c r="H33" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBulletBalloon3D.gd</t>
+        </is>
+      </c>
+      <c r="I33" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J33" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K33" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L33" s="51" t="inlineStr">
+        <is>
+          <t>弹芯球 r=0.070；外壳球 r=0.118；粗短锥尾迹 底0.104/长0.36；灯 energy1.30/range2.05m</t>
+        </is>
+      </c>
+      <c r="M33" s="51" t="inlineStr">
+        <is>
+          <t>原点=宿主原点（local position 保持 0，随 Projectile3D 变换）；朝向=弹体沿 local -Z，拖尾向 local +Z（身后）</t>
+        </is>
+      </c>
+      <c r="N33" s="51" t="inlineStr">
+        <is>
+          <t>玩家/敌人 气球弹模块（mod_bullet_balloon）</t>
+        </is>
+      </c>
+      <c r="O33" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P33" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q33" s="51" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_balloon_root_top3d.tscn + 脚本=src/vfx/VfxBulletBalloon3D.gd；根节点=VfxBulletBalloon3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="52">
       <c r="H34" s="101" t="n"/>
@@ -8366,7 +9072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="51" min="1" max="1"/>
@@ -8971,6 +9677,43 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="46" customHeight="1" s="52">
+      <c r="A21" s="51" t="inlineStr">
+        <is>
+          <t>v0.1.15</t>
+        </is>
+      </c>
+      <c r="B21" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C21" s="51" t="inlineStr">
+        <is>
+          <t>条目更新（待制作 → 已完成）+ 新增 Prefab</t>
+        </is>
+      </c>
+      <c r="D21" s="51" t="inlineStr">
+        <is>
+          <t>特效 · 子弹特效</t>
+        </is>
+      </c>
+      <c r="E21" s="51" t="inlineStr">
+        <is>
+          <t>把 8 个弹种专属弹体特效（VFX-BULLET-{STANDARD,STICKY,BOUNCE,PIERCING,EXPLOSIVE,HOMING,BLACKHOLE,BALLOON}-3D）从「待制作」推进到「已完成」：《3D-特效》分页登记 8 个实际存在的 PackedScene（FX01-08..FX01-15，为 FX01-06 通用弹体 VFX-BULLET-VISUAL-3D 的弹种专属变体）；《资产主表》逐行回填 O 列路径、T 列 SHA-256，K 列推进「已完成」并同步 N 规格/U 负责人/V 更新时间/W 来源。实现：共享基类 src/vfx/VfxBulletBody3D.gd 提供弹芯（胶囊/球）/外壳（弹色半透明）/尾迹（锥段/小珠/火星条）/跟随灯四层，8 个子类只覆写 _bullet_profile() 声明弹体形态、配色、尾迹构图与灯参数；由 Projectile3D 依 visual_id 经 BULLET_VISUAL_REGISTRY 路由为子节点持有，随 ProjectilePool3D 回收，刻意不进 VfxPool3D（避免弹体池与特效池双重 ownership）。专项验收 verify_bullet_vfx_profiles。</t>
+        </is>
+      </c>
+      <c r="F21" s="51" t="inlineStr">
+        <is>
+          <t>稳定 AssetID 全部保持不变（r27..r34 的 AssetID/子类/逻辑ID 逐格不变）；新增 8 个 Prefab 路径与哈希；O 列由「待定」变为去版本化运行路径（无 _vNNN），版本仍锁在 Prefab 根 meta asset_version=v001 与账本 M 列；纯视觉无碰撞体、不含玩法行为，运行时调用方式（AssetID/visual_id 路由）为向后兼容增强。</t>
+        </is>
+      </c>
+      <c r="G21" s="51" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3D-特效" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$34</definedName>
@@ -1441,22 +1441,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="52">
       <c r="A6" s="57">
-        <f>COUNTA('资产主表'!$A$6:$A$34)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$37)</f>
         <v/>
       </c>
       <c r="B6" s="55" t="n"/>
       <c r="C6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$34,"已完成")+COUNTIF('资产主表'!$K$6:$K$34,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$34,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$34,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$34,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$34,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$34,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$37,"已完成")+COUNTIF('资产主表'!$K$6:$K$37,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$37,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$37,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$37,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$37,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$37,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="55" t="n"/>
       <c r="E6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$34,"待制作")+COUNTIF('资产主表'!$K$6:$K$34,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$37,"待制作")+COUNTIF('资产主表'!$K$6:$K$37,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="55" t="n"/>
       <c r="G6" s="57">
-        <f>COUNTIF('资产主表'!$S$6:$S$34,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$37,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="55" t="n"/>
@@ -1525,11 +1525,11 @@
         </is>
       </c>
       <c r="B10" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$34,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$37,A10)</f>
         <v/>
       </c>
       <c r="C10" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$34=A10)*(('资产主表'!$K$6:$K$34="已完成")+('资产主表'!$K$6:$K$34="原型已接入")+('资产主表'!$K$6:$K$34="正式美术已接入")+('资产主表'!$K$6:$K$34="已优化并正式接入")+('资产主表'!$K$6:$K$34="Blender源已完成")+('资产主表'!$K$6:$K$34="已导入；优化完成")+('资产主表'!$K$6:$K$34="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$37=A10)*(('资产主表'!$K$6:$K$37="已完成")+('资产主表'!$K$6:$K$37="原型已接入")+('资产主表'!$K$6:$K$37="正式美术已接入")+('资产主表'!$K$6:$K$37="已优化并正式接入")+('资产主表'!$K$6:$K$37="Blender源已完成")+('资产主表'!$K$6:$K$37="已导入；优化完成")+('资产主表'!$K$6:$K$37="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="62" t="n"/>
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="B11" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$34,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$37,A11)</f>
         <v/>
       </c>
       <c r="C11" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$34=A11)*(('资产主表'!$K$6:$K$34="已完成")+('资产主表'!$K$6:$K$34="原型已接入")+('资产主表'!$K$6:$K$34="正式美术已接入")+('资产主表'!$K$6:$K$34="已优化并正式接入")+('资产主表'!$K$6:$K$34="Blender源已完成")+('资产主表'!$K$6:$K$34="已导入；优化完成")+('资产主表'!$K$6:$K$34="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$37=A11)*(('资产主表'!$K$6:$K$37="已完成")+('资产主表'!$K$6:$K$37="原型已接入")+('资产主表'!$K$6:$K$37="正式美术已接入")+('资产主表'!$K$6:$K$37="已优化并正式接入")+('资产主表'!$K$6:$K$37="Blender源已完成")+('资产主表'!$K$6:$K$37="已导入；优化完成")+('资产主表'!$K$6:$K$37="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="62" t="n"/>
@@ -2109,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y34"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="51" min="1" max="1"/>
@@ -2381,7 +2381,7 @@
         <v/>
       </c>
       <c r="S6" s="63">
-        <f>IF(COUNTIF($R$6:$R$34,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="63" t="n"/>
@@ -2484,7 +2484,7 @@
         <v/>
       </c>
       <c r="S7" s="63">
-        <f>IF(COUNTIF($R$6:$R$34,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="63" t="n"/>
@@ -2587,7 +2587,7 @@
         <v/>
       </c>
       <c r="S8" s="63">
-        <f>IF(COUNTIF($R$6:$R$34,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="63" t="n"/>
@@ -2690,7 +2690,7 @@
         <v/>
       </c>
       <c r="S9" s="63">
-        <f>IF(COUNTIF($R$6:$R$34,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="63" t="n"/>
@@ -2797,7 +2797,7 @@
         <v/>
       </c>
       <c r="S10" s="63">
-        <f>IF(COUNTIF($R$6:$R$34,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="63" t="n"/>
@@ -2904,7 +2904,7 @@
         <v/>
       </c>
       <c r="S11" s="63">
-        <f>IF(COUNTIF($R$6:$R$34,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="63" t="n"/>
@@ -3011,7 +3011,7 @@
         <v/>
       </c>
       <c r="S12" s="63">
-        <f>IF(COUNTIF($R$6:$R$34,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="63" t="n"/>
@@ -3118,7 +3118,7 @@
         <v/>
       </c>
       <c r="S13" s="63">
-        <f>IF(COUNTIF($R$6:$R$34,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="63" t="n"/>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="S14" s="63">
-        <f>IF(COUNTIF($R$6:$R$34,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="63" t="n"/>
@@ -3332,7 +3332,7 @@
         <v/>
       </c>
       <c r="S15" s="63">
-        <f>IF(COUNTIF($R$6:$R$34,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="63" t="n"/>
@@ -3439,7 +3439,7 @@
         <v/>
       </c>
       <c r="S16" s="63">
-        <f>IF(COUNTIF($R$6:$R$34,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="63" t="n"/>
@@ -3558,7 +3558,7 @@
         <v/>
       </c>
       <c r="S17" s="55">
-        <f>IF(COUNTIF($R$6:$R$34,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="79" t="inlineStr">
@@ -3677,7 +3677,7 @@
         <v/>
       </c>
       <c r="S18" s="55">
-        <f>IF(COUNTIF($R$6:$R$34,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="79" t="inlineStr">
@@ -3800,7 +3800,7 @@
         <v/>
       </c>
       <c r="S19" s="55">
-        <f>IF(COUNTIF($R$6:$R$34,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="79" t="inlineStr">
@@ -3924,7 +3924,7 @@
         <v/>
       </c>
       <c r="S20" s="55">
-        <f>IF(COUNTIF($R$6:$R$34,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="79" t="inlineStr">
@@ -4040,7 +4040,7 @@
         <v/>
       </c>
       <c r="S21" s="55">
-        <f>IF(COUNTIF($R$6:$R$34,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="79" t="inlineStr">
@@ -4159,7 +4159,7 @@
         <v/>
       </c>
       <c r="S22" s="55">
-        <f>IF(COUNTIF($R$6:$R$34,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="79" t="inlineStr">
@@ -4278,7 +4278,7 @@
         <v/>
       </c>
       <c r="S23" s="55">
-        <f>IF(COUNTIF($R$6:$R$34,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="79" t="inlineStr">
@@ -4397,7 +4397,7 @@
         <v/>
       </c>
       <c r="S24" s="55">
-        <f>IF(COUNTIF($R$6:$R$34,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="79" t="inlineStr">
@@ -4516,7 +4516,7 @@
         <v/>
       </c>
       <c r="S25" s="55">
-        <f>IF(COUNTIF($R$6:$R$34,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="79" t="inlineStr">
@@ -4635,7 +4635,7 @@
         <v/>
       </c>
       <c r="S26" s="79">
-        <f>IF(COUNTIF($R$6:$R$34,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="79" t="inlineStr">
@@ -4760,7 +4760,7 @@
         <v/>
       </c>
       <c r="S27" s="76">
-        <f>IF(COUNTIF($R$6:$R$34,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="76" t="inlineStr">
@@ -4881,7 +4881,7 @@
         <v/>
       </c>
       <c r="S28" s="76">
-        <f>IF(COUNTIF($R$6:$R$34,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="76" t="inlineStr">
@@ -5002,7 +5002,7 @@
         <v/>
       </c>
       <c r="S29" s="76">
-        <f>IF(COUNTIF($R$6:$R$34,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="76" t="inlineStr">
@@ -5123,7 +5123,7 @@
         <v/>
       </c>
       <c r="S30" s="76">
-        <f>IF(COUNTIF($R$6:$R$34,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="76" t="inlineStr">
@@ -5244,7 +5244,7 @@
         <v/>
       </c>
       <c r="S31" s="76">
-        <f>IF(COUNTIF($R$6:$R$34,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="76" t="inlineStr">
@@ -5365,7 +5365,7 @@
         <v/>
       </c>
       <c r="S32" s="76">
-        <f>IF(COUNTIF($R$6:$R$34,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="76" t="inlineStr">
@@ -5486,7 +5486,7 @@
         <v/>
       </c>
       <c r="S33" s="76">
-        <f>IF(COUNTIF($R$6:$R$34,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="76" t="inlineStr">
@@ -5607,7 +5607,7 @@
         <v/>
       </c>
       <c r="S34" s="76">
-        <f>IF(COUNTIF($R$6:$R$34,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$37,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="76" t="inlineStr">
@@ -5634,6 +5634,367 @@
       <c r="Y34" s="76" t="inlineStr">
         <is>
           <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_balloon_root_top3d.tscn + 脚本=src/vfx/VfxBulletBalloon3D.gd；根节点=VfxBulletBalloon3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S11「膨胀弹体、较重尾迹与命中体积一致，不能只改伤害数值」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="931.3" customHeight="1" s="52">
+      <c r="A35" s="76" t="inlineStr">
+        <is>
+          <t>VFX-MONSTER-ROAR-ICON-3D</t>
+        </is>
+      </c>
+      <c r="B35" s="76" t="inlineStr">
+        <is>
+          <t>怪物启动吼叫头顶图标</t>
+        </is>
+      </c>
+      <c r="C35" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D35" s="76" t="inlineStr">
+        <is>
+          <t>战斗反馈</t>
+        </is>
+      </c>
+      <c r="E35" s="76" t="inlineStr">
+        <is>
+          <t>FX01-16</t>
+        </is>
+      </c>
+      <c r="F35" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G35" s="76" t="n"/>
+      <c r="H35" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I35" s="76" t="inlineStr">
+        <is>
+          <t>startup_roar_icon</t>
+        </is>
+      </c>
+      <c r="J35" s="76" t="inlineStr">
+        <is>
+          <t>普通怪/精英（Boss 豁免）</t>
+        </is>
+      </c>
+      <c r="K35" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L35" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M35" s="76" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="N35" s="76" t="inlineStr">
+        <is>
+          <t>PackedScene/程序 Sprite3D（256² RGBA 透明底贴图；世界边长 = 头顶血条宽 × 0.42，钳制 0.45–1.20 m）</t>
+        </is>
+      </c>
+      <c r="O35" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_monster_roar_icon_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P35" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxMonsterRoarIcon3D.gd; src/enemy3d/MonsterStartupProfile.gd</t>
+        </is>
+      </c>
+      <c r="Q35" s="76" t="inlineStr">
+        <is>
+          <t>吼叫;咆哮;启动过程;警觉;头顶图标;体型匹配;roar;startup;3D-icon</t>
+        </is>
+      </c>
+      <c r="R35" s="76">
+        <f>LOWER(TRIM(C35)&amp;"|"&amp;TRIM(D35)&amp;"|"&amp;TRIM(E35)&amp;"|"&amp;TRIM(F35)&amp;"|"&amp;TRIM(H35)&amp;"|"&amp;TRIM(I35))</f>
+        <v/>
+      </c>
+      <c r="S35" s="76">
+        <f>IF(COUNTIF($R$6:$R$37,R35)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T35" s="76" t="inlineStr">
+        <is>
+          <t>f89109188bae4361cda58cb8c866e3c4d91b9eff4cd2b5259810e5830f4dc403</t>
+        </is>
+      </c>
+      <c r="U35" s="76" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V35" s="77" t="n">
+        <v>46309</v>
+      </c>
+      <c r="W35" s="76" t="inlineStr">
+        <is>
+          <t>原创程序几何/Sprite3D；卡通贴图为 gpt-image-2 绘制（四版迭代 v004 入选），原图留 art_source/vfx/combat_3d/vfx_monster_roar_icon/source/v001/</t>
+        </is>
+      </c>
+      <c r="X35" s="76" t="inlineStr">
+        <is>
+          <t>FX01-16</t>
+        </is>
+      </c>
+      <c r="Y35" s="76" t="inlineStr">
+        <is>
+          <t>怪物从 idle/patrol 进入攻击前的 0.30–0.60s 启动过程里，转向玩家之后头顶弹出的一次性提示。**2026-10-14 改版 v002（业主指定）**：① 图形由「怪兽大嘴」换成**红色感叹号**（整支统一纯红 #FD0104，粗黑描边保留，青色高光已去掉）；② **增加「弹出后停顿一下」的节奏** —— 四段：① 弹出 0.70→1.15（t=0.10 过冲）② 回稳 →1.00（t=0.18）③ **停顿：0.18→hold 全程严格静止** ④ 淡出。实测三段停顿 scale 逐位相同（0.7031/0.7031/0.7031），由 `verify_monster_startup_roar` 钉住；③ 图标与血条的间隙由「固定 0.12m」改为**按图标边长 0.30 的比例**（`ICON_BAR_GAP_RATIO`）—— 感叹号的圆点落在方框底部，固定米数会直接贴住血条（预览实测 elite/boss 档间隙 −1px 即重叠，改成比例后六档间隙 +4~+10px 等比）。贴图 `assets/art/vfx/textures/vfx_monster_roar_icon_atlas_v001.png`（256² RGBA 透明底，`gpt-image-2` 绘制，SHA-256 `8eaf880e2eb2be1e…`；三版迭代 v003 入选，原图留 `art_source/vfx/combat_3d/vfx_monster_roar_icon/source/v002/`）。尺寸仍**按体型等比**：`icon_edge = clamp(头顶血条宽 × 0.42, 0.45, 1.20)` m，偏移 `icon_offset_y = 血条高/2 + 0.30×icon_edge + icon_edge/2`；体型输入直接复用 `Enemy3D.HEALTH_BAR_SIZE_BY_KIND`（刻意不新建第二份体型表）。摆放与朝向复用头顶血条同族口径：`BILLBOARD_ENABLED` + 关闭深度测试；每怪一个常驻 Sprite3D 由怪物自身持有、随怪物创建销毁，**刻意不进 `VfxPool3D`**。⚠️ 死亡/硬直/房间停用/目标失效必须调 `dismiss()`，否则会出现「已死还在吼」的假信息。Boss 由 `MonsterStartupProfile.plays_startup()` 豁免。纯视觉无碰撞体。验收 `verify_monster_startup_roar`（samples=221，含停顿段「必须真静止」的正面判据与负向对照）。视觉证据：`outputs/monster_roar_icon_size_contact_sheet.png`（六档体型）、`outputs/monster_startup_capture.png`（真引擎三帧）、`outputs/monster_startup_capture_pop_rhythm.png`（弹出→停顿节奏取样条）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="76" t="inlineStr">
+        <is>
+          <t>VFX-DEATH-BLAST-3D</t>
+        </is>
+      </c>
+      <c r="B36" s="76" t="inlineStr">
+        <is>
+          <t>胖子僵尸死亡自爆特效</t>
+        </is>
+      </c>
+      <c r="C36" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D36" s="76" t="inlineStr">
+        <is>
+          <t>战斗反馈</t>
+        </is>
+      </c>
+      <c r="E36" s="76" t="inlineStr">
+        <is>
+          <t>FX01-17</t>
+        </is>
+      </c>
+      <c r="F36" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G36" s="76" t="n"/>
+      <c r="H36" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I36" s="76" t="inlineStr">
+        <is>
+          <t>death_blast</t>
+        </is>
+      </c>
+      <c r="J36" s="76" t="inlineStr">
+        <is>
+          <t>远征01 胖子僵尸死亡自爆</t>
+        </is>
+      </c>
+      <c r="K36" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L36" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M36" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N36" s="76" t="inlineStr">
+        <is>
+          <t>PackedScene/程序几何（亮芯 + 2 层冲击环 + 9 星芒 + 8 碎屑 + 1 盏 BlastLight；lifetime 0.62s；size 由规格半径 ×0.6 传入）</t>
+        </is>
+      </c>
+      <c r="O36" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_death_blast_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P36" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxDeathBlast3D.gd; src/enemy3d/Enemy3D.gd</t>
+        </is>
+      </c>
+      <c r="Q36" s="76" t="inlineStr">
+        <is>
+          <t>死亡自爆;胖子僵尸;爆炸;冲击环;星芒;BlastLight;death-blast</t>
+        </is>
+      </c>
+      <c r="R36" s="76">
+        <f>LOWER(TRIM(C36)&amp;"|"&amp;TRIM(D36)&amp;"|"&amp;TRIM(E36)&amp;"|"&amp;TRIM(F36)&amp;"|"&amp;TRIM(H36)&amp;"|"&amp;TRIM(I36))</f>
+        <v/>
+      </c>
+      <c r="S36" s="76">
+        <f>IF(COUNTIF($R$6:$R$37,R36)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T36" s="76" t="inlineStr">
+        <is>
+          <t>0b875db8cad687b62001f4775f800569603808996f70e8c497e63b0c5b7700bb</t>
+        </is>
+      </c>
+      <c r="U36" s="76" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V36" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="W36" s="76" t="inlineStr">
+        <is>
+          <t>原创/待确认</t>
+        </is>
+      </c>
+      <c r="X36" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y36" s="76" t="inlineStr">
+        <is>
+          <t>远征01 关卡级（不写该关 monster_rules.death_explosion 的关卡无本表现）。全向对称、不消费 context.forward/normal；纯视觉无碰撞体。尺寸由调用方按规格半径 ×0.6 传入（5.0m ⇒ size 3.0 ⇒ 内环≈4.75m / 外环≈5.29m）。专项验收 verify_death_blast_vfx。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BLAST-ZONE-3D</t>
+        </is>
+      </c>
+      <c r="B37" s="76" t="inlineStr">
+        <is>
+          <t>自爆地面残留伤害场</t>
+        </is>
+      </c>
+      <c r="C37" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D37" s="76" t="inlineStr">
+        <is>
+          <t>战斗反馈</t>
+        </is>
+      </c>
+      <c r="E37" s="76" t="inlineStr">
+        <is>
+          <t>FX01-18</t>
+        </is>
+      </c>
+      <c r="F37" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G37" s="76" t="n"/>
+      <c r="H37" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I37" s="76" t="inlineStr">
+        <is>
+          <t>lingering_hazard</t>
+        </is>
+      </c>
+      <c r="J37" s="76" t="inlineStr">
+        <is>
+          <t>远征01 胖子僵尸自爆地面残留</t>
+        </is>
+      </c>
+      <c r="K37" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L37" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M37" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N37" s="76" t="inlineStr">
+        <is>
+          <t>PackedScene/程序几何（场底面 + 外缘定环 + 3 脉冲环 + 6 上升余烬 + 1 盏 ZoneLight；lifetime = 场地持续时长，默认 3.0s）</t>
+        </is>
+      </c>
+      <c r="O37" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_blast_zone_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P37" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBlastZone3D.gd; src/enemy3d/DeathBlastZone3D.gd</t>
+        </is>
+      </c>
+      <c r="Q37" s="76" t="inlineStr">
+        <is>
+          <t>地面伤害场;持续伤害;自爆残留;范围伤害;3秒;blast-zone;ground-hazard</t>
+        </is>
+      </c>
+      <c r="R37" s="76">
+        <f>LOWER(TRIM(C37)&amp;"|"&amp;TRIM(D37)&amp;"|"&amp;TRIM(E37)&amp;"|"&amp;TRIM(F37)&amp;"|"&amp;TRIM(H37)&amp;"|"&amp;TRIM(I37))</f>
+        <v/>
+      </c>
+      <c r="S37" s="76">
+        <f>IF(COUNTIF($R$6:$R$37,R37)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T37" s="76" t="inlineStr">
+        <is>
+          <t>4345764d662753b126383e006b0027d3012be2d6a50cd094da955a9afc6cee6e</t>
+        </is>
+      </c>
+      <c r="U37" s="76" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V37" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="W37" s="76" t="inlineStr">
+        <is>
+          <t>原创/待确认</t>
+        </is>
+      </c>
+      <c r="X37" s="76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y37" s="76" t="inlineStr">
+        <is>
+          <t>**纯视觉**：不含碰撞体、不结算伤害；伤害由玩法节点 src/enemy3d/DeathBlastZone3D.gd 按周期处理。地面朝向契约：整件平铺 XZ，调用方在地面高度 activate 且不旋转。宿主自持、**刻意不进 VfxPool3D**（同 FX01-16 / FX03-03 口径）。专项验收 verify_death_blast_vfx。</t>
         </is>
       </c>
     </row>
@@ -5858,13 +6219,13 @@
     <cfRule type="containsText" priority="3" operator="containsText" dxfId="8" text="待制作"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,子弹特效,音效,音乐"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,design_only,authored,exported_pending_godot_validation,validated,active,已从运行场景移除,白盒组件"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5913,11 +6274,10 @@
     <row r="2" ht="33.75" customHeight="1" s="52">
       <c r="A2" s="83" t="inlineStr">
         <is>
-          <t>特效按独立 Prefab 原则：每个特效一个独立 .tscn；Prefab 是特效唯一出口；账本和调用代码读 Prefab。本 sheet 共 22 条，按 5 大类分组，每条 VFX 有内部编号 FX&lt;大类&gt;-&lt;序号&gt;。状态：✅ 完成（Prefab + 脚本 + 接入齐）/ 🟡 待落地（已登记 AssetID，文件未创建）/ 🟠 老形态（迁移完成后删除）。规范见 docs/v0.1/14.6_特效系统与制作规范.md。【2026-09-11 进度】FX01 战斗反馈 5 条 + FX02 受击飘字 2 条 共 7 条完成；FX03/04 已实装但命名待对齐。【2026-09-21 进度】新增 FX01-06 VFX-BULLET-VISUAL-3D（飞行子弹纯视觉，含 ProjectileLight，由 Projectile3D 持有、不进 VfxPool）；FX01-01 / FX01-02 升 v002 卡通重做（枪口新增 MuzzleLight、命中改按命中法线对齐）；三类共同验收 verify_combat_vfx_toon_v002。【2026-09-22 进度】新增 FX01-07 VFX-SHELL-CASING-3D：开火抛壳、重力落地、最多两次小弹跳后静止，接入 WeaponModel3D 与 VfxPool3D。。 【2026-10-13 进度】新增 8 个逐弹种专属弹体 Prefab（FX01-08..FX01-15，VFX-BULLET-{STANDARD,STICKY,BOUNCE,PIERCING,EXPLOSIVE,HOMING,BLACKHOLE,BALLOON}-3D），为 FX01-06 通用弹体的弹种专属变体：共享基类 VfxBulletBody3D（弹芯/外壳/尾迹/跟随灯分层），由 Projectile3D 依 visual_id 路由、随 ProjectilePool3D 回收，不进 VfxPool；专项验收 verify_bullet_vfx_profiles。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>特效按独立 Prefab 原则：每个特效一个独立 .tscn；Prefab 是特效唯一出口；账本和调用代码读 Prefab。本 sheet 共 25 条，按 5 大类分组，每条 VFX 有内部编号 FX&lt;大类&gt;-&lt;序号&gt;。状态：✅ 完成（Prefab + 脚本 + 接入齐）/ 🟡 待落地（已登记 AssetID，文件未创建）/ 🟠 老形态（迁移完成后删除）。规范见 docs/v0.1/14.6_特效系统与制作规范.md。【2026-09-11 进度】FX01 战斗反馈 5 条 + FX02 受击飘字 2 条 共 7 条完成；FX03/04 已实装但命名待对齐。【2026-09-21 进度】新增 FX01-06 VFX-BULLET-VISUAL-3D（飞行子弹纯视觉，含 ProjectileLight，由 Projectile3D 持有、不进 VfxPool）；FX01-01 / FX01-02 升 v002 卡通重做（枪口新增 MuzzleLight、命中改按命中法线对齐）；三类共同验收 verify_combat_vfx_toon_v002。【2026-09-22 进度】新增 FX01-07 VFX-SHELL-CASING-3D：开火抛壳、重力落地、最多两次小弹跳后静止，接入 WeaponModel3D 与 VfxPool3D。。 【2026-10-13 进度】新增 8 个逐弹种专属弹体 Prefab（FX01-08..FX01-15，VFX-BULLET-{STANDARD,STICKY,BOUNCE,PIERCING,EXPLOSIVE,HOMING,BLACKHOLE,BALLOON}-3D），为 FX01-06 通用弹体的弹种专属变体：共享基类 VfxBulletBody3D（弹芯/外壳/尾迹/跟随灯分层），由 Projectile3D 依 visual_id 路由、随 ProjectilePool3D 回收，不进 VfxPool；专项验收 verify_bullet_vfx_profiles。 【2026-10-14 进度】新增 FX01-16 VFX-MONSTER-ROAR-ICON-3D 怪物启动吼叫头顶图标：怪物从 idle/patrol 进攻击前的 0.30–0.60s 启动过程里，转向玩家后头顶弹出的一次性吼叫提示（业主设计，见 docs/v0.1/06A_怪物AI系统完整设计_评审稿.md §6.1.1）。独立 Prefab + 脚本 VfxMonsterRoarIcon3D + 256² RGBA 透明底贴图（gpt-image-2）。**尺寸按体型等比**：世界边长 = 该怪头顶血条宽 × 0.42，钳制 0.45–1.20m，公式真源 src/enemy3d/MonsterStartupProfile.gd。每怪常驻 Sprite3D 由怪物自身持有，刻意不进 VfxPool3D；Boss 豁免。专项验收 verify_monster_startup_roar。 【2026-10-14 进度】新增 FX01-17 VFX-DEATH-BLAST-3D 与 FX01-18 VFX-BLAST-ZONE-3D：远征01 胖子僵尸死亡自爆的**爆炸 + 地面残留伤害场**一整套（业主指定「自爆没有特效」+「地上留一个持续伤害的范围效果，持续3秒」）。爆炸走 VfxPool3D 路由；地面场由玩法节点 DeathBlastZone3D 宿主自持、刻意不进池。专项验收 verify_death_blast_vfx。【2026-10-14 改版】FX01-16 升 v002（业主指定）：图形改为**红色感叹号**，并新增**「弹出后停顿一下」**的节奏 —— ① 弹出 0.70→1.15（过冲）② 回稳 →1.00 ③ 停顿（严格静止）④ 淡出；图标-血条间隙由固定 0.12m 改为按图标边长 0.30 的比例。</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="84" t="inlineStr">
         <is>
@@ -7281,12 +7641,12 @@
           <t>assets/art/vfx/combat_3d/vfx_bullet_standard_root_top3d.tscn</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
@@ -7368,12 +7728,12 @@
           <t>assets/art/vfx/combat_3d/vfx_bullet_sticky_root_top3d.tscn</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
@@ -7455,12 +7815,12 @@
           <t>assets/art/vfx/combat_3d/vfx_bullet_bounce_root_top3d.tscn</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
@@ -7542,12 +7902,12 @@
           <t>assets/art/vfx/combat_3d/vfx_bullet_piercing_root_top3d.tscn</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
@@ -7629,12 +7989,12 @@
           <t>assets/art/vfx/combat_3d/vfx_bullet_explosive_root_top3d.tscn</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
@@ -7716,12 +8076,12 @@
           <t>assets/art/vfx/combat_3d/vfx_bullet_homing_root_top3d.tscn</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
@@ -7803,12 +8163,12 @@
           <t>assets/art/vfx/combat_3d/vfx_bullet_blackhole_root_top3d.tscn</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
@@ -7890,12 +8250,12 @@
           <t>assets/art/vfx/combat_3d/vfx_bullet_balloon_root_top3d.tscn</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="51" t="inlineStr">
         <is>
           <t>无（程序几何）</t>
         </is>
@@ -7956,30 +8316,312 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="52">
-      <c r="H34" s="101" t="n"/>
-      <c r="I34" s="51" t="n"/>
-      <c r="N34" s="51" t="n"/>
+    <row r="34" ht="66" customHeight="1" s="52">
+      <c r="A34" s="97" t="inlineStr">
+        <is>
+          <t>▼ 01 战斗反馈（续）· 怪物启动表现</t>
+        </is>
+      </c>
+      <c r="B34" s="98" t="n"/>
+      <c r="C34" s="98" t="n"/>
+      <c r="D34" s="98" t="n"/>
+      <c r="E34" s="98" t="n"/>
+      <c r="F34" s="98" t="n"/>
+      <c r="G34" s="98" t="n"/>
+      <c r="H34" s="98" t="n"/>
+      <c r="I34" s="98" t="n"/>
+      <c r="J34" s="98" t="n"/>
+      <c r="K34" s="98" t="n"/>
+      <c r="L34" s="98" t="n"/>
+      <c r="M34" s="98" t="n"/>
+      <c r="N34" s="98" t="n"/>
+      <c r="O34" s="98" t="n"/>
+      <c r="P34" s="99" t="n"/>
+      <c r="Q34" s="92" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="52">
-      <c r="H35" s="101" t="n"/>
-      <c r="I35" s="51" t="n"/>
-      <c r="N35" s="51" t="n"/>
+      <c r="A35" s="100" t="inlineStr">
+        <is>
+          <t>FX01-16</t>
+        </is>
+      </c>
+      <c r="B35" s="101" t="inlineStr">
+        <is>
+          <t>VFX-MONSTER-ROAR-ICON-3D</t>
+        </is>
+      </c>
+      <c r="C35" s="51" t="inlineStr">
+        <is>
+          <t>怪物启动吼叫头顶图标</t>
+        </is>
+      </c>
+      <c r="D35" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_monster_roar_icon_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E35" s="51" t="inlineStr">
+        <is>
+          <t>无（程序 Sprite3D + gpt-image-2 贴图）</t>
+        </is>
+      </c>
+      <c r="F35" s="51" t="inlineStr">
+        <is>
+          <t>无（贴图非 Blender 产物）</t>
+        </is>
+      </c>
+      <c r="G35" s="51" t="inlineStr">
+        <is>
+          <t>怪物启动过程的头顶吼叫提示：怪物从待机/巡游进入攻击前有 0.30–0.60s 随机启动过程，转向玩家后头顶弹出本图标（业主 2026-10-14 设计），随后才进入攻击。尺寸按体型等比：世界边长 = 该怪头顶血条宽 × 0.42，钳制 0.45–1.20 m，因此 8 档体型各不同（炸弹果 0.483m → Boss 1.113m）；公式真源 src/enemy3d/MonsterStartupProfile.gd。</t>
+        </is>
+      </c>
+      <c r="H35" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxMonsterRoarIcon3D.gd</t>
+        </is>
+      </c>
+      <c r="I35" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J35" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K35" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L35" s="51" t="inlineStr">
+        <is>
+          <t>原生贴图 256² × pixel_size 0.005 = 世界 1.28m/边；运行时按目标边长重算基准缩放（0.352–0.938）；弹出段 ×0.70→×1.08→×1.00；图标世界边长 0.483 / 0.580 / 0.651 / 0.756 / 0.861 / 1.113 m（对应 6 档体型）</t>
+        </is>
+      </c>
+      <c r="M35" s="51" t="inlineStr">
+        <is>
+          <t>原点=怪物头顶锚点上方（偏移 = 血条高/2 + 0.12 + 图标边长/2，相对头顶血条槽根）；朝向=BILLBOARD_ENABLED 永久朝向摄像机、关闭深度测试（不被怪物身体或墙挡住）</t>
+        </is>
+      </c>
+      <c r="N35" s="51" t="inlineStr">
+        <is>
+          <t>普通怪与唯一精英头顶（Boss 豁免）</t>
+        </is>
+      </c>
+      <c r="O35" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P35" s="101" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="Q35" s="51" t="inlineStr">
+        <is>
+          <t>已实装 v002（2026-10-14 业主指定改版）；Prefab=assets/art/vfx/combat_3d/vfx_monster_roar_icon_root_top3d.tscn；贴图=assets/art/vfx/textures/vfx_monster_roar_icon_atlas_v001.png；根节点=VfxMonsterRoarIcon3D(Node3D)；脚本=src/vfx/VfxMonsterRoarIcon3D.gd。**本次改版**：图形换为纯红感叹号；**新增「弹出后停顿」节奏** —— 四段 ① 弹出 0.70→1.15（过冲）② 回稳 →1.00 ③ **停顿：严格静止** ④ 淡出，停顿段实测 scale 逐位相同；图标与血条间隙改为按图标边长 0.30 的比例（原固定 0.12m 会贴住血条）。尺寸按体型等比（血条宽 × 0.42，钳制 0.45–1.20m），公式真源 src/enemy3d/MonsterStartupProfile.gd。归属：每怪常驻 Sprite3D 由怪物自身持有，**刻意不进 VfxPool3D**；提前退场 `dismiss()` 幂等；纯视觉无碰撞体。验收 verify_monster_startup_roar。设计见 docs/v0.1/06A_怪物AI系统完整设计_评审稿.md §6.1.1，施工见 06 §3.2。</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="52">
-      <c r="H36" s="101" t="n"/>
-      <c r="I36" s="51" t="n"/>
-      <c r="N36" s="51" t="n"/>
+      <c r="A36" s="97" t="inlineStr">
+        <is>
+          <t>▼ 01 战斗反馈（续）· 死亡自爆（远征01）</t>
+        </is>
+      </c>
+      <c r="B36" s="98" t="n"/>
+      <c r="C36" s="98" t="n"/>
+      <c r="D36" s="98" t="n"/>
+      <c r="E36" s="98" t="n"/>
+      <c r="F36" s="98" t="n"/>
+      <c r="G36" s="98" t="n"/>
+      <c r="H36" s="98" t="n"/>
+      <c r="I36" s="98" t="n"/>
+      <c r="J36" s="98" t="n"/>
+      <c r="K36" s="98" t="n"/>
+      <c r="L36" s="98" t="n"/>
+      <c r="M36" s="98" t="n"/>
+      <c r="N36" s="98" t="n"/>
+      <c r="O36" s="98" t="n"/>
+      <c r="P36" s="99" t="n"/>
+      <c r="Q36" s="92" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="52">
-      <c r="H37" s="101" t="n"/>
-      <c r="I37" s="51" t="n"/>
-      <c r="N37" s="51" t="n"/>
+      <c r="A37" s="100" t="inlineStr">
+        <is>
+          <t>FX01-17</t>
+        </is>
+      </c>
+      <c r="B37" s="101" t="inlineStr">
+        <is>
+          <t>VFX-DEATH-BLAST-3D</t>
+        </is>
+      </c>
+      <c r="C37" s="51" t="inlineStr">
+        <is>
+          <t>胖子僵尸死亡自爆特效</t>
+        </is>
+      </c>
+      <c r="D37" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_death_blast_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E37" s="51" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="F37" s="51" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="G37" s="51" t="inlineStr">
+        <is>
+          <t>远征01 胖子僵尸被打死瞬间的一次性爆炸视觉（业主 2026-10-14「胖子僵尸被打死后自爆没有特效，需要增加一个」）：SphereMesh 亮芯 + 2 层错峰冲击环（TorusMesh，环面躺在 XZ、读作地面冲击波）+ 9 道放射星芒（BoxMesh，Quaternion(UP,dir) 对齐水平放射、长短错峰）+ 8 块飞散碎屑（外抛 + 上抛弧线 + 自旋）+ 一盏 OmniLight3D（名 BlastLight，shadow_enabled=false）。**全向对称**，刻意不消费 context.forward / context.normal。经 VfxPool3D 按 AssetID 路由。</t>
+        </is>
+      </c>
+      <c r="H37" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxDeathBlast3D.gd</t>
+        </is>
+      </c>
+      <c r="I37" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J37" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K37" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L37" s="51" t="inlineStr">
+        <is>
+          <t>亮芯半径 0.18×size×(0.55→2.40)；冲击环外缘 0.72×size×(0.30→2.20 内环 / 0.20→2.45 外环)，size=3.0 时内环≈4.75m、外环≈5.29m；lifetime 0.62s；BlastLight range 6.0m×size、峰值 light_energy 9.0、寿命末端归零</t>
+        </is>
+      </c>
+      <c r="M37" s="51" t="inlineStr">
+        <is>
+          <t>原点=根节点中心；**无朝向契约（全向对称）**</t>
+        </is>
+      </c>
+      <c r="N37" s="51" t="inlineStr">
+        <is>
+          <t>远征01 胖子僵尸死亡自爆（Enemy3D._detonate_death_explosion）</t>
+        </is>
+      </c>
+      <c r="O37" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P37" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q37" s="51" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_death_blast_root_top3d.tscn + 脚本=src/vfx/VfxDeathBlast3D.gd；根节点=VfxDeathBlast3D(Node3D)；FX编号 FX01-17；调用方=Enemy3D._detonate_death_explosion（经 VfxPool3D.acquire(FX01_DEATH_BLAST, …)）；纯视觉无碰撞体；与 **FX01-18** 配对成「爆炸 + 地面残留」一整套；验收=verify_death_blast_vfx。</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="52">
-      <c r="H38" s="101" t="n"/>
-      <c r="I38" s="51" t="n"/>
-      <c r="N38" s="51" t="n"/>
+      <c r="A38" s="100" t="inlineStr">
+        <is>
+          <t>FX01-18</t>
+        </is>
+      </c>
+      <c r="B38" s="101" t="inlineStr">
+        <is>
+          <t>VFX-BLAST-ZONE-3D</t>
+        </is>
+      </c>
+      <c r="C38" s="51" t="inlineStr">
+        <is>
+          <t>自爆地面残留伤害场</t>
+        </is>
+      </c>
+      <c r="D38" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_blast_zone_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E38" s="51" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="F38" s="51" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="G38" s="51" t="inlineStr">
+        <is>
+          <t>自爆后**留在地上的持续伤害范围**的视觉层（业主 2026-10-14「在地上留一个持续伤害的范围效果，持续3秒」）：半透明场底面（CylinderMesh 薄片）+ 外缘定环（把杀伤边界钉死）+ 3 层错峰脉冲环 + 6 枚上升余烬 + 一盏 OmniLight3D（名 ZoneLight，shadow_enabled=false）。**纯视觉**：不含碰撞体、不结算伤害 —— 伤害由玩法节点 src/enemy3d/DeathBlastZone3D.gd 按周期处理。**地面朝向契约**：整件平铺在 XZ 平面，调用方在地面高度 activate 且不做任何旋转。</t>
+        </is>
+      </c>
+      <c r="H38" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBlastZone3D.gd</t>
+        </is>
+      </c>
+      <c r="I38" s="51" t="inlineStr">
+        <is>
+          <t>无（纯视觉；伤害在玩法节点结算）</t>
+        </is>
+      </c>
+      <c r="J38" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K38" s="51" t="inlineStr">
+        <is>
+          <t>无CollisionObject3D/CollisionShape3D</t>
+        </is>
+      </c>
+      <c r="L38" s="51" t="inlineStr">
+        <is>
+          <t>场底面半径 = size（＝规格半径）；外缘定环半径 = size；脉冲环 0.45→1.0×size；lifetime = context.zone_seconds（默认 3.0s）；ZoneLight range 4.5m×size、峰值 light_energy 3.4、寿命末端归零</t>
+        </is>
+      </c>
+      <c r="M38" s="51" t="inlineStr">
+        <is>
+          <t>原点=根节点中心（＝地面上的圆心）；朝向=**平铺 XZ，调用方不旋转**</t>
+        </is>
+      </c>
+      <c r="N38" s="51" t="inlineStr">
+        <is>
+          <t>远征01 胖子僵尸自爆地面残留（DeathBlastZone3D 子实例）</t>
+        </is>
+      </c>
+      <c r="O38" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P38" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q38" s="51" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_blast_zone_root_top3d.tscn + 脚本=src/vfx/VfxBlastZone3D.gd；根节点=VfxBlastZone3D(Node3D)；FX编号 FX01-18；**宿主自持、刻意不进 VfxPool3D**（生命周期归 DeathBlastZone3D，同 FX01-16 头顶图标、FX03-03 收音机音符口径）；AssetID 常量见 DeathBlastZone3D.ZONE_VFX_ASSET_ID；验收=verify_death_blast_vfx。</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="52">
       <c r="H39" s="101" t="n"/>
@@ -9072,7 +9714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="51" min="1" max="1"/>
@@ -9714,6 +10356,117 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="46" customHeight="1" s="52">
+      <c r="A22" s="51" t="inlineStr">
+        <is>
+          <t>v0.1.16</t>
+        </is>
+      </c>
+      <c r="B22" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C22" s="51" t="inlineStr">
+        <is>
+          <t>新增条目 + 新增 Prefab 分页</t>
+        </is>
+      </c>
+      <c r="D22" s="51" t="inlineStr">
+        <is>
+          <t>特效 · 资产主表 / 3D-特效</t>
+        </is>
+      </c>
+      <c r="E22" s="51" t="inlineStr">
+        <is>
+          <t>新增 FX01-16 VFX-MONSTER-ROAR-ICON-3D「怪物启动吼叫头顶图标」：怪物从待机/巡游进入攻击前的 0.30–0.60s 启动过程里，转向玩家后头顶弹出的一次性吼叫提示（业主 2026-10-14 设计，见 06A §6.1.1）。独立 Prefab + 脚本 + 256² RGBA 透明底贴图（gpt-image-2 绘制，四版迭代）。尺寸按体型等比（血条宽 × 0.42，钳制 0.45–1.20m），体型输入复用 Enemy3D.HEALTH_BAR_SIZE_BY_KIND。《总览》公式、DataValidation 与查重区间同步扩至新行；无损基线连带重建（3D-特效 摘要漂移）。</t>
+        </is>
+      </c>
+      <c r="F22" s="51" t="inlineStr">
+        <is>
+          <t>新增一个稳定 AssetID 与 Prefab 路径；既有条目的身份、路径、状态与哈希逐格保留；纯视觉无碰撞体、不含玩法行为，不进 VfxPool3D；Boss 豁免不叠加既有激活流程。</t>
+        </is>
+      </c>
+      <c r="G22" s="51" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" s="52">
+      <c r="A23" s="51" t="inlineStr">
+        <is>
+          <t>v0.1.17</t>
+        </is>
+      </c>
+      <c r="B23" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C23" s="51" t="inlineStr">
+        <is>
+          <t>新增条目 + 新增 Prefab 分页</t>
+        </is>
+      </c>
+      <c r="D23" s="51" t="inlineStr">
+        <is>
+          <t>特效 · 资产主表 / 3D-特效</t>
+        </is>
+      </c>
+      <c r="E23" s="51" t="inlineStr">
+        <is>
+          <t>新增 FX01-17 VFX-DEATH-BLAST-3D「胖子僵尸死亡自爆特效」与 FX01-18 VFX-BLAST-ZONE-3D「自爆地面残留伤害场」：前者是一次性爆炸视觉（亮芯 + 2 层冲击环 + 9 星芒 + 8 碎屑 + BlastLight，lifetime 0.62s），走 VfxPool3D 路由；后者是自爆后留在地上、持续 3 秒的持续伤害范围之**视觉层**（场底面 + 外缘定环 + 3 脉冲环 + 6 余烬 + ZoneLight），由玩法节点 DeathBlastZone3D 宿主自持、**刻意不进 VfxPool3D**。伤害结算（敌我通吃、同房过滤、首跳排在 tick_interval）在 src/enemy3d/DeathBlastZone3D.gd，规格落在远征01 monster_rules.death_explosion.fat_zombie03.zone。</t>
+        </is>
+      </c>
+      <c r="F23" s="51" t="inlineStr">
+        <is>
+          <t>新增两个稳定 AssetID 与 Prefab 路径；既有条目的身份、路径、状态与哈希逐格保留；两个 Prefab 均为纯视觉、无碰撞体、不含玩法逻辑；未配置 zone 段的关卡（塔楼等）逐行为 0。</t>
+        </is>
+      </c>
+      <c r="G23" s="51" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" s="52">
+      <c r="A24" s="51" t="inlineStr">
+        <is>
+          <t>v0.1.18</t>
+        </is>
+      </c>
+      <c r="B24" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C24" s="51" t="inlineStr">
+        <is>
+          <t>条目更新（改版升版）</t>
+        </is>
+      </c>
+      <c r="D24" s="51" t="inlineStr">
+        <is>
+          <t>特效 · 资产主表 / 3D-特效</t>
+        </is>
+      </c>
+      <c r="E24" s="51" t="inlineStr">
+        <is>
+          <t>FX01-16 VFX-MONSTER-ROAR-ICON-3D 改版 v002（业主 2026-10-14 指定）：① 图形由「怪兽大嘴」改为**红色感叹号**（整支统一纯红、粗黑描边、去掉青色高光）；② **新增「弹出后停顿一下」的动画节奏** ——① 弹出 0.70→1.15（t=0.10 过冲）② 回稳 →1.00（t=0.18）③ 停顿（0.18→hold 全程严格静止）④ 淡出，停顿段 scale 实测逐位相同；③ 图标与血条的间隙由固定 0.12m 改为**按图标边长 0.30 的比例**（感叹号圆点落在方框底部，固定米数会贴住血条，预览实测 elite/boss 档间隙 −1px 即重叠）。贴图重制（gpt-image-2 三版迭代），原图留 art_source/.../source/v002/。Prefab 路径与 SHA 未变；仅资产内容、版本与备注更新。</t>
+        </is>
+      </c>
+      <c r="F24" s="51" t="inlineStr">
+        <is>
+          <t>AssetID / Prefab 路径 / **Prefab SHA 均不变**（.tscn 未改）；仅资产版本升 v002 与备注更新，调用方式（AssetID 路由 + 每怪常驻 Sprite3D）不变；尺寸公式中「间隙」一项由常量改为比例，六档体型下的图标-血条间隙统一变为等比（+4~+10px），不遮挡血条。</t>
+        </is>
+      </c>
+      <c r="G24" s="51" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -603,7 +603,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -925,6 +925,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1441,22 +1447,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="52">
       <c r="A6" s="57">
-        <f>COUNTA('资产主表'!$A$6:$A$37)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$40)</f>
         <v/>
       </c>
       <c r="B6" s="55" t="n"/>
       <c r="C6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$37,"已完成")+COUNTIF('资产主表'!$K$6:$K$37,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$37,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$37,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$37,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$37,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$37,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$40,"已完成")+COUNTIF('资产主表'!$K$6:$K$40,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$40,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$40,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$40,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$40,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$40,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="55" t="n"/>
       <c r="E6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$37,"待制作")+COUNTIF('资产主表'!$K$6:$K$37,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$40,"待制作")+COUNTIF('资产主表'!$K$6:$K$40,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="55" t="n"/>
       <c r="G6" s="57">
-        <f>COUNTIF('资产主表'!$S$6:$S$37,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$40,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="55" t="n"/>
@@ -1525,11 +1531,11 @@
         </is>
       </c>
       <c r="B10" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$37,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$40,A10)</f>
         <v/>
       </c>
       <c r="C10" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$37=A10)*(('资产主表'!$K$6:$K$37="已完成")+('资产主表'!$K$6:$K$37="原型已接入")+('资产主表'!$K$6:$K$37="正式美术已接入")+('资产主表'!$K$6:$K$37="已优化并正式接入")+('资产主表'!$K$6:$K$37="Blender源已完成")+('资产主表'!$K$6:$K$37="已导入；优化完成")+('资产主表'!$K$6:$K$37="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$40=A10)*(('资产主表'!$K$6:$K$40="已完成")+('资产主表'!$K$6:$K$40="原型已接入")+('资产主表'!$K$6:$K$40="正式美术已接入")+('资产主表'!$K$6:$K$40="已优化并正式接入")+('资产主表'!$K$6:$K$40="Blender源已完成")+('资产主表'!$K$6:$K$40="已导入；优化完成")+('资产主表'!$K$6:$K$40="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="62" t="n"/>
@@ -1547,11 +1553,11 @@
         </is>
       </c>
       <c r="B11" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$37,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$40,A11)</f>
         <v/>
       </c>
       <c r="C11" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$37=A11)*(('资产主表'!$K$6:$K$37="已完成")+('资产主表'!$K$6:$K$37="原型已接入")+('资产主表'!$K$6:$K$37="正式美术已接入")+('资产主表'!$K$6:$K$37="已优化并正式接入")+('资产主表'!$K$6:$K$37="Blender源已完成")+('资产主表'!$K$6:$K$37="已导入；优化完成")+('资产主表'!$K$6:$K$37="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$40=A11)*(('资产主表'!$K$6:$K$40="已完成")+('资产主表'!$K$6:$K$40="原型已接入")+('资产主表'!$K$6:$K$40="正式美术已接入")+('资产主表'!$K$6:$K$40="已优化并正式接入")+('资产主表'!$K$6:$K$40="Blender源已完成")+('资产主表'!$K$6:$K$40="已导入；优化完成")+('资产主表'!$K$6:$K$40="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="62" t="n"/>
@@ -2109,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y37"/>
+  <dimension ref="A1:Y40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="51" min="1" max="1"/>
@@ -2381,7 +2387,7 @@
         <v/>
       </c>
       <c r="S6" s="63">
-        <f>IF(COUNTIF($R$6:$R$37,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="63" t="n"/>
@@ -2484,7 +2490,7 @@
         <v/>
       </c>
       <c r="S7" s="63">
-        <f>IF(COUNTIF($R$6:$R$37,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="63" t="n"/>
@@ -2587,7 +2593,7 @@
         <v/>
       </c>
       <c r="S8" s="63">
-        <f>IF(COUNTIF($R$6:$R$37,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="63" t="n"/>
@@ -2690,7 +2696,7 @@
         <v/>
       </c>
       <c r="S9" s="63">
-        <f>IF(COUNTIF($R$6:$R$37,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="63" t="n"/>
@@ -2797,7 +2803,7 @@
         <v/>
       </c>
       <c r="S10" s="63">
-        <f>IF(COUNTIF($R$6:$R$37,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="63" t="n"/>
@@ -2904,7 +2910,7 @@
         <v/>
       </c>
       <c r="S11" s="63">
-        <f>IF(COUNTIF($R$6:$R$37,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="63" t="n"/>
@@ -3011,7 +3017,7 @@
         <v/>
       </c>
       <c r="S12" s="63">
-        <f>IF(COUNTIF($R$6:$R$37,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="63" t="n"/>
@@ -3118,7 +3124,7 @@
         <v/>
       </c>
       <c r="S13" s="63">
-        <f>IF(COUNTIF($R$6:$R$37,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="63" t="n"/>
@@ -3225,7 +3231,7 @@
         <v/>
       </c>
       <c r="S14" s="63">
-        <f>IF(COUNTIF($R$6:$R$37,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="63" t="n"/>
@@ -3332,7 +3338,7 @@
         <v/>
       </c>
       <c r="S15" s="63">
-        <f>IF(COUNTIF($R$6:$R$37,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="63" t="n"/>
@@ -3439,7 +3445,7 @@
         <v/>
       </c>
       <c r="S16" s="63">
-        <f>IF(COUNTIF($R$6:$R$37,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="63" t="n"/>
@@ -3558,7 +3564,7 @@
         <v/>
       </c>
       <c r="S17" s="55">
-        <f>IF(COUNTIF($R$6:$R$37,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="79" t="inlineStr">
@@ -3677,7 +3683,7 @@
         <v/>
       </c>
       <c r="S18" s="55">
-        <f>IF(COUNTIF($R$6:$R$37,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="79" t="inlineStr">
@@ -3800,7 +3806,7 @@
         <v/>
       </c>
       <c r="S19" s="55">
-        <f>IF(COUNTIF($R$6:$R$37,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="79" t="inlineStr">
@@ -3924,7 +3930,7 @@
         <v/>
       </c>
       <c r="S20" s="55">
-        <f>IF(COUNTIF($R$6:$R$37,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="79" t="inlineStr">
@@ -4040,7 +4046,7 @@
         <v/>
       </c>
       <c r="S21" s="55">
-        <f>IF(COUNTIF($R$6:$R$37,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="79" t="inlineStr">
@@ -4159,7 +4165,7 @@
         <v/>
       </c>
       <c r="S22" s="55">
-        <f>IF(COUNTIF($R$6:$R$37,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="79" t="inlineStr">
@@ -4278,7 +4284,7 @@
         <v/>
       </c>
       <c r="S23" s="55">
-        <f>IF(COUNTIF($R$6:$R$37,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="79" t="inlineStr">
@@ -4397,7 +4403,7 @@
         <v/>
       </c>
       <c r="S24" s="55">
-        <f>IF(COUNTIF($R$6:$R$37,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="79" t="inlineStr">
@@ -4516,7 +4522,7 @@
         <v/>
       </c>
       <c r="S25" s="55">
-        <f>IF(COUNTIF($R$6:$R$37,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="79" t="inlineStr">
@@ -4635,7 +4641,7 @@
         <v/>
       </c>
       <c r="S26" s="79">
-        <f>IF(COUNTIF($R$6:$R$37,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="79" t="inlineStr">
@@ -4663,9 +4669,10 @@
           <t>FX01-06</t>
         </is>
       </c>
-      <c r="Y26" s="79" t="inlineStr">
-        <is>
-          <t>由《3D-特效》分页 FX01-06 补登进《资产主表》——该 Prefab 此前只登记在分页，主表缺行，与「《资产主表》＝唯一登记源」的口径不符。宿主唯一生命周期：由 Projectile3D 作为子节点持有，随 ProjectilePool3D 回收；刻意不进 VfxPool3D 注册表，避免弹体池与特效池双重所有权（见 14.6 §1.3/§3.5 与 skill vfx-combat-effect-authoring）。本行同时是 8 个弹种专属弹体特效的变体父体（G 列指向本 AssetID），弹种专属 Prefab 落地后仍复用本行的弹芯/外壳/拖尾几何分层，仅按弹种替换外观与行为段。</t>
+      <c r="Y26" s="111" t="inlineStr">
+        <is>
+          <t>由《3D-特效》分页 FX01-06 补登进《资产主表》——该 Prefab 此前只登记在分页，主表缺行，与「《资产主表》＝唯一登记源」的口径不符。宿主唯一生命周期：由 Projectile3D 作为子节点持有，随 ProjectilePool3D 回收；刻意不进 VfxPool3D 注册表，避免弹体池与特效池双重所有权（见 14.6 §1.3/§3.5 与 skill vfx-combat-effect-authoring）。本行同时是 8 个弹种专属弹体特效的变体父体（G 列指向本 AssetID），弹种专属 Prefab 落地后仍复用本行的弹芯/外壳/拖尾几何分层，仅按弹种替换外观与行为段。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4767,7 @@
         <v/>
       </c>
       <c r="S27" s="76">
-        <f>IF(COUNTIF($R$6:$R$37,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="76" t="inlineStr">
@@ -4784,9 +4791,10 @@
         </is>
       </c>
       <c r="X27" s="76" t="n"/>
-      <c r="Y27" s="76" t="inlineStr">
-        <is>
-          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_standard_root_top3d.tscn + 脚本=src/vfx/VfxBulletStandard3D.gd；根节点=VfxBulletStandard3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S17「使用清晰中性弹体、尾迹和命中；不附加误导性的元素效果」。</t>
+      <c r="Y27" s="112" t="inlineStr">
+        <is>
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_standard_root_top3d.tscn + 脚本=src/vfx/VfxBulletStandard3D.gd；根节点=VfxBulletStandard3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S17「使用清晰中性弹体、尾迹和命中；不附加误导性的元素效果」。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4889,7 @@
         <v/>
       </c>
       <c r="S28" s="76">
-        <f>IF(COUNTIF($R$6:$R$37,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="76" t="inlineStr">
@@ -4905,9 +4913,10 @@
         </is>
       </c>
       <c r="X28" s="76" t="n"/>
-      <c r="Y28" s="76" t="inlineStr">
-        <is>
-          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_sticky_root_top3d.tscn + 脚本=src/vfx/VfxBulletSticky3D.gd；根节点=VfxBulletSticky3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S18「命中后弹体留在表面并显示倒计时/状态，结束时反馈与结算同步」。</t>
+      <c r="Y28" s="112" t="inlineStr">
+        <is>
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_sticky_root_top3d.tscn + 脚本=src/vfx/VfxBulletSticky3D.gd；根节点=VfxBulletSticky3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S18「命中后弹体留在表面并显示倒计时/状态，结束时反馈与结算同步」。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5011,7 @@
         <v/>
       </c>
       <c r="S29" s="76">
-        <f>IF(COUNTIF($R$6:$R$37,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="76" t="inlineStr">
@@ -5026,9 +5035,10 @@
         </is>
       </c>
       <c r="X29" s="76" t="n"/>
-      <c r="Y29" s="76" t="inlineStr">
-        <is>
-          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_bounce_root_top3d.tscn + 脚本=src/vfx/VfxBulletBounce3D.gd；根节点=VfxBulletBounce3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S13「反弹点有折线闪光与计数递减，飞行方向变化清楚可读」。</t>
+      <c r="Y29" s="112" t="inlineStr">
+        <is>
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_bounce_root_top3d.tscn + 脚本=src/vfx/VfxBulletBounce3D.gd；根节点=VfxBulletBounce3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S13「反弹点有折线闪光与计数递减，飞行方向变化清楚可读」。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5133,7 @@
         <v/>
       </c>
       <c r="S30" s="76">
-        <f>IF(COUNTIF($R$6:$R$37,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="76" t="inlineStr">
@@ -5147,9 +5157,10 @@
         </is>
       </c>
       <c r="X30" s="76" t="n"/>
-      <c r="Y30" s="76" t="inlineStr">
-        <is>
-          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_piercing_root_top3d.tscn + 脚本=src/vfx/VfxBulletPiercing3D.gd；根节点=VfxBulletPiercing3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S16「穿透命中显示连续贯穿线与剩余层数，不在首个目标处假性消失」。</t>
+      <c r="Y30" s="112" t="inlineStr">
+        <is>
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_piercing_root_top3d.tscn + 脚本=src/vfx/VfxBulletPiercing3D.gd；根节点=VfxBulletPiercing3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S16「穿透命中显示连续贯穿线与剩余层数，不在首个目标处假性消失」。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5255,7 @@
         <v/>
       </c>
       <c r="S31" s="76">
-        <f>IF(COUNTIF($R$6:$R$37,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="76" t="inlineStr">
@@ -5268,9 +5279,10 @@
         </is>
       </c>
       <c r="X31" s="76" t="n"/>
-      <c r="Y31" s="76" t="inlineStr">
-        <is>
-          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_explosive_root_top3d.tscn + 脚本=src/vfx/VfxBulletExplosive3D.gd；根节点=VfxBulletExplosive3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S14「弹体、尾迹、爆炸半径与伤害时点同步，低特效下保留轮廓圈」。</t>
+      <c r="Y31" s="112" t="inlineStr">
+        <is>
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_explosive_root_top3d.tscn + 脚本=src/vfx/VfxBulletExplosive3D.gd；根节点=VfxBulletExplosive3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S14「弹体、尾迹、爆炸半径与伤害时点同步，低特效下保留轮廓圈」。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5377,7 @@
         <v/>
       </c>
       <c r="S32" s="76">
-        <f>IF(COUNTIF($R$6:$R$37,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="76" t="inlineStr">
@@ -5389,9 +5401,10 @@
         </is>
       </c>
       <c r="X32" s="76" t="n"/>
-      <c r="Y32" s="76" t="inlineStr">
-        <is>
-          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_homing_root_top3d.tscn + 脚本=src/vfx/VfxBulletHoming3D.gd；根节点=VfxBulletHoming3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S15「锁定框、弯曲尾迹和转向动作一致；目标丢失有解除提示」。</t>
+      <c r="Y32" s="112" t="inlineStr">
+        <is>
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_homing_root_top3d.tscn + 脚本=src/vfx/VfxBulletHoming3D.gd；根节点=VfxBulletHoming3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S15「锁定框、弯曲尾迹和转向动作一致；目标丢失有解除提示」。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5499,7 @@
         <v/>
       </c>
       <c r="S33" s="76">
-        <f>IF(COUNTIF($R$6:$R$37,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="76" t="inlineStr">
@@ -5510,9 +5523,10 @@
         </is>
       </c>
       <c r="X33" s="76" t="n"/>
-      <c r="Y33" s="76" t="inlineStr">
-        <is>
-          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_blackhole_root_top3d.tscn + 脚本=src/vfx/VfxBulletBlackhole3D.gd；根节点=VfxBulletBlackhole3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S12「黑洞核心、吸入流线和范围边界清晰；命中/结束有收束反馈」。</t>
+      <c r="Y33" s="112" t="inlineStr">
+        <is>
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_blackhole_root_top3d.tscn + 脚本=src/vfx/VfxBulletBlackhole3D.gd；根节点=VfxBulletBlackhole3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S12「黑洞核心、吸入流线和范围边界清晰；命中/结束有收束反馈」。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5621,7 @@
         <v/>
       </c>
       <c r="S34" s="76">
-        <f>IF(COUNTIF($R$6:$R$37,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="76" t="inlineStr">
@@ -5631,9 +5645,10 @@
         </is>
       </c>
       <c r="X34" s="76" t="n"/>
-      <c r="Y34" s="76" t="inlineStr">
-        <is>
-          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_balloon_root_top3d.tscn + 脚本=src/vfx/VfxBulletBalloon3D.gd；根节点=VfxBulletBalloon3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S11「膨胀弹体、较重尾迹与命中体积一致，不能只改伤害数值」。</t>
+      <c r="Y34" s="112" t="inlineStr">
+        <is>
+          <t>已制成并实装：Prefab=assets/art/vfx/combat_3d/vfx_bullet_balloon_root_top3d.tscn + 脚本=src/vfx/VfxBulletBalloon3D.gd；根节点=VfxBulletBalloon3D(Node3D)；《3D-特效》分页编号见该页（FX01-06 系列）。变体父体 VFX-BULLET-VISUAL-3D（复用其弹芯/外壳/拖尾几何分层，仅按弹种换外观与行为段）。调用方 Projectile3D._build_visual() 经 BULLET_VISUAL_REGISTRY 按 visual_id 路由，作为子节点持有、生命周期随 ProjectilePool3D，刻意不进 VfxPool3D；纯视觉无碰撞体。验收：verify_bullet_vfx_profiles（8 profile 可区分 + AssetID 路由 + 尺寸线性 + 端到端开火 + 无碰撞 + 反向对照）。设计依据：内容库《武器》S11「膨胀弹体、较重尾迹与命中体积一致，不能只改伤害数值」。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5739,7 @@
         <v/>
       </c>
       <c r="S35" s="76">
-        <f>IF(COUNTIF($R$6:$R$37,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="76" t="inlineStr">
@@ -5815,12 +5830,12 @@
       </c>
       <c r="M36" s="76" t="inlineStr">
         <is>
-          <t>v001</t>
+          <t>v002</t>
         </is>
       </c>
       <c r="N36" s="76" t="inlineStr">
         <is>
-          <t>PackedScene/程序几何（亮芯 + 2 层冲击环 + 9 星芒 + 8 碎屑 + 1 盏 BlastLight；lifetime 0.62s；size 由规格半径 ×0.6 传入）</t>
+          <t>PackedScene/程序几何（12 枚绿色方块爆开 + 14 枚抛物线飞溅 + 4 块扁平方形地面液体 + 3 层绿色冲击波 + 1 盏 GooLight；lifetime 1.35s；无碰撞体）</t>
         </is>
       </c>
       <c r="O36" s="76" t="inlineStr">
@@ -5843,12 +5858,12 @@
         <v/>
       </c>
       <c r="S36" s="76">
-        <f>IF(COUNTIF($R$6:$R$37,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="76" t="inlineStr">
         <is>
-          <t>0b875db8cad687b62001f4775f800569603808996f70e8c497e63b0c5b7700bb</t>
+          <t>7a88ecd3f4df05e4224484cd369dfe2a1d6ccca5140e1140ef2114d8ac6a19ab</t>
         </is>
       </c>
       <c r="U36" s="76" t="inlineStr">
@@ -5873,7 +5888,7 @@
       </c>
       <c r="Y36" s="76" t="inlineStr">
         <is>
-          <t>远征01 关卡级（不写该关 monster_rules.death_explosion 的关卡无本表现）。全向对称、不消费 context.forward/normal；纯视觉无碰撞体。尺寸由调用方按规格半径 ×0.6 传入（5.0m ⇒ size 3.0 ⇒ 内环≈4.75m / 外环≈5.29m）。专项验收 verify_death_blast_vfx。</t>
+          <t>**v002 整体重做（业主 2026-10-14）**：业主第三轮把口径更正为「**把小僵尸的死亡特效放大两倍给胖子僵尸用**，然后带一个绿色冲击波的效果，同样去掉胖子僵尸的倒地动画播放」——也就是本件 = **FX01-19 那套死亡表现（绿方块爆开 + 抛物线飞溅 + 地面液体）×2 + 3 层绿色冲击波**，不是另做一套橙红自爆。v001 的「亮芯 + 2 层冲击环 + 9 道放射星芒 + 8 块飞散碎屑」整组退役。**结构**：身体完全来自 `src/vfx/VfxGooDeathBase3D.gd`（与小僵尸死亡件是同一段代码），本件只覆盖 `_asset_id()` / `_asset_version()` = v002 / `_shockwave_enabled()` = true 三点 ——两件因此不可能在节奏 / 配色 / 落地数学上漂移。**尺寸**：由调用方固定 `Enemy3D.FAT_DEATH_EFFECT_SIZE = 2.0`（业主「放大两倍」），**替换** v001 的「按伤害半径 ×0.6 反推」口径 ⇒ 冲击波外缘 ≈3.1m 不再等于远征01 的 5.0m 伤害半径，它变成风格元素、不再充当半径指示（要说清楚：观感上「炸得多大」与「掉多少血」现在是两条独立的线）。**表现 ≠ 玩法**：`Enemy3D._detonate_death_explosion()` 里视觉那一行不受 `damage` 影响 ——规格 `damage&lt;=0`（本关不自爆）只是不掉血，不是「连死亡表现都不给」；塔楼里被去掉倒地动画的胖子僵尸因此仍有死亡表现。**地面契约**：`context.floor_y` 唯一真源（未传时按「胸口 = 脚底 + 0.65」反推，绝不写死 0）；冲击波平铺 XZ。纯视觉无碰撞体，走 VfxPool3D（FX01_DEATH_BLAST）。与 FX01-18 `VFX-BLAST-ZONE-3D` 的分工未变（那件仍是自爆后留在地上的持续伤害场视觉层）。验收 `verify_death_blast_vfx`（12 方块 + 14 飞溅 + 4 液体 + 3 冲击波 / GooLight 真源与包络 / 尺寸线性 / 冲击波峰值外缘扫描 / 绕竖直轴全向对称（**只看水平分量** —— 抬高式俯仰让三维模长天然 ~2.7）/ 地面平铺含倾斜对照 / 游戏侧选区与到点收场 / 端到端含 `zone.enabled=false` 对照，`samples=12`）。</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5979,7 @@
         <v/>
       </c>
       <c r="S37" s="76">
-        <f>IF(COUNTIF($R$6:$R$37,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$40,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="76" t="inlineStr">
@@ -5995,6 +6010,378 @@
       <c r="Y37" s="76" t="inlineStr">
         <is>
           <t>**纯视觉**：不含碰撞体、不结算伤害；伤害由玩法节点 src/enemy3d/DeathBlastZone3D.gd 按周期处理。地面朝向契约：整件平铺 XZ，调用方在地面高度 activate 且不旋转。宿主自持、**刻意不进 VfxPool3D**（同 FX01-16 / FX03-03 口径）。专项验收 verify_death_blast_vfx。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="76" t="inlineStr">
+        <is>
+          <t>VFX-ZOMBIE-GOO-DEATH-3D</t>
+        </is>
+      </c>
+      <c r="B38" s="76" t="inlineStr">
+        <is>
+          <t>僵尸死亡绿色方块爆开特效</t>
+        </is>
+      </c>
+      <c r="C38" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D38" s="76" t="inlineStr">
+        <is>
+          <t>战斗反馈</t>
+        </is>
+      </c>
+      <c r="E38" s="76" t="inlineStr">
+        <is>
+          <t>FX01-19</t>
+        </is>
+      </c>
+      <c r="F38" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G38" s="76" t="n"/>
+      <c r="H38" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I38" s="76" t="inlineStr">
+        <is>
+          <t>death_goo_burst</t>
+        </is>
+      </c>
+      <c r="J38" s="76" t="inlineStr">
+        <is>
+          <t>小僵尸/警察僵尸死亡（远征01 与塔楼通用）</t>
+        </is>
+      </c>
+      <c r="K38" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L38" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M38" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N38" s="76" t="inlineStr">
+        <is>
+          <t>PackedScene/程序几何（12 绿色方块爆炸粒子 + 14 抛物线飞溅粒子 + 4 块扁平方形地面液体 + 1 盏 GooLight；lifetime 1.35s；无碰撞体）</t>
+        </is>
+      </c>
+      <c r="O38" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_zombie_goo_death_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P38" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxZombieGooDeath3D.gd; src/enemy3d/Enemy3D.gd</t>
+        </is>
+      </c>
+      <c r="Q38" s="76" t="inlineStr">
+        <is>
+          <t>僵尸死亡;绿色方块;爆开;飞溅;抛物线;地面液体;停留0.5秒;下沉消失;goo-death;3D</t>
+        </is>
+      </c>
+      <c r="R38" s="76">
+        <f>LOWER(TRIM(C38)&amp;"|"&amp;TRIM(D38)&amp;"|"&amp;TRIM(E38)&amp;"|"&amp;TRIM(F38)&amp;"|"&amp;TRIM(H38)&amp;"|"&amp;TRIM(I38))</f>
+        <v/>
+      </c>
+      <c r="S38" s="76">
+        <f>IF(COUNTIF($R$6:$R$40,R38)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T38" s="76" t="inlineStr">
+        <is>
+          <t>c8c05ce1f2d020756ad75a5bbbffa5dd0b758b1834b1d1cc7731c355c32f384d</t>
+        </is>
+      </c>
+      <c r="U38" s="76" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V38" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="W38" s="76" t="inlineStr">
+        <is>
+          <t>原创程序几何</t>
+        </is>
+      </c>
+      <c r="X38" s="76" t="inlineStr">
+        <is>
+          <t>FX01-19</t>
+        </is>
+      </c>
+      <c r="Y38" s="76" t="inlineStr">
+        <is>
+          <t>业主口径（2026-10-14）：「绿色方块爆开的粒子，掉落地面，然后地面上有方形像液体一样的扁平模型，停留 0.5 秒后慢慢下沉消失；由三部分组成 —— 爆炸的粒子 / 飞溅出去的粒子 / 地上的液体；节奏要有打击力度感、粒子不要太小、需要有大小的变化动画」，并「配置在小僵尸和警察僵尸死亡后，状态机上去掉倒地动画」。三部分：A `Burst0..11` 爆炸粒子（尺度 0.25 → 1.15 → 0.35 倍，0.24s 收干净）；B `Splat0..13` 飞溅粒子（g = 30 抛物线，解析式求落点，落地压扁后缩没）；C `Puddle0..3` 地上液体（落在飞溅粒子**真实落点**上，出现 → **严格停留 0.50s** → 下沉 0.30m 并淡出）。颜色恒为僵尸绿（调用方本色只作 25% 偏移，保证「绿色」读法不被小僵尸暗红 / 警察青冲掉）。`context.floor_y` 是地面高度**唯一真源**（未传时按调用方「胸口 = 脚底 + 0.65」口径反推，绝不写死 0）。纯视觉无碰撞体，走 `VfxPool3D`（FX01_ZOMBIE_GOO_DEATH）。调用方 `Enemy3D._die()`：`GOO_DEATH_KINDS = [melee_chaser, ranged_caster]` 走 `_spawn_goo_death_burst()` + `_retire_goo_death_visual()`（模型同帧收起、节点本帧回收、不进死亡显影组）⇒ **去掉 2.4s 倒地动画与尸体**；其余怪（胖子 / Boss 等）行为逐字不变。验收 `verify_zombie_goo_death_vfx`（资产契约 / 灯真源 / 三段节奏含停留窗口行为测量 / 尺度变化倍率 4.6 / 地面平铺含倾斜 90° 对照 / `floor_y` 三向对照 / 尺寸线性 / 无碰撞 / 端到端含「死亡同帧模型已收起」与「2 帧内回收」/ 胖子僵尸反向对照，samples=14；反向对照四组：怪种表改成 exploder、PUDDLE_HOLD_SEC 改 0.30、忽略 `context.floor_y` 均精准变红）；`verify_melee_zombie_death_visibility` 同步改写为新契约（死前追踪照旧 / 死后无尸体 / 组不残留 / 结算恰好一次，`--negative-untracked` 反向对照精准变红）。【第二轮订正：本件未改版】业主 2026-10-14 第三轮明确「**小僵尸的死亡特效不要改变**」⇒ 本件回到上面这版（v001），**无绿色冲击波**；中途那一版「放大 2 倍 + 绿色冲击波」被业主指名是**给胖子僵尸用的**，已落在 FX01-17 `VFX-DEATH-BLAST-3D`（v002）。两件现共用 `src/vfx/VfxGooDeathBase3D.gd` 的身体（本件是 v001 的逐字副本），差别只有「尺寸（调用方 1.0 vs 2.0）」与「有没有冲击波（无 vs 有）」两个旋钮。冲击波开关是**子类覆盖点**，验收对两侧都做了断言（本件冲击波数必须为 0 且 `Shockwave*` 节点不存在；FX01-17 必须 3 层且能扫、能收）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="76" t="inlineStr">
+        <is>
+          <t>VFX-GOO-HIT-3D</t>
+        </is>
+      </c>
+      <c r="B39" s="76" t="inlineStr">
+        <is>
+          <t>僵尸命中爆点特效</t>
+        </is>
+      </c>
+      <c r="C39" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D39" s="76" t="inlineStr">
+        <is>
+          <t>战斗反馈</t>
+        </is>
+      </c>
+      <c r="E39" s="76" t="inlineStr">
+        <is>
+          <t>FX01-20</t>
+        </is>
+      </c>
+      <c r="F39" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G39" s="76" t="n"/>
+      <c r="H39" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I39" s="76" t="inlineStr">
+        <is>
+          <t>hit_goo_burst</t>
+        </is>
+      </c>
+      <c r="J39" s="76" t="inlineStr">
+        <is>
+          <t>小僵尸/警察僵尸/胖子僵尸被枪击或近战命中（跨关卡通用）</t>
+        </is>
+      </c>
+      <c r="K39" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L39" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M39" s="76" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="N39" s="76" t="inlineStr">
+        <is>
+          <t>PackedScene/程序几何（12 枚绿色方块爆开，0.26s；无灯、无碰撞体）</t>
+        </is>
+      </c>
+      <c r="O39" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_goo_hit_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P39" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxGooHit3D.gd; src/combat3d/Projectile3D.gd; src/player3d/melee/PlayerMeleeCombat3D.gd</t>
+        </is>
+      </c>
+      <c r="Q39" s="76" t="inlineStr">
+        <is>
+          <t>僵尸命中;受击;绿方块;爆开;goo-hit;枪击;近战;3D</t>
+        </is>
+      </c>
+      <c r="R39" s="76">
+        <f>LOWER(TRIM(C39)&amp;"|"&amp;TRIM(D39)&amp;"|"&amp;TRIM(E39)&amp;"|"&amp;TRIM(F39)&amp;"|"&amp;TRIM(H39)&amp;"|"&amp;TRIM(I39))</f>
+        <v/>
+      </c>
+      <c r="S39" s="76">
+        <f>IF(COUNTIF($R$6:$R$40,R39)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T39" s="76" t="inlineStr">
+        <is>
+          <t>2d932489f0e382a39305c1dd04a9d26b72ad4458e6b745cfe92ea836746b67a2</t>
+        </is>
+      </c>
+      <c r="U39" s="76" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V39" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="W39" s="76" t="inlineStr">
+        <is>
+          <t>原创程序几何</t>
+        </is>
+      </c>
+      <c r="X39" s="76" t="inlineStr">
+        <is>
+          <t>FX01-20</t>
+        </is>
+      </c>
+      <c r="Y39" s="76" t="inlineStr">
+        <is>
+          <t>业主口径（2026-10-14）历轮：
+① 首版：「使用爆炸粒子 ×12 的这个特效，**作为一个独立特效**，作为打中小僵尸、警察僵尸、胖子僵尸的受到枪击的特效」，追问后明确「**枪击 + 近战都用**」⇒ v001 = 12 枚绿方块从命中点炸开、0.26s。
+② **本版 v002**：「**小僵尸和警察僵尸的受击特效太大了**，**使用击中其它物体的那个特效**，然后**改成绿色**即可，放大大概 **10%**」⇒ 造型语言整体换成 FX01-21 `VFX-METAL-SPARK-HIT-3D` 那一套（5 颗方块 + 2 根长条火星），色板换成僵尸绿（方块亮绿 / 长条深一档绿）。本件与 FX01-21 **共用同一个父类** `VfxMetalSparkHit3D`（父类只暴露「资产身份」与「色板三项」两个钩子）⇒ 形状 / 件数 / 方向 / 尺度包络 / 外推曲线 / 长条拉伸**逐字相同**，两件不可能各自漂移。
+③ 同轮：「受击的盒子**没有贴着模型**，碰撞盒里陷进去坐标大概 **0.2 米**」⇒ 命中点必须先过 `Enemy3D.hit_effect_anchor()` 沿**外法线反向**收进模型 `HIT_EFFECT_INSET_M = 0.20` 米才出生（弹体是在碰撞壳表面判命中的，壳比模型大一圈）。收进去只对**怪**做 —— 墙面 / 掩体收了会钻进墙里。
+「大 10%」**不写在本件内部**，由调用方按档位给：枪击走 `Projectile3D.ZOMBIE_HIT_SIZE_RATIO = 1.10`（`GOO_HIT_SIZE_TARGET/ABSORB = METAL_SPARK_SIZE_TARGET/ABSORB × 1.10` ⇒ 0.374 / 0.462）；近战走 `PlayerMeleeCombat3D.ZOMBIE_HIT_BASE_SIZE = 0.42` —— 近战件那套 `size`（0.88~1.6）是按 FX01-05 的内部基准定的，直接喂给火星造型会把方块放大到糊住半个怪，那正是业主说的「太大」。
+AssetID 里的 “goo” 是**历史名**（v001 是绿方块爆开）；保留不改名 —— AssetID 是账本与 Prefab meta 的**稳定键**，改名等于让既有登记条目失锚。
+**刻意无灯**：每发子弹 / 每次近战都生成的高频件（射速上限 12 发/s）。
+**消费 `context.normal`**（v002 起与 FX01-21 同形 ⇒ 贴合被击面）；近战侧由 `PlayerMeleeCombat3D._hit_surface_normal()` 给「从怪体中心指向玩家」的外法线。
+【贴肉量实测】真渲染现读几何（小僵尸 melee_chaser）：碰撞柱半径 1.020（玩法口径，从 collision_shape.shape 现读）、壳表面命中点 (0, 1.05, 1.02)、退 0.2m 后 (0, 1.05, 0.82) ⇒ 模型可视件半宽 0.810，**退完离模型只剩 0.010m（1cm）**。业主估的「大概 0.2 米」几乎精确，这个值不用再调。以后美术若收窄模型，`gap_after_inset` 会变大，那时再回调 `Enemy3D.HIT_EFFECT_INSET_M`（唯一旋钮，别去动特效几何）。
+【机位教训】验「某个方向上的一小段位移」时，**机位必须垂直于那段位移** —— goo_hit / goo_hit_float 第一版用斜前机位，0.2m 正好落在视线方向 ⇒ 两张图肉眼看不出区别（等于没验）；改侧视（沿 +X 看回原点）后 0.2m 落在屏幕横轴，一眼可读。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="76" t="inlineStr">
+        <is>
+          <t>VFX-METAL-SPARK-HIT-3D</t>
+        </is>
+      </c>
+      <c r="B40" s="76" t="inlineStr">
+        <is>
+          <t>金属打击火星命中特效</t>
+        </is>
+      </c>
+      <c r="C40" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D40" s="76" t="inlineStr">
+        <is>
+          <t>战斗反馈</t>
+        </is>
+      </c>
+      <c r="E40" s="76" t="inlineStr">
+        <is>
+          <t>FX01-21</t>
+        </is>
+      </c>
+      <c r="F40" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G40" s="76" t="n"/>
+      <c r="H40" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I40" s="76" t="inlineStr">
+        <is>
+          <t>hit_metal_spark</t>
+        </is>
+      </c>
+      <c r="J40" s="76" t="inlineStr">
+        <is>
+          <t>击中非僵尸三兄弟的一切目标（墙面/掩体/地面/其它怪种）</t>
+        </is>
+      </c>
+      <c r="K40" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L40" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M40" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N40" s="76" t="inlineStr">
+        <is>
+          <t>PackedScene/程序几何（5 颗白色方块 + 2 根金色长条火星，0.32s；无灯、无碰撞体）</t>
+        </is>
+      </c>
+      <c r="O40" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_metal_spark_hit_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P40" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxMetalSparkHit3D.gd; src/combat3d/Projectile3D.gd</t>
+        </is>
+      </c>
+      <c r="Q40" s="76" t="inlineStr">
+        <is>
+          <t>命中;受击;金属;火星;白色方块;金色长条;metal-spark;切平面;3D</t>
+        </is>
+      </c>
+      <c r="R40" s="76">
+        <f>LOWER(TRIM(C40)&amp;"|"&amp;TRIM(D40)&amp;"|"&amp;TRIM(E40)&amp;"|"&amp;TRIM(F40)&amp;"|"&amp;TRIM(H40)&amp;"|"&amp;TRIM(I40))</f>
+        <v/>
+      </c>
+      <c r="S40" s="76">
+        <f>IF(COUNTIF($R$6:$R$40,R40)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T40" s="76" t="inlineStr">
+        <is>
+          <t>79571e7eb19be6b4e8dde1d7c3b050142ba246269ea1770f54f631d1068b94ec</t>
+        </is>
+      </c>
+      <c r="U40" s="76" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V40" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="W40" s="76" t="inlineStr">
+        <is>
+          <t>原创程序几何</t>
+        </is>
+      </c>
+      <c r="X40" s="76" t="inlineStr">
+        <is>
+          <t>FX01-21</t>
+        </is>
+      </c>
+      <c r="Y40" s="76" t="inlineStr">
+        <is>
+          <t>业主口径（2026-10-14）：原本是「原来那个特效缩小 60%，作为击中其它物体的特效」，追问缩小读数后业主改为「**重新制作一个**，通过一个打击到金属的粒子反馈的特效，用白色方块粒子和 2 根长条的金色火星一样飞溅去替代，这个不要用太多粒子，**4-5 颗 + 2 根金色火星**即可」⇒ 本件是**新资产**，不是 VFX-IMPACT-3D 的改版；VFX-IMPACT-3D 保持原样，继续服务它剩下的用途（非僵尸怪种死亡爆点、护盾弹开）。造型：5 颗白方块（`ToonVfxGeometry.unit_cube_mesh()`）+ 2 根金色长条火星（`ToonVfxGeometry.streak_mesh()`，**长轴 = 本地 Z** ⇒ `scale.z` 直接就是米数，长度 0.50 → 1.30 × size，从短粗拉成细长）。朝向契约 `context.normal`（**本件是唯一消费法线的战斗命中件**）：局部 +Y 对齐法线 ⇒ 局部 XZ 就是被击表面；**金色火星在切平面内擦出**（沿表面擦出去，|世界方向·法线| ≤ 0.20 有断言）、白方块沿法线向外喷。朝向用 `Basis.looking_at`（把本地 **-Z** 对到切向）—— 不能写 `Quaternion(UP, dir)`，后者是把 +Y 转过去，会让火星指向天上。**刻意无灯**：与 FX01-20 同理（高频件）。尺寸 `Projectile3D.METAL_SPARK_SIZE_TARGET = 0.34`（业主「受击的特效也不要太大」）。纯视觉无碰撞体，走 VfxPool3D（FX01_METAL_SPARK_HIT）。真渲染校准（`outputs/combat_vfx_batch2/combat_vfx_batch2_timeline.png`）：首版张角 0.34 rad、长 0.22→0.78 ⇒ 两根几乎重叠、读成「一根小凸起」；抬到 0.62 rad / 0.50→1.30 才成了「长条」。首版白方块切向占比 0.35~0.8、外推 0.30m ⇒ 5 颗挤成一坨，抬高切向占比并加大外推后才读成一撮碎屑。</t>
         </is>
       </c>
     </row>
@@ -6219,13 +6606,13 @@
     <cfRule type="containsText" priority="3" operator="containsText" dxfId="8" text="待制作"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,子弹特效,音效,音乐"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,design_only,authored,exported_pending_godot_validation,validated,active,已从运行场景移除,白盒组件"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6948,9 +7335,10 @@
           <t>v001</t>
         </is>
       </c>
-      <c r="Q13" s="51" t="inlineStr">
-        <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_visual_root_top3d.tscn + 脚本=src/vfx/VfxBulletVisual3D.gd；根节点=VfxBulletVisual3D(Node3D)；FX编号 FX01-06；调用方：Projectile3D._build_visual() 实例化为子节点并委托 activate/deactivate/apply_growth/set_trail_visible；碰撞由 Projectile3D 自持（半径 0.12 球），本视觉 Prefab 内无碰撞体；验收：verify_combat_vfx_toon_v002。</t>
+      <c r="Q13" s="109" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_visual_root_top3d.tscn + 脚本=src/vfx/VfxBulletVisual3D.gd；根节点=VfxBulletVisual3D(Node3D)；FX编号 FX01-06；调用方：Projectile3D._build_visual() 实例化为子节点并委托 activate/deactivate/apply_growth/set_trail_visible；碰撞由 Projectile3D 自持（半径 0.12 球），本视觉 Prefab 内无碰撞体；验收：verify_combat_vfx_toon_v002。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -7701,9 +8089,10 @@
           <t>v001</t>
         </is>
       </c>
-      <c r="Q26" s="51" t="inlineStr">
-        <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_standard_root_top3d.tscn + 脚本=src/vfx/VfxBulletStandard3D.gd；根节点=VfxBulletStandard3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+      <c r="Q26" s="109" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_standard_root_top3d.tscn + 脚本=src/vfx/VfxBulletStandard3D.gd；根节点=VfxBulletStandard3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -7788,9 +8177,10 @@
           <t>v001</t>
         </is>
       </c>
-      <c r="Q27" s="51" t="inlineStr">
-        <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_sticky_root_top3d.tscn + 脚本=src/vfx/VfxBulletSticky3D.gd；根节点=VfxBulletSticky3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+      <c r="Q27" s="109" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_sticky_root_top3d.tscn + 脚本=src/vfx/VfxBulletSticky3D.gd；根节点=VfxBulletSticky3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -7875,9 +8265,10 @@
           <t>v001</t>
         </is>
       </c>
-      <c r="Q28" s="51" t="inlineStr">
-        <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_bounce_root_top3d.tscn + 脚本=src/vfx/VfxBulletBounce3D.gd；根节点=VfxBulletBounce3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+      <c r="Q28" s="109" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_bounce_root_top3d.tscn + 脚本=src/vfx/VfxBulletBounce3D.gd；根节点=VfxBulletBounce3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -7962,9 +8353,10 @@
           <t>v001</t>
         </is>
       </c>
-      <c r="Q29" s="51" t="inlineStr">
-        <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_piercing_root_top3d.tscn + 脚本=src/vfx/VfxBulletPiercing3D.gd；根节点=VfxBulletPiercing3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+      <c r="Q29" s="109" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_piercing_root_top3d.tscn + 脚本=src/vfx/VfxBulletPiercing3D.gd；根节点=VfxBulletPiercing3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -8049,9 +8441,10 @@
           <t>v001</t>
         </is>
       </c>
-      <c r="Q30" s="51" t="inlineStr">
-        <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_explosive_root_top3d.tscn + 脚本=src/vfx/VfxBulletExplosive3D.gd；根节点=VfxBulletExplosive3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+      <c r="Q30" s="109" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_explosive_root_top3d.tscn + 脚本=src/vfx/VfxBulletExplosive3D.gd；根节点=VfxBulletExplosive3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -8136,9 +8529,10 @@
           <t>v001</t>
         </is>
       </c>
-      <c r="Q31" s="51" t="inlineStr">
-        <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_homing_root_top3d.tscn + 脚本=src/vfx/VfxBulletHoming3D.gd；根节点=VfxBulletHoming3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+      <c r="Q31" s="109" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_homing_root_top3d.tscn + 脚本=src/vfx/VfxBulletHoming3D.gd；根节点=VfxBulletHoming3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -8223,9 +8617,10 @@
           <t>v001</t>
         </is>
       </c>
-      <c r="Q32" s="51" t="inlineStr">
-        <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_blackhole_root_top3d.tscn + 脚本=src/vfx/VfxBulletBlackhole3D.gd；根节点=VfxBulletBlackhole3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+      <c r="Q32" s="109" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_blackhole_root_top3d.tscn + 脚本=src/vfx/VfxBulletBlackhole3D.gd；根节点=VfxBulletBlackhole3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -8310,9 +8705,10 @@
           <t>v001</t>
         </is>
       </c>
-      <c r="Q33" s="51" t="inlineStr">
-        <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_balloon_root_top3d.tscn + 脚本=src/vfx/VfxBulletBalloon3D.gd；根节点=VfxBulletBalloon3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。</t>
+      <c r="Q33" s="109" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_bullet_balloon_root_top3d.tscn + 脚本=src/vfx/VfxBulletBalloon3D.gd；根节点=VfxBulletBalloon3D(Node3D)；变体父体 VFX-BULLET-VISUAL-3D；调用方 Projectile3D._build_visual()（BULLET_VISUAL_REGISTRY 路由）；无碰撞体；不进 VfxPool3D；验收：verify_bullet_vfx_profiles。
+【枪族弹体尺寸档 2026-10-14】业主「每把枪的子弹大小要做出区分」+「散射喷壶的子弹太小了，出生和结束都增加 2 倍」+「减面，减到 100 个面以下先」：① **尺寸两层**：弹体视觉尺寸 = 弹种 profile × 枪身族档位（档位真源 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG，键 = 枪身 tags 族标识，不是 gun_id —— 按族声明，新增同族枪自动继承）。三档：散射喷壶 shotgun 各向同性 ×2.00 + 由小变大（出生 0.84、0.30s 线性长到 2.00；grow_from = 0.42 是**比例**，保持不变即出生与长满两端同步 ×2）；反胃榴弹筒 launcher ×1.55；弹弓狙击 sniper 横向 ×0.95 + 沿飞行轴 ×2.0（净长 1.90 倍）；其余枪中性档。轴向拉伸只落各件自己的局部长轴与尾迹段距，不写父级 scale/rotation（父级非均匀缩放 × 子级旋转 = 剪切变形）。② **链路**：WeaponModel3D 解析 → projectile_config.gun_bullet_geometry → Projectile3D._gun_bullet_geometry → activate 的 context（axial_scale / grow_from / grow_duration）→ VfxBulletBody3D；子投射物继承，池化复借在 configure 与 deactivate 双处复位。③ **纯视觉边界**：枪身档位不进碰撞半径 —— Projectile3D 的 _visual_scale_factor()（弹种 × 命运 × 枪身族，供视觉）与 _collision_scale_factor()（只含弹种 × 命运，供 0.12 基准球）已拆开，验收有正面断言钉住。④ **低面数档**：弹芯/外壳由 CapsuleMesh 改为 4 边棱柱（CylinderMesh，16 面/件）—— CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」等价平盖圆柱且贵 8 面，rings=1 要 48 面/件、两件即吃掉 100 面全部预算；尾迹锥 4 段（12 面）、滴珠改 BoxMesh（16→12 面，滴珠世界尺寸仅 0.011~0.018m 不可分辨）、黑洞/气球球核 SphereMesh 4×1（16 面）。单弹总面数 **44~80**（改前 468~1020，降 92%~94%）；均值 819 → **61.3**；霰弹枪一次 5 发 3660 → **220** 面。**件数与尾迹构图未动**（件数属账本与验收契约）。缩放不改变面数。分段常量集中在 VfxBulletBody3D 顶部与 VfxBulletVisual3D._SEGMENTS。⑤ **验收**：verify_bullet_vfx_profiles（samples=69）—— 9 枪档位 + 生长包络步进 + 中性档不启用 + 复借复位 + 碰撞半径守卫 + 面数预算（上限 100 与逐弹种实测值双层钉住，期望硬编码在验收侧）；反向对照 RC1~RC8 全部精准变红后还原复绿（文件 md5 与改前一致）。</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8825,7 @@
     <row r="36" ht="15" customHeight="1" s="52">
       <c r="A36" s="97" t="inlineStr">
         <is>
-          <t>▼ 01 战斗反馈（续）· 死亡自爆（远征01）</t>
+          <t>▼ 01 战斗反馈（续）· 死亡表现与命中分流</t>
         </is>
       </c>
       <c r="B36" s="98" t="n"/>
@@ -8462,7 +8858,7 @@
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>胖子僵尸死亡自爆特效</t>
+          <t>胖子僵尸死亡表现（小僵尸死亡表现 ×2 + 绿色冲击波）</t>
         </is>
       </c>
       <c r="D37" s="101" t="inlineStr">
@@ -8482,7 +8878,7 @@
       </c>
       <c r="G37" s="51" t="inlineStr">
         <is>
-          <t>远征01 胖子僵尸被打死瞬间的一次性爆炸视觉（业主 2026-10-14「胖子僵尸被打死后自爆没有特效，需要增加一个」）：SphereMesh 亮芯 + 2 层错峰冲击环（TorusMesh，环面躺在 XZ、读作地面冲击波）+ 9 道放射星芒（BoxMesh，Quaternion(UP,dir) 对齐水平放射、长短错峰）+ 8 块飞散碎屑（外抛 + 上抛弧线 + 自旋）+ 一盏 OmniLight3D（名 BlastLight，shadow_enabled=false）。**全向对称**，刻意不消费 context.forward / context.normal。经 VfxPool3D 按 AssetID 路由。</t>
+          <t>胖子僵尸被打死瞬间的死亡表现（业主 2026-10-14「把小僵尸的死亡特效放大两倍给胖子僵尸用，然后带一个绿色冲击波的效果」）：12 枚绿方块从胸口炸开 → 14 枚抛物线飞溅、落地压扁缩没 → 4 块扁平方形地面液体落在飞溅粒子的真实落点（出现 → 严格停留 0.50s → 下沉 0.30m 淡出）→ 3 层绿色冲击波贴地向外扫；全程 1.35s。</t>
         </is>
       </c>
       <c r="H37" s="101" t="inlineStr">
@@ -8507,12 +8903,12 @@
       </c>
       <c r="L37" s="51" t="inlineStr">
         <is>
-          <t>亮芯半径 0.18×size×(0.55→2.40)；冲击环外缘 0.72×size×(0.30→2.20 内环 / 0.20→2.45 外环)，size=3.0 时内环≈4.75m、外环≈5.29m；lifetime 0.62s；BlastLight range 6.0m×size、峰值 light_energy 9.0、寿命末端归零</t>
+          <t>基准方块 0.34m（爆炸粒子）/ 0.26m（飞溅粒子）；地面液体 0.72m × (0.86~1.16)；GooLight 范围 4.2 × size、能量峰值 6.0、0.34s 归零；绿色冲击波 3 层、外缘 ≈1.548 × size；lifetime 1.35s。**调用方固定 size = 2.0**（Enemy3D.FAT_DEATH_EFFECT_SIZE）</t>
         </is>
       </c>
       <c r="M37" s="51" t="inlineStr">
         <is>
-          <t>原点=根节点中心；**无朝向契约（全向对称）**</t>
+          <t>原点 = 根节点中心（＝怪胸口，脚底 + 0.65m）；**无朝向契约（全向对称）**；地面件（液体 + 冲击波）平铺 XZ、只绕 Y 轴转</t>
         </is>
       </c>
       <c r="N37" s="51" t="inlineStr">
@@ -8527,12 +8923,12 @@
       </c>
       <c r="P37" s="101" t="inlineStr">
         <is>
-          <t>v001</t>
+          <t>v002</t>
         </is>
       </c>
       <c r="Q37" s="51" t="inlineStr">
         <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_death_blast_root_top3d.tscn + 脚本=src/vfx/VfxDeathBlast3D.gd；根节点=VfxDeathBlast3D(Node3D)；FX编号 FX01-17；调用方=Enemy3D._detonate_death_explosion（经 VfxPool3D.acquire(FX01_DEATH_BLAST, …)）；纯视觉无碰撞体；与 **FX01-18** 配对成「爆炸 + 地面残留」一整套；验收=verify_death_blast_vfx。</t>
+          <t>已实装 v002（2026-10-14 整体重做）；Prefab=assets/art/vfx/combat_3d/vfx_death_blast_root_top3d.tscn + 脚本=src/vfx/VfxDeathBlast3D.gd（extends src/vfx/VfxGooDeathBase3D.gd，只覆盖资产身份与冲击波开关）+ 驱动 src/enemy3d/Enemy3D.gd；走 VfxPool3D 的 FX01_DEATH_BLAST；验收 verify_death_blast_vfx（samples=12）。⚠ 尺寸不再按伤害半径反推 —— 观感与伤害是两条独立的线。</t>
         </is>
       </c>
     </row>
@@ -8624,19 +9020,265 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="52">
-      <c r="H39" s="101" t="n"/>
-      <c r="I39" s="51" t="n"/>
-      <c r="N39" s="51" t="n"/>
+      <c r="A39" s="100" t="inlineStr">
+        <is>
+          <t>FX01-19</t>
+        </is>
+      </c>
+      <c r="B39" s="101" t="inlineStr">
+        <is>
+          <t>VFX-ZOMBIE-GOO-DEATH-3D</t>
+        </is>
+      </c>
+      <c r="C39" s="51" t="inlineStr">
+        <is>
+          <t>僵尸死亡绿色方块爆开特效</t>
+        </is>
+      </c>
+      <c r="D39" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_zombie_goo_death_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E39" s="51" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="F39" s="51" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="G39" s="51" t="inlineStr">
+        <is>
+          <t>小僵尸 / 警察僵尸被打死瞬间的一次性死亡表现（业主 2026-10-14）：12 枚绿色方块从胸口炸开（尺度过冲 4.6 倍后收缩，0.24s 收干净）→ 14 枚方块按 g=30 抛物线飞溅、落地压扁后缩没 → 4 块扁平方形「液体」落在飞溅粒子的真实落点上，出现后**严格停留 0.50s**，再慢慢下沉 0.30m 并淡出；全程 1.35s。全向对称，刻意不消费 forward/normal。</t>
+        </is>
+      </c>
+      <c r="H39" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxZombieGooDeath3D.gd</t>
+        </is>
+      </c>
+      <c r="I39" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J39" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K39" s="51" t="inlineStr">
+        <is>
+          <t>无CollisionObject3D/CollisionShape3D</t>
+        </is>
+      </c>
+      <c r="L39" s="51" t="inlineStr">
+        <is>
+          <t>基准方块 0.34m（爆炸粒子）/ 0.26m（飞溅粒子）；地面液体 0.72m × (0.86~1.16)；GooLight 范围 4.2 × size、能量峰值 6.0；lifetime 1.35s</t>
+        </is>
+      </c>
+      <c r="M39" s="51" t="inlineStr">
+        <is>
+          <t>原点 = 根节点中心（＝怪胸口，脚底 + 0.65m）；**无朝向契约（全向对称）**；地面件平铺 XZ、只绕 Y 轴转</t>
+        </is>
+      </c>
+      <c r="N39" s="51" t="inlineStr">
+        <is>
+          <t>小僵尸（melee_chaser）/ 警察僵尸（ranged_caster）死亡（Enemy3D._die → _spawn_goo_death_burst）</t>
+        </is>
+      </c>
+      <c r="O39" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P39" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q39" s="51" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_zombie_goo_death_root_top3d.tscn + 脚本=src/vfx/VfxZombieGooDeath3D.gd；根节点=VfxZombieGooDeath3D(Node3D)；走 VfxPool3D 的 FX01_ZOMBIE_GOO_DEATH；调用方 Enemy3D._die()（goo 怪种无尸体、无倒地动画）；验收 verify_zombie_goo_death_vfx（samples=14）。</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="52">
-      <c r="H40" s="101" t="n"/>
-      <c r="I40" s="51" t="n"/>
-      <c r="N40" s="51" t="n"/>
+      <c r="A40" s="100" t="inlineStr">
+        <is>
+          <t>FX01-20</t>
+        </is>
+      </c>
+      <c r="B40" s="101" t="inlineStr">
+        <is>
+          <t>VFX-GOO-HIT-3D</t>
+        </is>
+      </c>
+      <c r="C40" s="51" t="inlineStr">
+        <is>
+          <t>僵尸受击特效（绿色金属火星）</t>
+        </is>
+      </c>
+      <c r="D40" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_goo_hit_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E40" s="51" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="F40" s="51" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="G40" s="51" t="inlineStr">
+        <is>
+          <t>子弹或近战打中「僵尸三兄弟」（小僵尸 / 警察僵尸 / 胖子僵尸）时的受击反馈。**v002（2026-10-14 第四轮）**：造型整体换成 FX01-21 `VFX-METAL-SPARK-HIT-3D` 那一套（5 颗绿方块 + 2 根绿色长条火星），寿命 0.32s；与 FX01-21 **逐字同形、只差色板**（共用父类 `VfxMetalSparkHit3D`）；尺寸由调用方按同档位 ×1.10 给；**消费 `context.normal`**；命中点先经 `Enemy3D.hit_effect_anchor()` 收进模型 0.2m。刻意无灯（高频件）。</t>
+        </is>
+      </c>
+      <c r="H40" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxGooHit3D.gd</t>
+        </is>
+      </c>
+      <c r="I40" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J40" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K40" s="51" t="inlineStr">
+        <is>
+          <t>无CollisionObject3D/CollisionShape3D</t>
+        </is>
+      </c>
+      <c r="L40" s="51" t="inlineStr">
+        <is>
+          <t>方块 5 颗（基准边长 0.16m）+ 长条火星 2 根（长 0.50→1.30 × size，沿切平面擦出）；尺度包络 0.45→1.05→0.30；lifetime 0.32s；尺寸 = 金属火星同档位 ×1.10（枪击目标档 0.374 / 吸收档 0.462；近战基准 0.42）；命中点沿外法线反向下沉 0.20m；无灯</t>
+        </is>
+      </c>
+      <c r="M40" s="51" t="inlineStr">
+        <is>
+          <t>原点 = 命中点（已沿外法线反向下沉 0.20m）；**消费 context.normal**：局部 +Y 对齐被击面，长条火星落在切平面内（|方向·法线| ≤ 0.20）</t>
+        </is>
+      </c>
+      <c r="N40" s="51" t="inlineStr">
+        <is>
+          <t>小僵尸/警察僵尸/胖子僵尸被枪击或近战命中（Projectile3D / PlayerMeleeCombat3D）</t>
+        </is>
+      </c>
+      <c r="O40" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P40" s="101" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="Q40" s="51" t="inlineStr">
+        <is>
+          <t>已实装 v002；Prefab = assets/art/vfx/combat_3d/vfx_goo_hit_root_top3d.tscn + 脚本 = src/vfx/VfxGooHit3D.gd（extends VfxMetalSparkHit3D）；走 VfxPool3D 的 FX01_GOO_HIT；调用方 Projectile3D._spawn_hit_effect() / PlayerMeleeCombat3D._spawn_hit_feedback()，分流入口 Enemy3D.uses_goo_hit_burst()；验收 verify_hit_routing_vfx（samples=27，含「与 FX01-21 同形」双向对照、贴肉落点三向判定、尺寸路由静态门禁）。</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="52">
-      <c r="H41" s="101" t="n"/>
-      <c r="I41" s="51" t="n"/>
-      <c r="N41" s="51" t="n"/>
+      <c r="A41" s="100" t="inlineStr">
+        <is>
+          <t>FX01-21</t>
+        </is>
+      </c>
+      <c r="B41" s="101" t="inlineStr">
+        <is>
+          <t>VFX-METAL-SPARK-HIT-3D</t>
+        </is>
+      </c>
+      <c r="C41" s="51" t="inlineStr">
+        <is>
+          <t>金属打击火星命中特效</t>
+        </is>
+      </c>
+      <c r="D41" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_metal_spark_hit_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E41" s="51" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="F41" s="51" t="inlineStr">
+        <is>
+          <t>无（程序几何）</t>
+        </is>
+      </c>
+      <c r="G41" s="51" t="inlineStr">
+        <is>
+          <t>打在墙面 / 掩体 / 地面 / 非僵尸怪种上的命中反馈（业主 2026-10-14「重新制作一个…打击到金属的粒子反馈」）：5 颗白色方块沿法线外喷 + 2 根金色长条火星在**切平面内**擦出（从短粗拉成细长），全程 0.32s。**唯一消费 context.normal 的战斗命中件**；刻意无灯（高频件）。</t>
+        </is>
+      </c>
+      <c r="H41" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxMetalSparkHit3D.gd</t>
+        </is>
+      </c>
+      <c r="I41" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J41" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K41" s="51" t="inlineStr">
+        <is>
+          <t>无CollisionObject3D/CollisionShape3D</t>
+        </is>
+      </c>
+      <c r="L41" s="51" t="inlineStr">
+        <is>
+          <t>白方块基准 0.16m；金色长条 0.50→1.30 × size、截面 0.055m；两梗张角 ±0.62 rad；lifetime 0.32s；无灯</t>
+        </is>
+      </c>
+      <c r="M41" s="51" t="inlineStr">
+        <is>
+          <t>原点 = 命中点；朝向 = 局部 +Y 对齐 context.normal（缺省 UP）⇒ 局部 XZ 即被击表面；金色火星沿切平面、白方块沿法线</t>
+        </is>
+      </c>
+      <c r="N41" s="51" t="inlineStr">
+        <is>
+          <t>击中非僵尸三兄弟的一切目标（Projectile3D 的命中/反弹/落地/链电路径）</t>
+        </is>
+      </c>
+      <c r="O41" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P41" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q41" s="51" t="inlineStr">
+        <is>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_metal_spark_hit_root_top3d.tscn + 脚本=src/vfx/VfxMetalSparkHit3D.gd；走 VfxPool3D 的 FX01_METAL_SPARK_HIT；替代原本「把 VFX-IMPACT-3D 缩小 60%」的临时口径（业主改口为重新制作）；VFX-IMPACT-3D 保留给非僵尸死亡爆点 / 护盾弹开；验收 verify_hit_routing_vfx（samples=26）。</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="52">
       <c r="H42" s="101" t="n"/>
@@ -9714,7 +10356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="51" min="1" max="1"/>
@@ -10467,6 +11109,228 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="109" t="inlineStr">
+        <is>
+          <t>v0.1.19</t>
+        </is>
+      </c>
+      <c r="B25" s="109" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C25" s="109" t="inlineStr">
+        <is>
+          <t>条目更新（尺寸契约）</t>
+        </is>
+      </c>
+      <c r="D25" s="109" t="inlineStr">
+        <is>
+          <t>特效 · 子弹特效 / 3D-特效</t>
+        </is>
+      </c>
+      <c r="E25" s="109" t="inlineStr">
+        <is>
+          <t>按枪族给弹体视觉定尺寸档：弹体尺寸改为「弹种 profile × 枪身族档位」两层。新增 WeaponModel3D.BULLET_GEOMETRY_BY_GUN_TAG（按枪身 tags 族标识登记）：shotgun 由小变大（出生 42% / 0.30s 长满）、launcher ×1.55、sniper 横向 ×0.95 + 沿飞行轴 ×2.0，其余枪中性（1.0/1.0/无生长）。VfxBulletBody3D 新增 axial_scale / grow_from / grow_duration 三项 context 入参与确定性生长包络；轴向拉伸只落各件局部长轴与尾迹段距，不写父级 scale/rotation（避免非均匀缩放 × 子级旋转的剪切）。Projectile3D 新增 _gun_bullet_geometry 随 configure 读取、activate 下发，子投射物继承。验收 verify_bullet_vfx_profiles 扩至 samples=59，反向对照三组。</t>
+        </is>
+      </c>
+      <c r="F25" s="109" t="inlineStr">
+        <is>
+          <t>稳定 AssetID / Prefab 路径 / Prefab SHA / 版本号全部不变（未改 .tscn）；仅运行时尺寸契约变化（缺省 context 一律中性 ⇒ 未上档的枪外观逐帧不变）；无碰撞体改动、不含玩法数值。</t>
+        </is>
+      </c>
+      <c r="G25" s="109" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="109" t="inlineStr">
+        <is>
+          <t>v0.1.20</t>
+        </is>
+      </c>
+      <c r="B26" s="109" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C26" s="109" t="inlineStr">
+        <is>
+          <t>新增条目 + 新增 Prefab 分页</t>
+        </is>
+      </c>
+      <c r="D26" s="109" t="inlineStr">
+        <is>
+          <t>特效 · 资产主表 / 3D-特效</t>
+        </is>
+      </c>
+      <c r="E26" s="109" t="inlineStr">
+        <is>
+          <t>新增 FX01-19 VFX-ZOMBIE-GOO-DEATH-3D「僵尸死亡绿色方块爆开特效」（业主 2026-10-14）：① 爆炸粒子 12 枚绿色方块（尺度 0.25→1.15→0.35，0.24s 收干净）；② 飞溅粒子 14 枚（g=30 抛物线，解析式求落点，落地压扁缩没）；③ 地面液体 4 块扁平方形（落在飞溅真实落点，出现后严格停留 0.50s，再下沉 0.30m 淡出）；全程 1.35s，纯视觉无碰撞体，走 VfxPool3D。接线：Enemy3D._die() 对 GOO_DEATH_KINDS=[melee_chaser, ranged_caster] 借出该特效，并以 _retire_goo_death_visual() **去掉 2.4s 倒地动画与尸体**（模型同帧收起、节点本帧回收、不进死亡显影组）；其余怪行为逐字不变。新增专项 verify_zombie_goo_death_vfx（samples=14，含四组反向对照）；verify_melee_zombie_death_visibility 同步改写为新契约。</t>
+        </is>
+      </c>
+      <c r="F26" s="109" t="inlineStr">
+        <is>
+          <t>新增一个稳定 AssetID 与 Prefab 路径；既有条目的 AssetID / 路径 / 状态 / 哈希逐格保留（含另一会话未提交的子弹特效尺寸档备注，未改动）。行为面为「小僵尸 / 警察僵尸死亡表现替换」，属业主指定的显式变更：该两类怪不再播倒地动画、不留尸体；胖子僵尸 / Boss 等其它怪种的死亡链路逐字不变（由 verify_fat_zombie03_death_visibility 与 verify_zombie_goo_death_vfx 的双向对照守护）。</t>
+        </is>
+      </c>
+      <c r="G26" s="109" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="109" t="inlineStr">
+        <is>
+          <t>v0.1.21</t>
+        </is>
+      </c>
+      <c r="B27" s="109" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C27" s="109" t="inlineStr">
+        <is>
+          <t>条目更新（尺寸档调整 + 契约修正）</t>
+        </is>
+      </c>
+      <c r="D27" s="109" t="inlineStr">
+        <is>
+          <t>特效 · 子弹特效 / 3D-特效</t>
+        </is>
+      </c>
+      <c r="E27" s="109" t="inlineStr">
+        <is>
+          <t>① 散射喷壶弹体 ×2（业主「子弹太小了，出生和结束都增加 2 倍」）：shotgun 档位 scale 1.00 → 2.00，grow_from 0.42 保持不变 ⇒ 出生 0.42→0.84、长满 1.00→2.00，比例关系与过程感不变。② **修正一处契约未兑现**：v0.1.19 备注声明「本档位不改碰撞半径」，但实现上 Projectile3D._apply_visual_configuration() 复用了含枪身倍率的 _visual_scale_factor() 计算碰撞球半径，霰弹 ×2 会把判定半径从 0.12 悄悄抬到 0.24。本轮把倍率拆成 _visual_scale_factor()（弹种 × 命运 × 枪身）与 _collision_scale_factor()（只含弹种 × 命运），碰撞半径回到基准 0.12，兑现纯视觉契约；balloon 弹的 1.55 弹种倍率仍照常进入碰撞（既有行为不变）。③ Projectile3D.get_orientation_snapshot() 暴露 collision_radius 供验收读取；验收 verify_bullet_vfx_profiles 扩至 samples=60，新增「纯视觉边界」正面断言，反向对照 RC4（shotgun.scale→1.0）/ RC5（碰撞倍率误含枪身档位）均精准变红。④ 弹体规模实测（探针 _scratch/probe_bullet_mesh_stats）：标准弹 732 三角面 / 3 件，八弹种 468~1020 面（均值 819），件数 3~6；缩放不改变面数。</t>
+        </is>
+      </c>
+      <c r="F27" s="109" t="inlineStr">
+        <is>
+          <t>稳定 AssetID / Prefab 路径 / Prefab SHA / 版本号全部不变（未改 .tscn）；仅运行时尺寸与碰撞半径口径变化：霰弹枪观感 ×2，其碰撞判定与改动前逐位相同；其余枪外观与判定均不变。⚠️ 本行补录：本事务原写入的 v0.1.20 日志行被并发会话的同编号写入覆盖（对方新增 VFX-ZOMBIE-GOO-DEATH-3D），备注改动未受影响；此处以 v0.1.21 补录，内容完整。</t>
+        </is>
+      </c>
+      <c r="G27" s="109" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="109" t="inlineStr">
+        <is>
+          <t>v0.1.22</t>
+        </is>
+      </c>
+      <c r="B28" s="109" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C28" s="109" t="inlineStr">
+        <is>
+          <t>新增条目 + 条目更新（改版升版）</t>
+        </is>
+      </c>
+      <c r="D28" s="109" t="inlineStr">
+        <is>
+          <t>特效 · 资产主表 / 3D-特效</t>
+        </is>
+      </c>
+      <c r="E28" s="109" t="inlineStr">
+        <is>
+          <t>① 新增 FX01-20 VFX-GOO-HIT-3D「僵尸命中爆点特效」——12 枚绿方块从命中点炸开、0.26s，刻意无灯、刻意不消费 normal；由 Projectile3D._spawn_hit_effect() 与 PlayerMeleeCombat3D._spawn_hit_feedback() 共用分流入口 Enemy3D.uses_goo_hit_burst()（ZOMBIE_KINDS = melee_chaser / ranged_caster / fat_zombie03）。② 新增 FX01-21 VFX-METAL-SPARK-HIT-3D「金属打击火星命中特效」——5 颗白方块 + 2 根金色长条火星，火星沿切平面擦出；替代原本「把 VFX-IMPACT-3D 缩小 60%」的临时口径（业主改口为重新制作）；VFX-IMPACT-3D 保留给非僵尸死亡爆点 / 护盾弹开，命中路径不再借它。③ FX01-17 VFX-DEATH-BLAST-3D 整体重做并升 v002：改为「小僵尸的死亡表现 ×2 + 3 层绿色冲击波」（业主把口径更正为「把小僵尸的特效放大两倍给胖子僵尸用」），v001 的亮芯/星芒/碎屑整组退役；尺寸由调用方固定 2.0，不再按伤害半径反推。④ FX01-19 VFX-ZOMBIE-GOO-DEATH-3D 保持 v001 不变（业主「小僵尸的死亡特效不要改变」）；中途那一版「×2 + 冲击波」撤回，冲击波改为只有胖子僵尸那条有。⑤ 结构：抽 src/vfx/VfxGooDeathBase3D.gd 作两条僵尸死亡链路的共享身体（子类只覆盖资产身份与冲击波开关，尺寸由调用方给）；抽 src/vfx/ToonVfxBurst.gd 作方块爆开/冲击波的共享运动学（纯静态、确定性、无 randf）。⑥ 受击特效尺寸下调约 40%（业主「受击的特效也不要太大，小一点」）。⑦ 新增专项 verify_hit_routing_vfx（samples=26）；verify_death_blast_vfx 改按新设计；verify_zombie_goo_death_vfx 回到 v001 并新增冲击波开关的两侧断言。</t>
+        </is>
+      </c>
+      <c r="F28" s="109" t="inlineStr">
+        <is>
+          <t>新增两个稳定 AssetID 与 Prefab 路径；既有条目的 AssetID / 路径 / 状态逐格保留。FX01-17 因换造型语言升 v002 ⇒ 该行 Prefab SHA 变化（属显式改版，非漂移）。行为面：胖子僵尸的死亡表现改为与小僵尸同源 ×2 + 绿色冲击波；命中特效按「僵尸三兄弟 vs 其余」分流（枪击与近战同一判据）。小僵尸 / 警察僵尸的死亡表现逐字未变。</t>
+        </is>
+      </c>
+      <c r="G28" s="109" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="109" t="inlineStr">
+        <is>
+          <t>v0.1.23</t>
+        </is>
+      </c>
+      <c r="B29" s="109" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C29" s="109" t="inlineStr">
+        <is>
+          <t>条目更新（减面 + 尺寸契约补齐）</t>
+        </is>
+      </c>
+      <c r="D29" s="109" t="inlineStr">
+        <is>
+          <t>特效 · 子弹特效 / 3D-特效</t>
+        </is>
+      </c>
+      <c r="E29" s="109" t="inlineStr">
+        <is>
+          <t>弹体视觉**减面到 100 面以内**（业主「减面，减到 100 个面以下先」）。先用探针 _scratch/probe_mesh_lod_sweep 实测 CapsuleMesh / CylinderMesh / SphereMesh / BoxMesh 的分段→面数表，再据此定档：关键发现是 CapsuleMesh 的圆头来自 rings，rings=0 的「胶囊」= 平盖圆柱且比 CylinderMesh 贵 8 面（24 vs 16），而 rings=1 需 48 面/件、弹芯+外壳两件即吃掉 100 面全部预算 ⇒ 弹芯与外壳改 4 边棱柱。尾迹锥 rs=12→4（12 面）、滴珠 SphereMesh→BoxMesh（16→12 面）、黑洞/气球球核 SphereMesh 12×6→4×1（16 面）。结果：八弹种 44~80 面（改前 468~1020），均值 819→61.3，全部 &lt; 100；霰弹一次 5 发 3660→220 面。件数与尾迹构图未动（件数是账本与验收 EXPECTED_TRAIL_PARTS 的契约）。新增 prism 键为低面数弹体形状，旧键 capsule 在低面数档下按棱柱产出以免误用高价图元。验收 verify_bullet_vfx_profiles 扩至 samples=69，新增面数预算用例（上限 100 + 逐弹种实测值双层硬编码）；反向对照 RC6（MESH_SEGMENTS→12 精确报 132 面）/ RC7（SPHERE_RINGS→6 精确报 148 面）/ RC8（通用弹体 _SEGMENTS→12 精确报 132 面）均精准变红。另：本行同时收口 v0.1.19/v0.1.21 的尺寸档与碰撞分离契约（见备注列完整表述）。</t>
+        </is>
+      </c>
+      <c r="F29" s="109" t="inlineStr">
+        <is>
+          <t>稳定 AssetID / Prefab 路径 / Prefab SHA / 版本号全部不变（未改 .tscn，几何为运行时程序生成）；纯视觉：碰撞半径 / 伤害 / 射程 / 灯光契约均未动；外观为更低面数的方形棱柱（端面平），已记入开发记录并给出升档方案。</t>
+        </is>
+      </c>
+      <c r="G29" s="109" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="109" t="inlineStr">
+        <is>
+          <t>v0.1.23</t>
+        </is>
+      </c>
+      <c r="B30" s="109" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C30" s="109" t="inlineStr">
+        <is>
+          <t>条目更新（改版升版 + 落点契约）</t>
+        </is>
+      </c>
+      <c r="D30" s="109" t="inlineStr">
+        <is>
+          <t>特效 · 资产主表 / 3D-特效</t>
+        </is>
+      </c>
+      <c r="E30" s="109" t="inlineStr">
+        <is>
+          <t>FX01-20 VFX-GOO-HIT-3D 升 v002（业主 2026-10-14 第四轮）：① 造型语言由「12 枚绿方块爆开」换成 FX01-21 `VFX-METAL-SPARK-HIT-3D` 那一套 —— 5 颗方块 + 2 根长条火星，色板换成僵尸绿；两件共用父类 `VfxMetalSparkHit3D`（父类只留「资产身份 + 色板三项」钩子）⇒ 几何与运动学**逐字相同**，两件不可能各自漂移。② 尺寸不再独立定档：改为金属火星同档位 ×1.10（业主「放大大概 10%」）—— `Projectile3D.ZOMBIE_HIT_SIZE_RATIO = 1.10`，`GOO_HIT_SIZE_TARGET/ABSORB` 由金属那组派生（0.374 / 0.462）；近战侧新增 `PlayerMeleeCombat3D.ZOMBIE_HIT_BASE_SIZE = 0.42`，不再把近战件那套 size（0.88~1.6，按 FX01-05 基准定的）直接喂给火星造型（那正是业主说的「太大」）。③ 新增**贴肉落点契约**（业主同轮「受击的盒子没有贴着模型，碰撞盒里陷进去坐标大概 0.2 米」）：`Enemy3D.HIT_EFFECT_INSET_M = 0.20` + `hit_effect_anchor(hit_point, surface_normal)`，把碰撞壳上的命中点沿外法线反向收进模型；`Projectile3D._spawn_hit_effect()` 对 Enemy3D 一律先收，墙面 / 掩体不收（收了会钻进墙里）。④ 朝向契约由「全向对称、不消费 normal」改为**消费 `context.normal`**（v002 与 FX01-21 同形）；近战侧由 `PlayerMeleeCombat3D._hit_surface_normal()` 补「从怪体中心指向玩家」的外法线。⑤ 验收：`verify_hit_routing_vfx` 改按 v002（samples 26 → **27**），新增「两件同形」双向对照（同一 size 下件数 / 方块尺度 / 外推量 / 长条长度逐项相等，且颜色必须不同）、贴肉落点三向判定（给定法线 0.2m / 换法线落点跟着换 / 零法线兜底一致）、以及两条静态门禁（Projectile3D 必须过 hit_effect_anchor 且尺寸派生自 1.10；近战必须用 ZOMBIE_HIT_BASE_SIZE）。</t>
+        </is>
+      </c>
+      <c r="F30" s="109" t="inlineStr">
+        <is>
+          <t>既有条目的 AssetID / 路径 / 状态 / 其他分页逐格保留；本行只升 FX01-20 的版本与 Prefab SHA（脚本改动不改 tscn 结构，但 tscn 内 meta 版本号随 v002 更新 ⇒ SHA 变化，属显式升版、非漂移）。行为面：僵尸三兄弟的受击特效整体变小并转绿（与打其它物体的那件同形、大 10%），命中落点贴回模型 0.2m；FX01-21 与其他特效逐字未变。</t>
+        </is>
+      </c>
+      <c r="G30" s="109" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -6251,7 +6251,7 @@
       </c>
       <c r="Y39" s="76" t="inlineStr">
         <is>
-          <t>业主口径（2026-10-14）历轮：
+          <t xml:space="preserve">业主口径（2026-10-14）历轮：
 ① 首版：「使用爆炸粒子 ×12 的这个特效，**作为一个独立特效**，作为打中小僵尸、警察僵尸、胖子僵尸的受到枪击的特效」，追问后明确「**枪击 + 近战都用**」⇒ v001 = 12 枚绿方块从命中点炸开、0.26s。
 ② **本版 v002**：「**小僵尸和警察僵尸的受击特效太大了**，**使用击中其它物体的那个特效**，然后**改成绿色**即可，放大大概 **10%**」⇒ 造型语言整体换成 FX01-21 `VFX-METAL-SPARK-HIT-3D` 那一套（5 颗方块 + 2 根长条火星），色板换成僵尸绿（方块亮绿 / 长条深一档绿）。本件与 FX01-21 **共用同一个父类** `VfxMetalSparkHit3D`（父类只暴露「资产身份」与「色板三项」两个钩子）⇒ 形状 / 件数 / 方向 / 尺度包络 / 外推曲线 / 长条拉伸**逐字相同**，两件不可能各自漂移。
 ③ 同轮：「受击的盒子**没有贴着模型**，碰撞盒里陷进去坐标大概 **0.2 米**」⇒ 命中点必须先过 `Enemy3D.hit_effect_anchor()` 沿**外法线反向**收进模型 `HIT_EFFECT_INSET_M = 0.20` 米才出生（弹体是在碰撞壳表面判命中的，壳比模型大一圈）。收进去只对**怪**做 —— 墙面 / 掩体收了会钻进墙里。
@@ -6259,8 +6259,16 @@
 AssetID 里的 “goo” 是**历史名**（v001 是绿方块爆开）；保留不改名 —— AssetID 是账本与 Prefab meta 的**稳定键**，改名等于让既有登记条目失锚。
 **刻意无灯**：每发子弹 / 每次近战都生成的高频件（射速上限 12 发/s）。
 **消费 `context.normal`**（v002 起与 FX01-21 同形 ⇒ 贴合被击面）；近战侧由 `PlayerMeleeCombat3D._hit_surface_normal()` 给「从怪体中心指向玩家」的外法线。
-【贴肉量实测】真渲染现读几何（小僵尸 melee_chaser）：碰撞柱半径 1.020（玩法口径，从 collision_shape.shape 现读）、壳表面命中点 (0, 1.05, 1.02)、退 0.2m 后 (0, 1.05, 0.82) ⇒ 模型可视件半宽 0.810，**退完离模型只剩 0.010m（1cm）**。业主估的「大概 0.2 米」几乎精确，这个值不用再调。以后美术若收窄模型，`gap_after_inset` 会变大，那时再回调 `Enemy3D.HIT_EFFECT_INSET_M`（唯一旋钮，别去动特效几何）。
-【机位教训】验「某个方向上的一小段位移」时，**机位必须垂直于那段位移** —— goo_hit / goo_hit_float 第一版用斜前机位，0.2m 正好落在视线方向 ⇒ 两张图肉眼看不出区别（等于没验）；改侧视（沿 +X 看回原点）后 0.2m 落在屏幕横轴，一眼可读。</t>
+【贴肉落点实测（2026-10-15 复查修正）】**初版只做「固定下沉 0.20m」是不够的，真渲染实拍仍然悬空** ——业主第四轮的「大概 0.2 米」只是初估。根因：碰撞壳是**玩法口径的圆柱**（世界半径 melee 0.714 / ranged 0.770 / fat 0.770，各向同性），模型是**各向异性**的：
+  · 小僵尸  壳 0.714 vs 模型半宽 X 0.448 / Z 0.334 ⇒ 正面打，壳面比模型多 0.27~0.38m；
+  · 警察僵尸 壳 0.770 vs 模型半宽 X 0.449 / Z 0.602 ⇒ 同上；
+  · 胖子僵尸 壳 0.770 vs 模型半宽 X **1.839** / Z 0.712 ⇒ 反过来，壳面**已经在模型里面**。
+⇒ 一个常数不可能同时满足三只怪 × 各方向。现改为**按模型实测几何现算**：取「命中高度那一层的横截面 + 全高 Y」的包围盒，沿外法线反向射线求**进入**盒子的距离 `travel`，退让 = `travel + 0.03`（咬进肉里 3cm）；`travel == 0`（命中点已在模型内，胖子僵尸 X 向）时**不推**，否则埋进胖身子读成「从肚子里炸」（实测不加这条守卫会被推深到 0.912）。真渲染复验：小僵尸正面 壳半径 0.714 → 落点 0.302，退 0.412，落点落在模型半宽 0.332 之内、画面里爆点从「圆柱壳外圈」移到**僵尸手臂上**。
+踩过的三个坑（都写进代码注释了）：① 用**整只怪**的包围盒 ⇒ 头顶丸子头/脚边件把 Z 半宽从 0.332 撑到 0.622，退让少算 0.29m，解析读数说「距模型 0.000」而画面明显在外圈；必须按**命中高度切片**。② 包围盒**不能缓存** ⇒ 正式模型异步挂载，缓存会锁到「只有占位件」的那一版。③ 「盒心支撑函数」近似不行 ⇒ 支撑平面在角上相切，命中点偏离盒心时会残留 0.32~0.54m 悬空，必须用逐轴 slab 夹逼的射线求交。
+【容差】猪队友场景：模型包围盒按**轴对齐**算，而躯干是斜的 ⇒ 背面打会差约 0.25m，下一轮可考虑改用命中高度处的**水平最近顶点**（顶点数很小：小僵尸 1543 / 胖子 1513 / 警察 16468）。
+【机位教训】验「某个方向上的一小段位移」时，**机位必须垂直于那段位移** —— 第一版预览用斜前机位，0.2m 正好落在视线方向 ⇒ 两张图肉眼看不出区别（等于没验）；改侧视（沿 +X 看回原点）后才能读出。
+【双向判据】验收对「贴肉」是**两侧**都钉的：既要求落点不再悬空（距模型 ≤ 0.05m），也要求**不许比原始壳面命中点更深**（±0.05m）。只判「在盒内」是单向的 —— 实测把包围盒故意算大 2.6 倍，单向判据照样全绿。
+</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -1447,22 +1447,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="52">
       <c r="A6" s="57">
-        <f>COUNTA('资产主表'!$A$6:$A$40)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$42)</f>
         <v/>
       </c>
       <c r="B6" s="55" t="n"/>
       <c r="C6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$40,"已完成")+COUNTIF('资产主表'!$K$6:$K$40,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$40,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$40,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$40,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$40,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$40,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$42,"已完成")+COUNTIF('资产主表'!$K$6:$K$42,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$42,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$42,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$42,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$42,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$42,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="55" t="n"/>
       <c r="E6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$40,"待制作")+COUNTIF('资产主表'!$K$6:$K$40,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$42,"待制作")+COUNTIF('资产主表'!$K$6:$K$42,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="55" t="n"/>
       <c r="G6" s="57">
-        <f>COUNTIF('资产主表'!$S$6:$S$40,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$42,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="55" t="n"/>
@@ -1531,11 +1531,11 @@
         </is>
       </c>
       <c r="B10" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$40,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$42,A10)</f>
         <v/>
       </c>
       <c r="C10" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$40=A10)*(('资产主表'!$K$6:$K$40="已完成")+('资产主表'!$K$6:$K$40="原型已接入")+('资产主表'!$K$6:$K$40="正式美术已接入")+('资产主表'!$K$6:$K$40="已优化并正式接入")+('资产主表'!$K$6:$K$40="Blender源已完成")+('资产主表'!$K$6:$K$40="已导入；优化完成")+('资产主表'!$K$6:$K$40="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$42=A10)*(('资产主表'!$K$6:$K$42="已完成")+('资产主表'!$K$6:$K$42="原型已接入")+('资产主表'!$K$6:$K$42="正式美术已接入")+('资产主表'!$K$6:$K$42="已优化并正式接入")+('资产主表'!$K$6:$K$42="Blender源已完成")+('资产主表'!$K$6:$K$42="已导入；优化完成")+('资产主表'!$K$6:$K$42="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="62" t="n"/>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B11" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$40,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$42,A11)</f>
         <v/>
       </c>
       <c r="C11" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$40=A11)*(('资产主表'!$K$6:$K$40="已完成")+('资产主表'!$K$6:$K$40="原型已接入")+('资产主表'!$K$6:$K$40="正式美术已接入")+('资产主表'!$K$6:$K$40="已优化并正式接入")+('资产主表'!$K$6:$K$40="Blender源已完成")+('资产主表'!$K$6:$K$40="已导入；优化完成")+('资产主表'!$K$6:$K$40="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$42=A11)*(('资产主表'!$K$6:$K$42="已完成")+('资产主表'!$K$6:$K$42="原型已接入")+('资产主表'!$K$6:$K$42="正式美术已接入")+('资产主表'!$K$6:$K$42="已优化并正式接入")+('资产主表'!$K$6:$K$42="Blender源已完成")+('资产主表'!$K$6:$K$42="已导入；优化完成")+('资产主表'!$K$6:$K$42="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="62" t="n"/>
@@ -2115,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y40"/>
+  <dimension ref="A1:Y42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="51" min="1" max="1"/>
@@ -2387,7 +2387,7 @@
         <v/>
       </c>
       <c r="S6" s="63">
-        <f>IF(COUNTIF($R$6:$R$40,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="63" t="n"/>
@@ -2490,7 +2490,7 @@
         <v/>
       </c>
       <c r="S7" s="63">
-        <f>IF(COUNTIF($R$6:$R$40,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="63" t="n"/>
@@ -2593,7 +2593,7 @@
         <v/>
       </c>
       <c r="S8" s="63">
-        <f>IF(COUNTIF($R$6:$R$40,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="63" t="n"/>
@@ -2696,7 +2696,7 @@
         <v/>
       </c>
       <c r="S9" s="63">
-        <f>IF(COUNTIF($R$6:$R$40,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="63" t="n"/>
@@ -2803,7 +2803,7 @@
         <v/>
       </c>
       <c r="S10" s="63">
-        <f>IF(COUNTIF($R$6:$R$40,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="63" t="n"/>
@@ -2910,7 +2910,7 @@
         <v/>
       </c>
       <c r="S11" s="63">
-        <f>IF(COUNTIF($R$6:$R$40,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="63" t="n"/>
@@ -3017,7 +3017,7 @@
         <v/>
       </c>
       <c r="S12" s="63">
-        <f>IF(COUNTIF($R$6:$R$40,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="63" t="n"/>
@@ -3124,7 +3124,7 @@
         <v/>
       </c>
       <c r="S13" s="63">
-        <f>IF(COUNTIF($R$6:$R$40,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="63" t="n"/>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="S14" s="63">
-        <f>IF(COUNTIF($R$6:$R$40,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="63" t="n"/>
@@ -3338,7 +3338,7 @@
         <v/>
       </c>
       <c r="S15" s="63">
-        <f>IF(COUNTIF($R$6:$R$40,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="63" t="n"/>
@@ -3445,7 +3445,7 @@
         <v/>
       </c>
       <c r="S16" s="63">
-        <f>IF(COUNTIF($R$6:$R$40,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="63" t="n"/>
@@ -3564,7 +3564,7 @@
         <v/>
       </c>
       <c r="S17" s="55">
-        <f>IF(COUNTIF($R$6:$R$40,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="79" t="inlineStr">
@@ -3683,7 +3683,7 @@
         <v/>
       </c>
       <c r="S18" s="55">
-        <f>IF(COUNTIF($R$6:$R$40,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="79" t="inlineStr">
@@ -3806,7 +3806,7 @@
         <v/>
       </c>
       <c r="S19" s="55">
-        <f>IF(COUNTIF($R$6:$R$40,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="79" t="inlineStr">
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="S20" s="55">
-        <f>IF(COUNTIF($R$6:$R$40,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="79" t="inlineStr">
@@ -4046,7 +4046,7 @@
         <v/>
       </c>
       <c r="S21" s="55">
-        <f>IF(COUNTIF($R$6:$R$40,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="79" t="inlineStr">
@@ -4165,7 +4165,7 @@
         <v/>
       </c>
       <c r="S22" s="55">
-        <f>IF(COUNTIF($R$6:$R$40,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="79" t="inlineStr">
@@ -4284,7 +4284,7 @@
         <v/>
       </c>
       <c r="S23" s="55">
-        <f>IF(COUNTIF($R$6:$R$40,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="79" t="inlineStr">
@@ -4403,7 +4403,7 @@
         <v/>
       </c>
       <c r="S24" s="55">
-        <f>IF(COUNTIF($R$6:$R$40,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="79" t="inlineStr">
@@ -4522,7 +4522,7 @@
         <v/>
       </c>
       <c r="S25" s="55">
-        <f>IF(COUNTIF($R$6:$R$40,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="79" t="inlineStr">
@@ -4641,7 +4641,7 @@
         <v/>
       </c>
       <c r="S26" s="79">
-        <f>IF(COUNTIF($R$6:$R$40,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="79" t="inlineStr">
@@ -4767,7 +4767,7 @@
         <v/>
       </c>
       <c r="S27" s="76">
-        <f>IF(COUNTIF($R$6:$R$40,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="76" t="inlineStr">
@@ -4889,7 +4889,7 @@
         <v/>
       </c>
       <c r="S28" s="76">
-        <f>IF(COUNTIF($R$6:$R$40,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="76" t="inlineStr">
@@ -5011,7 +5011,7 @@
         <v/>
       </c>
       <c r="S29" s="76">
-        <f>IF(COUNTIF($R$6:$R$40,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="76" t="inlineStr">
@@ -5133,7 +5133,7 @@
         <v/>
       </c>
       <c r="S30" s="76">
-        <f>IF(COUNTIF($R$6:$R$40,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="76" t="inlineStr">
@@ -5255,7 +5255,7 @@
         <v/>
       </c>
       <c r="S31" s="76">
-        <f>IF(COUNTIF($R$6:$R$40,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="76" t="inlineStr">
@@ -5377,7 +5377,7 @@
         <v/>
       </c>
       <c r="S32" s="76">
-        <f>IF(COUNTIF($R$6:$R$40,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="76" t="inlineStr">
@@ -5499,7 +5499,7 @@
         <v/>
       </c>
       <c r="S33" s="76">
-        <f>IF(COUNTIF($R$6:$R$40,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="76" t="inlineStr">
@@ -5621,7 +5621,7 @@
         <v/>
       </c>
       <c r="S34" s="76">
-        <f>IF(COUNTIF($R$6:$R$40,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="76" t="inlineStr">
@@ -5739,7 +5739,7 @@
         <v/>
       </c>
       <c r="S35" s="76">
-        <f>IF(COUNTIF($R$6:$R$40,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="76" t="inlineStr">
@@ -5858,7 +5858,7 @@
         <v/>
       </c>
       <c r="S36" s="76">
-        <f>IF(COUNTIF($R$6:$R$40,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="76" t="inlineStr">
@@ -5979,7 +5979,7 @@
         <v/>
       </c>
       <c r="S37" s="76">
-        <f>IF(COUNTIF($R$6:$R$40,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="76" t="inlineStr">
@@ -6100,7 +6100,7 @@
         <v/>
       </c>
       <c r="S38" s="76">
-        <f>IF(COUNTIF($R$6:$R$40,R38)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R38)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T38" s="76" t="inlineStr">
@@ -6221,7 +6221,7 @@
         <v/>
       </c>
       <c r="S39" s="76">
-        <f>IF(COUNTIF($R$6:$R$40,R39)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R39)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T39" s="76" t="inlineStr">
@@ -6359,7 +6359,7 @@
         <v/>
       </c>
       <c r="S40" s="76">
-        <f>IF(COUNTIF($R$6:$R$40,R40)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$42,R40)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T40" s="76" t="inlineStr">
@@ -6390,6 +6390,248 @@
       <c r="Y40" s="76" t="inlineStr">
         <is>
           <t>业主口径（2026-10-14）：原本是「原来那个特效缩小 60%，作为击中其它物体的特效」，追问缩小读数后业主改为「**重新制作一个**，通过一个打击到金属的粒子反馈的特效，用白色方块粒子和 2 根长条的金色火星一样飞溅去替代，这个不要用太多粒子，**4-5 颗 + 2 根金色火星**即可」⇒ 本件是**新资产**，不是 VFX-IMPACT-3D 的改版；VFX-IMPACT-3D 保持原样，继续服务它剩下的用途（非僵尸怪种死亡爆点、护盾弹开）。造型：5 颗白方块（`ToonVfxGeometry.unit_cube_mesh()`）+ 2 根金色长条火星（`ToonVfxGeometry.streak_mesh()`，**长轴 = 本地 Z** ⇒ `scale.z` 直接就是米数，长度 0.50 → 1.30 × size，从短粗拉成细长）。朝向契约 `context.normal`（**本件是唯一消费法线的战斗命中件**）：局部 +Y 对齐法线 ⇒ 局部 XZ 就是被击表面；**金色火星在切平面内擦出**（沿表面擦出去，|世界方向·法线| ≤ 0.20 有断言）、白方块沿法线向外喷。朝向用 `Basis.looking_at`（把本地 **-Z** 对到切向）—— 不能写 `Quaternion(UP, dir)`，后者是把 +Y 转过去，会让火星指向天上。**刻意无灯**：与 FX01-20 同理（高频件）。尺寸 `Projectile3D.METAL_SPARK_SIZE_TARGET = 0.34`（业主「受击的特效也不要太大」）。纯视觉无碰撞体，走 VfxPool3D（FX01_METAL_SPARK_HIT）。真渲染校准（`outputs/combat_vfx_batch2/combat_vfx_batch2_timeline.png`）：首版张角 0.34 rad、长 0.22→0.78 ⇒ 两根几乎重叠、读成「一根小凸起」；抬到 0.62 rad / 0.50→1.30 才成了「长条」。首版白方块切向占比 0.35~0.8、外推 0.30m ⇒ 5 颗挤成一坨，抬高切向占比并加大外推后才读成一撮碎屑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="76" t="inlineStr">
+        <is>
+          <t>VFX-FATE-ROCK-3D</t>
+        </is>
+      </c>
+      <c r="B41" s="76" t="inlineStr">
+        <is>
+          <t>力量滚石弹</t>
+        </is>
+      </c>
+      <c r="C41" s="76" t="inlineStr">
+        <is>
+          <t>子弹特效</t>
+        </is>
+      </c>
+      <c r="D41" s="76" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="E41" s="76" t="inlineStr">
+        <is>
+          <t>fate_rock</t>
+        </is>
+      </c>
+      <c r="F41" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G41" s="76" t="n"/>
+      <c r="H41" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I41" s="76" t="inlineStr">
+        <is>
+          <t>fate_rock</t>
+        </is>
+      </c>
+      <c r="J41" s="76" t="inlineStr">
+        <is>
+          <t>力量命运卡</t>
+        </is>
+      </c>
+      <c r="K41" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L41" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M41" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N41" s="76" t="inlineStr">
+        <is>
+          <t>低多边形石头，直径0.36m；随弹体滚动，不进入VfxPool3D</t>
+        </is>
+      </c>
+      <c r="O41" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_fate_rock_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P41" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxFateRock3D.gd; docs/v0.1/14_技术施工_命运塔罗牌组.md</t>
+        </is>
+      </c>
+      <c r="Q41" s="76" t="inlineStr">
+        <is>
+          <t>命运;力量;滚石;碎裂</t>
+        </is>
+      </c>
+      <c r="R41" s="76">
+        <f>LOWER(TRIM(C41)&amp;"|"&amp;TRIM(D41)&amp;"|"&amp;TRIM(E41)&amp;"|"&amp;TRIM(F41)&amp;"|"&amp;TRIM(H41)&amp;"|"&amp;TRIM(I41))</f>
+        <v/>
+      </c>
+      <c r="S41" s="76">
+        <f>IF(COUNTIF($R$6:$R$42,R41)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T41" s="76" t="inlineStr">
+        <is>
+          <t>e85c77c8f7d178fd9cabe8a806e729bd81c4a9cd9969c3ec468cdbb302930138</t>
+        </is>
+      </c>
+      <c r="U41" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V41" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="W41" s="76" t="inlineStr">
+        <is>
+          <t>原创Prefab几何</t>
+        </is>
+      </c>
+      <c r="X41" s="76" t="inlineStr">
+        <is>
+          <t>FX01-22</t>
+        </is>
+      </c>
+      <c r="Y41" s="76" t="inlineStr">
+        <is>
+          <t>低多边形石头，直径0.36m；随弹体滚动，不进入VfxPool3D；行为由Projectile3D持有；碰撞不在VFX里。；隔离专项及真实渲染已验收，见2026-10-16_star_physical_mounts开发记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="76" t="inlineStr">
+        <is>
+          <t>VFX-FATE-ROCK-SHATTER-3D</t>
+        </is>
+      </c>
+      <c r="B42" s="76" t="inlineStr">
+        <is>
+          <t>力量碎石爆散</t>
+        </is>
+      </c>
+      <c r="C42" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D42" s="76" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="E42" s="76" t="inlineStr">
+        <is>
+          <t>fate_rock_shatter</t>
+        </is>
+      </c>
+      <c r="F42" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G42" s="76" t="n"/>
+      <c r="H42" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I42" s="76" t="inlineStr">
+        <is>
+          <t>fate_rock_shatter</t>
+        </is>
+      </c>
+      <c r="J42" s="76" t="inlineStr">
+        <is>
+          <t>力量命运卡</t>
+        </is>
+      </c>
+      <c r="K42" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L42" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M42" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N42" s="76" t="inlineStr">
+        <is>
+          <t>8枚石块径向飞散，0.55s；无灯无碰撞；进入VfxPool3D</t>
+        </is>
+      </c>
+      <c r="O42" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_fate_rock_shatter_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P42" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxFateRockShatter3D.gd; docs/v0.1/14_技术施工_命运塔罗牌组.md</t>
+        </is>
+      </c>
+      <c r="Q42" s="76" t="inlineStr">
+        <is>
+          <t>命运;力量;滚石;碎裂</t>
+        </is>
+      </c>
+      <c r="R42" s="76">
+        <f>LOWER(TRIM(C42)&amp;"|"&amp;TRIM(D42)&amp;"|"&amp;TRIM(E42)&amp;"|"&amp;TRIM(F42)&amp;"|"&amp;TRIM(H42)&amp;"|"&amp;TRIM(I42))</f>
+        <v/>
+      </c>
+      <c r="S42" s="76">
+        <f>IF(COUNTIF($R$6:$R$42,R42)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T42" s="76" t="inlineStr">
+        <is>
+          <t>8e25fad8d8af63c4f41ea3d8ac6b6ddc44c0a702c7f7fcd546dfac2ebddc4726</t>
+        </is>
+      </c>
+      <c r="U42" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V42" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="W42" s="76" t="inlineStr">
+        <is>
+          <t>原创Prefab几何</t>
+        </is>
+      </c>
+      <c r="X42" s="76" t="inlineStr">
+        <is>
+          <t>FX01-23</t>
+        </is>
+      </c>
+      <c r="Y42" s="76" t="inlineStr">
+        <is>
+          <t>8枚石块径向飞散，0.55s；无灯无碰撞；进入VfxPool3D；行为由Projectile3D持有；碰撞不在VFX里。；隔离专项及真实渲染已验收，见2026-10-16_star_physical_mounts开发记录。</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6843,7 @@
     <row r="427" ht="84.75" customHeight="1" s="52"/>
     <row r="429" ht="120" customHeight="1" s="52"/>
   </sheetData>
-  <autoFilter ref="A5:Y34"/>
+  <autoFilter ref="A5:Y42"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -6614,13 +6856,13 @@
     <cfRule type="containsText" priority="3" operator="containsText" dxfId="8" text="待制作"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,子弹特效,音效,音乐"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,design_only,authored,exported_pending_godot_validation,validated,active,已从运行场景移除,白盒组件"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6673,6 +6915,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="84" t="inlineStr">
         <is>
@@ -9289,14 +9532,178 @@
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="52">
-      <c r="H42" s="101" t="n"/>
-      <c r="I42" s="51" t="n"/>
-      <c r="N42" s="51" t="n"/>
+      <c r="A42" s="100" t="inlineStr">
+        <is>
+          <t>FX01-22</t>
+        </is>
+      </c>
+      <c r="B42" s="101" t="inlineStr">
+        <is>
+          <t>VFX-FATE-ROCK-3D</t>
+        </is>
+      </c>
+      <c r="C42" s="51" t="inlineStr">
+        <is>
+          <t>力量滚石弹</t>
+        </is>
+      </c>
+      <c r="D42" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_fate_rock_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E42" s="51" t="inlineStr">
+        <is>
+          <t>无（Prefab几何）</t>
+        </is>
+      </c>
+      <c r="F42" s="51" t="inlineStr">
+        <is>
+          <t>无（Prefab几何）</t>
+        </is>
+      </c>
+      <c r="G42" s="51" t="inlineStr">
+        <is>
+          <t>低多边形石头，直径0.36m；随弹体滚动，不进入VfxPool3D</t>
+        </is>
+      </c>
+      <c r="H42" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxFateRock3D.gd</t>
+        </is>
+      </c>
+      <c r="I42" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J42" s="51" t="inlineStr">
+        <is>
+          <t>Projectile3D玩法碰撞</t>
+        </is>
+      </c>
+      <c r="K42" s="51" t="inlineStr">
+        <is>
+          <t>无CollisionObject3D/CollisionShape3D</t>
+        </is>
+      </c>
+      <c r="L42" s="51" t="inlineStr">
+        <is>
+          <t>0.36m</t>
+        </is>
+      </c>
+      <c r="M42" s="51" t="inlineStr">
+        <is>
+          <t>原点=弹心；-Z前向；局部X滚动</t>
+        </is>
+      </c>
+      <c r="N42" s="51" t="inlineStr">
+        <is>
+          <t>Projectile3D</t>
+        </is>
+      </c>
+      <c r="O42" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P42" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q42" s="51" t="inlineStr">
+        <is>
+          <t>verify_star_physical_mounts与真实渲染通过；开发记录2026-10-16_star_physical_mounts.md</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="52">
-      <c r="H43" s="101" t="n"/>
-      <c r="I43" s="51" t="n"/>
-      <c r="N43" s="51" t="n"/>
+      <c r="A43" s="100" t="inlineStr">
+        <is>
+          <t>FX01-23</t>
+        </is>
+      </c>
+      <c r="B43" s="101" t="inlineStr">
+        <is>
+          <t>VFX-FATE-ROCK-SHATTER-3D</t>
+        </is>
+      </c>
+      <c r="C43" s="51" t="inlineStr">
+        <is>
+          <t>力量碎石爆散</t>
+        </is>
+      </c>
+      <c r="D43" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_fate_rock_shatter_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E43" s="51" t="inlineStr">
+        <is>
+          <t>无（Prefab几何）</t>
+        </is>
+      </c>
+      <c r="F43" s="51" t="inlineStr">
+        <is>
+          <t>无（Prefab几何）</t>
+        </is>
+      </c>
+      <c r="G43" s="51" t="inlineStr">
+        <is>
+          <t>8枚石块径向飞散，0.55s；无灯无碰撞；进入VfxPool3D</t>
+        </is>
+      </c>
+      <c r="H43" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxFateRockShatter3D.gd</t>
+        </is>
+      </c>
+      <c r="I43" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J43" s="51" t="inlineStr">
+        <is>
+          <t>Projectile3D玩法碰撞</t>
+        </is>
+      </c>
+      <c r="K43" s="51" t="inlineStr">
+        <is>
+          <t>无CollisionObject3D/CollisionShape3D</t>
+        </is>
+      </c>
+      <c r="L43" s="51" t="inlineStr">
+        <is>
+          <t>0.55s，8枚碎块</t>
+        </is>
+      </c>
+      <c r="M43" s="51" t="inlineStr">
+        <is>
+          <t>原点=命中点；径向碎裂</t>
+        </is>
+      </c>
+      <c r="N43" s="51" t="inlineStr">
+        <is>
+          <t>Projectile3D</t>
+        </is>
+      </c>
+      <c r="O43" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P43" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q43" s="51" t="inlineStr">
+        <is>
+          <t>verify_star_physical_mounts与真实渲染通过；开发记录2026-10-16_star_physical_mounts.md</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="52">
       <c r="H44" s="101" t="n"/>
@@ -10364,7 +10771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="51" min="1" max="1"/>
@@ -11339,6 +11746,43 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>v0.1.star-r3</t>
+        </is>
+      </c>
+      <c r="B31" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C31" s="51" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D31" s="51" t="inlineStr">
+        <is>
+          <t>FX01-22/23</t>
+        </is>
+      </c>
+      <c r="E31" s="51" t="inlineStr">
+        <is>
+          <t>力量石头弹与碎裂独立Prefab；正式路由接入，验收中</t>
+        </is>
+      </c>
+      <c r="F31" s="51" t="inlineStr">
+        <is>
+          <t>不改旧资产路径</t>
+        </is>
+      </c>
+      <c r="G31" s="51" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -3569,7 +3569,7 @@
       </c>
       <c r="T17" s="79" t="inlineStr">
         <is>
-          <t>66ab8d6bc0e2729ca56c7f3c46a588e5f74890cfdf02b90de1fdc46fd1a67648</t>
+          <t>9457d360dc6529e42502980b94188d13f76da5efb581b261cfb9b8adbd0f5ff6</t>
         </is>
       </c>
       <c r="U17" s="79" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="T18" s="79" t="inlineStr">
         <is>
-          <t>2ee5109b1876ea2114ac5c73b4bd0e2fc0348e1209a9d2ca16bc8ef9834ff357</t>
+          <t>59cd5409b33ff9fae9c541b357699249d8f0574bc21add6fec2d1fdfd89a098e</t>
         </is>
       </c>
       <c r="U18" s="79" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="T19" s="79" t="inlineStr">
         <is>
-          <t>3405769a7da2c227a4ad0239e08963851ff8b739dcaff1f80fd8d5e35eb705ce</t>
+          <t>3a5f9e551802a19e6415e15ee32cea76fe74545bf64af0fcb847c54d3972e740</t>
         </is>
       </c>
       <c r="U19" s="79" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="T20" s="79" t="inlineStr">
         <is>
-          <t>b389efe1d1fcfd30087a6d3f3f2784effee95cf6c54769fde27ecb6806011a05</t>
+          <t>66d910c4fbcfd63176427c8012d3b6dbb11c4e0999587b34a3a66d6202920017</t>
         </is>
       </c>
       <c r="U20" s="79" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="T21" s="79" t="inlineStr">
         <is>
-          <t>a19f4266f8be8a302e5002fd118aa5e34a7de8a6dbd282807fb21522a8e12814</t>
+          <t>df2cb64e06aa312f19a4c330a13c37b8c36f6884308c900181a7597a051fbf93</t>
         </is>
       </c>
       <c r="U21" s="55" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="T26" s="79" t="inlineStr">
         <is>
-          <t>a3c84c7e8842369fee46a224880589f1470e2beb68b2205a5ad41c4659832685</t>
+          <t>2293c574f80d5d6103c0088c5fc385c1b9bd72600cc71c61bf2e4748d9f6b2d2</t>
         </is>
       </c>
       <c r="U26" s="79" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="T27" s="76" t="inlineStr">
         <is>
-          <t>d85bb501f79d65493fa2225b0af3516873bf73e1b5c8060e6055fc6bdd7a6530</t>
+          <t>4568edb503262d863cb17629936935e4b1f02678de623f67776667c41df8f455</t>
         </is>
       </c>
       <c r="U27" s="76" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="T28" s="76" t="inlineStr">
         <is>
-          <t>a9ecbcc2cf4b74001414b802a5acb0615289fdc8d28ed96fa1360cca52665c4b</t>
+          <t>778be3a1a693e11c1bed08c51c511df742e8502c74c60fc6c3d9919f00141c8b</t>
         </is>
       </c>
       <c r="U28" s="76" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="T29" s="76" t="inlineStr">
         <is>
-          <t>49bd24a7c468a829e6e7dffe5b6d79c93e9edb4dd3986d9489d151058ba8f6bd</t>
+          <t>c31373aa7b45d6539702f03f12f5536ee5a5766e694e2612f82b9887c1280517</t>
         </is>
       </c>
       <c r="U29" s="76" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="T30" s="76" t="inlineStr">
         <is>
-          <t>450125ae4af8dfe45964f78542d09c5e604bc348a56ef52454378b1430daa37c</t>
+          <t>7dac07ff53a03e159245a033af9cd01cde83837d57c1cc8d96e0fdd2aa13aed3</t>
         </is>
       </c>
       <c r="U30" s="76" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="T31" s="76" t="inlineStr">
         <is>
-          <t>8c1ce8b1e775b884b01e6644cd75f57d9cb47cd18e1a3a41e8374f600d84e93d</t>
+          <t>16668244baa6415476e9f53a7207843de1ec43981cc46b8fba3b77259c43aa66</t>
         </is>
       </c>
       <c r="U31" s="76" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="T32" s="76" t="inlineStr">
         <is>
-          <t>f3f7ad5dcce3205908cf0a115ce425f6030daf4427ede2d394b6997192546032</t>
+          <t>7b674e50097eef28c900780031f808ddc6077efed1194dae6debe74b710fe87e</t>
         </is>
       </c>
       <c r="U32" s="76" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="T33" s="76" t="inlineStr">
         <is>
-          <t>1f7c02ebe353097eda9d818ce583b9a12935917c69f80929bfc0142d7fa417f2</t>
+          <t>3e3b832d8bbd74d0c82fded0ff4e416722a17b2a64af56d8ebee4a4cc03c354a</t>
         </is>
       </c>
       <c r="U33" s="76" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="T34" s="76" t="inlineStr">
         <is>
-          <t>e711140cc2daba69230168a54f8f1e03a958015e2c88be8baeaf6f3b1d320e6d</t>
+          <t>4cf2bd23539184d121d209a180475951bd7ae9478b35e8be565ca15515dc36cf</t>
         </is>
       </c>
       <c r="U34" s="76" t="inlineStr">
@@ -6915,7 +6915,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="84" t="inlineStr">
         <is>
@@ -7716,7 +7715,7 @@
       </c>
       <c r="G16" s="51" t="inlineStr">
         <is>
-          <t>受击伤害数字上升飘字；Label3D + 黑边 + 颜色编码（红/橙/暴击金）；参数 effect_color + context.text_value。</t>
+          <t>受击伤害数字上升飘字；Label3D + 漫画风超粗字形 + 粗近黑勾边 + 颜色编码（红/橙/暴击金）；参数 effect_color + context.text_value/magnitude/critical + 五维随机（spawn_offset/rise_scale/drift/pop_scale/duration_scale）。</t>
         </is>
       </c>
       <c r="H16" s="101" t="inlineStr">
@@ -7741,7 +7740,7 @@
       </c>
       <c r="L16" s="101" t="inlineStr">
         <is>
-          <t>Label3D pixel_size=0.010；lifetime 0.72s</t>
+          <t>Label3D pixel_size=0.00375；MSDF 128 + msdf_pixel_range 64（描边可达上限 ≈ range/2）；字号分档 116/134/152（世界字高 0.435/0.503/0.570 m）；描边 26/30/34；lifetime 0.70s × duration_scale；基线上升 0.90m</t>
         </is>
       </c>
       <c r="M16" s="51" t="inlineStr">
@@ -7761,12 +7760,12 @@
       </c>
       <c r="P16" s="101" t="inlineStr">
         <is>
-          <t>v001</t>
+          <t>v003</t>
         </is>
       </c>
       <c r="Q16" s="51" t="inlineStr">
         <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_damage_number_root_top3d_v001.tscn + 脚本=src/vfx/VfxDamageNumber3D.gd；根节点=VfxDamageNumber3D(Node3D)；FX编号 FX02-01；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value</t>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_damage_number_root_top3d.tscn + 脚本=src/vfx/VfxDamageNumber3D.gd；根节点=VfxDamageNumber3D(Node3D)；FX编号 FX02-01；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由。【2026-10-16 样式重做】字体与样式真源收敛到 src/vfx/DamageNumberStyle.gd（漫画风超粗体：字体链首选 Impact、字重 900、MSDF 128；近黑粗勾边 ≈ 字高 22%）；随机数只活在调用方 Enemy3D._damage_number_context()，特效脚本对同一 context 逐位可复现。【P0 修复】_on_tick 原以**赋值**写 position（position.y = rise_t × 距离），出生坐标第一帧即被清零 —— 实测实机飘字跑到世界原点上方不到 1 米、与怪物楼层无关；改为 position = _origin_local + 偏移。Prefab 路径去掉历史误写的 _v001 后缀。【2026-10-17 勾边修复】**勾边修复：`msdf_pixel_range` 太小导致描边被截成 1px 细丝**。Godot 的 MSDF 字体下描边可达上限 ≈ msdf_pixel_range / 2，默认 16 只够到 8，而本件声明 26/30/34 ⇒ 被提前截断（症状：不报错不变红，且 outline_size 填 26 与 116 渲染结果逐像素完全相同）。修法：`DamageNumberStyle.MSDF_PIXEL_RANGE = 64`，在 `make_font()` 里赋给 `SystemFont.msdf_pixel_range`；三条链路共用该字体工厂，一处即全覆盖。定档实测（字形高约 108px 定尺拍摄）：range 16 → 实画 6px、48 → 21px、64/80 → 26px 足额、96 → 左右不对称（一侧整条丢失）⇒ 取 64，验收另设上界护栏 80。验收新增常量钉子 + 下界不等式 + 逐档「实例真带该值」断言；反向对照三组（16／96／删赋值）均精准变红后复绿。实机距离 A/B：描边像素 160 → 13,421（×83.9）。</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7792,7 @@
       </c>
       <c r="G17" s="51" t="inlineStr">
         <is>
-          <t>治疗/恢复数字上升飘字；Label3D + 绿色调（+ 白色描边）；参数 context.text_value。</t>
+          <t>治疗/恢复数字上升飘字；Label3D + 漫画风超粗字形 + 粗近黑勾边 + 治疗绿；参数 context.text_value/magnitude + 五维随机（同 FX02-01）。</t>
         </is>
       </c>
       <c r="H17" s="101" t="inlineStr">
@@ -7818,7 +7817,7 @@
       </c>
       <c r="L17" s="101" t="inlineStr">
         <is>
-          <t>Label3D pixel_size=0.010；lifetime 0.72s</t>
+          <t>Label3D pixel_size=0.00375；MSDF 128 + msdf_pixel_range 64（描边可达上限 ≈ range/2）；字号 116（世界字高 0.435 m）；描边 26；lifetime 0.70s × duration_scale；基线上升 0.90m</t>
         </is>
       </c>
       <c r="M17" s="51" t="inlineStr">
@@ -7838,12 +7837,12 @@
       </c>
       <c r="P17" s="101" t="inlineStr">
         <is>
-          <t>v001</t>
+          <t>v003</t>
         </is>
       </c>
       <c r="Q17" s="51" t="inlineStr">
         <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_heal_number_root_top3d_v001.tscn + 脚本=src/vfx/VfxHealNumber3D.gd；根节点=VfxHealNumber3D(Node3D)；FX编号 FX02-02；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value</t>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_heal_number_root_top3d.tscn + 脚本=src/vfx/VfxHealNumber3D.gd；根节点=VfxHealNumber3D(Node3D)；FX编号 FX02-02；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value；调用方：Enemy3D._spawn_heal_number 经 VfxPool3D 路由（2026-10-16 起；此前治疗误借 VFX-DAMAGE-NUMBER-3D ⇒ 回血飘红字「0」，而本 AssetID 全工程零调用方）。【2026-10-16 样式重做】字体与样式取 src/vfx/DamageNumberStyle.gd，与 FX02-01 同源。Prefab 路径去掉历史误写的 _v001 后缀。【2026-10-17 勾边修复】**勾边修复：`msdf_pixel_range` 太小导致描边被截成 1px 细丝**。Godot 的 MSDF 字体下描边可达上限 ≈ msdf_pixel_range / 2，默认 16 只够到 8，而本件声明 26/30/34 ⇒ 被提前截断（症状：不报错不变红，且 outline_size 填 26 与 116 渲染结果逐像素完全相同）。修法：`DamageNumberStyle.MSDF_PIXEL_RANGE = 64`，在 `make_font()` 里赋给 `SystemFont.msdf_pixel_range`；三条链路共用该字体工厂，一处即全覆盖。定档实测（字形高约 108px 定尺拍摄）：range 16 → 实画 6px、48 → 21px、64/80 → 26px 足额、96 → 左右不对称（一侧整条丢失）⇒ 取 64，验收另设上界护栏 80。验收新增常量钉子 + 下界不等式 + 逐档「实例真带该值」断言；反向对照三组（16／96／删赋值）均精准变红后复绿。实机距离 A/B：描边像素 160 → 13,421（×83.9）。</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="51" min="1" max="1"/>
@@ -10798,6 +10797,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="52">
       <c r="A5" s="58" t="inlineStr">
         <is>
@@ -11780,6 +11780,80 @@
       <c r="G31" s="51" t="inlineStr">
         <is>
           <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>v0.1.24</t>
+        </is>
+      </c>
+      <c r="B32" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C32" s="51" t="inlineStr">
+        <is>
+          <t>条目更新（样式重做 + P0 修复 + 调用方收口）</t>
+        </is>
+      </c>
+      <c r="D32" s="51" t="inlineStr">
+        <is>
+          <t>特效 · 3D-特效（FX02-01 / FX02-02）</t>
+        </is>
+      </c>
+      <c r="E32" s="51" t="inlineStr">
+        <is>
+          <t>数字飘字字体与样式重做（业主：「先收口，然后要修改字体和样式，走漫画风格的粗体+沟边的，大一点，然后字体飘起的力度感强一些，不要太整齐，带一些随机」）。① 收口四项：删 Enemy3D 里与 _spawn_damage_number 双发的 _spawn_effect("VFX-DAMAGE-NUMBER-3D")（无 context ⇒ 飘红字 0，2026-09-21 审计 P0-1）；治疗改走 VFX-HEAL-NUMBER-3D；字体口径收敛到新建单一真源 src/vfx/DamageNumberStyle.gd；verify_3d_enemy_behavior_flow 的字体断言改从池取生效实例。② 样式：漫画风超粗体（Impact 链 / 字重 900 / MSDF 128）+ 粗勾边（26/30/34 ≈ 字高 22%）+ 放大（世界字高 0.320 → 0.435/0.503/0.570 m，普通档 1.36×）。③ 力度：基线上升 0.60 → 0.90 m、改 ease-out cubic、出生弹出 [1.28,1.48] 后 0.14s 收束。④ 随机：五维全由调用方生成，特效脚本保持逐位确定性。⑤ P0：_on_tick 原以赋值写 position，出生坐标第一帧被清零（飘字跑到世界原点上方不到 1 米）；改为叠加出生点基准。</t>
+        </is>
+      </c>
+      <c r="F32" s="51" t="inlineStr">
+        <is>
+          <t>AssetID / Prefab 路径 / 版本号（升 v002）稳定；Prefab .tscn 文件逐字未改（样式全在脚本侧）；VfxPool3D 注册表未动；碰撞/伤害/存档无影响。既有条目 AssetID / 路径 / 状态逐格保留。</t>
+        </is>
+      </c>
+      <c r="G32" s="51" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>v0.1.25</t>
+        </is>
+      </c>
+      <c r="B33" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C33" s="51" t="inlineStr">
+        <is>
+          <t>条目更新（勾边修复）</t>
+        </is>
+      </c>
+      <c r="D33" s="51" t="inlineStr">
+        <is>
+          <t>特效 · 3D-特效（FX02-01 / FX02-02）</t>
+        </is>
+      </c>
+      <c r="E33" s="51" t="inlineStr">
+        <is>
+          <t>数字飘字黑色勾边修复（业主：「要带黑色描边，我说的是伤害飘字」）。上一轮 v003.9 把描边定到 26/30/34 并声称按字高 22%，但实机从来没画出来过：Godot 的 MSDF 字体下描边可达上限 ≈ msdf_pixel_range / 2，默认 16 只够到 8，26/30/34 远超上限被提前截断成约 1px 细丝（症状：不报错、不变红，且 outline_size 填 26 与填 116 渲染结果逐像素完全相同）。修法：DamageNumberStyle 新增 MSDF_PIXEL_RANGE = 64 并在 make_font() 赋值，VfxDamageNumber3D / VfxHealNumber3D / CombatDamageNumber3D 三条链路共用该工厂故一处即全覆盖。定档：需求 range = 2 × max(描边 × msdf_size / 字号) = 2 × (34 × 128 / 152) ≈ 57.4 ⇒ 取 64；实测 range 16 → 6px、48 → 21px、64/80 → 26px 足额、96 → 左右不对称（过大反崩）⇒ 护栏上界 80。验收新增常量钉子 + 下界不等式 + 上界护栏 + 逐档「实机实例真带该值」断言；反向对照三组（range→16 / range→96 / 删掉 make_font 里那行赋值）均精准变红后还原复绿。</t>
+        </is>
+      </c>
+      <c r="F33" s="51" t="inlineStr">
+        <is>
+          <t>AssetID / Prefab 路径 / 版本号（升 v003）稳定；Prefab .tscn 文件逐字未改（纯脚本侧）；VfxPool3D 注册表未动；碰撞/伤害/存档无影响。既有条目 AssetID / 路径 / 状态逐格保留。</t>
+        </is>
+      </c>
+      <c r="G33" s="51" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -1447,22 +1447,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="52">
       <c r="A6" s="57">
-        <f>COUNTA('资产主表'!$A$6:$A$42)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$47)</f>
         <v/>
       </c>
       <c r="B6" s="55" t="n"/>
       <c r="C6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$42,"已完成")+COUNTIF('资产主表'!$K$6:$K$42,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$42,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$42,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$42,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$42,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$42,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$47,"已完成")+COUNTIF('资产主表'!$K$6:$K$47,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$47,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$47,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$47,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$47,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$47,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="55" t="n"/>
       <c r="E6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$42,"待制作")+COUNTIF('资产主表'!$K$6:$K$42,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$47,"待制作")+COUNTIF('资产主表'!$K$6:$K$47,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="55" t="n"/>
       <c r="G6" s="57">
-        <f>COUNTIF('资产主表'!$S$6:$S$42,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$47,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="55" t="n"/>
@@ -1531,11 +1531,11 @@
         </is>
       </c>
       <c r="B10" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$42,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$47,A10)</f>
         <v/>
       </c>
       <c r="C10" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$42=A10)*(('资产主表'!$K$6:$K$42="已完成")+('资产主表'!$K$6:$K$42="原型已接入")+('资产主表'!$K$6:$K$42="正式美术已接入")+('资产主表'!$K$6:$K$42="已优化并正式接入")+('资产主表'!$K$6:$K$42="Blender源已完成")+('资产主表'!$K$6:$K$42="已导入；优化完成")+('资产主表'!$K$6:$K$42="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$47=A10)*(('资产主表'!$K$6:$K$47="已完成")+('资产主表'!$K$6:$K$47="原型已接入")+('资产主表'!$K$6:$K$47="正式美术已接入")+('资产主表'!$K$6:$K$47="已优化并正式接入")+('资产主表'!$K$6:$K$47="Blender源已完成")+('资产主表'!$K$6:$K$47="已导入；优化完成")+('资产主表'!$K$6:$K$47="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="62" t="n"/>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B11" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$42,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$47,A11)</f>
         <v/>
       </c>
       <c r="C11" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$42=A11)*(('资产主表'!$K$6:$K$42="已完成")+('资产主表'!$K$6:$K$42="原型已接入")+('资产主表'!$K$6:$K$42="正式美术已接入")+('资产主表'!$K$6:$K$42="已优化并正式接入")+('资产主表'!$K$6:$K$42="Blender源已完成")+('资产主表'!$K$6:$K$42="已导入；优化完成")+('资产主表'!$K$6:$K$42="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$47=A11)*(('资产主表'!$K$6:$K$47="已完成")+('资产主表'!$K$6:$K$47="原型已接入")+('资产主表'!$K$6:$K$47="正式美术已接入")+('资产主表'!$K$6:$K$47="已优化并正式接入")+('资产主表'!$K$6:$K$47="Blender源已完成")+('资产主表'!$K$6:$K$47="已导入；优化完成")+('资产主表'!$K$6:$K$47="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="62" t="n"/>
@@ -2115,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Y47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="51" min="1" max="1"/>
@@ -2387,7 +2387,7 @@
         <v/>
       </c>
       <c r="S6" s="63">
-        <f>IF(COUNTIF($R$6:$R$42,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="63" t="n"/>
@@ -2490,7 +2490,7 @@
         <v/>
       </c>
       <c r="S7" s="63">
-        <f>IF(COUNTIF($R$6:$R$42,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="63" t="n"/>
@@ -2593,7 +2593,7 @@
         <v/>
       </c>
       <c r="S8" s="63">
-        <f>IF(COUNTIF($R$6:$R$42,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="63" t="n"/>
@@ -2696,7 +2696,7 @@
         <v/>
       </c>
       <c r="S9" s="63">
-        <f>IF(COUNTIF($R$6:$R$42,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="63" t="n"/>
@@ -2803,7 +2803,7 @@
         <v/>
       </c>
       <c r="S10" s="63">
-        <f>IF(COUNTIF($R$6:$R$42,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="63" t="n"/>
@@ -2910,7 +2910,7 @@
         <v/>
       </c>
       <c r="S11" s="63">
-        <f>IF(COUNTIF($R$6:$R$42,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="63" t="n"/>
@@ -3017,7 +3017,7 @@
         <v/>
       </c>
       <c r="S12" s="63">
-        <f>IF(COUNTIF($R$6:$R$42,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="63" t="n"/>
@@ -3124,7 +3124,7 @@
         <v/>
       </c>
       <c r="S13" s="63">
-        <f>IF(COUNTIF($R$6:$R$42,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="63" t="n"/>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="S14" s="63">
-        <f>IF(COUNTIF($R$6:$R$42,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="63" t="n"/>
@@ -3338,7 +3338,7 @@
         <v/>
       </c>
       <c r="S15" s="63">
-        <f>IF(COUNTIF($R$6:$R$42,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="63" t="n"/>
@@ -3445,7 +3445,7 @@
         <v/>
       </c>
       <c r="S16" s="63">
-        <f>IF(COUNTIF($R$6:$R$42,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="63" t="n"/>
@@ -3564,7 +3564,7 @@
         <v/>
       </c>
       <c r="S17" s="55">
-        <f>IF(COUNTIF($R$6:$R$42,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="79" t="inlineStr">
@@ -3683,7 +3683,7 @@
         <v/>
       </c>
       <c r="S18" s="55">
-        <f>IF(COUNTIF($R$6:$R$42,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="79" t="inlineStr">
@@ -3806,7 +3806,7 @@
         <v/>
       </c>
       <c r="S19" s="55">
-        <f>IF(COUNTIF($R$6:$R$42,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="79" t="inlineStr">
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="S20" s="55">
-        <f>IF(COUNTIF($R$6:$R$42,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="79" t="inlineStr">
@@ -4046,7 +4046,7 @@
         <v/>
       </c>
       <c r="S21" s="55">
-        <f>IF(COUNTIF($R$6:$R$42,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="79" t="inlineStr">
@@ -4165,7 +4165,7 @@
         <v/>
       </c>
       <c r="S22" s="55">
-        <f>IF(COUNTIF($R$6:$R$42,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="79" t="inlineStr">
@@ -4284,7 +4284,7 @@
         <v/>
       </c>
       <c r="S23" s="55">
-        <f>IF(COUNTIF($R$6:$R$42,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="79" t="inlineStr">
@@ -4403,7 +4403,7 @@
         <v/>
       </c>
       <c r="S24" s="55">
-        <f>IF(COUNTIF($R$6:$R$42,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="79" t="inlineStr">
@@ -4522,7 +4522,7 @@
         <v/>
       </c>
       <c r="S25" s="55">
-        <f>IF(COUNTIF($R$6:$R$42,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="79" t="inlineStr">
@@ -4641,7 +4641,7 @@
         <v/>
       </c>
       <c r="S26" s="79">
-        <f>IF(COUNTIF($R$6:$R$42,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="79" t="inlineStr">
@@ -4767,7 +4767,7 @@
         <v/>
       </c>
       <c r="S27" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="76" t="inlineStr">
@@ -4889,7 +4889,7 @@
         <v/>
       </c>
       <c r="S28" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="76" t="inlineStr">
@@ -5011,7 +5011,7 @@
         <v/>
       </c>
       <c r="S29" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="76" t="inlineStr">
@@ -5133,7 +5133,7 @@
         <v/>
       </c>
       <c r="S30" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="76" t="inlineStr">
@@ -5255,7 +5255,7 @@
         <v/>
       </c>
       <c r="S31" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="76" t="inlineStr">
@@ -5377,7 +5377,7 @@
         <v/>
       </c>
       <c r="S32" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="76" t="inlineStr">
@@ -5499,7 +5499,7 @@
         <v/>
       </c>
       <c r="S33" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="76" t="inlineStr">
@@ -5621,7 +5621,7 @@
         <v/>
       </c>
       <c r="S34" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="76" t="inlineStr">
@@ -5739,7 +5739,7 @@
         <v/>
       </c>
       <c r="S35" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="76" t="inlineStr">
@@ -5858,7 +5858,7 @@
         <v/>
       </c>
       <c r="S36" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="76" t="inlineStr">
@@ -5979,7 +5979,7 @@
         <v/>
       </c>
       <c r="S37" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="76" t="inlineStr">
@@ -6100,7 +6100,7 @@
         <v/>
       </c>
       <c r="S38" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R38)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R38)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T38" s="76" t="inlineStr">
@@ -6221,7 +6221,7 @@
         <v/>
       </c>
       <c r="S39" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R39)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R39)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T39" s="76" t="inlineStr">
@@ -6359,7 +6359,7 @@
         <v/>
       </c>
       <c r="S40" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R40)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R40)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T40" s="76" t="inlineStr">
@@ -6480,7 +6480,7 @@
         <v/>
       </c>
       <c r="S41" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R41)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R41)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T41" s="76" t="inlineStr">
@@ -6601,7 +6601,7 @@
         <v/>
       </c>
       <c r="S42" s="76">
-        <f>IF(COUNTIF($R$6:$R$42,R42)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$47,R42)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T42" s="76" t="inlineStr">
@@ -6632,6 +6632,601 @@
       <c r="Y42" s="76" t="inlineStr">
         <is>
           <t>8枚石块径向飞散，0.55s；无灯无碰撞；进入VfxPool3D；行为由Projectile3D持有；碰撞不在VFX里。；隔离专项及真实渲染已验收，见2026-10-16_star_physical_mounts开发记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="70" customHeight="1" s="52">
+      <c r="A43" s="76" t="inlineStr">
+        <is>
+          <t>VFX-MELEE-AXE-CHARGE-3D</t>
+        </is>
+      </c>
+      <c r="B43" s="76" t="inlineStr">
+        <is>
+          <t>战斧蓄力环</t>
+        </is>
+      </c>
+      <c r="C43" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D43" s="76" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="E43" s="76" t="inlineStr">
+        <is>
+          <t>melee_axe_charge</t>
+        </is>
+      </c>
+      <c r="F43" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G43" s="76" t="n"/>
+      <c r="H43" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I43" s="76" t="inlineStr">
+        <is>
+          <t>axe_charge</t>
+        </is>
+      </c>
+      <c r="J43" s="76" t="inlineStr">
+        <is>
+          <t>三类近战</t>
+        </is>
+      </c>
+      <c r="K43" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L43" s="76" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M43" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N43" s="76" t="inlineStr">
+        <is>
+          <t>静态Prefab几何+Shader；无碰撞</t>
+        </is>
+      </c>
+      <c r="O43" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_axe_charge_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P43" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxAxeCharge3D.gd；docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
+        </is>
+      </c>
+      <c r="Q43" s="76" t="inlineStr">
+        <is>
+          <t>战斧蓄力环</t>
+        </is>
+      </c>
+      <c r="R43" s="76">
+        <f>LOWER(TRIM(C43)&amp;"|"&amp;TRIM(D43)&amp;"|"&amp;TRIM(E43)&amp;"|"&amp;TRIM(F43)&amp;"|"&amp;TRIM(H43)&amp;"|"&amp;TRIM(I43))</f>
+        <v/>
+      </c>
+      <c r="S43" s="76">
+        <f>IF(COUNTIF($R$6:$R$47,R43)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T43" s="76" t="inlineStr">
+        <is>
+          <t>701ecaa4330435775c16ac939922ccc6fc8a17010de45c3240d654b2e71fb8b7</t>
+        </is>
+      </c>
+      <c r="U43" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V43" s="77" t="n">
+        <v>46311</v>
+      </c>
+      <c r="W43" s="76" t="inlineStr">
+        <is>
+          <t>原创Godot几何与Shader</t>
+        </is>
+      </c>
+      <c r="X43" s="76" t="inlineStr">
+        <is>
+          <t>FX01-24</t>
+        </is>
+      </c>
+      <c r="Y43" s="76" t="inlineStr">
+        <is>
+          <t>收缩橙金双环，随玩家，持有至释放；池化/跟随/回收/真实渲染通过；无伤害逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="70" customHeight="1" s="52">
+      <c r="A44" s="76" t="inlineStr">
+        <is>
+          <t>VFX-MELEE-AXE-CLEAVE-3D</t>
+        </is>
+      </c>
+      <c r="B44" s="76" t="inlineStr">
+        <is>
+          <t>战斧下劈弧光</t>
+        </is>
+      </c>
+      <c r="C44" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D44" s="76" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="E44" s="76" t="inlineStr">
+        <is>
+          <t>melee_axe_cleave</t>
+        </is>
+      </c>
+      <c r="F44" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G44" s="76" t="n"/>
+      <c r="H44" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I44" s="76" t="inlineStr">
+        <is>
+          <t>axe_cleave</t>
+        </is>
+      </c>
+      <c r="J44" s="76" t="inlineStr">
+        <is>
+          <t>三类近战</t>
+        </is>
+      </c>
+      <c r="K44" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L44" s="76" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M44" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N44" s="76" t="inlineStr">
+        <is>
+          <t>静态Prefab几何+Shader；无碰撞</t>
+        </is>
+      </c>
+      <c r="O44" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_axe_cleave_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P44" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxAxeCleave3D.gd；docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
+        </is>
+      </c>
+      <c r="Q44" s="76" t="inlineStr">
+        <is>
+          <t>战斧下劈弧光</t>
+        </is>
+      </c>
+      <c r="R44" s="76">
+        <f>LOWER(TRIM(C44)&amp;"|"&amp;TRIM(D44)&amp;"|"&amp;TRIM(E44)&amp;"|"&amp;TRIM(F44)&amp;"|"&amp;TRIM(H44)&amp;"|"&amp;TRIM(I44))</f>
+        <v/>
+      </c>
+      <c r="S44" s="76">
+        <f>IF(COUNTIF($R$6:$R$47,R44)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T44" s="76" t="inlineStr">
+        <is>
+          <t>7b5a11e6d3120623b404a81cd62d0e265852cd77fecb41f6c4043ec4459eeb9f</t>
+        </is>
+      </c>
+      <c r="U44" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V44" s="77" t="n">
+        <v>46311</v>
+      </c>
+      <c r="W44" s="76" t="inlineStr">
+        <is>
+          <t>原创Godot几何与Shader</t>
+        </is>
+      </c>
+      <c r="X44" s="76" t="inlineStr">
+        <is>
+          <t>FX01-25</t>
+        </is>
+      </c>
+      <c r="Y44" s="76" t="inlineStr">
+        <is>
+          <t>竖向橙金弧，随玩家朝向，有效阶段消退；池化/跟随/回收/真实渲染通过；无伤害逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="70" customHeight="1" s="52">
+      <c r="A45" s="76" t="inlineStr">
+        <is>
+          <t>VFX-MELEE-AXE-IMPACT-3D</t>
+        </is>
+      </c>
+      <c r="B45" s="76" t="inlineStr">
+        <is>
+          <t>战斧触地冲击</t>
+        </is>
+      </c>
+      <c r="C45" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D45" s="76" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="E45" s="76" t="inlineStr">
+        <is>
+          <t>melee_axe_impact</t>
+        </is>
+      </c>
+      <c r="F45" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G45" s="76" t="n"/>
+      <c r="H45" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I45" s="76" t="inlineStr">
+        <is>
+          <t>axe_impact</t>
+        </is>
+      </c>
+      <c r="J45" s="76" t="inlineStr">
+        <is>
+          <t>三类近战</t>
+        </is>
+      </c>
+      <c r="K45" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L45" s="76" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M45" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N45" s="76" t="inlineStr">
+        <is>
+          <t>静态Prefab几何+Shader；无碰撞</t>
+        </is>
+      </c>
+      <c r="O45" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_axe_impact_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P45" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxAxeImpact3D.gd；docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
+        </is>
+      </c>
+      <c r="Q45" s="76" t="inlineStr">
+        <is>
+          <t>战斧触地冲击</t>
+        </is>
+      </c>
+      <c r="R45" s="76">
+        <f>LOWER(TRIM(C45)&amp;"|"&amp;TRIM(D45)&amp;"|"&amp;TRIM(E45)&amp;"|"&amp;TRIM(F45)&amp;"|"&amp;TRIM(H45)&amp;"|"&amp;TRIM(I45))</f>
+        <v/>
+      </c>
+      <c r="S45" s="76">
+        <f>IF(COUNTIF($R$6:$R$47,R45)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T45" s="76" t="inlineStr">
+        <is>
+          <t>46b1b343a0d62d13ad6d04df74e20598630794d1641c128c98682cee05f6e8c5</t>
+        </is>
+      </c>
+      <c r="U45" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V45" s="77" t="n">
+        <v>46311</v>
+      </c>
+      <c r="W45" s="76" t="inlineStr">
+        <is>
+          <t>原创Godot几何与Shader</t>
+        </is>
+      </c>
+      <c r="X45" s="76" t="inlineStr">
+        <is>
+          <t>FX01-26</t>
+        </is>
+      </c>
+      <c r="Y45" s="76" t="inlineStr">
+        <is>
+          <t>落点扩散环与8枚碎屑，世界锚定；池化/跟随/回收/真实渲染通过；无伤害逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="70" customHeight="1" s="52">
+      <c r="A46" s="76" t="inlineStr">
+        <is>
+          <t>VFX-MELEE-BLADE-SWEEP-3D</t>
+        </is>
+      </c>
+      <c r="B46" s="76" t="inlineStr">
+        <is>
+          <t>大剑横扫弧光</t>
+        </is>
+      </c>
+      <c r="C46" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D46" s="76" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="E46" s="76" t="inlineStr">
+        <is>
+          <t>melee_blade_sweep</t>
+        </is>
+      </c>
+      <c r="F46" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G46" s="76" t="n"/>
+      <c r="H46" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I46" s="76" t="inlineStr">
+        <is>
+          <t>blade_sweep</t>
+        </is>
+      </c>
+      <c r="J46" s="76" t="inlineStr">
+        <is>
+          <t>三类近战</t>
+        </is>
+      </c>
+      <c r="K46" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L46" s="76" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M46" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N46" s="76" t="inlineStr">
+        <is>
+          <t>静态Prefab几何+Shader；无碰撞</t>
+        </is>
+      </c>
+      <c r="O46" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_blade_sweep_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P46" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBladeSweep3D.gd；docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
+        </is>
+      </c>
+      <c r="Q46" s="76" t="inlineStr">
+        <is>
+          <t>大剑横扫弧光</t>
+        </is>
+      </c>
+      <c r="R46" s="76">
+        <f>LOWER(TRIM(C46)&amp;"|"&amp;TRIM(D46)&amp;"|"&amp;TRIM(E46)&amp;"|"&amp;TRIM(F46)&amp;"|"&amp;TRIM(H46)&amp;"|"&amp;TRIM(I46))</f>
+        <v/>
+      </c>
+      <c r="S46" s="76">
+        <f>IF(COUNTIF($R$6:$R$47,R46)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T46" s="76" t="inlineStr">
+        <is>
+          <t>6d06196bc0249b8be7713a8407673da3aa627627bff517f0c644a199eebce79b</t>
+        </is>
+      </c>
+      <c r="U46" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V46" s="77" t="n">
+        <v>46311</v>
+      </c>
+      <c r="W46" s="76" t="inlineStr">
+        <is>
+          <t>原创Godot几何与Shader</t>
+        </is>
+      </c>
+      <c r="X46" s="76" t="inlineStr">
+        <is>
+          <t>FX01-27</t>
+        </is>
+      </c>
+      <c r="Y46" s="76" t="inlineStr">
+        <is>
+          <t>蓝白弧，第二击反向，随玩家；池化/跟随/回收/真实渲染通过；无伤害逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="70" customHeight="1" s="52">
+      <c r="A47" s="76" t="inlineStr">
+        <is>
+          <t>VFX-MELEE-BLADE-WHIRLWIND-3D</t>
+        </is>
+      </c>
+      <c r="B47" s="76" t="inlineStr">
+        <is>
+          <t>大剑旋风环</t>
+        </is>
+      </c>
+      <c r="C47" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D47" s="76" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="E47" s="76" t="inlineStr">
+        <is>
+          <t>melee_blade_whirlwind</t>
+        </is>
+      </c>
+      <c r="F47" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G47" s="76" t="n"/>
+      <c r="H47" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I47" s="76" t="inlineStr">
+        <is>
+          <t>blade_whirlwind</t>
+        </is>
+      </c>
+      <c r="J47" s="76" t="inlineStr">
+        <is>
+          <t>三类近战</t>
+        </is>
+      </c>
+      <c r="K47" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L47" s="76" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M47" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N47" s="76" t="inlineStr">
+        <is>
+          <t>静态Prefab几何+Shader；无碰撞</t>
+        </is>
+      </c>
+      <c r="O47" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_blade_whirlwind_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P47" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBladeWhirlwind3D.gd；docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
+        </is>
+      </c>
+      <c r="Q47" s="76" t="inlineStr">
+        <is>
+          <t>大剑旋风环</t>
+        </is>
+      </c>
+      <c r="R47" s="76">
+        <f>LOWER(TRIM(C47)&amp;"|"&amp;TRIM(D47)&amp;"|"&amp;TRIM(E47)&amp;"|"&amp;TRIM(F47)&amp;"|"&amp;TRIM(H47)&amp;"|"&amp;TRIM(I47))</f>
+        <v/>
+      </c>
+      <c r="S47" s="76">
+        <f>IF(COUNTIF($R$6:$R$47,R47)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T47" s="76" t="inlineStr">
+        <is>
+          <t>48ece915e68370e24e06f9f53ed382585176d5bccfb4bf3133359632806dfc41</t>
+        </is>
+      </c>
+      <c r="U47" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V47" s="77" t="n">
+        <v>46311</v>
+      </c>
+      <c r="W47" s="76" t="inlineStr">
+        <is>
+          <t>原创Godot几何与Shader</t>
+        </is>
+      </c>
+      <c r="X47" s="76" t="inlineStr">
+        <is>
+          <t>FX01-28</t>
+        </is>
+      </c>
+      <c r="Y47" s="76" t="inlineStr">
+        <is>
+          <t>蓝白双层断续环，每0.55秒旋转，释放/中断归还；池化/跟随/回收/真实渲染通过；无伤害逻辑</t>
         </is>
       </c>
     </row>
@@ -6856,13 +7451,13 @@
     <cfRule type="containsText" priority="3" operator="containsText" dxfId="8" text="待制作"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,子弹特效,音效,音乐"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,design_only,authored,exported_pending_godot_validation,validated,active,已从运行场景移除,白盒组件"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7740,7 +8335,7 @@
       </c>
       <c r="L16" s="101" t="inlineStr">
         <is>
-          <t>Label3D pixel_size=0.00375；MSDF 128 + msdf_pixel_range 64（描边可达上限 ≈ range/2）；字号分档 116/134/152（世界字高 0.435/0.503/0.570 m）；描边 26/30/34；lifetime 0.70s × duration_scale；基线上升 0.90m</t>
+          <t>Label3D pixel_size=0.00375；MSDF 128 + msdf_pixel_range 64（描边可达上限 ≈ range/2）；字号分档 116/134/152（世界字高 0.435/0.503/0.570 m）；描边 13/15/17；lifetime 0.70s × duration_scale；基线上升 0.90m</t>
         </is>
       </c>
       <c r="M16" s="51" t="inlineStr">
@@ -7760,12 +8355,12 @@
       </c>
       <c r="P16" s="101" t="inlineStr">
         <is>
-          <t>v003</t>
+          <t>v004</t>
         </is>
       </c>
       <c r="Q16" s="51" t="inlineStr">
         <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_damage_number_root_top3d.tscn + 脚本=src/vfx/VfxDamageNumber3D.gd；根节点=VfxDamageNumber3D(Node3D)；FX编号 FX02-01；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由。【2026-10-16 样式重做】字体与样式真源收敛到 src/vfx/DamageNumberStyle.gd（漫画风超粗体：字体链首选 Impact、字重 900、MSDF 128；近黑粗勾边 ≈ 字高 22%）；随机数只活在调用方 Enemy3D._damage_number_context()，特效脚本对同一 context 逐位可复现。【P0 修复】_on_tick 原以**赋值**写 position（position.y = rise_t × 距离），出生坐标第一帧即被清零 —— 实测实机飘字跑到世界原点上方不到 1 米、与怪物楼层无关；改为 position = _origin_local + 偏移。Prefab 路径去掉历史误写的 _v001 后缀。【2026-10-17 勾边修复】**勾边修复：`msdf_pixel_range` 太小导致描边被截成 1px 细丝**。Godot 的 MSDF 字体下描边可达上限 ≈ msdf_pixel_range / 2，默认 16 只够到 8，而本件声明 26/30/34 ⇒ 被提前截断（症状：不报错不变红，且 outline_size 填 26 与 116 渲染结果逐像素完全相同）。修法：`DamageNumberStyle.MSDF_PIXEL_RANGE = 64`，在 `make_font()` 里赋给 `SystemFont.msdf_pixel_range`；三条链路共用该字体工厂，一处即全覆盖。定档实测（字形高约 108px 定尺拍摄）：range 16 → 实画 6px、48 → 21px、64/80 → 26px 足额、96 → 左右不对称（一侧整条丢失）⇒ 取 64，验收另设上界护栏 80。验收新增常量钉子 + 下界不等式 + 逐档「实例真带该值」断言；反向对照三组（16／96／删赋值）均精准变红后复绿。实机距离 A/B：描边像素 160 → 13,421（×83.9）。</t>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_damage_number_root_top3d.tscn + 脚本=src/vfx/VfxDamageNumber3D.gd；根节点=VfxDamageNumber3D(Node3D)；FX编号 FX02-01；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由。【2026-10-16 样式重做】字体与样式真源收敛到 src/vfx/DamageNumberStyle.gd（漫画风超粗体：字体链首选 Impact、字重 900、MSDF 128；近黑粗勾边 ≈ 字高 22%）；随机数只活在调用方 Enemy3D._damage_number_context()，特效脚本对同一 context 逐位可复现。【P0 修复】_on_tick 原以**赋值**写 position（position.y = rise_t × 距离），出生坐标第一帧即被清零 —— 实测实机飘字跑到世界原点上方不到 1 米、与怪物楼层无关；改为 position = _origin_local + 偏移。Prefab 路径去掉历史误写的 _v001 后缀。【2026-10-17 勾边修复】**勾边修复：`msdf_pixel_range` 太小导致描边被截成 1px 细丝**。Godot 的 MSDF 字体下描边可达上限 ≈ msdf_pixel_range / 2，默认 16 只够到 8，而本件声明 26/30/34 ⇒ 被提前截断（症状：不报错不变红，且 outline_size 填 26 与 116 渲染结果逐像素完全相同）。修法：`DamageNumberStyle.MSDF_PIXEL_RANGE = 64`，在 `make_font()` 里赋给 `SystemFont.msdf_pixel_range`；三条链路共用该字体工厂，一处即全覆盖。定档实测（字形高约 108px 定尺拍摄）：range 16 → 实画 6px、48 → 21px、64/80 → 26px 足额、96 → 左右不对称（一侧整条丢失）⇒ 取 64，验收另设上界护栏 80。验收新增常量钉子 + 下界不等式 + 逐档「实例真带该值」断言；反向对照三组（16／96／删赋值）均精准变红后复绿。实机距离 A/B：描边像素 160 → 13,421（×83.9）。【2026-10-17 描边减半】**描边减半**（业主：「太粗了，缩小一半」）。v003 修好 `msdf_pixel_range` 后描边第一次足额渲染，实机看下来过粗 ⇒ 描边尺寸 26/30/34 → **13/15/17**（占字高 22% → 11%，描边色与淡出通道不变）。真源 `DamageNumberStyle.NORMAL/HEAVY/CRITICAL_OUTLINE_SIZE` 一处改动即覆盖三条链路。**距离场宽度不动**（仍 64）：需求 2 × max(描边 × msdf_size / 字号) 由 57.4 降到 28.7，64 依旧足额且支持描边到约 38 @ 字号 152，留余量以便后续微调不必重新定档。验收侧硬编码期望同步为 13/15/17、下界不等式随之重算为 28.7。反向对照两组：range→16（下界红）／真源描边偷偷改回 26（常量钉子红）—— 均精准变红后复绿。实机同帧 A/B（红色字形像素恒为 5,105 ⇒ 字形未变）：近黑描边像素 12,613 → 6,392（×0.507）。</t>
         </is>
       </c>
     </row>
@@ -7817,7 +8412,7 @@
       </c>
       <c r="L17" s="101" t="inlineStr">
         <is>
-          <t>Label3D pixel_size=0.00375；MSDF 128 + msdf_pixel_range 64（描边可达上限 ≈ range/2）；字号 116（世界字高 0.435 m）；描边 26；lifetime 0.70s × duration_scale；基线上升 0.90m</t>
+          <t>Label3D pixel_size=0.00375；MSDF 128 + msdf_pixel_range 64（描边可达上限 ≈ range/2）；字号 116（世界字高 0.435 m）；描边 13；lifetime 0.70s × duration_scale；基线上升 0.90m</t>
         </is>
       </c>
       <c r="M17" s="51" t="inlineStr">
@@ -7837,12 +8432,12 @@
       </c>
       <c r="P17" s="101" t="inlineStr">
         <is>
-          <t>v003</t>
+          <t>v004</t>
         </is>
       </c>
       <c r="Q17" s="51" t="inlineStr">
         <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_heal_number_root_top3d.tscn + 脚本=src/vfx/VfxHealNumber3D.gd；根节点=VfxHealNumber3D(Node3D)；FX编号 FX02-02；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value；调用方：Enemy3D._spawn_heal_number 经 VfxPool3D 路由（2026-10-16 起；此前治疗误借 VFX-DAMAGE-NUMBER-3D ⇒ 回血飘红字「0」，而本 AssetID 全工程零调用方）。【2026-10-16 样式重做】字体与样式取 src/vfx/DamageNumberStyle.gd，与 FX02-01 同源。Prefab 路径去掉历史误写的 _v001 后缀。【2026-10-17 勾边修复】**勾边修复：`msdf_pixel_range` 太小导致描边被截成 1px 细丝**。Godot 的 MSDF 字体下描边可达上限 ≈ msdf_pixel_range / 2，默认 16 只够到 8，而本件声明 26/30/34 ⇒ 被提前截断（症状：不报错不变红，且 outline_size 填 26 与 116 渲染结果逐像素完全相同）。修法：`DamageNumberStyle.MSDF_PIXEL_RANGE = 64`，在 `make_font()` 里赋给 `SystemFont.msdf_pixel_range`；三条链路共用该字体工厂，一处即全覆盖。定档实测（字形高约 108px 定尺拍摄）：range 16 → 实画 6px、48 → 21px、64/80 → 26px 足额、96 → 左右不对称（一侧整条丢失）⇒ 取 64，验收另设上界护栏 80。验收新增常量钉子 + 下界不等式 + 逐档「实例真带该值」断言；反向对照三组（16／96／删赋值）均精准变红后复绿。实机距离 A/B：描边像素 160 → 13,421（×83.9）。</t>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_heal_number_root_top3d.tscn + 脚本=src/vfx/VfxHealNumber3D.gd；根节点=VfxHealNumber3D(Node3D)；FX编号 FX02-02；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value；调用方：Enemy3D._spawn_heal_number 经 VfxPool3D 路由（2026-10-16 起；此前治疗误借 VFX-DAMAGE-NUMBER-3D ⇒ 回血飘红字「0」，而本 AssetID 全工程零调用方）。【2026-10-16 样式重做】字体与样式取 src/vfx/DamageNumberStyle.gd，与 FX02-01 同源。Prefab 路径去掉历史误写的 _v001 后缀。【2026-10-17 勾边修复】**勾边修复：`msdf_pixel_range` 太小导致描边被截成 1px 细丝**。Godot 的 MSDF 字体下描边可达上限 ≈ msdf_pixel_range / 2，默认 16 只够到 8，而本件声明 26/30/34 ⇒ 被提前截断（症状：不报错不变红，且 outline_size 填 26 与 116 渲染结果逐像素完全相同）。修法：`DamageNumberStyle.MSDF_PIXEL_RANGE = 64`，在 `make_font()` 里赋给 `SystemFont.msdf_pixel_range`；三条链路共用该字体工厂，一处即全覆盖。定档实测（字形高约 108px 定尺拍摄）：range 16 → 实画 6px、48 → 21px、64/80 → 26px 足额、96 → 左右不对称（一侧整条丢失）⇒ 取 64，验收另设上界护栏 80。验收新增常量钉子 + 下界不等式 + 逐档「实例真带该值」断言；反向对照三组（16／96／删赋值）均精准变红后复绿。实机距离 A/B：描边像素 160 → 13,421（×83.9）。【2026-10-17 描边减半】**描边减半**（业主：「太粗了，缩小一半」）。v003 修好 `msdf_pixel_range` 后描边第一次足额渲染，实机看下来过粗 ⇒ 描边尺寸 26/30/34 → **13/15/17**（占字高 22% → 11%，描边色与淡出通道不变）。真源 `DamageNumberStyle.NORMAL/HEAVY/CRITICAL_OUTLINE_SIZE` 一处改动即覆盖三条链路。**距离场宽度不动**（仍 64）：需求 2 × max(描边 × msdf_size / 字号) 由 57.4 降到 28.7，64 依旧足额且支持描边到约 38 @ 字号 152，留余量以便后续微调不必重新定档。验收侧硬编码期望同步为 13/15/17、下界不等式随之重算为 28.7。反向对照两组：range→16（下界红）／真源描边偷偷改回 26（常量钉子红）—— 均精准变红后复绿。实机同帧 A/B（红色字形像素恒为 5,105 ⇒ 字形未变）：近黑描边像素 12,613 → 6,392（×0.507）。</t>
         </is>
       </c>
     </row>
@@ -9704,30 +10299,390 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="52">
-      <c r="H44" s="101" t="n"/>
-      <c r="I44" s="51" t="n"/>
-      <c r="N44" s="51" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="52">
-      <c r="H45" s="101" t="n"/>
-      <c r="I45" s="51" t="n"/>
-      <c r="N45" s="51" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="52">
-      <c r="H46" s="101" t="n"/>
-      <c r="I46" s="51" t="n"/>
-      <c r="N46" s="51" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="52">
-      <c r="H47" s="101" t="n"/>
-      <c r="I47" s="51" t="n"/>
-      <c r="N47" s="51" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="52">
-      <c r="H48" s="101" t="n"/>
-      <c r="I48" s="51" t="n"/>
-      <c r="N48" s="51" t="n"/>
+    <row r="44" ht="70" customHeight="1" s="52">
+      <c r="A44" s="100" t="inlineStr">
+        <is>
+          <t>FX01-24</t>
+        </is>
+      </c>
+      <c r="B44" s="101" t="inlineStr">
+        <is>
+          <t>VFX-MELEE-AXE-CHARGE-3D</t>
+        </is>
+      </c>
+      <c r="C44" s="51" t="inlineStr">
+        <is>
+          <t>战斧蓄力环</t>
+        </is>
+      </c>
+      <c r="D44" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_axe_charge_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="G44" s="51" t="inlineStr">
+        <is>
+          <t>收缩橙金双环，随玩家，持有至释放</t>
+        </is>
+      </c>
+      <c r="H44" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxAxeCharge3D.gd</t>
+        </is>
+      </c>
+      <c r="I44" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J44" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K44" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L44" s="51" t="inlineStr">
+        <is>
+          <t>基础半径1m×size</t>
+        </is>
+      </c>
+      <c r="M44" s="51" t="inlineStr">
+        <is>
+          <t>local -Z前方；中心为特效原点</t>
+        </is>
+      </c>
+      <c r="N44" s="51" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D → VfxPool3D</t>
+        </is>
+      </c>
+      <c r="O44" s="51" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P44" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q44" s="101" t="inlineStr">
+        <is>
+          <t>docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="70" customHeight="1" s="52">
+      <c r="A45" s="100" t="inlineStr">
+        <is>
+          <t>FX01-25</t>
+        </is>
+      </c>
+      <c r="B45" s="101" t="inlineStr">
+        <is>
+          <t>VFX-MELEE-AXE-CLEAVE-3D</t>
+        </is>
+      </c>
+      <c r="C45" s="51" t="inlineStr">
+        <is>
+          <t>战斧下劈弧光</t>
+        </is>
+      </c>
+      <c r="D45" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_axe_cleave_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="G45" s="51" t="inlineStr">
+        <is>
+          <t>竖向橙金弧，随玩家朝向，有效阶段消退</t>
+        </is>
+      </c>
+      <c r="H45" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxAxeCleave3D.gd</t>
+        </is>
+      </c>
+      <c r="I45" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J45" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K45" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L45" s="51" t="inlineStr">
+        <is>
+          <t>基础半径1m×size</t>
+        </is>
+      </c>
+      <c r="M45" s="51" t="inlineStr">
+        <is>
+          <t>local -Z前方；中心为特效原点</t>
+        </is>
+      </c>
+      <c r="N45" s="51" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D → VfxPool3D</t>
+        </is>
+      </c>
+      <c r="O45" s="51" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P45" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q45" s="101" t="inlineStr">
+        <is>
+          <t>docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="70" customHeight="1" s="52">
+      <c r="A46" s="100" t="inlineStr">
+        <is>
+          <t>FX01-26</t>
+        </is>
+      </c>
+      <c r="B46" s="101" t="inlineStr">
+        <is>
+          <t>VFX-MELEE-AXE-IMPACT-3D</t>
+        </is>
+      </c>
+      <c r="C46" s="51" t="inlineStr">
+        <is>
+          <t>战斧触地冲击</t>
+        </is>
+      </c>
+      <c r="D46" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_axe_impact_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="G46" s="51" t="inlineStr">
+        <is>
+          <t>落点扩散环与8枚碎屑，世界锚定</t>
+        </is>
+      </c>
+      <c r="H46" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxAxeImpact3D.gd</t>
+        </is>
+      </c>
+      <c r="I46" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J46" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K46" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L46" s="51" t="inlineStr">
+        <is>
+          <t>基础半径1m×size</t>
+        </is>
+      </c>
+      <c r="M46" s="51" t="inlineStr">
+        <is>
+          <t>local -Z前方；中心为特效原点</t>
+        </is>
+      </c>
+      <c r="N46" s="51" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D → VfxPool3D</t>
+        </is>
+      </c>
+      <c r="O46" s="51" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P46" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q46" s="101" t="inlineStr">
+        <is>
+          <t>docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="70" customHeight="1" s="52">
+      <c r="A47" s="100" t="inlineStr">
+        <is>
+          <t>FX01-27</t>
+        </is>
+      </c>
+      <c r="B47" s="101" t="inlineStr">
+        <is>
+          <t>VFX-MELEE-BLADE-SWEEP-3D</t>
+        </is>
+      </c>
+      <c r="C47" s="51" t="inlineStr">
+        <is>
+          <t>大剑横扫弧光</t>
+        </is>
+      </c>
+      <c r="D47" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_blade_sweep_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="G47" s="51" t="inlineStr">
+        <is>
+          <t>蓝白弧，第二击反向，随玩家</t>
+        </is>
+      </c>
+      <c r="H47" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBladeSweep3D.gd</t>
+        </is>
+      </c>
+      <c r="I47" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J47" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K47" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L47" s="51" t="inlineStr">
+        <is>
+          <t>基础半径1m×size</t>
+        </is>
+      </c>
+      <c r="M47" s="51" t="inlineStr">
+        <is>
+          <t>local -Z前方；中心为特效原点</t>
+        </is>
+      </c>
+      <c r="N47" s="51" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D → VfxPool3D</t>
+        </is>
+      </c>
+      <c r="O47" s="51" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P47" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q47" s="101" t="inlineStr">
+        <is>
+          <t>docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="70" customHeight="1" s="52">
+      <c r="A48" s="100" t="inlineStr">
+        <is>
+          <t>FX01-28</t>
+        </is>
+      </c>
+      <c r="B48" s="101" t="inlineStr">
+        <is>
+          <t>VFX-MELEE-BLADE-WHIRLWIND-3D</t>
+        </is>
+      </c>
+      <c r="C48" s="51" t="inlineStr">
+        <is>
+          <t>大剑旋风环</t>
+        </is>
+      </c>
+      <c r="D48" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_blade_whirlwind_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="G48" s="51" t="inlineStr">
+        <is>
+          <t>蓝白双层断续环，每0.55秒旋转，释放/中断归还</t>
+        </is>
+      </c>
+      <c r="H48" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBladeWhirlwind3D.gd</t>
+        </is>
+      </c>
+      <c r="I48" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J48" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K48" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L48" s="51" t="inlineStr">
+        <is>
+          <t>基础半径1m×size</t>
+        </is>
+      </c>
+      <c r="M48" s="51" t="inlineStr">
+        <is>
+          <t>local -Z前方；中心为特效原点</t>
+        </is>
+      </c>
+      <c r="N48" s="51" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D → VfxPool3D</t>
+        </is>
+      </c>
+      <c r="O48" s="51" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P48" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q48" s="101" t="inlineStr">
+        <is>
+          <t>docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="52">
       <c r="H49" s="101" t="n"/>
@@ -10770,7 +11725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="51" min="1" max="1"/>
@@ -11857,6 +12812,80 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="70" customHeight="1" s="52">
+      <c r="A34" s="69" t="inlineStr">
+        <is>
+          <t>v0.1.26</t>
+        </is>
+      </c>
+      <c r="B34" s="69" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C34" s="62" t="inlineStr">
+        <is>
+          <t>五种近战专属VFX</t>
+        </is>
+      </c>
+      <c r="D34" s="62" t="inlineStr">
+        <is>
+          <t>近战差异 v041</t>
+        </is>
+      </c>
+      <c r="E34" s="62" t="inlineStr">
+        <is>
+          <t>FX01-24至28；独立Prefab，池化跟随与显式结束，动作机唯一调用。</t>
+        </is>
+      </c>
+      <c r="F34" s="62" t="inlineStr">
+        <is>
+          <t>docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
+        </is>
+      </c>
+      <c r="G34" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="69" t="inlineStr">
+        <is>
+          <t>v0.1.27</t>
+        </is>
+      </c>
+      <c r="B35" s="69" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C35" s="62" t="inlineStr">
+        <is>
+          <t>条目更新（描边减半）</t>
+        </is>
+      </c>
+      <c r="D35" s="62" t="inlineStr">
+        <is>
+          <t>特效 · 3D-特效（FX02-01 / FX02-02）</t>
+        </is>
+      </c>
+      <c r="E35" s="62" t="inlineStr">
+        <is>
+          <t>数字飘字描边减半（业主：「太粗了，缩小一半」）。v003 修好 msdf_pixel_range 后描边第一次足额渲染，实机反馈过粗 ⇒ 描边 26/30/34 → 13/15/17（占字高 22% → 11%）。真源 DamageNumberStyle 的 NORMAL/HEAVY/CRITICAL_OUTLINE_SIZE 一处改动即覆盖 VfxDamageNumber3D / VfxHealNumber3D / 兜底 CombatDamageNumber3D 三条链路。距离场宽度不动（仍 64）：需求 2 × max(描边 × msdf_size / 字号) 由 57.4 降到 28.7，64 依旧足额且支持描边到约 38 @ 字号 152，留余量以便后续微调不必重新定档。验收 verify_damage_number_style_flow 的硬编码期望同步为 13/15/17，下界不等式随之重算为 28.7；反向对照两组（range→16 下界红／真源描边偷偷改回 26 常量钉子红）均精准变红后还原复绿。实机同帧 A/B（红色字形像素恒为 5,105 ⇒ 字形本身未变）：近黑描边像素 12,613 → 6,392（×0.507）。</t>
+        </is>
+      </c>
+      <c r="F35" s="62" t="inlineStr">
+        <is>
+          <t>AssetID / Prefab 路径 / 版本号（升 v004）稳定；Prefab .tscn 文件逐字未改（纯样式常量）；VfxPool3D 注册表未动；碰撞 / 伤害 / 存档无影响。既有条目 AssetID / 路径 / 状态逐格保留。</t>
+        </is>
+      </c>
+      <c r="G35" s="62" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -1447,22 +1447,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="52">
       <c r="A6" s="57">
-        <f>COUNTA('资产主表'!$A$6:$A$47)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$52)</f>
         <v/>
       </c>
       <c r="B6" s="55" t="n"/>
       <c r="C6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$47,"已完成")+COUNTIF('资产主表'!$K$6:$K$47,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$47,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$47,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$47,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$47,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$47,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$52,"已完成")+COUNTIF('资产主表'!$K$6:$K$52,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$52,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$52,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$52,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$52,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$52,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="55" t="n"/>
       <c r="E6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$47,"待制作")+COUNTIF('资产主表'!$K$6:$K$47,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$52,"待制作")+COUNTIF('资产主表'!$K$6:$K$52,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="55" t="n"/>
       <c r="G6" s="57">
-        <f>COUNTIF('资产主表'!$S$6:$S$47,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$52,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="55" t="n"/>
@@ -1531,11 +1531,11 @@
         </is>
       </c>
       <c r="B10" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$47,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$52,A10)</f>
         <v/>
       </c>
       <c r="C10" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$47=A10)*(('资产主表'!$K$6:$K$47="已完成")+('资产主表'!$K$6:$K$47="原型已接入")+('资产主表'!$K$6:$K$47="正式美术已接入")+('资产主表'!$K$6:$K$47="已优化并正式接入")+('资产主表'!$K$6:$K$47="Blender源已完成")+('资产主表'!$K$6:$K$47="已导入；优化完成")+('资产主表'!$K$6:$K$47="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$52=A10)*(('资产主表'!$K$6:$K$52="已完成")+('资产主表'!$K$6:$K$52="原型已接入")+('资产主表'!$K$6:$K$52="正式美术已接入")+('资产主表'!$K$6:$K$52="已优化并正式接入")+('资产主表'!$K$6:$K$52="Blender源已完成")+('资产主表'!$K$6:$K$52="已导入；优化完成")+('资产主表'!$K$6:$K$52="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="62" t="n"/>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B11" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$47,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$52,A11)</f>
         <v/>
       </c>
       <c r="C11" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$47=A11)*(('资产主表'!$K$6:$K$47="已完成")+('资产主表'!$K$6:$K$47="原型已接入")+('资产主表'!$K$6:$K$47="正式美术已接入")+('资产主表'!$K$6:$K$47="已优化并正式接入")+('资产主表'!$K$6:$K$47="Blender源已完成")+('资产主表'!$K$6:$K$47="已导入；优化完成")+('资产主表'!$K$6:$K$47="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$52=A11)*(('资产主表'!$K$6:$K$52="已完成")+('资产主表'!$K$6:$K$52="原型已接入")+('资产主表'!$K$6:$K$52="正式美术已接入")+('资产主表'!$K$6:$K$52="已优化并正式接入")+('资产主表'!$K$6:$K$52="Blender源已完成")+('资产主表'!$K$6:$K$52="已导入；优化完成")+('资产主表'!$K$6:$K$52="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="62" t="n"/>
@@ -2115,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y47"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="51" min="1" max="1"/>
@@ -2387,7 +2387,7 @@
         <v/>
       </c>
       <c r="S6" s="63">
-        <f>IF(COUNTIF($R$6:$R$47,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="63" t="n"/>
@@ -2490,7 +2490,7 @@
         <v/>
       </c>
       <c r="S7" s="63">
-        <f>IF(COUNTIF($R$6:$R$47,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="63" t="n"/>
@@ -2593,7 +2593,7 @@
         <v/>
       </c>
       <c r="S8" s="63">
-        <f>IF(COUNTIF($R$6:$R$47,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="63" t="n"/>
@@ -2696,7 +2696,7 @@
         <v/>
       </c>
       <c r="S9" s="63">
-        <f>IF(COUNTIF($R$6:$R$47,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="63" t="n"/>
@@ -2803,7 +2803,7 @@
         <v/>
       </c>
       <c r="S10" s="63">
-        <f>IF(COUNTIF($R$6:$R$47,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="63" t="n"/>
@@ -2910,7 +2910,7 @@
         <v/>
       </c>
       <c r="S11" s="63">
-        <f>IF(COUNTIF($R$6:$R$47,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="63" t="n"/>
@@ -3017,7 +3017,7 @@
         <v/>
       </c>
       <c r="S12" s="63">
-        <f>IF(COUNTIF($R$6:$R$47,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="63" t="n"/>
@@ -3124,7 +3124,7 @@
         <v/>
       </c>
       <c r="S13" s="63">
-        <f>IF(COUNTIF($R$6:$R$47,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="63" t="n"/>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="S14" s="63">
-        <f>IF(COUNTIF($R$6:$R$47,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="63" t="n"/>
@@ -3338,7 +3338,7 @@
         <v/>
       </c>
       <c r="S15" s="63">
-        <f>IF(COUNTIF($R$6:$R$47,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="63" t="n"/>
@@ -3445,7 +3445,7 @@
         <v/>
       </c>
       <c r="S16" s="63">
-        <f>IF(COUNTIF($R$6:$R$47,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="63" t="n"/>
@@ -3564,7 +3564,7 @@
         <v/>
       </c>
       <c r="S17" s="55">
-        <f>IF(COUNTIF($R$6:$R$47,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="79" t="inlineStr">
@@ -3683,7 +3683,7 @@
         <v/>
       </c>
       <c r="S18" s="55">
-        <f>IF(COUNTIF($R$6:$R$47,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="79" t="inlineStr">
@@ -3806,7 +3806,7 @@
         <v/>
       </c>
       <c r="S19" s="55">
-        <f>IF(COUNTIF($R$6:$R$47,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="79" t="inlineStr">
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="S20" s="55">
-        <f>IF(COUNTIF($R$6:$R$47,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="79" t="inlineStr">
@@ -4046,7 +4046,7 @@
         <v/>
       </c>
       <c r="S21" s="55">
-        <f>IF(COUNTIF($R$6:$R$47,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="79" t="inlineStr">
@@ -4165,7 +4165,7 @@
         <v/>
       </c>
       <c r="S22" s="55">
-        <f>IF(COUNTIF($R$6:$R$47,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="79" t="inlineStr">
@@ -4284,7 +4284,7 @@
         <v/>
       </c>
       <c r="S23" s="55">
-        <f>IF(COUNTIF($R$6:$R$47,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="79" t="inlineStr">
@@ -4403,7 +4403,7 @@
         <v/>
       </c>
       <c r="S24" s="55">
-        <f>IF(COUNTIF($R$6:$R$47,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="79" t="inlineStr">
@@ -4522,7 +4522,7 @@
         <v/>
       </c>
       <c r="S25" s="55">
-        <f>IF(COUNTIF($R$6:$R$47,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="79" t="inlineStr">
@@ -4641,7 +4641,7 @@
         <v/>
       </c>
       <c r="S26" s="79">
-        <f>IF(COUNTIF($R$6:$R$47,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="79" t="inlineStr">
@@ -4767,7 +4767,7 @@
         <v/>
       </c>
       <c r="S27" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="76" t="inlineStr">
@@ -4889,7 +4889,7 @@
         <v/>
       </c>
       <c r="S28" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="76" t="inlineStr">
@@ -5011,7 +5011,7 @@
         <v/>
       </c>
       <c r="S29" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="76" t="inlineStr">
@@ -5133,7 +5133,7 @@
         <v/>
       </c>
       <c r="S30" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="76" t="inlineStr">
@@ -5255,7 +5255,7 @@
         <v/>
       </c>
       <c r="S31" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="76" t="inlineStr">
@@ -5377,7 +5377,7 @@
         <v/>
       </c>
       <c r="S32" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="76" t="inlineStr">
@@ -5499,7 +5499,7 @@
         <v/>
       </c>
       <c r="S33" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="76" t="inlineStr">
@@ -5621,7 +5621,7 @@
         <v/>
       </c>
       <c r="S34" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="76" t="inlineStr">
@@ -5739,7 +5739,7 @@
         <v/>
       </c>
       <c r="S35" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="76" t="inlineStr">
@@ -5858,7 +5858,7 @@
         <v/>
       </c>
       <c r="S36" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="76" t="inlineStr">
@@ -5979,7 +5979,7 @@
         <v/>
       </c>
       <c r="S37" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="76" t="inlineStr">
@@ -6100,7 +6100,7 @@
         <v/>
       </c>
       <c r="S38" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R38)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R38)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T38" s="76" t="inlineStr">
@@ -6221,7 +6221,7 @@
         <v/>
       </c>
       <c r="S39" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R39)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R39)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T39" s="76" t="inlineStr">
@@ -6359,7 +6359,7 @@
         <v/>
       </c>
       <c r="S40" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R40)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R40)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T40" s="76" t="inlineStr">
@@ -6480,7 +6480,7 @@
         <v/>
       </c>
       <c r="S41" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R41)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R41)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T41" s="76" t="inlineStr">
@@ -6601,7 +6601,7 @@
         <v/>
       </c>
       <c r="S42" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R42)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R42)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T42" s="76" t="inlineStr">
@@ -6722,7 +6722,7 @@
         <v/>
       </c>
       <c r="S43" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R43)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R43)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T43" s="76" t="inlineStr">
@@ -6841,7 +6841,7 @@
         <v/>
       </c>
       <c r="S44" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R44)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R44)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T44" s="76" t="inlineStr">
@@ -6960,7 +6960,7 @@
         <v/>
       </c>
       <c r="S45" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R45)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R45)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T45" s="76" t="inlineStr">
@@ -7079,7 +7079,7 @@
         <v/>
       </c>
       <c r="S46" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R46)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R46)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T46" s="76" t="inlineStr">
@@ -7198,7 +7198,7 @@
         <v/>
       </c>
       <c r="S47" s="76">
-        <f>IF(COUNTIF($R$6:$R$47,R47)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$52,R47)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T47" s="76" t="inlineStr">
@@ -7227,6 +7227,611 @@
       <c r="Y47" s="76" t="inlineStr">
         <is>
           <t>蓝白双层断续环，每0.55秒旋转，释放/中断归还；池化/跟随/回收/真实渲染通过；无伤害逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="70" customHeight="1" s="52">
+      <c r="A48" s="76" t="inlineStr">
+        <is>
+          <t>VFX-FATE-FIRE-3D</t>
+        </is>
+      </c>
+      <c r="B48" s="76" t="inlineStr">
+        <is>
+          <t>命运火焰跳动</t>
+        </is>
+      </c>
+      <c r="C48" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D48" s="76" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E48" s="76" t="inlineStr">
+        <is>
+          <t>fate_fire</t>
+        </is>
+      </c>
+      <c r="F48" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G48" s="76" t="n"/>
+      <c r="H48" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I48" s="76" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="J48" s="76" t="inlineStr">
+        <is>
+          <t>命运元素与战斗伤害</t>
+        </is>
+      </c>
+      <c r="K48" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L48" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M48" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N48" s="76" t="inlineStr">
+        <is>
+          <t>4枚橙红火舌错相跳动，状态Owner驱动结束</t>
+        </is>
+      </c>
+      <c r="O48" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_fate_fire_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P48" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxFateFire3D.gd; docs/v0.1/14.6_特效系统与制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q48" s="76" t="inlineStr">
+        <is>
+          <t>命运;低粒子;元素反馈</t>
+        </is>
+      </c>
+      <c r="R48" s="76">
+        <f>LOWER(TRIM(C48)&amp;"|"&amp;TRIM(D48)&amp;"|"&amp;TRIM(E48)&amp;"|"&amp;TRIM(F48)&amp;"|"&amp;TRIM(H48)&amp;"|"&amp;TRIM(I48))</f>
+        <v/>
+      </c>
+      <c r="S48" s="76">
+        <f>IF(COUNTIF($R$6:$R$52,R48)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T48" s="76" t="inlineStr">
+        <is>
+          <t>03902f15f0dd9025723b7c9aeb14a08b819a5ca4eda4c38a3a0ca77c9a070991</t>
+        </is>
+      </c>
+      <c r="U48" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V48" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="W48" s="76" t="inlineStr">
+        <is>
+          <t>原创Godot Prefab与脚本</t>
+        </is>
+      </c>
+      <c r="X48" s="76" t="inlineStr">
+        <is>
+          <t>FX01-29</t>
+        </is>
+      </c>
+      <c r="Y48" s="76" t="inlineStr">
+        <is>
+          <t>独立Prefab；无碰撞；机制与独立真实渲染验证，完整战局压力另验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="70" customHeight="1" s="52">
+      <c r="A49" s="76" t="inlineStr">
+        <is>
+          <t>VFX-FATE-FROST-3D</t>
+        </is>
+      </c>
+      <c r="B49" s="76" t="inlineStr">
+        <is>
+          <t>命运脚底冰霜</t>
+        </is>
+      </c>
+      <c r="C49" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D49" s="76" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E49" s="76" t="inlineStr">
+        <is>
+          <t>fate_frost</t>
+        </is>
+      </c>
+      <c r="F49" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G49" s="76" t="n"/>
+      <c r="H49" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I49" s="76" t="inlineStr">
+        <is>
+          <t>frost</t>
+        </is>
+      </c>
+      <c r="J49" s="76" t="inlineStr">
+        <is>
+          <t>命运元素与战斗伤害</t>
+        </is>
+      </c>
+      <c r="K49" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L49" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M49" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N49" s="76" t="inlineStr">
+        <is>
+          <t>4枚冰晶＋薄霜面，冻结/命运减速期间跟随脚底</t>
+        </is>
+      </c>
+      <c r="O49" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_fate_frost_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P49" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxFateFrost3D.gd; docs/v0.1/14.6_特效系统与制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q49" s="76" t="inlineStr">
+        <is>
+          <t>命运;低粒子;元素反馈</t>
+        </is>
+      </c>
+      <c r="R49" s="76">
+        <f>LOWER(TRIM(C49)&amp;"|"&amp;TRIM(D49)&amp;"|"&amp;TRIM(E49)&amp;"|"&amp;TRIM(F49)&amp;"|"&amp;TRIM(H49)&amp;"|"&amp;TRIM(I49))</f>
+        <v/>
+      </c>
+      <c r="S49" s="76">
+        <f>IF(COUNTIF($R$6:$R$52,R49)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T49" s="76" t="inlineStr">
+        <is>
+          <t>e02f112d7004b76aa4211310aaa405666058d372a746f26a5af33f574dd49509</t>
+        </is>
+      </c>
+      <c r="U49" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V49" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="W49" s="76" t="inlineStr">
+        <is>
+          <t>原创Godot Prefab与脚本</t>
+        </is>
+      </c>
+      <c r="X49" s="76" t="inlineStr">
+        <is>
+          <t>FX01-30</t>
+        </is>
+      </c>
+      <c r="Y49" s="76" t="inlineStr">
+        <is>
+          <t>独立Prefab；无碰撞；机制与独立真实渲染验证，完整战局压力另验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="70" customHeight="1" s="52">
+      <c r="A50" s="76" t="inlineStr">
+        <is>
+          <t>VFX-FATE-POISON-3D</t>
+        </is>
+      </c>
+      <c r="B50" s="76" t="inlineStr">
+        <is>
+          <t>命运环绕毒雾</t>
+        </is>
+      </c>
+      <c r="C50" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D50" s="76" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E50" s="76" t="inlineStr">
+        <is>
+          <t>fate_poison</t>
+        </is>
+      </c>
+      <c r="F50" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G50" s="76" t="n"/>
+      <c r="H50" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I50" s="76" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+      <c r="J50" s="76" t="inlineStr">
+        <is>
+          <t>命运元素与战斗伤害</t>
+        </is>
+      </c>
+      <c r="K50" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L50" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M50" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N50" s="76" t="inlineStr">
+        <is>
+          <t>4团半透明绿雾环绕，叠层不增加粒子</t>
+        </is>
+      </c>
+      <c r="O50" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_fate_poison_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P50" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxFatePoison3D.gd; docs/v0.1/14.6_特效系统与制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q50" s="76" t="inlineStr">
+        <is>
+          <t>命运;低粒子;元素反馈</t>
+        </is>
+      </c>
+      <c r="R50" s="76">
+        <f>LOWER(TRIM(C50)&amp;"|"&amp;TRIM(D50)&amp;"|"&amp;TRIM(E50)&amp;"|"&amp;TRIM(F50)&amp;"|"&amp;TRIM(H50)&amp;"|"&amp;TRIM(I50))</f>
+        <v/>
+      </c>
+      <c r="S50" s="76">
+        <f>IF(COUNTIF($R$6:$R$52,R50)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T50" s="76" t="inlineStr">
+        <is>
+          <t>ecc785a682d13974154067c6c34c5c3fa8f10778054f830789aad4b34654929a</t>
+        </is>
+      </c>
+      <c r="U50" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V50" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="W50" s="76" t="inlineStr">
+        <is>
+          <t>原创Godot Prefab与脚本</t>
+        </is>
+      </c>
+      <c r="X50" s="76" t="inlineStr">
+        <is>
+          <t>FX01-31</t>
+        </is>
+      </c>
+      <c r="Y50" s="76" t="inlineStr">
+        <is>
+          <t>独立Prefab；无碰撞；机制与独立真实渲染验证，完整战局压力另验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="70" customHeight="1" s="52">
+      <c r="A51" s="76" t="inlineStr">
+        <is>
+          <t>VFX-FATE-LIGHTNING-3D</t>
+        </is>
+      </c>
+      <c r="B51" s="76" t="inlineStr">
+        <is>
+          <t>命运连锁闪电</t>
+        </is>
+      </c>
+      <c r="C51" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D51" s="76" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="E51" s="76" t="inlineStr">
+        <is>
+          <t>fate_lightning</t>
+        </is>
+      </c>
+      <c r="F51" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G51" s="76" t="n"/>
+      <c r="H51" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I51" s="76" t="inlineStr">
+        <is>
+          <t>lightning</t>
+        </is>
+      </c>
+      <c r="J51" s="76" t="inlineStr">
+        <is>
+          <t>命运元素与战斗伤害</t>
+        </is>
+      </c>
+      <c r="K51" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L51" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M51" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N51" s="76" t="inlineStr">
+        <is>
+          <t>4枚火星（两端各2）＋6段电弧/光晕；0.045s飞出，0.20s收尾</t>
+        </is>
+      </c>
+      <c r="O51" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_fate_lightning_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P51" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxFateLightning3D.gd; docs/v0.1/14.6_特效系统与制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q51" s="76" t="inlineStr">
+        <is>
+          <t>命运;低粒子;元素反馈</t>
+        </is>
+      </c>
+      <c r="R51" s="76">
+        <f>LOWER(TRIM(C51)&amp;"|"&amp;TRIM(D51)&amp;"|"&amp;TRIM(E51)&amp;"|"&amp;TRIM(F51)&amp;"|"&amp;TRIM(H51)&amp;"|"&amp;TRIM(I51))</f>
+        <v/>
+      </c>
+      <c r="S51" s="76">
+        <f>IF(COUNTIF($R$6:$R$52,R51)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T51" s="76" t="inlineStr">
+        <is>
+          <t>e7c4d18cc74177f6146c0f7bc9545671ab976479b7280db63dda40a300bb8e39</t>
+        </is>
+      </c>
+      <c r="U51" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V51" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="W51" s="76" t="inlineStr">
+        <is>
+          <t>原创Godot Prefab与脚本</t>
+        </is>
+      </c>
+      <c r="X51" s="76" t="inlineStr">
+        <is>
+          <t>FX01-32</t>
+        </is>
+      </c>
+      <c r="Y51" s="76" t="inlineStr">
+        <is>
+          <t>独立Prefab；无碰撞；机制与独立真实渲染验证，完整战局压力另验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="70" customHeight="1" s="52">
+      <c r="A52" s="76" t="inlineStr">
+        <is>
+          <t>VFX-DAMAGE-NUMBER-3D</t>
+        </is>
+      </c>
+      <c r="B52" s="76" t="inlineStr">
+        <is>
+          <t>伤害数字飘字特效</t>
+        </is>
+      </c>
+      <c r="C52" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D52" s="76" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="E52" s="76" t="inlineStr">
+        <is>
+          <t>damage_number_3d</t>
+        </is>
+      </c>
+      <c r="F52" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G52" s="76" t="n"/>
+      <c r="H52" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D</t>
+        </is>
+      </c>
+      <c r="I52" s="76" t="inlineStr">
+        <is>
+          <t>damage_number</t>
+        </is>
+      </c>
+      <c r="J52" s="76" t="inlineStr">
+        <is>
+          <t>命运元素与战斗伤害</t>
+        </is>
+      </c>
+      <c r="K52" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L52" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M52" s="76" t="inlineStr">
+        <is>
+          <t>v005</t>
+        </is>
+      </c>
+      <c r="N52" s="76" t="inlineStr">
+        <is>
+          <t>元素配色；0.56s先快后慢上升0.90m；字形与描边13/15/17保持</t>
+        </is>
+      </c>
+      <c r="O52" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_damage_number_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P52" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxDamageNumber3D.gd; docs/v0.1/14.6_特效系统与制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q52" s="76" t="inlineStr">
+        <is>
+          <t>命运;低粒子;元素反馈</t>
+        </is>
+      </c>
+      <c r="R52" s="76">
+        <f>LOWER(TRIM(C52)&amp;"|"&amp;TRIM(D52)&amp;"|"&amp;TRIM(E52)&amp;"|"&amp;TRIM(F52)&amp;"|"&amp;TRIM(H52)&amp;"|"&amp;TRIM(I52))</f>
+        <v/>
+      </c>
+      <c r="S52" s="76">
+        <f>IF(COUNTIF($R$6:$R$52,R52)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T52" s="76" t="inlineStr">
+        <is>
+          <t>a6f316bb5949dbcc1216782f92d014a5c5ffdde0ab73b31abad90b787d7f36cd</t>
+        </is>
+      </c>
+      <c r="U52" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V52" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="W52" s="76" t="inlineStr">
+        <is>
+          <t>原创Godot Prefab与脚本</t>
+        </is>
+      </c>
+      <c r="X52" s="76" t="inlineStr">
+        <is>
+          <t>FX02-01</t>
+        </is>
+      </c>
+      <c r="Y52" s="76" t="inlineStr">
+        <is>
+          <t>独立Prefab；无碰撞；机制与独立真实渲染验证，完整战局压力另验。</t>
         </is>
       </c>
     </row>
@@ -7438,7 +8043,7 @@
     <row r="427" ht="84.75" customHeight="1" s="52"/>
     <row r="429" ht="120" customHeight="1" s="52"/>
   </sheetData>
-  <autoFilter ref="A5:Y42"/>
+  <autoFilter ref="A5:Y52"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -7451,13 +8056,13 @@
     <cfRule type="containsText" priority="3" operator="containsText" dxfId="8" text="待制作"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,子弹特效,音效,音乐"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,design_only,authored,exported_pending_godot_validation,validated,active,已从运行场景移除,白盒组件"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7510,6 +8115,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="84" t="inlineStr">
         <is>
@@ -8310,7 +8916,7 @@
       </c>
       <c r="G16" s="51" t="inlineStr">
         <is>
-          <t>受击伤害数字上升飘字；Label3D + 漫画风超粗字形 + 粗近黑勾边 + 颜色编码（红/橙/暴击金）；参数 effect_color + context.text_value/magnitude/critical + 五维随机（spawn_offset/rise_scale/drift/pop_scale/duration_scale）。</t>
+          <t>元素配色；0.56s先快后慢上升0.90m；字形与描边13/15/17保持</t>
         </is>
       </c>
       <c r="H16" s="101" t="inlineStr">
@@ -8335,7 +8941,7 @@
       </c>
       <c r="L16" s="101" t="inlineStr">
         <is>
-          <t>Label3D pixel_size=0.00375；MSDF 128 + msdf_pixel_range 64（描边可达上限 ≈ range/2）；字号分档 116/134/152（世界字高 0.435/0.503/0.570 m）；描边 13/15/17；lifetime 0.70s × duration_scale；基线上升 0.90m</t>
+          <t>lifetime0.56s × duration_scale；上升0.90m；快速弹起减速淡出；元素色；字形116/134/152与描边13/15/17不变</t>
         </is>
       </c>
       <c r="M16" s="51" t="inlineStr">
@@ -8355,12 +8961,12 @@
       </c>
       <c r="P16" s="101" t="inlineStr">
         <is>
-          <t>v004</t>
+          <t>v005</t>
         </is>
       </c>
       <c r="Q16" s="51" t="inlineStr">
         <is>
-          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_damage_number_root_top3d.tscn + 脚本=src/vfx/VfxDamageNumber3D.gd；根节点=VfxDamageNumber3D(Node3D)；FX编号 FX02-01；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由。【2026-10-16 样式重做】字体与样式真源收敛到 src/vfx/DamageNumberStyle.gd（漫画风超粗体：字体链首选 Impact、字重 900、MSDF 128；近黑粗勾边 ≈ 字高 22%）；随机数只活在调用方 Enemy3D._damage_number_context()，特效脚本对同一 context 逐位可复现。【P0 修复】_on_tick 原以**赋值**写 position（position.y = rise_t × 距离），出生坐标第一帧即被清零 —— 实测实机飘字跑到世界原点上方不到 1 米、与怪物楼层无关；改为 position = _origin_local + 偏移。Prefab 路径去掉历史误写的 _v001 后缀。【2026-10-17 勾边修复】**勾边修复：`msdf_pixel_range` 太小导致描边被截成 1px 细丝**。Godot 的 MSDF 字体下描边可达上限 ≈ msdf_pixel_range / 2，默认 16 只够到 8，而本件声明 26/30/34 ⇒ 被提前截断（症状：不报错不变红，且 outline_size 填 26 与 116 渲染结果逐像素完全相同）。修法：`DamageNumberStyle.MSDF_PIXEL_RANGE = 64`，在 `make_font()` 里赋给 `SystemFont.msdf_pixel_range`；三条链路共用该字体工厂，一处即全覆盖。定档实测（字形高约 108px 定尺拍摄）：range 16 → 实画 6px、48 → 21px、64/80 → 26px 足额、96 → 左右不对称（一侧整条丢失）⇒ 取 64，验收另设上界护栏 80。验收新增常量钉子 + 下界不等式 + 逐档「实例真带该值」断言；反向对照三组（16／96／删赋值）均精准变红后复绿。实机距离 A/B：描边像素 160 → 13,421（×83.9）。【2026-10-17 描边减半】**描边减半**（业主：「太粗了，缩小一半」）。v003 修好 `msdf_pixel_range` 后描边第一次足额渲染，实机看下来过粗 ⇒ 描边尺寸 26/30/34 → **13/15/17**（占字高 22% → 11%，描边色与淡出通道不变）。真源 `DamageNumberStyle.NORMAL/HEAVY/CRITICAL_OUTLINE_SIZE` 一处改动即覆盖三条链路。**距离场宽度不动**（仍 64）：需求 2 × max(描边 × msdf_size / 字号) 由 57.4 降到 28.7，64 依旧足额且支持描边到约 38 @ 字号 152，留余量以便后续微调不必重新定档。验收侧硬编码期望同步为 13/15/17、下界不等式随之重算为 28.7。反向对照两组：range→16（下界红）／真源描边偷偷改回 26（常量钉子红）—— 均精准变红后复绿。实机同帧 A/B（红色字形像素恒为 5,105 ⇒ 字形未变）：近黑描边像素 12,613 → 6,392（×0.507）。</t>
+          <t>已实装；Prefab=assets/art/vfx/combat_3d/vfx_damage_number_root_top3d.tscn + 脚本=src/vfx/VfxDamageNumber3D.gd；根节点=VfxDamageNumber3D(Node3D)；FX编号 FX02-01；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由；接受 context.text_value；调用方：Enemy3D._spawn_damage_number 经 VfxPool3D 路由。【2026-10-16 样式重做】字体与样式真源收敛到 src/vfx/DamageNumberStyle.gd（漫画风超粗体：字体链首选 Impact、字重 900、MSDF 128；近黑粗勾边 ≈ 字高 22%）；随机数只活在调用方 Enemy3D._damage_number_context()，特效脚本对同一 context 逐位可复现。【P0 修复】_on_tick 原以**赋值**写 position（position.y = rise_t × 距离），出生坐标第一帧即被清零 —— 实测实机飘字跑到世界原点上方不到 1 米、与怪物楼层无关；改为 position = _origin_local + 偏移。Prefab 路径去掉历史误写的 _v001 后缀。【2026-10-17 勾边修复】**勾边修复：`msdf_pixel_range` 太小导致描边被截成 1px 细丝**。Godot 的 MSDF 字体下描边可达上限 ≈ msdf_pixel_range / 2，默认 16 只够到 8，而本件声明 26/30/34 ⇒ 被提前截断（症状：不报错不变红，且 outline_size 填 26 与 116 渲染结果逐像素完全相同）。修法：`DamageNumberStyle.MSDF_PIXEL_RANGE = 64`，在 `make_font()` 里赋给 `SystemFont.msdf_pixel_range`；三条链路共用该字体工厂，一处即全覆盖。定档实测（字形高约 108px 定尺拍摄）：range 16 → 实画 6px、48 → 21px、64/80 → 26px 足额、96 → 左右不对称（一侧整条丢失）⇒ 取 64，验收另设上界护栏 80。验收新增常量钉子 + 下界不等式 + 逐档「实例真带该值」断言；反向对照三组（16／96／删赋值）均精准变红后复绿。实机距离 A/B：描边像素 160 → 13,421（×83.9）。【2026-10-17 描边减半】**描边减半**（业主：「太粗了，缩小一半」）。v003 修好 `msdf_pixel_range` 后描边第一次足额渲染，实机看下来过粗 ⇒ 描边尺寸 26/30/34 → **13/15/17**（占字高 22% → 11%，描边色与淡出通道不变）。真源 `DamageNumberStyle.NORMAL/HEAVY/CRITICAL_OUTLINE_SIZE` 一处改动即覆盖三条链路。**距离场宽度不动**（仍 64）：需求 2 × max(描边 × msdf_size / 字号) 由 57.4 降到 28.7，64 依旧足额且支持描边到约 38 @ 字号 152，留余量以便后续微调不必重新定档。验收侧硬编码期望同步为 13/15/17、下界不等式随之重算为 28.7。反向对照两组：range→16（下界红）／真源描边偷偷改回 26（常量钉子红）—— 均精准变红后复绿。实机同帧 A/B（红色字形像素恒为 5,105 ⇒ 字形未变）：近黑描边像素 12,613 → 6,392（×0.507）。【2026-10-18】元素配色与更快飘动；补齐主表VFX-DAMAGE-NUMBER-3D登记，旧2D占位VFX-DAMAGE-NUMBER保留。</t>
         </is>
       </c>
     </row>
@@ -10685,24 +11291,352 @@
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="52">
-      <c r="H49" s="101" t="n"/>
-      <c r="I49" s="51" t="n"/>
-      <c r="N49" s="51" t="n"/>
+      <c r="A49" s="100" t="inlineStr">
+        <is>
+          <t>FX01-29</t>
+        </is>
+      </c>
+      <c r="B49" s="101" t="inlineStr">
+        <is>
+          <t>VFX-FATE-FIRE-3D</t>
+        </is>
+      </c>
+      <c r="C49" s="51" t="inlineStr">
+        <is>
+          <t>命运火焰跳动</t>
+        </is>
+      </c>
+      <c r="D49" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_fate_fire_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E49" s="51" t="inlineStr">
+        <is>
+          <t>无（Prefab几何）</t>
+        </is>
+      </c>
+      <c r="F49" s="51" t="inlineStr">
+        <is>
+          <t>无（Prefab几何）</t>
+        </is>
+      </c>
+      <c r="G49" s="51" t="inlineStr">
+        <is>
+          <t>4枚橙红火舌错相跳动，状态Owner驱动结束</t>
+        </is>
+      </c>
+      <c r="H49" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxFateFire3D.gd</t>
+        </is>
+      </c>
+      <c r="I49" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J49" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K49" s="51" t="inlineStr">
+        <is>
+          <t>无碰撞体</t>
+        </is>
+      </c>
+      <c r="L49" s="51" t="inlineStr">
+        <is>
+          <t>4枚橙红火舌错相跳动，状态Owner驱动结束</t>
+        </is>
+      </c>
+      <c r="M49" s="51" t="inlineStr">
+        <is>
+          <t>原点=脚底</t>
+        </is>
+      </c>
+      <c r="N49" s="51" t="inlineStr">
+        <is>
+          <t>Enemy3D</t>
+        </is>
+      </c>
+      <c r="O49" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P49" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q49" s="51" t="inlineStr">
+        <is>
+          <t>机制/池化/接线与真实渲染；docs/v0.1/development/2026-10-18_fate_elements.md</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="52">
-      <c r="H50" s="101" t="n"/>
-      <c r="I50" s="51" t="n"/>
-      <c r="N50" s="51" t="n"/>
+      <c r="A50" s="100" t="inlineStr">
+        <is>
+          <t>FX01-30</t>
+        </is>
+      </c>
+      <c r="B50" s="101" t="inlineStr">
+        <is>
+          <t>VFX-FATE-FROST-3D</t>
+        </is>
+      </c>
+      <c r="C50" s="51" t="inlineStr">
+        <is>
+          <t>命运脚底冰霜</t>
+        </is>
+      </c>
+      <c r="D50" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_fate_frost_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E50" s="51" t="inlineStr">
+        <is>
+          <t>无（Prefab几何）</t>
+        </is>
+      </c>
+      <c r="F50" s="51" t="inlineStr">
+        <is>
+          <t>无（Prefab几何）</t>
+        </is>
+      </c>
+      <c r="G50" s="51" t="inlineStr">
+        <is>
+          <t>4枚冰晶＋薄霜面，冻结/命运减速期间跟随脚底</t>
+        </is>
+      </c>
+      <c r="H50" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxFateFrost3D.gd</t>
+        </is>
+      </c>
+      <c r="I50" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J50" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K50" s="51" t="inlineStr">
+        <is>
+          <t>无碰撞体</t>
+        </is>
+      </c>
+      <c r="L50" s="51" t="inlineStr">
+        <is>
+          <t>4枚冰晶＋薄霜面，冻结/命运减速期间跟随脚底</t>
+        </is>
+      </c>
+      <c r="M50" s="51" t="inlineStr">
+        <is>
+          <t>原点=脚底</t>
+        </is>
+      </c>
+      <c r="N50" s="51" t="inlineStr">
+        <is>
+          <t>Enemy3D</t>
+        </is>
+      </c>
+      <c r="O50" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P50" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q50" s="51" t="inlineStr">
+        <is>
+          <t>机制/池化/接线与真实渲染；docs/v0.1/development/2026-10-18_fate_elements.md</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="52">
-      <c r="H51" s="101" t="n"/>
-      <c r="I51" s="51" t="n"/>
-      <c r="N51" s="51" t="n"/>
+      <c r="A51" s="100" t="inlineStr">
+        <is>
+          <t>FX01-31</t>
+        </is>
+      </c>
+      <c r="B51" s="101" t="inlineStr">
+        <is>
+          <t>VFX-FATE-POISON-3D</t>
+        </is>
+      </c>
+      <c r="C51" s="51" t="inlineStr">
+        <is>
+          <t>命运环绕毒雾</t>
+        </is>
+      </c>
+      <c r="D51" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_fate_poison_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E51" s="51" t="inlineStr">
+        <is>
+          <t>无（Prefab几何）</t>
+        </is>
+      </c>
+      <c r="F51" s="51" t="inlineStr">
+        <is>
+          <t>无（Prefab几何）</t>
+        </is>
+      </c>
+      <c r="G51" s="51" t="inlineStr">
+        <is>
+          <t>4团半透明绿雾环绕，叠层不增加粒子</t>
+        </is>
+      </c>
+      <c r="H51" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxFatePoison3D.gd</t>
+        </is>
+      </c>
+      <c r="I51" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J51" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K51" s="51" t="inlineStr">
+        <is>
+          <t>无碰撞体</t>
+        </is>
+      </c>
+      <c r="L51" s="51" t="inlineStr">
+        <is>
+          <t>4团半透明绿雾环绕，叠层不增加粒子</t>
+        </is>
+      </c>
+      <c r="M51" s="51" t="inlineStr">
+        <is>
+          <t>原点=脚底</t>
+        </is>
+      </c>
+      <c r="N51" s="51" t="inlineStr">
+        <is>
+          <t>Enemy3D</t>
+        </is>
+      </c>
+      <c r="O51" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P51" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q51" s="51" t="inlineStr">
+        <is>
+          <t>机制/池化/接线与真实渲染；docs/v0.1/development/2026-10-18_fate_elements.md</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="52">
-      <c r="H52" s="101" t="n"/>
-      <c r="I52" s="51" t="n"/>
-      <c r="N52" s="51" t="n"/>
+      <c r="A52" s="100" t="inlineStr">
+        <is>
+          <t>FX01-32</t>
+        </is>
+      </c>
+      <c r="B52" s="101" t="inlineStr">
+        <is>
+          <t>VFX-FATE-LIGHTNING-3D</t>
+        </is>
+      </c>
+      <c r="C52" s="51" t="inlineStr">
+        <is>
+          <t>命运连锁闪电</t>
+        </is>
+      </c>
+      <c r="D52" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_fate_lightning_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E52" s="51" t="inlineStr">
+        <is>
+          <t>无（Prefab几何）</t>
+        </is>
+      </c>
+      <c r="F52" s="51" t="inlineStr">
+        <is>
+          <t>无（Prefab几何）</t>
+        </is>
+      </c>
+      <c r="G52" s="51" t="inlineStr">
+        <is>
+          <t>4枚火星（两端各2）＋6段电弧/光晕；0.045s飞出，0.20s收尾</t>
+        </is>
+      </c>
+      <c r="H52" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxFateLightning3D.gd</t>
+        </is>
+      </c>
+      <c r="I52" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J52" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K52" s="51" t="inlineStr">
+        <is>
+          <t>无碰撞体</t>
+        </is>
+      </c>
+      <c r="L52" s="51" t="inlineStr">
+        <is>
+          <t>4枚火星（两端各2）＋6段电弧/光晕；0.045s飞出，0.20s收尾</t>
+        </is>
+      </c>
+      <c r="M52" s="51" t="inlineStr">
+        <is>
+          <t>原点=起点；context.end_position为世界终点</t>
+        </is>
+      </c>
+      <c r="N52" s="51" t="inlineStr">
+        <is>
+          <t>Projectile3D</t>
+        </is>
+      </c>
+      <c r="O52" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P52" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q52" s="51" t="inlineStr">
+        <is>
+          <t>机制/池化/接线与真实渲染；docs/v0.1/development/2026-10-18_fate_elements.md</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="52">
       <c r="H53" s="101" t="n"/>
@@ -11725,7 +12659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="51" min="1" max="1"/>
@@ -12886,6 +13820,43 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>v0.1.28</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>元素表现与数字升级</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>FX01-29至32/FX02-01</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>四个独立低粒子Prefab；伤害数字v005元素颜色与0.56秒；补齐既有3D数字主表登记</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>稳定ID/运行路径不带版本；旧2D占位保留</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -1447,22 +1447,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="52">
       <c r="A6" s="57">
-        <f>COUNTA('资产主表'!$A$6:$A$52)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$53)</f>
         <v/>
       </c>
       <c r="B6" s="55" t="n"/>
       <c r="C6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$52,"已完成")+COUNTIF('资产主表'!$K$6:$K$52,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$52,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$52,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$52,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$52,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$52,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$53,"已完成")+COUNTIF('资产主表'!$K$6:$K$53,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$53,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$53,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$53,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$53,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$53,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="55" t="n"/>
       <c r="E6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$52,"待制作")+COUNTIF('资产主表'!$K$6:$K$52,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$53,"待制作")+COUNTIF('资产主表'!$K$6:$K$53,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="55" t="n"/>
       <c r="G6" s="57">
-        <f>COUNTIF('资产主表'!$S$6:$S$52,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$53,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="55" t="n"/>
@@ -1531,11 +1531,11 @@
         </is>
       </c>
       <c r="B10" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$52,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$53,A10)</f>
         <v/>
       </c>
       <c r="C10" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$52=A10)*(('资产主表'!$K$6:$K$52="已完成")+('资产主表'!$K$6:$K$52="原型已接入")+('资产主表'!$K$6:$K$52="正式美术已接入")+('资产主表'!$K$6:$K$52="已优化并正式接入")+('资产主表'!$K$6:$K$52="Blender源已完成")+('资产主表'!$K$6:$K$52="已导入；优化完成")+('资产主表'!$K$6:$K$52="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$53=A10)*(('资产主表'!$K$6:$K$53="已完成")+('资产主表'!$K$6:$K$53="原型已接入")+('资产主表'!$K$6:$K$53="正式美术已接入")+('资产主表'!$K$6:$K$53="已优化并正式接入")+('资产主表'!$K$6:$K$53="Blender源已完成")+('资产主表'!$K$6:$K$53="已导入；优化完成")+('资产主表'!$K$6:$K$53="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="62" t="n"/>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B11" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$52,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$53,A11)</f>
         <v/>
       </c>
       <c r="C11" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$52=A11)*(('资产主表'!$K$6:$K$52="已完成")+('资产主表'!$K$6:$K$52="原型已接入")+('资产主表'!$K$6:$K$52="正式美术已接入")+('资产主表'!$K$6:$K$52="已优化并正式接入")+('资产主表'!$K$6:$K$52="Blender源已完成")+('资产主表'!$K$6:$K$52="已导入；优化完成")+('资产主表'!$K$6:$K$52="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$53=A11)*(('资产主表'!$K$6:$K$53="已完成")+('资产主表'!$K$6:$K$53="原型已接入")+('资产主表'!$K$6:$K$53="正式美术已接入")+('资产主表'!$K$6:$K$53="已优化并正式接入")+('资产主表'!$K$6:$K$53="Blender源已完成")+('资产主表'!$K$6:$K$53="已导入；优化完成")+('资产主表'!$K$6:$K$53="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="62" t="n"/>
@@ -2115,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y52"/>
+  <dimension ref="A1:Y53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="51" min="1" max="1"/>
@@ -2387,7 +2387,7 @@
         <v/>
       </c>
       <c r="S6" s="63">
-        <f>IF(COUNTIF($R$6:$R$52,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="63" t="n"/>
@@ -2490,7 +2490,7 @@
         <v/>
       </c>
       <c r="S7" s="63">
-        <f>IF(COUNTIF($R$6:$R$52,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="63" t="n"/>
@@ -2593,7 +2593,7 @@
         <v/>
       </c>
       <c r="S8" s="63">
-        <f>IF(COUNTIF($R$6:$R$52,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="63" t="n"/>
@@ -2696,7 +2696,7 @@
         <v/>
       </c>
       <c r="S9" s="63">
-        <f>IF(COUNTIF($R$6:$R$52,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="63" t="n"/>
@@ -2803,7 +2803,7 @@
         <v/>
       </c>
       <c r="S10" s="63">
-        <f>IF(COUNTIF($R$6:$R$52,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="63" t="n"/>
@@ -2910,7 +2910,7 @@
         <v/>
       </c>
       <c r="S11" s="63">
-        <f>IF(COUNTIF($R$6:$R$52,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="63" t="n"/>
@@ -3017,7 +3017,7 @@
         <v/>
       </c>
       <c r="S12" s="63">
-        <f>IF(COUNTIF($R$6:$R$52,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="63" t="n"/>
@@ -3124,7 +3124,7 @@
         <v/>
       </c>
       <c r="S13" s="63">
-        <f>IF(COUNTIF($R$6:$R$52,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="63" t="n"/>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="S14" s="63">
-        <f>IF(COUNTIF($R$6:$R$52,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="63" t="n"/>
@@ -3338,7 +3338,7 @@
         <v/>
       </c>
       <c r="S15" s="63">
-        <f>IF(COUNTIF($R$6:$R$52,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="63" t="n"/>
@@ -3445,7 +3445,7 @@
         <v/>
       </c>
       <c r="S16" s="63">
-        <f>IF(COUNTIF($R$6:$R$52,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="63" t="n"/>
@@ -3564,7 +3564,7 @@
         <v/>
       </c>
       <c r="S17" s="55">
-        <f>IF(COUNTIF($R$6:$R$52,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="79" t="inlineStr">
@@ -3683,7 +3683,7 @@
         <v/>
       </c>
       <c r="S18" s="55">
-        <f>IF(COUNTIF($R$6:$R$52,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="79" t="inlineStr">
@@ -3806,7 +3806,7 @@
         <v/>
       </c>
       <c r="S19" s="55">
-        <f>IF(COUNTIF($R$6:$R$52,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="79" t="inlineStr">
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="S20" s="55">
-        <f>IF(COUNTIF($R$6:$R$52,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="79" t="inlineStr">
@@ -4046,7 +4046,7 @@
         <v/>
       </c>
       <c r="S21" s="55">
-        <f>IF(COUNTIF($R$6:$R$52,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="79" t="inlineStr">
@@ -4165,7 +4165,7 @@
         <v/>
       </c>
       <c r="S22" s="55">
-        <f>IF(COUNTIF($R$6:$R$52,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="79" t="inlineStr">
@@ -4284,7 +4284,7 @@
         <v/>
       </c>
       <c r="S23" s="55">
-        <f>IF(COUNTIF($R$6:$R$52,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="79" t="inlineStr">
@@ -4403,7 +4403,7 @@
         <v/>
       </c>
       <c r="S24" s="55">
-        <f>IF(COUNTIF($R$6:$R$52,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="79" t="inlineStr">
@@ -4522,7 +4522,7 @@
         <v/>
       </c>
       <c r="S25" s="55">
-        <f>IF(COUNTIF($R$6:$R$52,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="79" t="inlineStr">
@@ -4641,7 +4641,7 @@
         <v/>
       </c>
       <c r="S26" s="79">
-        <f>IF(COUNTIF($R$6:$R$52,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="79" t="inlineStr">
@@ -4767,7 +4767,7 @@
         <v/>
       </c>
       <c r="S27" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="76" t="inlineStr">
@@ -4889,7 +4889,7 @@
         <v/>
       </c>
       <c r="S28" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="76" t="inlineStr">
@@ -5011,7 +5011,7 @@
         <v/>
       </c>
       <c r="S29" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="76" t="inlineStr">
@@ -5133,7 +5133,7 @@
         <v/>
       </c>
       <c r="S30" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="76" t="inlineStr">
@@ -5255,7 +5255,7 @@
         <v/>
       </c>
       <c r="S31" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="76" t="inlineStr">
@@ -5377,7 +5377,7 @@
         <v/>
       </c>
       <c r="S32" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="76" t="inlineStr">
@@ -5499,7 +5499,7 @@
         <v/>
       </c>
       <c r="S33" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="76" t="inlineStr">
@@ -5621,7 +5621,7 @@
         <v/>
       </c>
       <c r="S34" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="76" t="inlineStr">
@@ -5739,7 +5739,7 @@
         <v/>
       </c>
       <c r="S35" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="76" t="inlineStr">
@@ -5858,7 +5858,7 @@
         <v/>
       </c>
       <c r="S36" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="76" t="inlineStr">
@@ -5979,7 +5979,7 @@
         <v/>
       </c>
       <c r="S37" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="76" t="inlineStr">
@@ -6100,7 +6100,7 @@
         <v/>
       </c>
       <c r="S38" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R38)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R38)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T38" s="76" t="inlineStr">
@@ -6221,7 +6221,7 @@
         <v/>
       </c>
       <c r="S39" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R39)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R39)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T39" s="76" t="inlineStr">
@@ -6359,7 +6359,7 @@
         <v/>
       </c>
       <c r="S40" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R40)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R40)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T40" s="76" t="inlineStr">
@@ -6480,7 +6480,7 @@
         <v/>
       </c>
       <c r="S41" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R41)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R41)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T41" s="76" t="inlineStr">
@@ -6601,7 +6601,7 @@
         <v/>
       </c>
       <c r="S42" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R42)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R42)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T42" s="76" t="inlineStr">
@@ -6722,7 +6722,7 @@
         <v/>
       </c>
       <c r="S43" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R43)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R43)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T43" s="76" t="inlineStr">
@@ -6841,7 +6841,7 @@
         <v/>
       </c>
       <c r="S44" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R44)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R44)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T44" s="76" t="inlineStr">
@@ -6960,7 +6960,7 @@
         <v/>
       </c>
       <c r="S45" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R45)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R45)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T45" s="76" t="inlineStr">
@@ -7079,7 +7079,7 @@
         <v/>
       </c>
       <c r="S46" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R46)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R46)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T46" s="76" t="inlineStr">
@@ -7198,7 +7198,7 @@
         <v/>
       </c>
       <c r="S47" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R47)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R47)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T47" s="76" t="inlineStr">
@@ -7317,7 +7317,7 @@
         <v/>
       </c>
       <c r="S48" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R48)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R48)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T48" s="76" t="inlineStr">
@@ -7438,7 +7438,7 @@
         <v/>
       </c>
       <c r="S49" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R49)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R49)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T49" s="76" t="inlineStr">
@@ -7559,7 +7559,7 @@
         <v/>
       </c>
       <c r="S50" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R50)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R50)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T50" s="76" t="inlineStr">
@@ -7680,7 +7680,7 @@
         <v/>
       </c>
       <c r="S51" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R51)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R51)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T51" s="76" t="inlineStr">
@@ -7801,7 +7801,7 @@
         <v/>
       </c>
       <c r="S52" s="76">
-        <f>IF(COUNTIF($R$6:$R$52,R52)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$53,R52)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T52" s="76" t="inlineStr">
@@ -7832,6 +7832,127 @@
       <c r="Y52" s="76" t="inlineStr">
         <is>
           <t>独立Prefab；无碰撞；机制与独立真实渲染验证，完整战局压力另验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="70" customHeight="1" s="52">
+      <c r="A53" s="76" t="inlineStr">
+        <is>
+          <t>VFX-BOARD-DEBRIS-3D</t>
+        </is>
+      </c>
+      <c r="B53" s="76" t="inlineStr">
+        <is>
+          <t>暗门木板碎块飞溅</t>
+        </is>
+      </c>
+      <c r="C53" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D53" s="76" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="E53" s="76" t="inlineStr">
+        <is>
+          <t>board_debris_3d</t>
+        </is>
+      </c>
+      <c r="F53" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G53" s="76" t="n"/>
+      <c r="H53" s="76" t="inlineStr">
+        <is>
+          <t>空间3D（朝房间侧）</t>
+        </is>
+      </c>
+      <c r="I53" s="76" t="inlineStr">
+        <is>
+          <t>board_debris</t>
+        </is>
+      </c>
+      <c r="J53" s="76" t="inlineStr">
+        <is>
+          <t>暗门破板事件</t>
+        </is>
+      </c>
+      <c r="K53" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L53" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M53" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N53" s="76" t="inlineStr">
+        <is>
+          <t>8 大块（0.36~0.58m 长 × 0.16~0.26m 宽 × 0.07~0.10m 厚）+ 5 片小碎屑（0.045~0.085m）；2.85s 寿命；散布 3~5m</t>
+        </is>
+      </c>
+      <c r="O53" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_board_debris_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P53" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBoardDebris3D.gd; docs/v0.1/14.6_特效系统与制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q53" s="76" t="inlineStr">
+        <is>
+          <t>暗门;破板;木块;碎屑;大块;木板崩飞</t>
+        </is>
+      </c>
+      <c r="R53" s="76">
+        <f>LOWER(TRIM(C53)&amp;"|"&amp;TRIM(D53)&amp;"|"&amp;TRIM(E53)&amp;"|"&amp;TRIM(F53)&amp;"|"&amp;TRIM(H53)&amp;"|"&amp;TRIM(I53))</f>
+        <v/>
+      </c>
+      <c r="S53" s="76">
+        <f>IF(COUNTIF($R$6:$R$53,R53)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T53" s="76" t="inlineStr">
+        <is>
+          <t>8ca910cb20b27581965cff304912b70575b5bfd1ea6e79ea34f565e51ef7e4e5</t>
+        </is>
+      </c>
+      <c r="U53" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V53" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="W53" s="76" t="inlineStr">
+        <is>
+          <t>原创Godot Prefab与脚本</t>
+        </is>
+      </c>
+      <c r="X53" s="76" t="inlineStr">
+        <is>
+          <t>FX01-33</t>
+        </is>
+      </c>
+      <c r="Y53" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-19 新建（业主：「做一个门被打碎的木头飞出来的特效，大块一点的」）。8 大块 + 5 片小碎屑，程序化抛物飞行 → 触地弹跳 1 次 → 贴地滑行 → 放平静止（不接物理引擎，无碰撞体）；自带 DebrisLight（峰值 1.5 / 范围 3.6m / 无阴影 / 0.55s 归零）——塔内夜间光，无灯就是黑剪影。材质：金属度 metallic=0.0 / 反光度 roughness=0.86（PER_PIXEL 受光）+ 自发光 0.38（暗房里保住「木头」读法）。确定性：脚本内无 randf()，散开由调用方给的 context.seed 派生（同 seed 逐位可复现）。调用方 SecretDoor3D._break_open()：只在真打破时播，读档恢复 / 静默打开不重播。验收 tests/verification/verify_board_debris_vfx.tscn（9 条，含大块下限 0.30m + 上限 0.65m 双向）。</t>
         </is>
       </c>
     </row>
@@ -8056,13 +8177,13 @@
     <cfRule type="containsText" priority="3" operator="containsText" dxfId="8" text="待制作"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,子弹特效,音效,音乐"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,design_only,authored,exported_pending_godot_validation,validated,active,已从运行场景移除,白盒组件"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8115,7 +8236,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="84" t="inlineStr">
         <is>
@@ -11639,9 +11759,91 @@
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="52">
-      <c r="H53" s="101" t="n"/>
-      <c r="I53" s="51" t="n"/>
-      <c r="N53" s="51" t="n"/>
+      <c r="A53" s="100" t="inlineStr">
+        <is>
+          <t>FX01-33</t>
+        </is>
+      </c>
+      <c r="B53" s="101" t="inlineStr">
+        <is>
+          <t>VFX-BOARD-DEBRIS-3D</t>
+        </is>
+      </c>
+      <c r="C53" s="51" t="inlineStr">
+        <is>
+          <t>暗门木板碎块飞溅</t>
+        </is>
+      </c>
+      <c r="D53" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_board_debris_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E53" s="51" t="inlineStr">
+        <is>
+          <t>无（Prefab几何）</t>
+        </is>
+      </c>
+      <c r="F53" s="51" t="inlineStr">
+        <is>
+          <t>无（Prefab几何）</t>
+        </is>
+      </c>
+      <c r="G53" s="51" t="inlineStr">
+        <is>
+          <t>暗门木板被打碎时，整面板崩成 8 块大木片 + 5 片小碎屑飞向房间侧，抛物落地、弹一下、贴地滑行后停住；自带 0.55s 暖色短灯照亮碎块</t>
+        </is>
+      </c>
+      <c r="H53" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxBoardDebris3D.gd</t>
+        </is>
+      </c>
+      <c r="I53" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J53" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K53" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L53" s="51" t="inlineStr">
+        <is>
+          <t>8 大块（0.36~0.58m 长 × 0.16~0.26m 宽 × 0.07~0.10m 厚）+ 5 片小碎屑（0.045~0.085m）；2.85s 寿命；散布 3~5m</t>
+        </is>
+      </c>
+      <c r="M53" s="51" t="inlineStr">
+        <is>
+          <t>原点=门底中心（装配点），出生时抬高 1.25m 到门洞中部；局部 -Z 对齐 context.forward（门→房间侧），碎块朝房间内崩</t>
+        </is>
+      </c>
+      <c r="N53" s="51" t="inlineStr">
+        <is>
+          <t>暗门木板被打碎时（SecretDoor3D._break_open → VfxPool3D.acquire）</t>
+        </is>
+      </c>
+      <c r="O53" s="51" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P53" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q53" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-19 新建（业主：「做一个门被打碎的木头飞出来的特效，大块一点的」）。8 大块 + 5 片小碎屑，程序化抛物飞行 → 触地弹跳 1 次 → 贴地滑行 → 放平静止（不接物理引擎，无碰撞体）；自带 DebrisLight（峰值 1.5 / 范围 3.6m / 无阴影 / 0.55s 归零）——塔内夜间光，无灯就是黑剪影。材质：金属度 metallic=0.0 / 反光度 roughness=0.86（PER_PIXEL 受光）+ 自发光 0.38（暗房里保住「木头」读法）。确定性：脚本内无 randf()，散开由调用方给的 context.seed 派生（同 seed 逐位可复现）。调用方 SecretDoor3D._break_open()：只在真打破时播，读档恢复 / 静默打开不重播。验收 tests/verification/verify_board_debris_vfx.tscn（9 条，含大块下限 0.30m + 上限 0.65m 双向）。</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="52">
       <c r="H54" s="101" t="n"/>
@@ -12659,7 +12861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="51" min="1" max="1"/>
@@ -12686,7 +12888,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="52">
       <c r="A5" s="58" t="inlineStr">
         <is>
@@ -13820,38 +14021,75 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="36" s="52">
+      <c r="A36" s="51" t="inlineStr">
         <is>
           <t>v0.1.28</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="51" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="51" t="inlineStr">
         <is>
           <t>元素表现与数字升级</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="51" t="inlineStr">
         <is>
           <t>FX01-29至32/FX02-01</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="51" t="inlineStr">
         <is>
           <t>四个独立低粒子Prefab；伤害数字v005元素颜色与0.56秒；补齐既有3D数字主表登记</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="51" t="inlineStr">
         <is>
           <t>稳定ID/运行路径不带版本；旧2D占位保留</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="51" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" s="52">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>v0.1.29</t>
+        </is>
+      </c>
+      <c r="B37" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C37" s="51" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D37" s="51" t="inlineStr">
+        <is>
+          <t>特效 · 资产主表 / 3D-特效</t>
+        </is>
+      </c>
+      <c r="E37" s="51" t="inlineStr">
+        <is>
+          <t>新增 FX01-33 VFX-BOARD-DEBRIS-3D（暗门木板碎块飞溅）：8 大块木片（0.36~0.58m）+ 5 片小碎屑，程序化抛物/弹跳/滑行/静止，自带 DebrisLight 0.55s 短灯；调用方 SecretDoor3D._break_open()，读档恢复不重播。《资产主表》新增 r53，《3D-特效》新增 r53，《总览》区间由 $6:$52 扩到 $6:$53。</t>
+        </is>
+      </c>
+      <c r="F37" s="51" t="inlineStr">
+        <is>
+          <t>新增资产行 ⇒ 既有 47 行内容未变，但《总览》区间与查重结果公式区间随之变化，属预期；AssetID / 既有 Prefab 路径 / 既有条目 SHA 均未改动。</t>
+        </is>
+      </c>
+      <c r="G37" s="51" t="inlineStr">
         <is>
           <t>Codex</t>
         </is>

--- a/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3D-特效" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="域变更日志" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$52</definedName>
@@ -1447,22 +1447,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="52">
       <c r="A6" s="57">
-        <f>COUNTA('资产主表'!$A$6:$A$53)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$55)</f>
         <v/>
       </c>
       <c r="B6" s="55" t="n"/>
       <c r="C6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$53,"已完成")+COUNTIF('资产主表'!$K$6:$K$53,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$53,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$53,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$53,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$53,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$53,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$55,"已完成")+COUNTIF('资产主表'!$K$6:$K$55,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$55,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$55,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$55,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$55,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$55,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="55" t="n"/>
       <c r="E6" s="57">
-        <f>COUNTIF('资产主表'!$K$6:$K$53,"待制作")+COUNTIF('资产主表'!$K$6:$K$53,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$55,"待制作")+COUNTIF('资产主表'!$K$6:$K$55,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="55" t="n"/>
       <c r="G6" s="57">
-        <f>COUNTIF('资产主表'!$S$6:$S$53,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$55,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="55" t="n"/>
@@ -1531,11 +1531,11 @@
         </is>
       </c>
       <c r="B10" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$53,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$55,A10)</f>
         <v/>
       </c>
       <c r="C10" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$53=A10)*(('资产主表'!$K$6:$K$53="已完成")+('资产主表'!$K$6:$K$53="原型已接入")+('资产主表'!$K$6:$K$53="正式美术已接入")+('资产主表'!$K$6:$K$53="已优化并正式接入")+('资产主表'!$K$6:$K$53="Blender源已完成")+('资产主表'!$K$6:$K$53="已导入；优化完成")+('资产主表'!$K$6:$K$53="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$55=A10)*(('资产主表'!$K$6:$K$55="已完成")+('资产主表'!$K$6:$K$55="原型已接入")+('资产主表'!$K$6:$K$55="正式美术已接入")+('资产主表'!$K$6:$K$55="已优化并正式接入")+('资产主表'!$K$6:$K$55="Blender源已完成")+('资产主表'!$K$6:$K$55="已导入；优化完成")+('资产主表'!$K$6:$K$55="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="62" t="n"/>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B11" s="62">
-        <f>COUNTIF('资产主表'!$C$6:$C$53,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$55,A11)</f>
         <v/>
       </c>
       <c r="C11" s="62">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$53=A11)*(('资产主表'!$K$6:$K$53="已完成")+('资产主表'!$K$6:$K$53="原型已接入")+('资产主表'!$K$6:$K$53="正式美术已接入")+('资产主表'!$K$6:$K$53="已优化并正式接入")+('资产主表'!$K$6:$K$53="Blender源已完成")+('资产主表'!$K$6:$K$53="已导入；优化完成")+('资产主表'!$K$6:$K$53="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$55=A11)*(('资产主表'!$K$6:$K$55="已完成")+('资产主表'!$K$6:$K$55="原型已接入")+('资产主表'!$K$6:$K$55="正式美术已接入")+('资产主表'!$K$6:$K$55="已优化并正式接入")+('资产主表'!$K$6:$K$55="Blender源已完成")+('资产主表'!$K$6:$K$55="已导入；优化完成")+('资产主表'!$K$6:$K$55="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="62" t="n"/>
@@ -2115,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y53"/>
+  <dimension ref="A1:Y55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="51" min="1" max="1"/>
@@ -2387,7 +2387,7 @@
         <v/>
       </c>
       <c r="S6" s="63">
-        <f>IF(COUNTIF($R$6:$R$53,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="63" t="n"/>
@@ -2490,7 +2490,7 @@
         <v/>
       </c>
       <c r="S7" s="63">
-        <f>IF(COUNTIF($R$6:$R$53,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="63" t="n"/>
@@ -2593,7 +2593,7 @@
         <v/>
       </c>
       <c r="S8" s="63">
-        <f>IF(COUNTIF($R$6:$R$53,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="63" t="n"/>
@@ -2696,7 +2696,7 @@
         <v/>
       </c>
       <c r="S9" s="63">
-        <f>IF(COUNTIF($R$6:$R$53,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="63" t="n"/>
@@ -2803,7 +2803,7 @@
         <v/>
       </c>
       <c r="S10" s="63">
-        <f>IF(COUNTIF($R$6:$R$53,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="63" t="n"/>
@@ -2910,7 +2910,7 @@
         <v/>
       </c>
       <c r="S11" s="63">
-        <f>IF(COUNTIF($R$6:$R$53,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="63" t="n"/>
@@ -3017,7 +3017,7 @@
         <v/>
       </c>
       <c r="S12" s="63">
-        <f>IF(COUNTIF($R$6:$R$53,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="63" t="n"/>
@@ -3124,7 +3124,7 @@
         <v/>
       </c>
       <c r="S13" s="63">
-        <f>IF(COUNTIF($R$6:$R$53,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="63" t="n"/>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="S14" s="63">
-        <f>IF(COUNTIF($R$6:$R$53,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="63" t="n"/>
@@ -3338,7 +3338,7 @@
         <v/>
       </c>
       <c r="S15" s="63">
-        <f>IF(COUNTIF($R$6:$R$53,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="63" t="n"/>
@@ -3445,7 +3445,7 @@
         <v/>
       </c>
       <c r="S16" s="63">
-        <f>IF(COUNTIF($R$6:$R$53,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="63" t="n"/>
@@ -3564,7 +3564,7 @@
         <v/>
       </c>
       <c r="S17" s="55">
-        <f>IF(COUNTIF($R$6:$R$53,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="79" t="inlineStr">
@@ -3683,7 +3683,7 @@
         <v/>
       </c>
       <c r="S18" s="55">
-        <f>IF(COUNTIF($R$6:$R$53,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="79" t="inlineStr">
@@ -3806,7 +3806,7 @@
         <v/>
       </c>
       <c r="S19" s="55">
-        <f>IF(COUNTIF($R$6:$R$53,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="79" t="inlineStr">
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="S20" s="55">
-        <f>IF(COUNTIF($R$6:$R$53,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="79" t="inlineStr">
@@ -4046,7 +4046,7 @@
         <v/>
       </c>
       <c r="S21" s="55">
-        <f>IF(COUNTIF($R$6:$R$53,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="79" t="inlineStr">
@@ -4165,7 +4165,7 @@
         <v/>
       </c>
       <c r="S22" s="55">
-        <f>IF(COUNTIF($R$6:$R$53,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="79" t="inlineStr">
@@ -4284,7 +4284,7 @@
         <v/>
       </c>
       <c r="S23" s="55">
-        <f>IF(COUNTIF($R$6:$R$53,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="79" t="inlineStr">
@@ -4403,7 +4403,7 @@
         <v/>
       </c>
       <c r="S24" s="55">
-        <f>IF(COUNTIF($R$6:$R$53,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="79" t="inlineStr">
@@ -4522,7 +4522,7 @@
         <v/>
       </c>
       <c r="S25" s="55">
-        <f>IF(COUNTIF($R$6:$R$53,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="79" t="inlineStr">
@@ -4641,7 +4641,7 @@
         <v/>
       </c>
       <c r="S26" s="79">
-        <f>IF(COUNTIF($R$6:$R$53,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="79" t="inlineStr">
@@ -4767,7 +4767,7 @@
         <v/>
       </c>
       <c r="S27" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="76" t="inlineStr">
@@ -4889,7 +4889,7 @@
         <v/>
       </c>
       <c r="S28" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="76" t="inlineStr">
@@ -5011,7 +5011,7 @@
         <v/>
       </c>
       <c r="S29" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="76" t="inlineStr">
@@ -5133,7 +5133,7 @@
         <v/>
       </c>
       <c r="S30" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="76" t="inlineStr">
@@ -5255,7 +5255,7 @@
         <v/>
       </c>
       <c r="S31" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="76" t="inlineStr">
@@ -5377,7 +5377,7 @@
         <v/>
       </c>
       <c r="S32" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="76" t="inlineStr">
@@ -5499,7 +5499,7 @@
         <v/>
       </c>
       <c r="S33" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="76" t="inlineStr">
@@ -5621,7 +5621,7 @@
         <v/>
       </c>
       <c r="S34" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="76" t="inlineStr">
@@ -5739,7 +5739,7 @@
         <v/>
       </c>
       <c r="S35" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="76" t="inlineStr">
@@ -5858,7 +5858,7 @@
         <v/>
       </c>
       <c r="S36" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="76" t="inlineStr">
@@ -5979,7 +5979,7 @@
         <v/>
       </c>
       <c r="S37" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="76" t="inlineStr">
@@ -6100,7 +6100,7 @@
         <v/>
       </c>
       <c r="S38" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R38)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R38)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T38" s="76" t="inlineStr">
@@ -6221,7 +6221,7 @@
         <v/>
       </c>
       <c r="S39" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R39)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R39)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T39" s="76" t="inlineStr">
@@ -6359,7 +6359,7 @@
         <v/>
       </c>
       <c r="S40" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R40)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R40)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T40" s="76" t="inlineStr">
@@ -6480,7 +6480,7 @@
         <v/>
       </c>
       <c r="S41" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R41)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R41)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T41" s="76" t="inlineStr">
@@ -6601,7 +6601,7 @@
         <v/>
       </c>
       <c r="S42" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R42)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R42)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T42" s="76" t="inlineStr">
@@ -6722,7 +6722,7 @@
         <v/>
       </c>
       <c r="S43" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R43)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R43)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T43" s="76" t="inlineStr">
@@ -6841,7 +6841,7 @@
         <v/>
       </c>
       <c r="S44" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R44)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R44)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T44" s="76" t="inlineStr">
@@ -6960,7 +6960,7 @@
         <v/>
       </c>
       <c r="S45" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R45)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R45)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T45" s="76" t="inlineStr">
@@ -7079,7 +7079,7 @@
         <v/>
       </c>
       <c r="S46" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R46)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R46)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T46" s="76" t="inlineStr">
@@ -7198,7 +7198,7 @@
         <v/>
       </c>
       <c r="S47" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R47)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R47)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T47" s="76" t="inlineStr">
@@ -7317,7 +7317,7 @@
         <v/>
       </c>
       <c r="S48" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R48)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R48)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T48" s="76" t="inlineStr">
@@ -7438,7 +7438,7 @@
         <v/>
       </c>
       <c r="S49" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R49)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R49)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T49" s="76" t="inlineStr">
@@ -7559,7 +7559,7 @@
         <v/>
       </c>
       <c r="S50" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R50)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R50)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T50" s="76" t="inlineStr">
@@ -7680,7 +7680,7 @@
         <v/>
       </c>
       <c r="S51" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R51)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R51)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T51" s="76" t="inlineStr">
@@ -7801,7 +7801,7 @@
         <v/>
       </c>
       <c r="S52" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R52)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R52)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T52" s="76" t="inlineStr">
@@ -7922,7 +7922,7 @@
         <v/>
       </c>
       <c r="S53" s="76">
-        <f>IF(COUNTIF($R$6:$R$53,R53)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$55,R53)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T53" s="76" t="inlineStr">
@@ -7953,6 +7953,257 @@
       <c r="Y53" s="76" t="inlineStr">
         <is>
           <t>2026-10-19 新建（业主：「做一个门被打碎的木头飞出来的特效，大块一点的」）。8 大块 + 5 片小碎屑，程序化抛物飞行 → 触地弹跳 1 次 → 贴地滑行 → 放平静止（不接物理引擎，无碰撞体）；自带 DebrisLight（峰值 1.5 / 范围 3.6m / 无阴影 / 0.55s 归零）——塔内夜间光，无灯就是黑剪影。材质：金属度 metallic=0.0 / 反光度 roughness=0.86（PER_PIXEL 受光）+ 自发光 0.38（暗房里保住「木头」读法）。确定性：脚本内无 randf()，散开由调用方给的 context.seed 派生（同 seed 逐位可复现）。调用方 SecretDoor3D._break_open()：只在真打破时播，读档恢复 / 静默打开不重播。验收 tests/verification/verify_board_debris_vfx.tscn（9 条，含大块下限 0.30m + 上限 0.65m 双向）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="76" t="inlineStr">
+        <is>
+          <t>VFX-TELEPORT-OUT-3D</t>
+        </is>
+      </c>
+      <c r="B54" s="76" t="inlineStr">
+        <is>
+          <t>瞬移消失反馈特效</t>
+        </is>
+      </c>
+      <c r="C54" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D54" s="76" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="E54" s="76" t="inlineStr">
+        <is>
+          <t>teleport_out_3d</t>
+        </is>
+      </c>
+      <c r="F54" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G54" s="76" t="n"/>
+      <c r="H54" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D（地面对称）</t>
+        </is>
+      </c>
+      <c r="I54" s="76" t="inlineStr">
+        <is>
+          <t>teleport_out</t>
+        </is>
+      </c>
+      <c r="J54" s="76" t="inlineStr">
+        <is>
+          <t>怪物位移（blink 原点 / 原地消失）</t>
+        </is>
+      </c>
+      <c r="K54" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L54" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M54" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N54" s="76" t="inlineStr">
+        <is>
+          <t>水平能量环（基线外径 0.72m，尺度 1.35→0.15 倍收拢）+ 中心亮芯 + 7 根竖直能量丝（0.62→0.20m，随 t 上抽并变短）；lifetime 0.22s；整体尺寸档 effect_size（默认 1.0 ≈ 直径 1.4m）</t>
+        </is>
+      </c>
+      <c r="O54" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_teleport_out_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P54" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxTeleport3D.gd; docs/v0.1/14.6_特效系统与制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q54" s="76" t="inlineStr">
+        <is>
+          <t>瞬移;消失;blink;传送;消失点;位移;空尖弹;枪法师;逃跑怪</t>
+        </is>
+      </c>
+      <c r="R54" s="76">
+        <f>LOWER(TRIM(C54)&amp;"|"&amp;TRIM(D54)&amp;"|"&amp;TRIM(E54)&amp;"|"&amp;TRIM(F54)&amp;"|"&amp;TRIM(H54)&amp;"|"&amp;TRIM(I54))</f>
+        <v/>
+      </c>
+      <c r="S54" s="76">
+        <f>IF(COUNTIF($R$6:$R$55,R54)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T54" s="76" t="inlineStr">
+        <is>
+          <t>a466603951e5c4e8a67f572e1491de7ca01b0c9ab35ad31f60fd669369d2b01e</t>
+        </is>
+      </c>
+      <c r="U54" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V54" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="W54" s="76" t="inlineStr">
+        <is>
+          <t>原创Godot Prefab与脚本</t>
+        </is>
+      </c>
+      <c r="X54" s="76" t="inlineStr">
+        <is>
+          <t>FX01-34</t>
+        </is>
+      </c>
+      <c r="Y54" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-31 新建（业主：「带有瞬移还有位移的一些怪物，出现消失的那个位置需要有一些反馈特效……不然怪物突然消失出现很奇怪」）。
+**为什么必须有**：远征03 的 blink 是直接改 `global_position`（`Enemy3D._blink_to_random`），中间没有任何轨迹或过渡帧；`_vanish()` 同理是原地蒸发。修前只有 `avatar.flash_hit()` 闪白一下，玩家读到的是「模型抖了一下就没了」。
+视觉：环由大收小 ⇒ 读作「被抽走」；7 根竖丝向上抽离并变短 ⇒ 加强「离场」方向感。unshaded 自发光、无灯、不投影、无碰撞，夜间塔内不依赖场景光照（同 FX01-02 口径）。
+颜色取 `EnemyAvatar3D.COLORS[enemy_kind]`（由 `Enemy3D._spawn_effect_at` 下发），所以空尖弹是紫环、枪法师是浅紫环，玩家能顺带读出「是谁闪的」。
+**与 FX01-35 必须成对**：只播消失会被当成逃跑（玩家会去追一个已经不在那的敌人），只播出现会被当成凭空刷新。
+与 FX01-35 同脚本（`VfxTeleport3D.gd`），靠导出项 `mode` 区分方向；拆两件是因为池按 AssetID 分桶、账本按 AssetID 一行一件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="76" t="inlineStr">
+        <is>
+          <t>VFX-TELEPORT-IN-3D</t>
+        </is>
+      </c>
+      <c r="B55" s="76" t="inlineStr">
+        <is>
+          <t>瞬移出现反馈特效</t>
+        </is>
+      </c>
+      <c r="C55" s="76" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="D55" s="76" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="E55" s="76" t="inlineStr">
+        <is>
+          <t>teleport_in_3d</t>
+        </is>
+      </c>
+      <c r="F55" s="76" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G55" s="76" t="n"/>
+      <c r="H55" s="76" t="inlineStr">
+        <is>
+          <t>俯视3D（地面对称）</t>
+        </is>
+      </c>
+      <c r="I55" s="76" t="inlineStr">
+        <is>
+          <t>teleport_in</t>
+        </is>
+      </c>
+      <c r="J55" s="76" t="inlineStr">
+        <is>
+          <t>怪物位移（blink 落点）</t>
+        </is>
+      </c>
+      <c r="K55" s="76" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L55" s="76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M55" s="76" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N55" s="76" t="inlineStr">
+        <is>
+          <t>水平能量环（0.15→1.50 倍炸开）+ 中心亮芯（0.35t 处弹到最大再收）+ 7 根竖直能量丝（0.20→0.75m 向上冒出）；lifetime 0.26s；整体尺寸档 effect_size（默认 1.0 ≈ 直径 1.4m）</t>
+        </is>
+      </c>
+      <c r="O55" s="76" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_teleport_in_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P55" s="76" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxTeleport3D.gd; docs/v0.1/14.6_特效系统与制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q55" s="76" t="inlineStr">
+        <is>
+          <t>瞬移;出现;降临;blink;落点;传送;空尖弹;枪法师</t>
+        </is>
+      </c>
+      <c r="R55" s="76">
+        <f>LOWER(TRIM(C55)&amp;"|"&amp;TRIM(D55)&amp;"|"&amp;TRIM(E55)&amp;"|"&amp;TRIM(F55)&amp;"|"&amp;TRIM(H55)&amp;"|"&amp;TRIM(I55))</f>
+        <v/>
+      </c>
+      <c r="S55" s="76">
+        <f>IF(COUNTIF($R$6:$R$55,R55)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T55" s="76" t="inlineStr">
+        <is>
+          <t>99b3da32d42f35fff4fdd2f3620bf06cf2adc9adc234d104a5270ce53e750d35</t>
+        </is>
+      </c>
+      <c r="U55" s="76" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V55" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="W55" s="76" t="inlineStr">
+        <is>
+          <t>原创Godot Prefab与脚本</t>
+        </is>
+      </c>
+      <c r="X55" s="76" t="inlineStr">
+        <is>
+          <t>FX01-35</t>
+        </is>
+      </c>
+      <c r="Y55" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-31 新建（同 FX01-34 一批）。
+**为什么不能并进 FX01-34**：① 池按 asset_id 分桶，合并会让「消失」与「出现」抢同一批实例；② 账本要能分别查用量；③ 两者时间曲线方向相反（收拢 vs 炸开），参数无法共用。
+视觉：环由小炸开 + 亮芯弹一下 ⇒ 「凭空生成」；竖丝向上冒出（与 FX01-34 的「上抽」同向，读作同一个能量场）。
+**只挂在 blink 落点**，`_vanish()`（逃跑超时消失 / 抓握大师连抓空自毁）不播它 —— 那是真走了，播「出现」等于骗人。
+尺寸与 FX01-34 同为 `Enemy3D.TELEPORT_FX_SIZE = 1.0`；门禁 `tools/_egt_teleport_fx_probe.gd` 逐层验（注册 → 预制件 mode/时长/不投影 → 位移两端各播一件 + 池里真有活跃实例）。</t>
         </is>
       </c>
     </row>
@@ -11846,19 +12097,185 @@
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="52">
-      <c r="H54" s="101" t="n"/>
-      <c r="I54" s="51" t="n"/>
-      <c r="N54" s="51" t="n"/>
+      <c r="A54" s="97" t="inlineStr">
+        <is>
+          <t>▼ 01 战斗反馈（续）· 怪物位移表现（瞬移 / 消失）</t>
+        </is>
+      </c>
+      <c r="B54" s="98" t="n"/>
+      <c r="C54" s="98" t="n"/>
+      <c r="D54" s="98" t="n"/>
+      <c r="E54" s="98" t="n"/>
+      <c r="F54" s="98" t="n"/>
+      <c r="G54" s="98" t="n"/>
+      <c r="H54" s="98" t="n"/>
+      <c r="I54" s="98" t="n"/>
+      <c r="J54" s="98" t="n"/>
+      <c r="K54" s="98" t="n"/>
+      <c r="L54" s="98" t="n"/>
+      <c r="M54" s="98" t="n"/>
+      <c r="N54" s="98" t="n"/>
+      <c r="O54" s="98" t="n"/>
+      <c r="P54" s="99" t="n"/>
+      <c r="Q54" s="92" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1" s="52">
-      <c r="H55" s="101" t="n"/>
-      <c r="I55" s="51" t="n"/>
-      <c r="N55" s="51" t="n"/>
+      <c r="A55" s="100" t="inlineStr">
+        <is>
+          <t>FX01-34</t>
+        </is>
+      </c>
+      <c r="B55" s="101" t="inlineStr">
+        <is>
+          <t>VFX-TELEPORT-OUT-3D</t>
+        </is>
+      </c>
+      <c r="C55" s="51" t="inlineStr">
+        <is>
+          <t>瞬移消失反馈特效</t>
+        </is>
+      </c>
+      <c r="D55" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_teleport_out_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E55" s="51" t="n"/>
+      <c r="F55" s="51" t="n"/>
+      <c r="G55" s="51" t="inlineStr">
+        <is>
+          <t>怪物**凭空离场**时的位置反馈（业主 2026-10-31：「突然消失很奇怪」）。远征03 的 blink（空尖弹定时 / 枪法师出手后）与 `_vanish()`（逃跑型超时、抓握大师连抓空 3 次）都是直接改 transform，没有轨迹。视觉：水平能量环由 1.35 倍收拢到 0.15 倍（读作「被抽走」）+ 中心亮芯缩没 + 7 根竖直能量丝向上抽离并变短。0.22s。**纯视觉、无判定**：不改任何动画/状态机，不阻塞位移（位移在同一帧已完成）。</t>
+        </is>
+      </c>
+      <c r="H55" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxTeleport3D.gd</t>
+        </is>
+      </c>
+      <c r="I55" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J55" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K55" s="51" t="inlineStr">
+        <is>
+          <t>无CollisionObject3D/CollisionShape3D</t>
+        </is>
+      </c>
+      <c r="L55" s="51" t="inlineStr">
+        <is>
+          <t>环基线外径 0.72m × 尺度包络 1.35→0.15 × effect_size；亮芯 0.36m 球 ×(1−t)；竖直丝 7 根（截面 0.055m、长 0.62→0.20m、离地 0.10→1.15m）；lifetime 0.22s；无灯、不投影</t>
+        </is>
+      </c>
+      <c r="M55" s="51" t="inlineStr">
+        <is>
+          <t>原点 = 怪物脚底 + 0.65m（`Enemy3D.EFFECT_SPAWN_LIFT`）；**无朝向契约（全向对称）**；环面平铺 XZ 平面、不随怪转身</t>
+        </is>
+      </c>
+      <c r="N55" s="51" t="inlineStr">
+        <is>
+          <t>远征03 空尖弹 `egt_hollowpoint` / 枪法师 `egt_gunjurer` 的 blink **原点**；逃跑型 `egt_keybullet_kin` / `egt_chance_kin` 与抓握大师 `egt_gripmaster` 的 `_vanish()`</t>
+        </is>
+      </c>
+      <c r="O55" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P55" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q55" s="51" t="inlineStr">
+        <is>
+          <t>已实装；与 FX01-35 成对使用（只有一端会读错意图）。池注册见 `VfxPool3D.FX01_TELEPORT_OUT`；门禁 `tools/_egt_teleport_fx_probe.gd`。其余关卡未接（塔楼怪没有 blink / vanishing）。</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="52">
-      <c r="H56" s="101" t="n"/>
-      <c r="I56" s="51" t="n"/>
-      <c r="N56" s="51" t="n"/>
+      <c r="A56" s="100" t="inlineStr">
+        <is>
+          <t>FX01-35</t>
+        </is>
+      </c>
+      <c r="B56" s="101" t="inlineStr">
+        <is>
+          <t>VFX-TELEPORT-IN-3D</t>
+        </is>
+      </c>
+      <c r="C56" s="51" t="inlineStr">
+        <is>
+          <t>瞬移出现反馈特效</t>
+        </is>
+      </c>
+      <c r="D56" s="101" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/vfx_teleport_in_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="E56" s="51" t="n"/>
+      <c r="F56" s="51" t="n"/>
+      <c r="G56" s="51" t="inlineStr">
+        <is>
+          <t>怪物**凭空抵达**时的位置反馈，与 FX01-34 成对。视觉：水平能量环由 0.15 倍炸开到 1.50 倍 + 中心亮芯在 35% 处弹到最大再收 + 7 根竖直能量丝向上冒出。0.26s。**只在 blink 落点播**；`_vanish()` 不播（那是真离场，播「出现」会误导）。</t>
+        </is>
+      </c>
+      <c r="H56" s="101" t="inlineStr">
+        <is>
+          <t>src/vfx/VfxTeleport3D.gd</t>
+        </is>
+      </c>
+      <c r="I56" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J56" s="51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K56" s="51" t="inlineStr">
+        <is>
+          <t>无CollisionObject3D/CollisionShape3D</t>
+        </is>
+      </c>
+      <c r="L56" s="51" t="inlineStr">
+        <is>
+          <t>环基线外径 0.72m × 尺度包络 0.15→1.50 × effect_size；亮芯 0.36m 球（sin 弹一下）；竖直丝 7 根（长 0.20→0.75m、离地 0.63→0.08m）；lifetime 0.26s；无灯、不投影</t>
+        </is>
+      </c>
+      <c r="M56" s="51" t="inlineStr">
+        <is>
+          <t>原点 = 落点脚底 + 0.65m；**无朝向契约（全向对称）**；环面平铺 XZ 平面</t>
+        </is>
+      </c>
+      <c r="N56" s="51" t="inlineStr">
+        <is>
+          <t>远征03 空尖弹 / 枪法师 blink 的**落点**（`Enemy3D._blink_to_random` 成功分支）</t>
+        </is>
+      </c>
+      <c r="O56" s="51" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P56" s="101" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="Q56" s="51" t="inlineStr">
+        <is>
+          <t>已实装；拆成独立 AssetID 的理由见主表备注（池按 ID 分桶 / 账本按 ID 计件 / 时间方向相反）。</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="52">
       <c r="H57" s="101" t="n"/>
@@ -12861,7 +13278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="51" min="1" max="1"/>
@@ -14095,6 +14512,43 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>v0.1.30</t>
+        </is>
+      </c>
+      <c r="B38" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C38" s="51" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D38" s="51" t="inlineStr">
+        <is>
+          <t>特效 · 资产主表 / 3D-特效（FX01-34 / FX01-35）</t>
+        </is>
+      </c>
+      <c r="E38" s="51" t="inlineStr">
+        <is>
+          <t>新增两件瞬移位置反馈：`VFX-TELEPORT-OUT-3D`（消失，0.22s，环收拢 + 竖丝上抽）与 `VFX-TELEPORT-IN-3D`（出现，0.26s，环炸开 + 竖丝冒出）。触发点：远征03 的 blink 两端（空尖弹定时 / 枪法师出手后）与 `_vanish()`（逃跑型超时、抓握大师连抓空）。业主原话：「带有瞬移还有位移的一些怪物，出现消失的那个位置需要有一些反馈特效……不然怪物突然消失出现很奇怪」。</t>
+        </is>
+      </c>
+      <c r="F38" s="51" t="inlineStr">
+        <is>
+          <t>新增资产行 ⇒ 既有 47 行内容未变，但《总览》区间与查重结果公式区间随之扩大（$53→$55）；AssetID / Prefab 路径 / 版本号一经发布不再变更</t>
+        </is>
+      </c>
+      <c r="G38" s="51" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>
